--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
@@ -158,7 +158,7 @@
     <t>Annual Fundraising</t>
   </si>
   <si>
-    <t>Grants &amp; Contributions</t>
+    <t>Philanthropy</t>
   </si>
   <si>
     <t>Annual Fixed</t>
@@ -570,7 +570,7 @@
     <font>
       <i/>
       <color rgb="FF666666"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -586,13 +586,13 @@
     <font>
       <i/>
       <color rgb="FF888888"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <i/>
       <color rgb="FF9CA3AF"/>
-      <sz val="9"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>

--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="173">
   <si>
-    <t>Bright Horizons Microschool — Financial Model Assumptions</t>
+    <t>Bright Horizons Microschool - Financial Model Assumptions</t>
   </si>
   <si>
     <t>Yellow cells are editable inputs. All other cells in this workbook are formulas.</t>
@@ -314,7 +314,7 @@
     <t>Built by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
   <si>
-    <t>Bright Horizons Microschool — 5-Year Financial Model</t>
+    <t>Bright Horizons Microschool - 5-Year Financial Model</t>
   </si>
   <si>
     <t>REVENUE</t>
@@ -464,7 +464,7 @@
     <t>Break-Even Enrollment</t>
   </si>
   <si>
-    <t>Bright Horizons Microschool — 2026-27 Pro Forma</t>
+    <t>Bright Horizons Microschool - 2026-27 Pro Forma</t>
   </si>
   <si>
     <t>August</t>

--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
@@ -9,11 +9,11 @@
     <sheet sheetId="3" name="Year 1 Pro Forma" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Assumptions'!$A1:$J54</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Assumptions'!$A1:$J56</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Assumptions'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'5-Year Model'!$A1:$F73</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'5-Year Model'!$A1:$F75</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'5-Year Model'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Year 1 Pro Forma'!$A1:$N45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Year 1 Pro Forma'!$A1:$N46</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Year 1 Pro Forma'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="177">
   <si>
     <t>Bright Horizons Microschool - Financial Model Assumptions</t>
   </si>
@@ -164,6 +164,15 @@
     <t>Annual Fixed</t>
   </si>
   <si>
+    <t>Scholarship Discount</t>
+  </si>
+  <si>
+    <t>Tuition Offsets</t>
+  </si>
+  <si>
+    <t>% of Base</t>
+  </si>
+  <si>
     <t>STAFFING ROSTER</t>
   </si>
   <si>
@@ -285,6 +294,9 @@
   </si>
   <si>
     <t>Annual Payment</t>
+  </si>
+  <si>
+    <t>Equipment Loan</t>
   </si>
   <si>
     <t>GROWTH &amp; TIMING ASSUMPTIONS</t>
@@ -678,7 +690,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -697,6 +709,8 @@
     <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -704,7 +718,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1058,7 +1071,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1351,79 +1364,76 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B24" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C24" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D24" s="9">
+        <v>10</v>
+      </c>
+      <c r="E24" s="10">
+        <v>0</v>
+      </c>
+      <c r="F24" s="6">
+        <v>12</v>
+      </c>
+      <c r="G24" s="10">
+        <v>1</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="B27" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="F27" s="3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+      <c r="G27" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="H27" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="I27" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="D27" s="11">
-        <v>1</v>
-      </c>
-      <c r="E27" s="9">
-        <v>55000</v>
-      </c>
-      <c r="F27" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="G27" s="10">
-        <v>0.0765</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="C28" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>58</v>
       </c>
       <c r="D28" s="11">
         <v>1</v>
       </c>
       <c r="E28" s="9">
-        <v>45000</v>
+        <v>55000</v>
       </c>
       <c r="F28" s="10">
         <v>0.2</v>
@@ -1432,7 +1442,7 @@
         <v>0.0765</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>40</v>
@@ -1440,128 +1450,137 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>63</v>
-      </c>
       <c r="D29" s="11">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E29" s="9">
-        <v>28000</v>
+        <v>45000</v>
       </c>
       <c r="F29" s="10">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G29" s="10">
         <v>0.0765</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I29" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="31" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B30" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="D30" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="E30" s="9">
+        <v>28000</v>
+      </c>
+      <c r="F30" s="10">
+        <v>0</v>
+      </c>
+      <c r="G30" s="10">
+        <v>0.0765</v>
+      </c>
+      <c r="H30" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D31" s="3"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+      <c r="I30" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="3" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C32" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" s="3"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B33" s="9">
+        <v>71</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" s="9">
         <v>2500</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B34" s="10">
+      <c r="C34" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" s="10">
         <v>0.03</v>
       </c>
     </row>
-    <row r="36" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B36" s="3" t="s">
+    <row r="37" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D37" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E37" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="F37" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G36" s="3"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D37" s="9">
-        <v>2500</v>
-      </c>
-      <c r="E37" s="10">
-        <v>0.03</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>40</v>
-      </c>
+      <c r="G37" s="3"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B38" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>71</v>
-      </c>
       <c r="D38" s="9">
-        <v>300</v>
+        <v>2500</v>
       </c>
       <c r="E38" s="10">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>40</v>
@@ -1569,16 +1588,16 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B39" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="D39" s="9">
-        <v>2400</v>
+        <v>300</v>
       </c>
       <c r="E39" s="10">
         <v>0</v>
@@ -1589,16 +1608,16 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B40" s="4" t="s">
-        <v>78</v>
-      </c>
       <c r="C40" s="4" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D40" s="9">
-        <v>500</v>
+        <v>2400</v>
       </c>
       <c r="E40" s="10">
         <v>0</v>
@@ -1609,16 +1628,16 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D41" s="9">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E41" s="10">
         <v>0</v>
@@ -1629,16 +1648,16 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D42" s="9">
-        <v>3000</v>
+        <v>300</v>
       </c>
       <c r="E42" s="10">
         <v>0</v>
@@ -1647,107 +1666,153 @@
         <v>40</v>
       </c>
     </row>
-    <row r="44" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B44" s="3" t="s">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="B43" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D43" s="9">
+        <v>3000</v>
+      </c>
+      <c r="E43" s="10">
+        <v>0</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G44" s="3" t="s">
+      <c r="D45" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H44" s="3" t="s">
+      <c r="E45" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H45" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="46" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B47" s="10">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C46" s="12">
+        <v>0</v>
+      </c>
+      <c r="D46" s="9">
+        <v>30000</v>
+      </c>
+      <c r="E46" s="13">
+        <v>0.06</v>
+      </c>
+      <c r="F46" s="6">
+        <v>5</v>
+      </c>
+      <c r="G46" s="12">
+        <v>6960</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B49" s="10">
         <v>0.03</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B48" s="10">
-        <v>0.025</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B49" s="11">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="C49" s="12" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B50" s="10">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B51" s="10">
-        <v>0</v>
+        <v>95</v>
+      </c>
+      <c r="B51" s="11">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="C51" s="14" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B52" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="B54" s="13"/>
-      <c r="C54" s="13"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
+        <v>97</v>
+      </c>
+      <c r="B52" s="10">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B53" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B54" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B56" s="15"/>
+      <c r="C56" s="15"/>
+      <c r="D56" s="15"/>
+      <c r="E56" s="15"/>
+      <c r="F56" s="15"/>
+      <c r="G56" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B10:D10"/>
-    <mergeCell ref="A54:G54"/>
+    <mergeCell ref="A56:G56"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
@@ -1763,7 +1828,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1772,7 +1837,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1781,53 +1846,53 @@
       <c r="F1" s="1"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="16" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="18">
         <f>Assumptions!B17</f>
         <v>12</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="18">
         <f>Assumptions!C17</f>
         <v>18</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="18">
         <f>Assumptions!D17</f>
         <v>22</v>
       </c>
-      <c r="E3" s="16">
+      <c r="E3" s="18">
         <f>Assumptions!E17</f>
         <v>25</v>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="18">
         <f>Assumptions!F17</f>
         <v>25</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -1839,19 +1904,19 @@
       <c r="A6" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="12">
         <v>120000</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="12">
         <v>221400</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="12">
         <v>277365</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="12">
         <v>323067</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="12">
         <v>331144</v>
       </c>
     </row>
@@ -1859,19 +1924,19 @@
       <c r="A7" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="12">
         <v>2500</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="12">
         <v>4613</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="12">
         <v>5778</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="12">
         <v>6731</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="12">
         <v>6899</v>
       </c>
     </row>
@@ -1879,19 +1944,19 @@
       <c r="A8" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="12">
         <v>70000</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="12">
         <v>129150</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="12">
         <v>161796</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="12">
         <v>188456</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="12">
         <v>193167</v>
       </c>
     </row>
@@ -1899,1156 +1964,1201 @@
       <c r="A9" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="12">
         <v>4167</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="12">
         <v>5125</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="12">
         <v>5253</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="12">
         <v>5384</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="12">
         <v>5519</v>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B10" s="18">
-        <f>SUM(B6:B9)</f>
-        <v>196667</v>
-      </c>
-      <c r="C10" s="18">
-        <f>SUM(C6:C9)</f>
-        <v>360287</v>
-      </c>
-      <c r="D10" s="18">
-        <f>SUM(D6:D9)</f>
-        <v>450193</v>
-      </c>
-      <c r="E10" s="18">
-        <f>SUM(E6:E9)</f>
-        <v>523638</v>
-      </c>
-      <c r="F10" s="18">
-        <f>SUM(F6:F9)</f>
-        <v>536729</v>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B13" s="17">
-        <v>58506</v>
-      </c>
-      <c r="C13" s="17">
-        <v>72314</v>
-      </c>
-      <c r="D13" s="17">
-        <v>74483</v>
-      </c>
-      <c r="E13" s="17">
-        <v>76718</v>
-      </c>
-      <c r="F13" s="17">
-        <v>79019</v>
-      </c>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="12">
+        <v>-12000</v>
+      </c>
+      <c r="C10" s="12">
+        <v>-22140</v>
+      </c>
+      <c r="D10" s="12">
+        <v>-27736</v>
+      </c>
+      <c r="E10" s="12">
+        <v>-32307</v>
+      </c>
+      <c r="F10" s="12">
+        <v>-33114</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="19">
+        <f>SUM(B6:B10)</f>
+        <v>184667</v>
+      </c>
+      <c r="C11" s="19">
+        <f>SUM(C6:C10)</f>
+        <v>338147</v>
+      </c>
+      <c r="D11" s="19">
+        <f>SUM(D6:D10)</f>
+        <v>422456</v>
+      </c>
+      <c r="E11" s="19">
+        <f>SUM(E6:E10)</f>
+        <v>491331</v>
+      </c>
+      <c r="F11" s="19">
+        <f>SUM(F6:F10)</f>
+        <v>503615</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B14" s="17">
-        <v>47869</v>
-      </c>
-      <c r="C14" s="17">
-        <v>59166</v>
-      </c>
-      <c r="D14" s="17">
-        <v>60941</v>
-      </c>
-      <c r="E14" s="17">
-        <v>62769</v>
-      </c>
-      <c r="F14" s="17">
-        <v>64652</v>
+        <v>105</v>
+      </c>
+      <c r="B14" s="12">
+        <v>58506</v>
+      </c>
+      <c r="C14" s="12">
+        <v>72314</v>
+      </c>
+      <c r="D14" s="12">
+        <v>74483</v>
+      </c>
+      <c r="E14" s="12">
+        <v>76718</v>
+      </c>
+      <c r="F14" s="12">
+        <v>79019</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B15" s="17">
+        <v>106</v>
+      </c>
+      <c r="B15" s="12">
+        <v>47869</v>
+      </c>
+      <c r="C15" s="12">
+        <v>59166</v>
+      </c>
+      <c r="D15" s="12">
+        <v>60941</v>
+      </c>
+      <c r="E15" s="12">
+        <v>62769</v>
+      </c>
+      <c r="F15" s="12">
+        <v>64652</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B16" s="12">
         <v>12559</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C16" s="12">
         <v>15523</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D16" s="12">
         <v>15989</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E16" s="12">
         <v>16468</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F16" s="12">
         <v>16963</v>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B16" s="18">
-        <f>SUM(B13:B15)</f>
+    <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B17" s="19">
+        <f>SUM(B14:B16)</f>
         <v>118934</v>
       </c>
-      <c r="C16" s="18">
-        <f>SUM(C13:C15)</f>
+      <c r="C17" s="19">
+        <f>SUM(C14:C16)</f>
         <v>147003</v>
       </c>
-      <c r="D16" s="18">
-        <f>SUM(D13:D15)</f>
+      <c r="D17" s="19">
+        <f>SUM(D14:D16)</f>
         <v>151413</v>
       </c>
-      <c r="E16" s="18">
-        <f>SUM(E13:E15)</f>
+      <c r="E17" s="19">
+        <f>SUM(E14:E16)</f>
         <v>155955</v>
       </c>
-      <c r="F16" s="18">
-        <f>SUM(F13:F15)</f>
+      <c r="F17" s="19">
+        <f>SUM(F14:F16)</f>
         <v>160634</v>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
+    <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B20" s="17">
+        <v>81</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B21" s="12">
         <v>5000</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C21" s="12">
         <v>9225</v>
       </c>
-      <c r="D20" s="17">
+      <c r="D21" s="12">
         <v>11557</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E21" s="12">
         <v>13461</v>
       </c>
-      <c r="F20" s="17">
+      <c r="F21" s="12">
         <v>13798</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="B21" s="20">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B22" s="21">
         <v>5000</v>
       </c>
-      <c r="C21" s="20">
+      <c r="C22" s="21">
         <v>9225</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D22" s="21">
         <v>11557</v>
       </c>
-      <c r="E21" s="20">
+      <c r="E22" s="21">
         <v>13461</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F22" s="21">
         <v>13798</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B23" s="17">
+        <v>82</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B24" s="12">
         <v>3000</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C24" s="12">
         <v>5535</v>
       </c>
-      <c r="D23" s="17">
+      <c r="D24" s="12">
         <v>6934</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E24" s="12">
         <v>8077</v>
       </c>
-      <c r="F23" s="17">
+      <c r="F24" s="12">
         <v>8279</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="B24" s="20">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="B25" s="21">
         <v>3000</v>
       </c>
-      <c r="C24" s="20">
+      <c r="C25" s="21">
         <v>5535</v>
       </c>
-      <c r="D24" s="20">
+      <c r="D25" s="21">
         <v>6934</v>
       </c>
-      <c r="E24" s="20">
+      <c r="E25" s="21">
         <v>8077</v>
       </c>
-      <c r="F24" s="20">
+      <c r="F25" s="21">
         <v>8279</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B26" s="17">
-        <v>25000</v>
-      </c>
-      <c r="C26" s="17">
-        <v>30900</v>
-      </c>
-      <c r="D26" s="17">
-        <v>31827</v>
-      </c>
-      <c r="E26" s="17">
-        <v>32782</v>
-      </c>
-      <c r="F26" s="17">
-        <v>33765</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B27" s="17">
-        <v>3000</v>
-      </c>
-      <c r="C27" s="17">
-        <v>3690</v>
-      </c>
-      <c r="D27" s="17">
-        <v>3782</v>
-      </c>
-      <c r="E27" s="17">
-        <v>3877</v>
-      </c>
-      <c r="F27" s="17">
-        <v>3974</v>
+        <v>113</v>
+      </c>
+      <c r="B27" s="12">
+        <v>25000</v>
+      </c>
+      <c r="C27" s="12">
+        <v>30900</v>
+      </c>
+      <c r="D27" s="12">
+        <v>31827</v>
+      </c>
+      <c r="E27" s="12">
+        <v>32782</v>
+      </c>
+      <c r="F27" s="12">
+        <v>33765</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B28" s="17">
+        <v>114</v>
+      </c>
+      <c r="B28" s="12">
+        <v>3000</v>
+      </c>
+      <c r="C28" s="12">
+        <v>3690</v>
+      </c>
+      <c r="D28" s="12">
+        <v>3782</v>
+      </c>
+      <c r="E28" s="12">
+        <v>3877</v>
+      </c>
+      <c r="F28" s="12">
+        <v>3974</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" s="12">
         <v>2000</v>
       </c>
-      <c r="C28" s="17">
+      <c r="C29" s="12">
         <v>2460</v>
       </c>
-      <c r="D28" s="17">
+      <c r="D29" s="12">
         <v>2522</v>
       </c>
-      <c r="E28" s="17">
+      <c r="E29" s="12">
         <v>2585</v>
       </c>
-      <c r="F28" s="17">
+      <c r="F29" s="12">
         <v>2649</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="B29" s="20">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="21">
         <v>30000</v>
       </c>
-      <c r="C29" s="20">
+      <c r="C30" s="21">
         <v>37050</v>
       </c>
-      <c r="D29" s="20">
+      <c r="D30" s="21">
         <v>38131</v>
       </c>
-      <c r="E29" s="20">
+      <c r="E30" s="21">
         <v>39244</v>
       </c>
-      <c r="F29" s="20">
+      <c r="F30" s="21">
         <v>40388</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B31" s="17">
+        <v>84</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B32" s="12">
         <v>2500</v>
       </c>
-      <c r="C31" s="17">
+      <c r="C32" s="12">
         <v>3075</v>
       </c>
-      <c r="D31" s="17">
+      <c r="D32" s="12">
         <v>3152</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E32" s="12">
         <v>3231</v>
       </c>
-      <c r="F31" s="17">
+      <c r="F32" s="12">
         <v>3311</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="B32" s="20">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="B33" s="21">
         <v>2500</v>
       </c>
-      <c r="C32" s="20">
+      <c r="C33" s="21">
         <v>3075</v>
       </c>
-      <c r="D32" s="20">
+      <c r="D33" s="21">
         <v>3152</v>
       </c>
-      <c r="E32" s="20">
+      <c r="E33" s="21">
         <v>3231</v>
       </c>
-      <c r="F32" s="20">
+      <c r="F33" s="21">
         <v>3311</v>
       </c>
     </row>
-    <row r="33" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B33" s="18">
-        <f>B21+B24+B29+B32</f>
+    <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B34" s="19">
+        <f>B22+B25+B30+B33</f>
         <v>40500</v>
       </c>
-      <c r="C33" s="18">
-        <f>C21+C24+C29+C32</f>
+      <c r="C34" s="19">
+        <f>C22+C25+C30+C33</f>
         <v>54885</v>
       </c>
-      <c r="D33" s="18">
-        <f>D21+D24+D29+D32</f>
+      <c r="D34" s="19">
+        <f>D22+D25+D30+D33</f>
         <v>59774</v>
       </c>
-      <c r="E33" s="18">
-        <f>E21+E24+E29+E32</f>
+      <c r="E34" s="19">
+        <f>E22+E25+E30+E33</f>
         <v>64012</v>
       </c>
-      <c r="F33" s="18">
-        <f>F21+F24+F29+F32</f>
+      <c r="F34" s="19">
+        <f>F22+F25+F30+F33</f>
         <v>65776</v>
       </c>
-    </row>
-    <row r="35" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
     </row>
     <row r="36" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B36" s="18">
-        <v>0</v>
-      </c>
-      <c r="C36" s="18">
-        <v>0</v>
-      </c>
-      <c r="D36" s="18">
-        <v>0</v>
-      </c>
-      <c r="E36" s="18">
-        <v>0</v>
-      </c>
-      <c r="F36" s="18">
-        <v>0</v>
+        <v>120</v>
+      </c>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B37" s="12">
+        <v>6960</v>
+      </c>
+      <c r="C37" s="12">
+        <v>6960</v>
+      </c>
+      <c r="D37" s="12">
+        <v>6960</v>
+      </c>
+      <c r="E37" s="12">
+        <v>6960</v>
+      </c>
+      <c r="F37" s="12">
+        <v>6960</v>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="B39" s="20">
-        <f>B10</f>
-        <v>196667</v>
-      </c>
-      <c r="C39" s="20">
-        <f>C10</f>
-        <v>360287</v>
-      </c>
-      <c r="D39" s="20">
-        <f>D10</f>
-        <v>450193</v>
-      </c>
-      <c r="E39" s="20">
-        <f>E10</f>
-        <v>523638</v>
-      </c>
-      <c r="F39" s="20">
-        <f>F10</f>
-        <v>536729</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B40" s="17">
-        <f>B16</f>
-        <v>118934</v>
-      </c>
-      <c r="C40" s="17">
-        <f>C16</f>
-        <v>147003</v>
-      </c>
-      <c r="D40" s="17">
-        <f>D16</f>
-        <v>151413</v>
-      </c>
-      <c r="E40" s="17">
-        <f>E16</f>
-        <v>155955</v>
-      </c>
-      <c r="F40" s="17">
-        <f>F16</f>
-        <v>160634</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="B38" s="19">
+        <f>SUM(B37:B37)</f>
+        <v>6960</v>
+      </c>
+      <c r="C38" s="19">
+        <f>SUM(C37:C37)</f>
+        <v>6960</v>
+      </c>
+      <c r="D38" s="19">
+        <f>SUM(D37:D37)</f>
+        <v>6960</v>
+      </c>
+      <c r="E38" s="19">
+        <f>SUM(E37:E37)</f>
+        <v>6960</v>
+      </c>
+      <c r="F38" s="19">
+        <f>SUM(F37:F37)</f>
+        <v>6960</v>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B41" s="17">
-        <f>B33</f>
-        <v>40500</v>
-      </c>
-      <c r="C41" s="17">
-        <f>C33</f>
-        <v>54885</v>
-      </c>
-      <c r="D41" s="17">
-        <f>D33</f>
-        <v>59774</v>
-      </c>
-      <c r="E41" s="17">
-        <f>E33</f>
-        <v>64012</v>
-      </c>
-      <c r="F41" s="17">
-        <f>F33</f>
-        <v>65776</v>
+      <c r="A41" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="B41" s="21">
+        <f>B11</f>
+        <v>184667</v>
+      </c>
+      <c r="C41" s="21">
+        <f>C11</f>
+        <v>338147</v>
+      </c>
+      <c r="D41" s="21">
+        <f>D11</f>
+        <v>422456</v>
+      </c>
+      <c r="E41" s="21">
+        <f>E11</f>
+        <v>491331</v>
+      </c>
+      <c r="F41" s="21">
+        <f>F11</f>
+        <v>503615</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B42" s="17" t="str">
-        <f>B36</f>
-        <v>0</v>
-      </c>
-      <c r="C42" s="17" t="str">
-        <f>C36</f>
-        <v>0</v>
-      </c>
-      <c r="D42" s="17" t="str">
-        <f>D36</f>
-        <v>0</v>
-      </c>
-      <c r="E42" s="17" t="str">
-        <f>E36</f>
-        <v>0</v>
-      </c>
-      <c r="F42" s="17" t="str">
-        <f>F36</f>
-        <v>0</v>
+        <v>124</v>
+      </c>
+      <c r="B42" s="12">
+        <f>B17</f>
+        <v>118934</v>
+      </c>
+      <c r="C42" s="12">
+        <f>C17</f>
+        <v>147003</v>
+      </c>
+      <c r="D42" s="12">
+        <f>D17</f>
+        <v>151413</v>
+      </c>
+      <c r="E42" s="12">
+        <f>E17</f>
+        <v>155955</v>
+      </c>
+      <c r="F42" s="12">
+        <f>F17</f>
+        <v>160634</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="B43" s="20">
-        <f>B40+B41+B42</f>
-        <v>159434</v>
-      </c>
-      <c r="C43" s="20">
-        <f>C40+C41+C42</f>
-        <v>201888</v>
-      </c>
-      <c r="D43" s="20">
-        <f>D40+D41+D42</f>
-        <v>211187</v>
-      </c>
-      <c r="E43" s="20">
-        <f>E40+E41+E42</f>
-        <v>219967</v>
-      </c>
-      <c r="F43" s="20">
-        <f>F40+F41+F42</f>
-        <v>226410</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="A43" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B43" s="12">
+        <f>B34</f>
+        <v>40500</v>
+      </c>
+      <c r="C43" s="12">
+        <f>C34</f>
+        <v>54885</v>
+      </c>
+      <c r="D43" s="12">
+        <f>D34</f>
+        <v>59774</v>
+      </c>
+      <c r="E43" s="12">
+        <f>E34</f>
+        <v>64012</v>
+      </c>
+      <c r="F43" s="12">
+        <f>F34</f>
+        <v>65776</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B44" s="12">
+        <f>B38</f>
+        <v>6960</v>
+      </c>
+      <c r="C44" s="12">
+        <f>C38</f>
+        <v>6960</v>
+      </c>
+      <c r="D44" s="12">
+        <f>D38</f>
+        <v>6960</v>
+      </c>
+      <c r="E44" s="12">
+        <f>E38</f>
+        <v>6960</v>
+      </c>
+      <c r="F44" s="12">
+        <f>F38</f>
+        <v>6960</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B45" s="21">
+        <f>B42+B43+B44</f>
+        <v>166394</v>
+      </c>
+      <c r="C45" s="21">
+        <f>C42+C43+C44</f>
+        <v>208848</v>
+      </c>
+      <c r="D45" s="21">
+        <f>D42+D43+D44</f>
+        <v>218147</v>
+      </c>
+      <c r="E45" s="21">
+        <f>E42+E43+E44</f>
+        <v>226927</v>
+      </c>
+      <c r="F45" s="21">
+        <f>F42+F43+F44</f>
+        <v>233370</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="B45" s="22">
-        <f>B39-B43</f>
-        <v>37233</v>
-      </c>
-      <c r="C45" s="22">
-        <f>C39-C43</f>
-        <v>158399</v>
-      </c>
-      <c r="D45" s="22">
-        <f>D39-D43</f>
-        <v>239006</v>
-      </c>
-      <c r="E45" s="22">
-        <f>E39-E43</f>
-        <v>303671</v>
-      </c>
-      <c r="F45" s="22">
-        <f>F39-F43</f>
-        <v>310319</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B46" s="23">
-        <f>IF(B39=0,"",B45/B39)</f>
-        <v>0.19</v>
-      </c>
-      <c r="C46" s="23">
-        <f>IF(C39=0,"",C45/C39)</f>
-        <v>0.44</v>
-      </c>
-      <c r="D46" s="23">
-        <f>IF(D39=0,"",D45/D39)</f>
-        <v>0.53</v>
-      </c>
-      <c r="E46" s="23">
-        <f>IF(E39=0,"",E45/E39)</f>
-        <v>0.58</v>
-      </c>
-      <c r="F46" s="23">
-        <f>IF(F39=0,"",F45/F39)</f>
-        <v>0.58</v>
-      </c>
-    </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B47" s="17">
-        <f>B45</f>
-        <v>37233</v>
-      </c>
-      <c r="C47" s="17">
-        <f>B47+C45</f>
-        <v>195632</v>
-      </c>
-      <c r="D47" s="17">
-        <f>C47+D45</f>
-        <v>434638</v>
-      </c>
-      <c r="E47" s="17">
-        <f>D47+E45</f>
-        <v>738309</v>
-      </c>
-      <c r="F47" s="17">
-        <f>E47+F45</f>
-        <v>1048628</v>
-      </c>
-    </row>
-    <row r="49" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="15" t="s">
+      <c r="A47" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="B50" s="20">
-        <f>B39-B40-B41</f>
-        <v>37233</v>
-      </c>
-      <c r="C50" s="20">
-        <f>C39-C40-C41</f>
-        <v>158399</v>
-      </c>
-      <c r="D50" s="20">
-        <f>D39-D40-D41</f>
-        <v>239006</v>
-      </c>
-      <c r="E50" s="20">
-        <f>E39-E40-E41</f>
-        <v>303671</v>
-      </c>
-      <c r="F50" s="20">
-        <f>F39-F40-F41</f>
-        <v>310319</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
+      <c r="B47" s="23">
+        <f>B41-B45</f>
+        <v>18273</v>
+      </c>
+      <c r="C47" s="23">
+        <f>C41-C45</f>
+        <v>129299</v>
+      </c>
+      <c r="D47" s="23">
+        <f>D41-D45</f>
+        <v>204309</v>
+      </c>
+      <c r="E47" s="23">
+        <f>E41-E45</f>
+        <v>264404</v>
+      </c>
+      <c r="F47" s="23">
+        <f>F41-F45</f>
+        <v>270245</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B51" s="17" t="str">
-        <f>B42</f>
-        <v>0</v>
-      </c>
-      <c r="C51" s="17" t="str">
-        <f>C42</f>
-        <v>0</v>
-      </c>
-      <c r="D51" s="17" t="str">
-        <f>D42</f>
-        <v>0</v>
-      </c>
-      <c r="E51" s="17" t="str">
-        <f>E42</f>
-        <v>0</v>
-      </c>
-      <c r="F51" s="17" t="str">
-        <f>F42</f>
-        <v>0</v>
-      </c>
+      <c r="B48" s="24">
+        <f>IF(B41=0,"",B47/B41)</f>
+        <v>0.1</v>
+      </c>
+      <c r="C48" s="24">
+        <f>IF(C41=0,"",C47/C41)</f>
+        <v>0.38</v>
+      </c>
+      <c r="D48" s="24">
+        <f>IF(D41=0,"",D47/D41)</f>
+        <v>0.48</v>
+      </c>
+      <c r="E48" s="24">
+        <f>IF(E41=0,"",E47/E41)</f>
+        <v>0.54</v>
+      </c>
+      <c r="F48" s="24">
+        <f>IF(F41=0,"",F47/F41)</f>
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B49" s="12">
+        <f>B47</f>
+        <v>18273</v>
+      </c>
+      <c r="C49" s="12">
+        <f>B49+C47</f>
+        <v>147572</v>
+      </c>
+      <c r="D49" s="12">
+        <f>C49+D47</f>
+        <v>351881</v>
+      </c>
+      <c r="E49" s="12">
+        <f>D49+E47</f>
+        <v>616285</v>
+      </c>
+      <c r="F49" s="12">
+        <f>E49+F47</f>
+        <v>886530</v>
+      </c>
+    </row>
+    <row r="51" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="B52" s="24" t="str">
-        <f>IF(B51=0,"N/A",B50/B51)</f>
-        <v>N/A</v>
-      </c>
-      <c r="C52" s="24" t="str">
-        <f>IF(C51=0,"N/A",C50/C51)</f>
-        <v>N/A</v>
-      </c>
-      <c r="D52" s="24" t="str">
-        <f>IF(D51=0,"N/A",D50/D51)</f>
-        <v>N/A</v>
-      </c>
-      <c r="E52" s="24" t="str">
-        <f>IF(E51=0,"N/A",E50/E51)</f>
-        <v>N/A</v>
-      </c>
-      <c r="F52" s="24" t="str">
-        <f>IF(F51=0,"N/A",F50/F51)</f>
-        <v>N/A</v>
+      <c r="A52" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="B52" s="21">
+        <f>B41-B42-B43</f>
+        <v>25233</v>
+      </c>
+      <c r="C52" s="21">
+        <f>C41-C42-C43</f>
+        <v>136259</v>
+      </c>
+      <c r="D52" s="21">
+        <f>D41-D42-D43</f>
+        <v>211269</v>
+      </c>
+      <c r="E52" s="21">
+        <f>E41-E42-E43</f>
+        <v>271364</v>
+      </c>
+      <c r="F52" s="21">
+        <f>F41-F42-F43</f>
+        <v>277205</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B53" s="17" t="str">
-        <f>Assumptions!B52</f>
-        <v>0</v>
-      </c>
-      <c r="C53" s="17">
-        <f>B54</f>
-        <v>37233</v>
-      </c>
-      <c r="D53" s="17">
-        <f>C54</f>
-        <v>195632</v>
-      </c>
-      <c r="E53" s="17">
-        <f>D54</f>
-        <v>434638</v>
-      </c>
-      <c r="F53" s="17">
-        <f>E54</f>
-        <v>738309</v>
+        <v>133</v>
+      </c>
+      <c r="B53" s="12">
+        <f>B44</f>
+        <v>6960</v>
+      </c>
+      <c r="C53" s="12">
+        <f>C44</f>
+        <v>6960</v>
+      </c>
+      <c r="D53" s="12">
+        <f>D44</f>
+        <v>6960</v>
+      </c>
+      <c r="E53" s="12">
+        <f>E44</f>
+        <v>6960</v>
+      </c>
+      <c r="F53" s="12">
+        <f>F44</f>
+        <v>6960</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="B54" s="20">
-        <f>B53+B45</f>
-        <v>37233</v>
-      </c>
-      <c r="C54" s="20">
-        <f>C53+C45</f>
-        <v>195632</v>
-      </c>
-      <c r="D54" s="20">
-        <f>D53+D45</f>
-        <v>434638</v>
-      </c>
-      <c r="E54" s="20">
-        <f>E53+E45</f>
-        <v>738309</v>
-      </c>
-      <c r="F54" s="20">
-        <f>F53+F45</f>
-        <v>1048628</v>
+      <c r="A54" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="B54" s="25">
+        <f>IF(B53=0,"N/A",B52/B53)</f>
+        <v>3.63</v>
+      </c>
+      <c r="C54" s="25">
+        <f>IF(C53=0,"N/A",C52/C53)</f>
+        <v>19.58</v>
+      </c>
+      <c r="D54" s="25">
+        <f>IF(D53=0,"N/A",D52/D53)</f>
+        <v>30.35</v>
+      </c>
+      <c r="E54" s="25">
+        <f>IF(E53=0,"N/A",E52/E53)</f>
+        <v>38.99</v>
+      </c>
+      <c r="F54" s="25">
+        <f>IF(F53=0,"N/A",F52/F53)</f>
+        <v>39.83</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B55" s="25">
-        <f>IF(B43=0,"",B54/B43*365)</f>
-        <v>85</v>
-      </c>
-      <c r="C55" s="25">
-        <f>IF(C43=0,"",C54/C43*365)</f>
-        <v>354</v>
-      </c>
-      <c r="D55" s="25">
-        <f>IF(D43=0,"",D54/D43*365)</f>
-        <v>751</v>
-      </c>
-      <c r="E55" s="25">
-        <f>IF(E43=0,"",E54/E43*365)</f>
-        <v>1225</v>
-      </c>
-      <c r="F55" s="25">
-        <f>IF(F43=0,"",F54/F43*365)</f>
-        <v>1691</v>
+        <v>99</v>
+      </c>
+      <c r="B55" s="12" t="str">
+        <f>Assumptions!B54</f>
+        <v>0</v>
+      </c>
+      <c r="C55" s="12">
+        <f>B56</f>
+        <v>18273</v>
+      </c>
+      <c r="D55" s="12">
+        <f>C56</f>
+        <v>147572</v>
+      </c>
+      <c r="E55" s="12">
+        <f>D56</f>
+        <v>351881</v>
+      </c>
+      <c r="F55" s="12">
+        <f>E56</f>
+        <v>616285</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B56" s="26">
-        <f>IF(B43=0,"",B54/(B43/12))</f>
-        <v>2.8</v>
-      </c>
-      <c r="C56" s="26">
-        <f>IF(C43=0,"",C54/(C43/12))</f>
-        <v>11.6</v>
-      </c>
-      <c r="D56" s="26">
-        <f>IF(D43=0,"",D54/(D43/12))</f>
-        <v>24.7</v>
-      </c>
-      <c r="E56" s="26">
-        <f>IF(E43=0,"",E54/(E43/12))</f>
-        <v>40.3</v>
-      </c>
-      <c r="F56" s="26">
-        <f>IF(F43=0,"",F54/(F43/12))</f>
-        <v>55.6</v>
+      <c r="A56" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="B56" s="21">
+        <f>B55+B47</f>
+        <v>18273</v>
+      </c>
+      <c r="C56" s="21">
+        <f>C55+C47</f>
+        <v>147572</v>
+      </c>
+      <c r="D56" s="21">
+        <f>D55+D47</f>
+        <v>351881</v>
+      </c>
+      <c r="E56" s="21">
+        <f>E55+E47</f>
+        <v>616285</v>
+      </c>
+      <c r="F56" s="21">
+        <f>F55+F47</f>
+        <v>886530</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B57" s="23">
+        <v>136</v>
+      </c>
+      <c r="B57" s="26">
+        <f>IF(B45=0,"",B56/B45*365)</f>
+        <v>40</v>
+      </c>
+      <c r="C57" s="26">
+        <f>IF(C45=0,"",C56/C45*365)</f>
+        <v>258</v>
+      </c>
+      <c r="D57" s="26">
+        <f>IF(D45=0,"",D56/D45*365)</f>
+        <v>589</v>
+      </c>
+      <c r="E57" s="26">
+        <f>IF(E45=0,"",E56/E45*365)</f>
+        <v>991</v>
+      </c>
+      <c r="F57" s="26">
+        <f>IF(F45=0,"",F56/F45*365)</f>
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B58" s="27">
+        <f>IF(B45=0,"",B56/(B45/12))</f>
+        <v>1.3</v>
+      </c>
+      <c r="C58" s="27">
+        <f>IF(C45=0,"",C56/(C45/12))</f>
+        <v>8.5</v>
+      </c>
+      <c r="D58" s="27">
+        <f>IF(D45=0,"",D56/(D45/12))</f>
+        <v>19.4</v>
+      </c>
+      <c r="E58" s="27">
+        <f>IF(E45=0,"",E56/(E45/12))</f>
+        <v>32.6</v>
+      </c>
+      <c r="F58" s="27">
+        <f>IF(F45=0,"",F56/(F45/12))</f>
+        <v>45.6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B59" s="24">
         <f>IF(Assumptions!B12=0,"",B3/Assumptions!B12)</f>
         <v>0.48</v>
       </c>
-      <c r="C57" s="23">
+      <c r="C59" s="24">
         <f>IF(Assumptions!B12=0,"",C3/Assumptions!B12)</f>
         <v>0.72</v>
       </c>
-      <c r="D57" s="23">
+      <c r="D59" s="24">
         <f>IF(Assumptions!B12=0,"",D3/Assumptions!B12)</f>
         <v>0.88</v>
       </c>
-      <c r="E57" s="23">
+      <c r="E59" s="24">
         <f>IF(Assumptions!B12=0,"",E3/Assumptions!B12)</f>
         <v>1</v>
       </c>
-      <c r="F57" s="23">
+      <c r="F59" s="24">
         <f>IF(Assumptions!B12=0,"",F3/Assumptions!B12)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="59" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B60" s="4" t="str">
-        <f>IF(B51=0,"N/A",IF(B52&gt;=1.2,"PASS","FAIL"))</f>
-        <v>N/A</v>
-      </c>
-      <c r="C60" s="4" t="str">
-        <f>IF(C51=0,"N/A",IF(C52&gt;=1.2,"PASS","FAIL"))</f>
-        <v>N/A</v>
-      </c>
-      <c r="D60" s="4" t="str">
-        <f>IF(D51=0,"N/A",IF(D52&gt;=1.2,"PASS","FAIL"))</f>
-        <v>N/A</v>
-      </c>
-      <c r="E60" s="4" t="str">
-        <f>IF(E51=0,"N/A",IF(E52&gt;=1.2,"PASS","FAIL"))</f>
-        <v>N/A</v>
-      </c>
-      <c r="F60" s="4" t="str">
-        <f>IF(F51=0,"N/A",IF(F52&gt;=1.2,"PASS","FAIL"))</f>
-        <v>N/A</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B61" s="4" t="str">
-        <f>IF(B45&gt;0,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-      <c r="C61" s="4" t="str">
-        <f>IF(C45&gt;0,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-      <c r="D61" s="4" t="str">
-        <f>IF(D45&gt;0,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-      <c r="E61" s="4" t="str">
-        <f>IF(E45&gt;0,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-      <c r="F61" s="4" t="str">
-        <f>IF(F45&gt;0,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
+    <row r="61" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B62" s="4" t="str">
+        <f>IF(B53=0,"N/A",IF(B54&gt;=1.2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+      <c r="C62" s="4" t="str">
+        <f>IF(C53=0,"N/A",IF(C54&gt;=1.2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+      <c r="D62" s="4" t="str">
+        <f>IF(D53=0,"N/A",IF(D54&gt;=1.2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+      <c r="E62" s="4" t="str">
+        <f>IF(E53=0,"N/A",IF(E54&gt;=1.2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+      <c r="F62" s="4" t="str">
+        <f>IF(F53=0,"N/A",IF(F54&gt;=1.2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B63" s="4" t="str">
+        <f>IF(B47&gt;0,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="C63" s="4" t="str">
+        <f>IF(C47&gt;0,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="D63" s="4" t="str">
+        <f>IF(D47&gt;0,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="E63" s="4" t="str">
+        <f>IF(E47&gt;0,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="F63" s="4" t="str">
+        <f>IF(F47&gt;0,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B64" s="4" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(B3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C62" s="4" t="str">
+      <c r="C64" s="4" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(C3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="D62" s="4" t="str">
+      <c r="D64" s="4" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(D3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E62" s="4" t="str">
+      <c r="E64" s="4" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(E3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F62" s="4" t="str">
+      <c r="F64" s="4" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(F3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B63" s="4" t="str">
-        <f>IF(B43=0,"N/A",IF(B54/(B43/12)&gt;=2,"PASS","FAIL"))</f>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B65" s="4" t="str">
+        <f>IF(B45=0,"N/A",IF(B56/(B45/12)&gt;=2,"PASS","FAIL"))</f>
+        <v>FAIL</v>
+      </c>
+      <c r="C65" s="4" t="str">
+        <f>IF(C45=0,"N/A",IF(C56/(C45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="C63" s="4" t="str">
-        <f>IF(C43=0,"N/A",IF(C54/(C43/12)&gt;=2,"PASS","FAIL"))</f>
+      <c r="D65" s="4" t="str">
+        <f>IF(D45=0,"N/A",IF(D56/(D45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="D63" s="4" t="str">
-        <f>IF(D43=0,"N/A",IF(D54/(D43/12)&gt;=2,"PASS","FAIL"))</f>
+      <c r="E65" s="4" t="str">
+        <f>IF(E45=0,"N/A",IF(E56/(E45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E63" s="4" t="str">
-        <f>IF(E43=0,"N/A",IF(E54/(E43/12)&gt;=2,"PASS","FAIL"))</f>
+      <c r="F65" s="4" t="str">
+        <f>IF(F45=0,"N/A",IF(F56/(F45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F63" s="4" t="str">
-        <f>IF(F43=0,"N/A",IF(F54/(F43/12)&gt;=2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="65" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B66" s="17">
-        <f>IF(B3=0,"",B10/B3)</f>
-        <v>16389</v>
-      </c>
-      <c r="C66" s="17">
-        <f>IF(C3=0,"",C10/C3)</f>
-        <v>20016</v>
-      </c>
-      <c r="D66" s="17">
-        <f>IF(D3=0,"",D10/D3)</f>
-        <v>20463</v>
-      </c>
-      <c r="E66" s="17">
-        <f>IF(E3=0,"",E10/E3)</f>
-        <v>20946</v>
-      </c>
-      <c r="F66" s="17">
-        <f>IF(F3=0,"",F10/F3)</f>
-        <v>21469</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B67" s="17">
-        <f>IF(B3=0,"",B43/B3)</f>
-        <v>13286</v>
-      </c>
-      <c r="C67" s="17">
-        <f>IF(C3=0,"",C43/C3)</f>
-        <v>11216</v>
-      </c>
-      <c r="D67" s="17">
-        <f>IF(D3=0,"",D43/D3)</f>
-        <v>9599</v>
-      </c>
-      <c r="E67" s="17">
-        <f>IF(E3=0,"",E43/E3)</f>
-        <v>8799</v>
-      </c>
-      <c r="F67" s="17">
-        <f>IF(F3=0,"",F43/F3)</f>
-        <v>9056</v>
-      </c>
+    </row>
+    <row r="67" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B68" s="17">
-        <f>B40+B42</f>
-        <v>118934</v>
-      </c>
-      <c r="C68" s="17">
-        <f>C40+C42</f>
-        <v>147003</v>
-      </c>
-      <c r="D68" s="17">
-        <f>D40+D42</f>
-        <v>151413</v>
-      </c>
-      <c r="E68" s="17">
-        <f>E40+E42</f>
-        <v>155955</v>
-      </c>
-      <c r="F68" s="17">
-        <f>F40+F42</f>
-        <v>160634</v>
+        <v>145</v>
+      </c>
+      <c r="B68" s="12">
+        <f>IF(B3=0,"",B11/B3)</f>
+        <v>15389</v>
+      </c>
+      <c r="C68" s="12">
+        <f>IF(C3=0,"",C11/C3)</f>
+        <v>18786</v>
+      </c>
+      <c r="D68" s="12">
+        <f>IF(D3=0,"",D11/D3)</f>
+        <v>19203</v>
+      </c>
+      <c r="E68" s="12">
+        <f>IF(E3=0,"",E11/E3)</f>
+        <v>19653</v>
+      </c>
+      <c r="F68" s="12">
+        <f>IF(F3=0,"",F11/F3)</f>
+        <v>20145</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B69" s="17">
-        <f>IF(B3=0,"",B41/B3)</f>
-        <v>3375</v>
-      </c>
-      <c r="C69" s="17">
-        <f>IF(C3=0,"",C41/C3)</f>
-        <v>3049</v>
-      </c>
-      <c r="D69" s="17">
-        <f>IF(D3=0,"",D41/D3)</f>
-        <v>2717</v>
-      </c>
-      <c r="E69" s="17">
-        <f>IF(E3=0,"",E41/E3)</f>
-        <v>2560</v>
-      </c>
-      <c r="F69" s="17">
-        <f>IF(F3=0,"",F41/F3)</f>
-        <v>2631</v>
+        <v>146</v>
+      </c>
+      <c r="B69" s="12">
+        <f>IF(B3=0,"",B45/B3)</f>
+        <v>13866</v>
+      </c>
+      <c r="C69" s="12">
+        <f>IF(C3=0,"",C45/C3)</f>
+        <v>11603</v>
+      </c>
+      <c r="D69" s="12">
+        <f>IF(D3=0,"",D45/D3)</f>
+        <v>9916</v>
+      </c>
+      <c r="E69" s="12">
+        <f>IF(E3=0,"",E45/E3)</f>
+        <v>9077</v>
+      </c>
+      <c r="F69" s="12">
+        <f>IF(F3=0,"",F45/F3)</f>
+        <v>9335</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B70" s="17">
-        <f>IF(B3=0,"",B66-B69)</f>
-        <v>13014</v>
-      </c>
-      <c r="C70" s="17">
-        <f>IF(C3=0,"",C66-C69)</f>
-        <v>16967</v>
-      </c>
-      <c r="D70" s="17">
-        <f>IF(D3=0,"",D66-D69)</f>
-        <v>17746</v>
-      </c>
-      <c r="E70" s="17">
-        <f>IF(E3=0,"",E66-E69)</f>
-        <v>18385</v>
-      </c>
-      <c r="F70" s="17">
-        <f>IF(F3=0,"",F66-F69)</f>
-        <v>18838</v>
+        <v>147</v>
+      </c>
+      <c r="B70" s="12">
+        <f>B42+B44</f>
+        <v>125894</v>
+      </c>
+      <c r="C70" s="12">
+        <f>C42+C44</f>
+        <v>153963</v>
+      </c>
+      <c r="D70" s="12">
+        <f>D42+D44</f>
+        <v>158373</v>
+      </c>
+      <c r="E70" s="12">
+        <f>E42+E44</f>
+        <v>162915</v>
+      </c>
+      <c r="F70" s="12">
+        <f>F42+F44</f>
+        <v>167594</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="27" t="s">
-        <v>146</v>
-      </c>
-      <c r="B71" s="28">
-        <f>IF(B70&lt;=0,"N/A",ROUNDUP(B68/B70,0))</f>
+      <c r="A71" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B71" s="12">
+        <f>IF(B3=0,"",B43/B3)</f>
+        <v>3375</v>
+      </c>
+      <c r="C71" s="12">
+        <f>IF(C3=0,"",C43/C3)</f>
+        <v>3049</v>
+      </c>
+      <c r="D71" s="12">
+        <f>IF(D3=0,"",D43/D3)</f>
+        <v>2717</v>
+      </c>
+      <c r="E71" s="12">
+        <f>IF(E3=0,"",E43/E3)</f>
+        <v>2560</v>
+      </c>
+      <c r="F71" s="12">
+        <f>IF(F3=0,"",F43/F3)</f>
+        <v>2631</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B72" s="12">
+        <f>IF(B3=0,"",B68-B71)</f>
+        <v>12014</v>
+      </c>
+      <c r="C72" s="12">
+        <f>IF(C3=0,"",C68-C71)</f>
+        <v>15737</v>
+      </c>
+      <c r="D72" s="12">
+        <f>IF(D3=0,"",D68-D71)</f>
+        <v>16486</v>
+      </c>
+      <c r="E72" s="12">
+        <f>IF(E3=0,"",E68-E71)</f>
+        <v>17093</v>
+      </c>
+      <c r="F72" s="12">
+        <f>IF(F3=0,"",F68-F71)</f>
+        <v>17514</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="B73" s="29">
+        <f>IF(B72&lt;=0,"N/A",ROUNDUP(B70/B72,0))</f>
+        <v>11</v>
+      </c>
+      <c r="C73" s="29">
+        <f>IF(C72&lt;=0,"N/A",ROUNDUP(C70/C72,0))</f>
         <v>10</v>
       </c>
-      <c r="C71" s="28">
-        <f>IF(C70&lt;=0,"N/A",ROUNDUP(C68/C70,0))</f>
-        <v>9</v>
-      </c>
-      <c r="D71" s="28">
-        <f>IF(D70&lt;=0,"N/A",ROUNDUP(D68/D70,0))</f>
-        <v>9</v>
-      </c>
-      <c r="E71" s="28">
-        <f>IF(E70&lt;=0,"N/A",ROUNDUP(E68/E70,0))</f>
-        <v>9</v>
-      </c>
-      <c r="F71" s="28">
-        <f>IF(F70&lt;=0,"N/A",ROUNDUP(F68/F70,0))</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="B73" s="13"/>
-      <c r="C73" s="13"/>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
+      <c r="D73" s="29">
+        <f>IF(D72&lt;=0,"N/A",ROUNDUP(D70/D72,0))</f>
+        <v>10</v>
+      </c>
+      <c r="E73" s="29">
+        <f>IF(E72&lt;=0,"N/A",ROUNDUP(E70/E72,0))</f>
+        <v>10</v>
+      </c>
+      <c r="F73" s="29">
+        <f>IF(F72&lt;=0,"N/A",ROUNDUP(F70/F72,0))</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B75" s="15"/>
+      <c r="C75" s="15"/>
+      <c r="D75" s="15"/>
+      <c r="E75" s="15"/>
+      <c r="F75" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A73:F73"/>
+    <mergeCell ref="A75:F75"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
@@ -3064,7 +3174,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -3074,7 +3184,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3091,52 +3201,52 @@
       <c r="N1" s="1"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="G2" s="14" t="s">
+      <c r="C2" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="D2" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="E2" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="F2" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="G2" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="H2" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="M2" s="14" t="s">
+      <c r="I2" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="J2" s="16" t="s">
         <v>159</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="L2" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="M2" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -3156,43 +3266,43 @@
       <c r="A4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="12">
         <v>14400</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="12">
         <v>14400</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="12">
         <v>14400</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="12">
         <v>14400</v>
       </c>
-      <c r="F4" s="17">
+      <c r="F4" s="12">
         <v>14400</v>
       </c>
-      <c r="G4" s="17">
+      <c r="G4" s="12">
         <v>14400</v>
       </c>
-      <c r="H4" s="17">
+      <c r="H4" s="12">
         <v>14400</v>
       </c>
-      <c r="I4" s="17">
+      <c r="I4" s="12">
         <v>14400</v>
       </c>
-      <c r="J4" s="17">
+      <c r="J4" s="12">
         <v>14400</v>
       </c>
-      <c r="K4" s="17">
+      <c r="K4" s="12">
         <v>14400</v>
       </c>
-      <c r="L4" s="17">
-        <v>0</v>
-      </c>
-      <c r="M4" s="17">
-        <v>0</v>
-      </c>
-      <c r="N4" s="17">
+      <c r="L4" s="12">
+        <v>0</v>
+      </c>
+      <c r="M4" s="12">
+        <v>0</v>
+      </c>
+      <c r="N4" s="12">
         <f>SUM(B4:M4)</f>
         <v>120000</v>
       </c>
@@ -3201,43 +3311,43 @@
       <c r="A5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="12">
         <v>300</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="12">
         <v>300</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="12">
         <v>300</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="12">
         <v>300</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="12">
         <v>300</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="12">
         <v>300</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="12">
         <v>300</v>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="12">
         <v>300</v>
       </c>
-      <c r="J5" s="17">
+      <c r="J5" s="12">
         <v>300</v>
       </c>
-      <c r="K5" s="17">
+      <c r="K5" s="12">
         <v>300</v>
       </c>
-      <c r="L5" s="17">
-        <v>0</v>
-      </c>
-      <c r="M5" s="17">
-        <v>0</v>
-      </c>
-      <c r="N5" s="17">
+      <c r="L5" s="12">
+        <v>0</v>
+      </c>
+      <c r="M5" s="12">
+        <v>0</v>
+      </c>
+      <c r="N5" s="12">
         <f>SUM(B5:M5)</f>
         <v>2500</v>
       </c>
@@ -3246,43 +3356,43 @@
       <c r="A6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="12">
         <v>8400</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="12">
         <v>8400</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="12">
         <v>8400</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="12">
         <v>8400</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="12">
         <v>8400</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="12">
         <v>8400</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="12">
         <v>8400</v>
       </c>
-      <c r="I6" s="17">
+      <c r="I6" s="12">
         <v>8400</v>
       </c>
-      <c r="J6" s="17">
+      <c r="J6" s="12">
         <v>8400</v>
       </c>
-      <c r="K6" s="17">
+      <c r="K6" s="12">
         <v>8400</v>
       </c>
-      <c r="L6" s="17">
-        <v>0</v>
-      </c>
-      <c r="M6" s="17">
-        <v>0</v>
-      </c>
-      <c r="N6" s="17">
+      <c r="L6" s="12">
+        <v>0</v>
+      </c>
+      <c r="M6" s="12">
+        <v>0</v>
+      </c>
+      <c r="N6" s="12">
         <f>SUM(B6:M6)</f>
         <v>70000</v>
       </c>
@@ -3291,1220 +3401,1265 @@
       <c r="A7" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="12">
         <v>500</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="12">
         <v>500</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="12">
         <v>500</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="12">
         <v>500</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="12">
         <v>500</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="12">
         <v>500</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="12">
         <v>500</v>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="12">
         <v>500</v>
       </c>
-      <c r="J7" s="17">
+      <c r="J7" s="12">
         <v>500</v>
       </c>
-      <c r="K7" s="17">
+      <c r="K7" s="12">
         <v>500</v>
       </c>
-      <c r="L7" s="17">
-        <v>0</v>
-      </c>
-      <c r="M7" s="17">
-        <v>0</v>
-      </c>
-      <c r="N7" s="17">
+      <c r="L7" s="12">
+        <v>0</v>
+      </c>
+      <c r="M7" s="12">
+        <v>0</v>
+      </c>
+      <c r="N7" s="12">
         <f>SUM(B7:M7)</f>
         <v>4167</v>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B8" s="18">
-        <f>SUM(B4:B7)</f>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="12">
+        <v>0</v>
+      </c>
+      <c r="C8" s="12">
+        <v>0</v>
+      </c>
+      <c r="D8" s="12">
+        <v>0</v>
+      </c>
+      <c r="E8" s="12">
+        <v>0</v>
+      </c>
+      <c r="F8" s="12">
+        <v>0</v>
+      </c>
+      <c r="G8" s="12">
+        <v>0</v>
+      </c>
+      <c r="H8" s="12">
+        <v>0</v>
+      </c>
+      <c r="I8" s="12">
+        <v>0</v>
+      </c>
+      <c r="J8" s="12">
+        <v>0</v>
+      </c>
+      <c r="K8" s="12">
+        <v>0</v>
+      </c>
+      <c r="L8" s="12">
+        <v>0</v>
+      </c>
+      <c r="M8" s="12">
+        <v>0</v>
+      </c>
+      <c r="N8" s="12" t="str">
+        <f>SUM(B8:M8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" s="19">
+        <f>SUM(B4:B8)</f>
         <v>155900</v>
       </c>
-      <c r="C8" s="18">
-        <f>SUM(C4:C7)</f>
-        <v>8900</v>
-      </c>
-      <c r="D8" s="18">
-        <f>SUM(D4:D7)</f>
-        <v>8900</v>
-      </c>
-      <c r="E8" s="18">
-        <f>SUM(E4:E7)</f>
-        <v>8900</v>
-      </c>
-      <c r="F8" s="18">
-        <f>SUM(F4:F7)</f>
-        <v>8900</v>
-      </c>
-      <c r="G8" s="18">
-        <f>SUM(G4:G7)</f>
-        <v>8900</v>
-      </c>
-      <c r="H8" s="18">
-        <f>SUM(H4:H7)</f>
-        <v>8900</v>
-      </c>
-      <c r="I8" s="18">
-        <f>SUM(I4:I7)</f>
-        <v>8900</v>
-      </c>
-      <c r="J8" s="18">
-        <f>SUM(J4:J7)</f>
-        <v>8900</v>
-      </c>
-      <c r="K8" s="18">
-        <f>SUM(K4:K7)</f>
-        <v>8900</v>
-      </c>
-      <c r="L8" s="18" t="str">
-        <f>SUM(L4:L7)</f>
-        <v>0</v>
-      </c>
-      <c r="M8" s="18" t="str">
-        <f>SUM(M4:M7)</f>
-        <v>0</v>
-      </c>
-      <c r="N8" s="18">
-        <f>SUM(B8:M8)</f>
-        <v>236000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="C9" s="19">
+        <f>SUM(C4:C8)</f>
+        <v>7460</v>
+      </c>
+      <c r="D9" s="19">
+        <f>SUM(D4:D8)</f>
+        <v>7460</v>
+      </c>
+      <c r="E9" s="19">
+        <f>SUM(E4:E8)</f>
+        <v>7460</v>
+      </c>
+      <c r="F9" s="19">
+        <f>SUM(F4:F8)</f>
+        <v>7460</v>
+      </c>
+      <c r="G9" s="19">
+        <f>SUM(G4:G8)</f>
+        <v>7460</v>
+      </c>
+      <c r="H9" s="19">
+        <f>SUM(H4:H8)</f>
+        <v>7460</v>
+      </c>
+      <c r="I9" s="19">
+        <f>SUM(I4:I8)</f>
+        <v>7460</v>
+      </c>
+      <c r="J9" s="19">
+        <f>SUM(J4:J8)</f>
+        <v>7460</v>
+      </c>
+      <c r="K9" s="19">
+        <f>SUM(K4:K8)</f>
+        <v>7460</v>
+      </c>
+      <c r="L9" s="19">
+        <f>SUM(L4:L8)</f>
+        <v>-1440</v>
+      </c>
+      <c r="M9" s="19" t="str">
+        <f>SUM(M4:M8)</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="19">
+        <f>SUM(B9:M9)</f>
+        <v>221600</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B11" s="17">
-        <v>5851</v>
-      </c>
-      <c r="C11" s="17">
-        <v>5851</v>
-      </c>
-      <c r="D11" s="17">
-        <v>5851</v>
-      </c>
-      <c r="E11" s="17">
-        <v>5851</v>
-      </c>
-      <c r="F11" s="17">
-        <v>5851</v>
-      </c>
-      <c r="G11" s="17">
-        <v>5851</v>
-      </c>
-      <c r="H11" s="17">
-        <v>5851</v>
-      </c>
-      <c r="I11" s="17">
-        <v>5851</v>
-      </c>
-      <c r="J11" s="17">
-        <v>5851</v>
-      </c>
-      <c r="K11" s="17">
-        <v>5851</v>
-      </c>
-      <c r="L11" s="17">
-        <v>0</v>
-      </c>
-      <c r="M11" s="17">
-        <v>0</v>
-      </c>
-      <c r="N11" s="17">
-        <f>SUM(B11:M11)</f>
-        <v>58506</v>
-      </c>
+    <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="17">
-        <v>4787</v>
-      </c>
-      <c r="C12" s="17">
-        <v>4787</v>
-      </c>
-      <c r="D12" s="17">
-        <v>4787</v>
-      </c>
-      <c r="E12" s="17">
-        <v>4787</v>
-      </c>
-      <c r="F12" s="17">
-        <v>4787</v>
-      </c>
-      <c r="G12" s="17">
-        <v>4787</v>
-      </c>
-      <c r="H12" s="17">
-        <v>4787</v>
-      </c>
-      <c r="I12" s="17">
-        <v>4787</v>
-      </c>
-      <c r="J12" s="17">
-        <v>4787</v>
-      </c>
-      <c r="K12" s="17">
-        <v>4787</v>
-      </c>
-      <c r="L12" s="17">
-        <v>0</v>
-      </c>
-      <c r="M12" s="17">
-        <v>0</v>
-      </c>
-      <c r="N12" s="17">
+        <v>59</v>
+      </c>
+      <c r="B12" s="12">
+        <v>5851</v>
+      </c>
+      <c r="C12" s="12">
+        <v>5851</v>
+      </c>
+      <c r="D12" s="12">
+        <v>5851</v>
+      </c>
+      <c r="E12" s="12">
+        <v>5851</v>
+      </c>
+      <c r="F12" s="12">
+        <v>5851</v>
+      </c>
+      <c r="G12" s="12">
+        <v>5851</v>
+      </c>
+      <c r="H12" s="12">
+        <v>5851</v>
+      </c>
+      <c r="I12" s="12">
+        <v>5851</v>
+      </c>
+      <c r="J12" s="12">
+        <v>5851</v>
+      </c>
+      <c r="K12" s="12">
+        <v>5851</v>
+      </c>
+      <c r="L12" s="12">
+        <v>0</v>
+      </c>
+      <c r="M12" s="12">
+        <v>0</v>
+      </c>
+      <c r="N12" s="12">
         <f>SUM(B12:M12)</f>
-        <v>47869</v>
+        <v>58506</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="17">
+        <v>63</v>
+      </c>
+      <c r="B13" s="12">
+        <v>4787</v>
+      </c>
+      <c r="C13" s="12">
+        <v>4787</v>
+      </c>
+      <c r="D13" s="12">
+        <v>4787</v>
+      </c>
+      <c r="E13" s="12">
+        <v>4787</v>
+      </c>
+      <c r="F13" s="12">
+        <v>4787</v>
+      </c>
+      <c r="G13" s="12">
+        <v>4787</v>
+      </c>
+      <c r="H13" s="12">
+        <v>4787</v>
+      </c>
+      <c r="I13" s="12">
+        <v>4787</v>
+      </c>
+      <c r="J13" s="12">
+        <v>4787</v>
+      </c>
+      <c r="K13" s="12">
+        <v>4787</v>
+      </c>
+      <c r="L13" s="12">
+        <v>0</v>
+      </c>
+      <c r="M13" s="12">
+        <v>0</v>
+      </c>
+      <c r="N13" s="12">
+        <f>SUM(B13:M13)</f>
+        <v>47869</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="12">
         <v>1256</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C14" s="12">
         <v>1256</v>
       </c>
-      <c r="D13" s="17">
+      <c r="D14" s="12">
         <v>1256</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E14" s="12">
         <v>1256</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F14" s="12">
         <v>1256</v>
       </c>
-      <c r="G13" s="17">
+      <c r="G14" s="12">
         <v>1256</v>
       </c>
-      <c r="H13" s="17">
+      <c r="H14" s="12">
         <v>1256</v>
       </c>
-      <c r="I13" s="17">
+      <c r="I14" s="12">
         <v>1256</v>
       </c>
-      <c r="J13" s="17">
+      <c r="J14" s="12">
         <v>1256</v>
       </c>
-      <c r="K13" s="17">
+      <c r="K14" s="12">
         <v>1256</v>
       </c>
-      <c r="L13" s="17">
-        <v>0</v>
-      </c>
-      <c r="M13" s="17">
-        <v>0</v>
-      </c>
-      <c r="N13" s="17">
-        <f>SUM(B13:M13)</f>
+      <c r="L14" s="12">
+        <v>0</v>
+      </c>
+      <c r="M14" s="12">
+        <v>0</v>
+      </c>
+      <c r="N14" s="12">
+        <f>SUM(B14:M14)</f>
         <v>12559</v>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B14" s="18">
-        <f>SUM(B11:B13)</f>
+    <row r="15" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" s="19">
+        <f>SUM(B12:B14)</f>
         <v>11893</v>
       </c>
-      <c r="C14" s="18">
-        <f>SUM(C11:C13)</f>
+      <c r="C15" s="19">
+        <f>SUM(C12:C14)</f>
         <v>11893</v>
       </c>
-      <c r="D14" s="18">
-        <f>SUM(D11:D13)</f>
+      <c r="D15" s="19">
+        <f>SUM(D12:D14)</f>
         <v>11893</v>
       </c>
-      <c r="E14" s="18">
-        <f>SUM(E11:E13)</f>
+      <c r="E15" s="19">
+        <f>SUM(E12:E14)</f>
         <v>11893</v>
       </c>
-      <c r="F14" s="18">
-        <f>SUM(F11:F13)</f>
+      <c r="F15" s="19">
+        <f>SUM(F12:F14)</f>
         <v>11893</v>
       </c>
-      <c r="G14" s="18">
-        <f>SUM(G11:G13)</f>
+      <c r="G15" s="19">
+        <f>SUM(G12:G14)</f>
         <v>11893</v>
       </c>
-      <c r="H14" s="18">
-        <f>SUM(H11:H13)</f>
+      <c r="H15" s="19">
+        <f>SUM(H12:H14)</f>
         <v>11893</v>
       </c>
-      <c r="I14" s="18">
-        <f>SUM(I11:I13)</f>
+      <c r="I15" s="19">
+        <f>SUM(I12:I14)</f>
         <v>11893</v>
       </c>
-      <c r="J14" s="18">
-        <f>SUM(J11:J13)</f>
+      <c r="J15" s="19">
+        <f>SUM(J12:J14)</f>
         <v>11893</v>
       </c>
-      <c r="K14" s="18">
-        <f>SUM(K11:K13)</f>
+      <c r="K15" s="19">
+        <f>SUM(K12:K14)</f>
         <v>11893</v>
       </c>
-      <c r="L14" s="18" t="str">
-        <f>SUM(L11:L13)</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="18" t="str">
-        <f>SUM(M11:M13)</f>
-        <v>0</v>
-      </c>
-      <c r="N14" s="18">
-        <f>SUM(B14:M14)</f>
+      <c r="L15" s="19" t="str">
+        <f>SUM(L12:L14)</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="19" t="str">
+        <f>SUM(M12:M14)</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="19">
+        <f>SUM(B15:M15)</f>
         <v>118934</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
+    <row r="17" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="B18" s="17">
+        <v>81</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B19" s="12">
         <v>500</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C19" s="12">
         <v>500</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D19" s="12">
         <v>500</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E19" s="12">
         <v>500</v>
       </c>
-      <c r="F18" s="17">
+      <c r="F19" s="12">
         <v>500</v>
       </c>
-      <c r="G18" s="17">
+      <c r="G19" s="12">
         <v>500</v>
       </c>
-      <c r="H18" s="17">
+      <c r="H19" s="12">
         <v>500</v>
       </c>
-      <c r="I18" s="17">
+      <c r="I19" s="12">
         <v>500</v>
       </c>
-      <c r="J18" s="17">
+      <c r="J19" s="12">
         <v>500</v>
       </c>
-      <c r="K18" s="17">
+      <c r="K19" s="12">
         <v>500</v>
       </c>
-      <c r="L18" s="17">
-        <v>0</v>
-      </c>
-      <c r="M18" s="17">
-        <v>0</v>
-      </c>
-      <c r="N18" s="17">
-        <f>SUM(B18:M18)</f>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="B19" s="20">
-        <v>500</v>
-      </c>
-      <c r="C19" s="20">
-        <v>500</v>
-      </c>
-      <c r="D19" s="20">
-        <v>500</v>
-      </c>
-      <c r="E19" s="20">
-        <v>500</v>
-      </c>
-      <c r="F19" s="20">
-        <v>500</v>
-      </c>
-      <c r="G19" s="20">
-        <v>500</v>
-      </c>
-      <c r="H19" s="20">
-        <v>500</v>
-      </c>
-      <c r="I19" s="20">
-        <v>500</v>
-      </c>
-      <c r="J19" s="20">
-        <v>500</v>
-      </c>
-      <c r="K19" s="20">
-        <v>500</v>
-      </c>
-      <c r="L19" s="20">
-        <v>0</v>
-      </c>
-      <c r="M19" s="20">
-        <v>0</v>
-      </c>
-      <c r="N19" s="20">
+      <c r="L19" s="12">
+        <v>0</v>
+      </c>
+      <c r="M19" s="12">
+        <v>0</v>
+      </c>
+      <c r="N19" s="12">
         <f>SUM(B19:M19)</f>
         <v>5000</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
+      <c r="A20" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="21">
+        <v>500</v>
+      </c>
+      <c r="C20" s="21">
+        <v>500</v>
+      </c>
+      <c r="D20" s="21">
+        <v>500</v>
+      </c>
+      <c r="E20" s="21">
+        <v>500</v>
+      </c>
+      <c r="F20" s="21">
+        <v>500</v>
+      </c>
+      <c r="G20" s="21">
+        <v>500</v>
+      </c>
+      <c r="H20" s="21">
+        <v>500</v>
+      </c>
+      <c r="I20" s="21">
+        <v>500</v>
+      </c>
+      <c r="J20" s="21">
+        <v>500</v>
+      </c>
+      <c r="K20" s="21">
+        <v>500</v>
+      </c>
+      <c r="L20" s="21">
+        <v>0</v>
+      </c>
+      <c r="M20" s="21">
+        <v>0</v>
+      </c>
+      <c r="N20" s="21">
+        <f>SUM(B20:M20)</f>
+        <v>5000</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="B21" s="17">
+        <v>82</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="4"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B22" s="12">
         <v>300</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C22" s="12">
         <v>300</v>
       </c>
-      <c r="D21" s="17">
+      <c r="D22" s="12">
         <v>300</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E22" s="12">
         <v>300</v>
       </c>
-      <c r="F21" s="17">
+      <c r="F22" s="12">
         <v>300</v>
       </c>
-      <c r="G21" s="17">
+      <c r="G22" s="12">
         <v>300</v>
       </c>
-      <c r="H21" s="17">
+      <c r="H22" s="12">
         <v>300</v>
       </c>
-      <c r="I21" s="17">
+      <c r="I22" s="12">
         <v>300</v>
       </c>
-      <c r="J21" s="17">
+      <c r="J22" s="12">
         <v>300</v>
       </c>
-      <c r="K21" s="17">
+      <c r="K22" s="12">
         <v>300</v>
       </c>
-      <c r="L21" s="17">
-        <v>0</v>
-      </c>
-      <c r="M21" s="17">
-        <v>0</v>
-      </c>
-      <c r="N21" s="17">
-        <f>SUM(B21:M21)</f>
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="B22" s="20">
-        <v>300</v>
-      </c>
-      <c r="C22" s="20">
-        <v>300</v>
-      </c>
-      <c r="D22" s="20">
-        <v>300</v>
-      </c>
-      <c r="E22" s="20">
-        <v>300</v>
-      </c>
-      <c r="F22" s="20">
-        <v>300</v>
-      </c>
-      <c r="G22" s="20">
-        <v>300</v>
-      </c>
-      <c r="H22" s="20">
-        <v>300</v>
-      </c>
-      <c r="I22" s="20">
-        <v>300</v>
-      </c>
-      <c r="J22" s="20">
-        <v>300</v>
-      </c>
-      <c r="K22" s="20">
-        <v>300</v>
-      </c>
-      <c r="L22" s="20">
-        <v>0</v>
-      </c>
-      <c r="M22" s="20">
-        <v>0</v>
-      </c>
-      <c r="N22" s="20">
+      <c r="L22" s="12">
+        <v>0</v>
+      </c>
+      <c r="M22" s="12">
+        <v>0</v>
+      </c>
+      <c r="N22" s="12">
         <f>SUM(B22:M22)</f>
         <v>3000</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
+      <c r="A23" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="B23" s="21">
+        <v>300</v>
+      </c>
+      <c r="C23" s="21">
+        <v>300</v>
+      </c>
+      <c r="D23" s="21">
+        <v>300</v>
+      </c>
+      <c r="E23" s="21">
+        <v>300</v>
+      </c>
+      <c r="F23" s="21">
+        <v>300</v>
+      </c>
+      <c r="G23" s="21">
+        <v>300</v>
+      </c>
+      <c r="H23" s="21">
+        <v>300</v>
+      </c>
+      <c r="I23" s="21">
+        <v>300</v>
+      </c>
+      <c r="J23" s="21">
+        <v>300</v>
+      </c>
+      <c r="K23" s="21">
+        <v>300</v>
+      </c>
+      <c r="L23" s="21">
+        <v>0</v>
+      </c>
+      <c r="M23" s="21">
+        <v>0</v>
+      </c>
+      <c r="N23" s="21">
+        <f>SUM(B23:M23)</f>
+        <v>3000</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="B24" s="17">
-        <v>2500</v>
-      </c>
-      <c r="C24" s="17">
-        <v>2500</v>
-      </c>
-      <c r="D24" s="17">
-        <v>2500</v>
-      </c>
-      <c r="E24" s="17">
-        <v>2500</v>
-      </c>
-      <c r="F24" s="17">
-        <v>2500</v>
-      </c>
-      <c r="G24" s="17">
-        <v>2500</v>
-      </c>
-      <c r="H24" s="17">
-        <v>2500</v>
-      </c>
-      <c r="I24" s="17">
-        <v>2500</v>
-      </c>
-      <c r="J24" s="17">
-        <v>2500</v>
-      </c>
-      <c r="K24" s="17">
-        <v>2500</v>
-      </c>
-      <c r="L24" s="17">
-        <v>0</v>
-      </c>
-      <c r="M24" s="17">
-        <v>0</v>
-      </c>
-      <c r="N24" s="17">
-        <f>SUM(B24:M24)</f>
-        <v>25000</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B25" s="17">
-        <v>300</v>
-      </c>
-      <c r="C25" s="17">
-        <v>300</v>
-      </c>
-      <c r="D25" s="17">
-        <v>300</v>
-      </c>
-      <c r="E25" s="17">
-        <v>300</v>
-      </c>
-      <c r="F25" s="17">
-        <v>300</v>
-      </c>
-      <c r="G25" s="17">
-        <v>300</v>
-      </c>
-      <c r="H25" s="17">
-        <v>300</v>
-      </c>
-      <c r="I25" s="17">
-        <v>300</v>
-      </c>
-      <c r="J25" s="17">
-        <v>300</v>
-      </c>
-      <c r="K25" s="17">
-        <v>300</v>
-      </c>
-      <c r="L25" s="17">
-        <v>0</v>
-      </c>
-      <c r="M25" s="17">
-        <v>0</v>
-      </c>
-      <c r="N25" s="17">
+        <v>166</v>
+      </c>
+      <c r="B25" s="12">
+        <v>2500</v>
+      </c>
+      <c r="C25" s="12">
+        <v>2500</v>
+      </c>
+      <c r="D25" s="12">
+        <v>2500</v>
+      </c>
+      <c r="E25" s="12">
+        <v>2500</v>
+      </c>
+      <c r="F25" s="12">
+        <v>2500</v>
+      </c>
+      <c r="G25" s="12">
+        <v>2500</v>
+      </c>
+      <c r="H25" s="12">
+        <v>2500</v>
+      </c>
+      <c r="I25" s="12">
+        <v>2500</v>
+      </c>
+      <c r="J25" s="12">
+        <v>2500</v>
+      </c>
+      <c r="K25" s="12">
+        <v>2500</v>
+      </c>
+      <c r="L25" s="12">
+        <v>0</v>
+      </c>
+      <c r="M25" s="12">
+        <v>0</v>
+      </c>
+      <c r="N25" s="12">
         <f>SUM(B25:M25)</f>
-        <v>3000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="B26" s="17">
+        <v>167</v>
+      </c>
+      <c r="B26" s="12">
+        <v>300</v>
+      </c>
+      <c r="C26" s="12">
+        <v>300</v>
+      </c>
+      <c r="D26" s="12">
+        <v>300</v>
+      </c>
+      <c r="E26" s="12">
+        <v>300</v>
+      </c>
+      <c r="F26" s="12">
+        <v>300</v>
+      </c>
+      <c r="G26" s="12">
+        <v>300</v>
+      </c>
+      <c r="H26" s="12">
+        <v>300</v>
+      </c>
+      <c r="I26" s="12">
+        <v>300</v>
+      </c>
+      <c r="J26" s="12">
+        <v>300</v>
+      </c>
+      <c r="K26" s="12">
+        <v>300</v>
+      </c>
+      <c r="L26" s="12">
+        <v>0</v>
+      </c>
+      <c r="M26" s="12">
+        <v>0</v>
+      </c>
+      <c r="N26" s="12">
+        <f>SUM(B26:M26)</f>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B27" s="12">
         <v>200</v>
       </c>
-      <c r="C26" s="17">
+      <c r="C27" s="12">
         <v>200</v>
       </c>
-      <c r="D26" s="17">
+      <c r="D27" s="12">
         <v>200</v>
       </c>
-      <c r="E26" s="17">
+      <c r="E27" s="12">
         <v>200</v>
       </c>
-      <c r="F26" s="17">
+      <c r="F27" s="12">
         <v>200</v>
       </c>
-      <c r="G26" s="17">
+      <c r="G27" s="12">
         <v>200</v>
       </c>
-      <c r="H26" s="17">
+      <c r="H27" s="12">
         <v>200</v>
       </c>
-      <c r="I26" s="17">
+      <c r="I27" s="12">
         <v>200</v>
       </c>
-      <c r="J26" s="17">
+      <c r="J27" s="12">
         <v>200</v>
       </c>
-      <c r="K26" s="17">
+      <c r="K27" s="12">
         <v>200</v>
       </c>
-      <c r="L26" s="17">
-        <v>0</v>
-      </c>
-      <c r="M26" s="17">
-        <v>0</v>
-      </c>
-      <c r="N26" s="17">
-        <f>SUM(B26:M26)</f>
+      <c r="L27" s="12">
+        <v>0</v>
+      </c>
+      <c r="M27" s="12">
+        <v>0</v>
+      </c>
+      <c r="N27" s="12">
+        <f>SUM(B27:M27)</f>
         <v>2000</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="B27" s="20">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B28" s="21">
         <v>3000</v>
       </c>
-      <c r="C27" s="20">
+      <c r="C28" s="21">
         <v>3000</v>
       </c>
-      <c r="D27" s="20">
+      <c r="D28" s="21">
         <v>3000</v>
       </c>
-      <c r="E27" s="20">
+      <c r="E28" s="21">
         <v>3000</v>
       </c>
-      <c r="F27" s="20">
+      <c r="F28" s="21">
         <v>3000</v>
       </c>
-      <c r="G27" s="20">
+      <c r="G28" s="21">
         <v>3000</v>
       </c>
-      <c r="H27" s="20">
+      <c r="H28" s="21">
         <v>3000</v>
       </c>
-      <c r="I27" s="20">
+      <c r="I28" s="21">
         <v>3000</v>
       </c>
-      <c r="J27" s="20">
+      <c r="J28" s="21">
         <v>3000</v>
       </c>
-      <c r="K27" s="20">
+      <c r="K28" s="21">
         <v>3000</v>
       </c>
-      <c r="L27" s="20">
-        <v>0</v>
-      </c>
-      <c r="M27" s="20">
-        <v>0</v>
-      </c>
-      <c r="N27" s="20">
-        <f>SUM(B27:M27)</f>
+      <c r="L28" s="21">
+        <v>0</v>
+      </c>
+      <c r="M28" s="21">
+        <v>0</v>
+      </c>
+      <c r="N28" s="21">
+        <f>SUM(B28:M28)</f>
         <v>30000</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="B29" s="17">
+        <v>84</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B30" s="12">
         <v>250</v>
       </c>
-      <c r="C29" s="17">
+      <c r="C30" s="12">
         <v>250</v>
       </c>
-      <c r="D29" s="17">
+      <c r="D30" s="12">
         <v>250</v>
       </c>
-      <c r="E29" s="17">
+      <c r="E30" s="12">
         <v>250</v>
       </c>
-      <c r="F29" s="17">
+      <c r="F30" s="12">
         <v>250</v>
       </c>
-      <c r="G29" s="17">
+      <c r="G30" s="12">
         <v>250</v>
       </c>
-      <c r="H29" s="17">
+      <c r="H30" s="12">
         <v>250</v>
       </c>
-      <c r="I29" s="17">
+      <c r="I30" s="12">
         <v>250</v>
       </c>
-      <c r="J29" s="17">
+      <c r="J30" s="12">
         <v>250</v>
       </c>
-      <c r="K29" s="17">
+      <c r="K30" s="12">
         <v>250</v>
       </c>
-      <c r="L29" s="17">
-        <v>0</v>
-      </c>
-      <c r="M29" s="17">
-        <v>0</v>
-      </c>
-      <c r="N29" s="17">
-        <f>SUM(B29:M29)</f>
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="B30" s="20">
-        <v>250</v>
-      </c>
-      <c r="C30" s="20">
-        <v>250</v>
-      </c>
-      <c r="D30" s="20">
-        <v>250</v>
-      </c>
-      <c r="E30" s="20">
-        <v>250</v>
-      </c>
-      <c r="F30" s="20">
-        <v>250</v>
-      </c>
-      <c r="G30" s="20">
-        <v>250</v>
-      </c>
-      <c r="H30" s="20">
-        <v>250</v>
-      </c>
-      <c r="I30" s="20">
-        <v>250</v>
-      </c>
-      <c r="J30" s="20">
-        <v>250</v>
-      </c>
-      <c r="K30" s="20">
-        <v>250</v>
-      </c>
-      <c r="L30" s="20">
-        <v>0</v>
-      </c>
-      <c r="M30" s="20">
-        <v>0</v>
-      </c>
-      <c r="N30" s="20">
+      <c r="L30" s="12">
+        <v>0</v>
+      </c>
+      <c r="M30" s="12">
+        <v>0</v>
+      </c>
+      <c r="N30" s="12">
         <f>SUM(B30:M30)</f>
         <v>2500</v>
       </c>
     </row>
-    <row r="31" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B31" s="18">
-        <f>B19+B22+B27+B30</f>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31" s="21">
+        <v>250</v>
+      </c>
+      <c r="C31" s="21">
+        <v>250</v>
+      </c>
+      <c r="D31" s="21">
+        <v>250</v>
+      </c>
+      <c r="E31" s="21">
+        <v>250</v>
+      </c>
+      <c r="F31" s="21">
+        <v>250</v>
+      </c>
+      <c r="G31" s="21">
+        <v>250</v>
+      </c>
+      <c r="H31" s="21">
+        <v>250</v>
+      </c>
+      <c r="I31" s="21">
+        <v>250</v>
+      </c>
+      <c r="J31" s="21">
+        <v>250</v>
+      </c>
+      <c r="K31" s="21">
+        <v>250</v>
+      </c>
+      <c r="L31" s="21">
+        <v>0</v>
+      </c>
+      <c r="M31" s="21">
+        <v>0</v>
+      </c>
+      <c r="N31" s="21">
+        <f>SUM(B31:M31)</f>
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B32" s="19">
+        <f>B20+B23+B28+B31</f>
         <v>4050</v>
       </c>
-      <c r="C31" s="18">
-        <f>C19+C22+C27+C30</f>
+      <c r="C32" s="19">
+        <f>C20+C23+C28+C31</f>
         <v>4050</v>
       </c>
-      <c r="D31" s="18">
-        <f>D19+D22+D27+D30</f>
+      <c r="D32" s="19">
+        <f>D20+D23+D28+D31</f>
         <v>4050</v>
       </c>
-      <c r="E31" s="18">
-        <f>E19+E22+E27+E30</f>
+      <c r="E32" s="19">
+        <f>E20+E23+E28+E31</f>
         <v>4050</v>
       </c>
-      <c r="F31" s="18">
-        <f>F19+F22+F27+F30</f>
+      <c r="F32" s="19">
+        <f>F20+F23+F28+F31</f>
         <v>4050</v>
       </c>
-      <c r="G31" s="18">
-        <f>G19+G22+G27+G30</f>
+      <c r="G32" s="19">
+        <f>G20+G23+G28+G31</f>
         <v>4050</v>
       </c>
-      <c r="H31" s="18">
-        <f>H19+H22+H27+H30</f>
+      <c r="H32" s="19">
+        <f>H20+H23+H28+H31</f>
         <v>4050</v>
       </c>
-      <c r="I31" s="18">
-        <f>I19+I22+I27+I30</f>
+      <c r="I32" s="19">
+        <f>I20+I23+I28+I31</f>
         <v>4050</v>
       </c>
-      <c r="J31" s="18">
-        <f>J19+J22+J27+J30</f>
+      <c r="J32" s="19">
+        <f>J20+J23+J28+J31</f>
         <v>4050</v>
       </c>
-      <c r="K31" s="18">
-        <f>K19+K22+K27+K30</f>
+      <c r="K32" s="19">
+        <f>K20+K23+K28+K31</f>
         <v>4050</v>
       </c>
-      <c r="L31" s="18" t="str">
-        <f>L19+L22+L27+L30</f>
-        <v>0</v>
-      </c>
-      <c r="M31" s="18" t="str">
-        <f>M19+M22+M27+M30</f>
-        <v>0</v>
-      </c>
-      <c r="N31" s="18">
-        <f>SUM(B31:M31)</f>
+      <c r="L32" s="19" t="str">
+        <f>L20+L23+L28+L31</f>
+        <v>0</v>
+      </c>
+      <c r="M32" s="19" t="str">
+        <f>M20+M23+M28+M31</f>
+        <v>0</v>
+      </c>
+      <c r="N32" s="19">
+        <f>SUM(B32:M32)</f>
         <v>40500</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="B33" s="17">
-        <v>0</v>
-      </c>
-      <c r="C33" s="17">
-        <v>0</v>
-      </c>
-      <c r="D33" s="17">
-        <v>0</v>
-      </c>
-      <c r="E33" s="17">
-        <v>0</v>
-      </c>
-      <c r="F33" s="17">
-        <v>0</v>
-      </c>
-      <c r="G33" s="17">
-        <v>0</v>
-      </c>
-      <c r="H33" s="17">
-        <v>0</v>
-      </c>
-      <c r="I33" s="17">
-        <v>0</v>
-      </c>
-      <c r="J33" s="17">
-        <v>0</v>
-      </c>
-      <c r="K33" s="17">
-        <v>0</v>
-      </c>
-      <c r="L33" s="17">
-        <v>0</v>
-      </c>
-      <c r="M33" s="17">
-        <v>0</v>
-      </c>
-      <c r="N33" s="17" t="str">
-        <f>SUM(B33:M33)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="B34" s="12">
+        <v>580</v>
+      </c>
+      <c r="C34" s="12">
+        <v>580</v>
+      </c>
+      <c r="D34" s="12">
+        <v>580</v>
+      </c>
+      <c r="E34" s="12">
+        <v>580</v>
+      </c>
+      <c r="F34" s="12">
+        <v>580</v>
+      </c>
+      <c r="G34" s="12">
+        <v>580</v>
+      </c>
+      <c r="H34" s="12">
+        <v>580</v>
+      </c>
+      <c r="I34" s="12">
+        <v>580</v>
+      </c>
+      <c r="J34" s="12">
+        <v>580</v>
+      </c>
+      <c r="K34" s="12">
+        <v>580</v>
+      </c>
+      <c r="L34" s="12">
+        <v>580</v>
+      </c>
+      <c r="M34" s="12">
+        <v>580</v>
+      </c>
+      <c r="N34" s="12">
+        <f>SUM(B34:M34)</f>
+        <v>6960</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="35" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="B36" s="20">
-        <f>B14+B31+B33</f>
-        <v>15943</v>
-      </c>
-      <c r="C36" s="20">
-        <f>C14+C31+C33</f>
-        <v>15943</v>
-      </c>
-      <c r="D36" s="20">
-        <f>D14+D31+D33</f>
-        <v>15943</v>
-      </c>
-      <c r="E36" s="20">
-        <f>E14+E31+E33</f>
-        <v>15943</v>
-      </c>
-      <c r="F36" s="20">
-        <f>F14+F31+F33</f>
-        <v>15943</v>
-      </c>
-      <c r="G36" s="20">
-        <f>G14+G31+G33</f>
-        <v>15943</v>
-      </c>
-      <c r="H36" s="20">
-        <f>H14+H31+H33</f>
-        <v>15943</v>
-      </c>
-      <c r="I36" s="20">
-        <f>I14+I31+I33</f>
-        <v>15943</v>
-      </c>
-      <c r="J36" s="20">
-        <f>J14+J31+J33</f>
-        <v>15943</v>
-      </c>
-      <c r="K36" s="20">
-        <f>K14+K31+K33</f>
-        <v>15943</v>
-      </c>
-      <c r="L36" s="20" t="str">
-        <f>L14+L31+L33</f>
-        <v>0</v>
-      </c>
-      <c r="M36" s="20" t="str">
-        <f>M14+M31+M33</f>
-        <v>0</v>
-      </c>
-      <c r="N36" s="20">
-        <f>SUM(B36:M36)</f>
-        <v>159430</v>
-      </c>
+    <row r="36" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="B37" s="20">
-        <f>B8-B36</f>
-        <v>139957</v>
-      </c>
-      <c r="C37" s="20">
-        <f>C8-C36</f>
-        <v>-7043</v>
-      </c>
-      <c r="D37" s="20">
-        <f>D8-D36</f>
-        <v>-7043</v>
-      </c>
-      <c r="E37" s="20">
-        <f>E8-E36</f>
-        <v>-7043</v>
-      </c>
-      <c r="F37" s="20">
-        <f>F8-F36</f>
-        <v>-7043</v>
-      </c>
-      <c r="G37" s="20">
-        <f>G8-G36</f>
-        <v>-7043</v>
-      </c>
-      <c r="H37" s="20">
-        <f>H8-H36</f>
-        <v>-7043</v>
-      </c>
-      <c r="I37" s="20">
-        <f>I8-I36</f>
-        <v>-7043</v>
-      </c>
-      <c r="J37" s="20">
-        <f>J8-J36</f>
-        <v>-7043</v>
-      </c>
-      <c r="K37" s="20">
-        <f>K8-K36</f>
-        <v>-7043</v>
-      </c>
-      <c r="L37" s="20" t="str">
-        <f>L8-L36</f>
-        <v>0</v>
-      </c>
-      <c r="M37" s="20" t="str">
-        <f>M8-M36</f>
-        <v>0</v>
-      </c>
-      <c r="N37" s="20">
+      <c r="A37" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B37" s="21">
+        <f>B15+B32+B34</f>
+        <v>16523</v>
+      </c>
+      <c r="C37" s="21">
+        <f>C15+C32+C34</f>
+        <v>16523</v>
+      </c>
+      <c r="D37" s="21">
+        <f>D15+D32+D34</f>
+        <v>16523</v>
+      </c>
+      <c r="E37" s="21">
+        <f>E15+E32+E34</f>
+        <v>16523</v>
+      </c>
+      <c r="F37" s="21">
+        <f>F15+F32+F34</f>
+        <v>16523</v>
+      </c>
+      <c r="G37" s="21">
+        <f>G15+G32+G34</f>
+        <v>16523</v>
+      </c>
+      <c r="H37" s="21">
+        <f>H15+H32+H34</f>
+        <v>16523</v>
+      </c>
+      <c r="I37" s="21">
+        <f>I15+I32+I34</f>
+        <v>16523</v>
+      </c>
+      <c r="J37" s="21">
+        <f>J15+J32+J34</f>
+        <v>16523</v>
+      </c>
+      <c r="K37" s="21">
+        <f>K15+K32+K34</f>
+        <v>16523</v>
+      </c>
+      <c r="L37" s="21">
+        <f>L15+L32+L34</f>
+        <v>580</v>
+      </c>
+      <c r="M37" s="21">
+        <f>M15+M32+M34</f>
+        <v>580</v>
+      </c>
+      <c r="N37" s="21">
         <f>SUM(B37:M37)</f>
-        <v>76570</v>
+        <v>166390</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="B38" s="20">
-        <f>0+B37</f>
-        <v>139957</v>
-      </c>
-      <c r="C38" s="20">
-        <f>B38+C37</f>
-        <v>132914</v>
-      </c>
-      <c r="D38" s="20">
-        <f>C38+D37</f>
-        <v>125871</v>
-      </c>
-      <c r="E38" s="20">
-        <f>D38+E37</f>
-        <v>118828</v>
-      </c>
-      <c r="F38" s="20">
-        <f>E38+F37</f>
-        <v>111785</v>
-      </c>
-      <c r="G38" s="20">
-        <f>F38+G37</f>
-        <v>104742</v>
-      </c>
-      <c r="H38" s="20">
-        <f>G38+H37</f>
-        <v>97699</v>
-      </c>
-      <c r="I38" s="20">
-        <f>H38+I37</f>
-        <v>90656</v>
-      </c>
-      <c r="J38" s="20">
-        <f>I38+J37</f>
-        <v>83613</v>
-      </c>
-      <c r="K38" s="20">
-        <f>J38+K37</f>
-        <v>76570</v>
-      </c>
-      <c r="L38" s="20">
-        <f>K38+L37</f>
-        <v>76570</v>
-      </c>
-      <c r="M38" s="20">
-        <f>L38+M37</f>
-        <v>76570</v>
-      </c>
-      <c r="N38" s="20">
-        <f>M38</f>
-        <v>76570</v>
-      </c>
-    </row>
-    <row r="40" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B41" s="17">
-        <v>0</v>
-      </c>
+      <c r="A38" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="B38" s="21">
+        <f>B9-B37</f>
+        <v>139377</v>
+      </c>
+      <c r="C38" s="21">
+        <f>C9-C37</f>
+        <v>-9063</v>
+      </c>
+      <c r="D38" s="21">
+        <f>D9-D37</f>
+        <v>-9063</v>
+      </c>
+      <c r="E38" s="21">
+        <f>E9-E37</f>
+        <v>-9063</v>
+      </c>
+      <c r="F38" s="21">
+        <f>F9-F37</f>
+        <v>-9063</v>
+      </c>
+      <c r="G38" s="21">
+        <f>G9-G37</f>
+        <v>-9063</v>
+      </c>
+      <c r="H38" s="21">
+        <f>H9-H37</f>
+        <v>-9063</v>
+      </c>
+      <c r="I38" s="21">
+        <f>I9-I37</f>
+        <v>-9063</v>
+      </c>
+      <c r="J38" s="21">
+        <f>J9-J37</f>
+        <v>-9063</v>
+      </c>
+      <c r="K38" s="21">
+        <f>K9-K37</f>
+        <v>-9063</v>
+      </c>
+      <c r="L38" s="21">
+        <f>L9-L37</f>
+        <v>-2020</v>
+      </c>
+      <c r="M38" s="21">
+        <f>M9-M37</f>
+        <v>-580</v>
+      </c>
+      <c r="N38" s="21">
+        <f>SUM(B38:M38)</f>
+        <v>55210</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="B39" s="21">
+        <f>0+B38</f>
+        <v>139377</v>
+      </c>
+      <c r="C39" s="21">
+        <f>B39+C38</f>
+        <v>130314</v>
+      </c>
+      <c r="D39" s="21">
+        <f>C39+D38</f>
+        <v>121251</v>
+      </c>
+      <c r="E39" s="21">
+        <f>D39+E38</f>
+        <v>112188</v>
+      </c>
+      <c r="F39" s="21">
+        <f>E39+F38</f>
+        <v>103125</v>
+      </c>
+      <c r="G39" s="21">
+        <f>F39+G38</f>
+        <v>94062</v>
+      </c>
+      <c r="H39" s="21">
+        <f>G39+H38</f>
+        <v>84999</v>
+      </c>
+      <c r="I39" s="21">
+        <f>H39+I38</f>
+        <v>75936</v>
+      </c>
+      <c r="J39" s="21">
+        <f>I39+J38</f>
+        <v>66873</v>
+      </c>
+      <c r="K39" s="21">
+        <f>J39+K38</f>
+        <v>57810</v>
+      </c>
+      <c r="L39" s="21">
+        <f>K39+L38</f>
+        <v>55790</v>
+      </c>
+      <c r="M39" s="21">
+        <f>L39+M38</f>
+        <v>55210</v>
+      </c>
+      <c r="N39" s="21">
+        <f>M39</f>
+        <v>55210</v>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="B42" s="20">
-        <f>M38</f>
-        <v>76570</v>
+        <v>99</v>
+      </c>
+      <c r="B42" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="B43" s="17">
-        <f>MIN(B38:M38)</f>
-        <v>76570</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="13"/>
-      <c r="J45" s="13"/>
-      <c r="K45" s="13"/>
-      <c r="L45" s="13"/>
-      <c r="M45" s="13"/>
-      <c r="N45" s="13"/>
+        <v>175</v>
+      </c>
+      <c r="B43" s="21">
+        <f>M39</f>
+        <v>55210</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B44" s="12">
+        <f>MIN(B39:M39)</f>
+        <v>55210</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B46" s="15"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="15"/>
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
+      <c r="K46" s="15"/>
+      <c r="L46" s="15"/>
+      <c r="M46" s="15"/>
+      <c r="N46" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A45:N45"/>
+    <mergeCell ref="A46:N46"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
@@ -4,29 +4,104 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Assumptions" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="5-Year Model" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Year 1 Pro Forma" state="visible" r:id="rId6"/>
+    <sheet sheetId="1" name="Instructions" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Assumptions" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="5-Year Model" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Year 1 Pro Forma" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Financial Health" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Assumptions'!$A1:$J56</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Assumptions'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'5-Year Model'!$A1:$F75</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'5-Year Model'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Year 1 Pro Forma'!$A1:$N46</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Year 1 Pro Forma'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instructions'!$A1:$B29</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Instructions'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$J56</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'5-Year Model'!$A1:$F75</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N46</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$G26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="241">
+  <si>
+    <t>How to Use This Workbook</t>
+  </si>
+  <si>
+    <t>Cell Color Legend</t>
+  </si>
+  <si>
+    <t>Blue cells are editable inputs — change these to update your model.</t>
+  </si>
+  <si>
+    <t>White cells contain formulas — do not edit (they recalculate automatically).</t>
+  </si>
+  <si>
+    <t>Green cells are key outputs and summary metrics.</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
+  </si>
+  <si>
+    <t>Structure</t>
+  </si>
+  <si>
+    <t>5-Year Model: Detailed revenue, expense, and cash projections</t>
+  </si>
+  <si>
+    <t>Pro Forma: Consolidated income statement</t>
+  </si>
+  <si>
+    <t>Actuals vs Projections: Variance tracking</t>
+  </si>
+  <si>
+    <t>Financial Health: Key metrics dashboard</t>
+  </si>
+  <si>
+    <t>Debt Service Convention</t>
+  </si>
+  <si>
+    <t>operating expense on the Operating Statement. This is a standard</t>
+  </si>
+  <si>
+    <t>simplification used in school financial underwriting that ensures internal</t>
+  </si>
+  <si>
+    <t>consistency across all tabs.</t>
+  </si>
+  <si>
+    <t>Tips</t>
+  </si>
+  <si>
+    <t>Check the Financial Health dashboard for an at-a-glance assessment.</t>
+  </si>
+  <si>
+    <t>Review key metrics: net margin, cash runway, and DSCR.</t>
+  </si>
+  <si>
+    <t>Disclaimer</t>
+  </si>
+  <si>
+    <t>a loan commitment, or a guarantee of funding. All projections are based on</t>
+  </si>
+  <si>
+    <t>user-provided assumptions and should be independently verified.</t>
+  </si>
   <si>
     <t>Bright Horizons Microschool - Financial Model Assumptions</t>
   </si>
   <si>
-    <t>Yellow cells are editable inputs. All other cells in this workbook are formulas.</t>
+    <t>Blue cells are editable inputs. All other cells in this workbook are formulas.</t>
   </si>
   <si>
     <t>SCHOOL PROFILE</t>
@@ -143,9 +218,6 @@
     <t>Per Student</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Registration Fee</t>
   </si>
   <si>
@@ -552,6 +624,132 @@
   </si>
   <si>
     <t>Minimum Cash Month</t>
+  </si>
+  <si>
+    <t>Bright Horizons Microschool — Financial Health Dashboard</t>
+  </si>
+  <si>
+    <t>Generated March 26, 2026</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Year 1</t>
+  </si>
+  <si>
+    <t>Year 2</t>
+  </si>
+  <si>
+    <t>Year 3</t>
+  </si>
+  <si>
+    <t>Year 4</t>
+  </si>
+  <si>
+    <t>Year 5</t>
+  </si>
+  <si>
+    <t>Enrollment</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Personnel</t>
+  </si>
+  <si>
+    <t>Operating Expenses</t>
+  </si>
+  <si>
+    <t>Net Income</t>
+  </si>
+  <si>
+    <t>Net Margin</t>
+  </si>
+  <si>
+    <t>FINANCIAL HEALTH SIGNALS</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Assessment</t>
+  </si>
+  <si>
+    <t>Watch Item</t>
+  </si>
+  <si>
+    <t>Viability</t>
+  </si>
+  <si>
+    <t>● Healthy</t>
+  </si>
+  <si>
+    <t>The model reaches profit early and sustains strong margins through Year 5.</t>
+  </si>
+  <si>
+    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+  </si>
+  <si>
+    <t>Liquidity</t>
+  </si>
+  <si>
+    <t>Cash stays positive throughout the projection and reserves exceed 3 months of expenses.</t>
+  </si>
+  <si>
+    <t>Maintain reserves as a buffer against seasonal revenue dips.</t>
+  </si>
+  <si>
+    <t>Staffing Burden</t>
+  </si>
+  <si>
+    <t>Staffing at 32% of revenue leaves room for facilities, programs, and reserves.</t>
+  </si>
+  <si>
+    <t>As you add staff, ensure staffing stays below 60% of revenue.</t>
+  </si>
+  <si>
+    <t>Facility Burden</t>
+  </si>
+  <si>
+    <t>Facility costs at 4% of revenue are well-managed and leave budget for programs.</t>
+  </si>
+  <si>
+    <t>Watch for rent escalation clauses that could push this higher over time.</t>
+  </si>
+  <si>
+    <t>Debt Affordability</t>
+  </si>
+  <si>
+    <t>DSCR of 39.83x provides comfortable coverage of debt payments with room to spare.</t>
+  </si>
+  <si>
+    <t>Maintain this ratio as you take on any additional debt.</t>
+  </si>
+  <si>
+    <t>Revenue Concentration</t>
+  </si>
+  <si>
+    <t>Revenue is anchored to enrollment-driven income — the strongest foundation for a school model. A focused revenue stream is a strength when backed by dependable demand.</t>
+  </si>
+  <si>
+    <t>Continue to pressure-test enrollment assumptions: recruitment pipeline, waitlist depth, retention rates, and collection reliability.</t>
+  </si>
+  <si>
+    <t>Reserve Strength</t>
+  </si>
+  <si>
+    <t>47.1 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+  </si>
+  <si>
+    <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>7 Healthy  |  0 Watch  |  0 Needs Attention</t>
   </si>
 </sst>
 </file>
@@ -565,11 +763,27 @@
     <numFmt numFmtId="167" formatCode="0.00x"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1E293B"/>
+      <sz val="16"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1E293B"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -586,12 +800,7 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF1E293B"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
+      <color rgb="FF1E3A5F"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -624,8 +833,20 @@
       <sz val="12"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF16A34A"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -639,12 +860,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFDE8"/>
+        <fgColor rgb="FFDBEAFE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -690,45 +916,74 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1071,6 +1326,163 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="B2:B29"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;10&amp;BBright Horizons Microschool&amp;R&amp;8&amp;IInstructions</oddHeader>
+    <oddFooter>&amp;L&amp;8Built by SchoolStack Budget  •  budget.schoolstack.ai&amp;C&amp;8Page &amp;P of &amp;N&amp;R&amp;8&amp;D</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:J56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -1081,731 +1493,731 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="A1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="11">
+        <v>12</v>
+      </c>
+      <c r="C17" s="11">
+        <v>18</v>
+      </c>
+      <c r="D17" s="11">
+        <v>22</v>
+      </c>
+      <c r="E17" s="11">
+        <v>25</v>
+      </c>
+      <c r="F17" s="11">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="12">
+        <v>12000</v>
+      </c>
+      <c r="E20" s="13">
+        <v>0</v>
+      </c>
+      <c r="F20" s="9">
+        <v>10</v>
+      </c>
+      <c r="G20" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="H20" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="5" t="s">
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="12">
+        <v>250</v>
+      </c>
+      <c r="E21" s="13">
+        <v>0</v>
+      </c>
+      <c r="F21" s="9">
+        <v>12</v>
+      </c>
+      <c r="G21" s="13">
+        <v>1</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" s="12">
+        <v>7000</v>
+      </c>
+      <c r="E22" s="13">
+        <v>0</v>
+      </c>
+      <c r="F22" s="9">
+        <v>12</v>
+      </c>
+      <c r="G22" s="13">
+        <v>1</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="12">
+        <v>5000</v>
+      </c>
+      <c r="E23" s="13">
+        <v>0</v>
+      </c>
+      <c r="F23" s="9">
+        <v>12</v>
+      </c>
+      <c r="G23" s="13">
+        <v>1</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="5" t="s">
+      <c r="E24" s="13">
+        <v>0</v>
+      </c>
+      <c r="F24" s="9">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="6">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" s="3"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="8">
-        <v>12</v>
-      </c>
-      <c r="C17" s="8">
-        <v>18</v>
-      </c>
-      <c r="D17" s="8">
-        <v>22</v>
-      </c>
-      <c r="E17" s="8">
-        <v>25</v>
-      </c>
-      <c r="F17" s="8">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="9">
-        <v>12000</v>
-      </c>
-      <c r="E20" s="10">
-        <v>0</v>
-      </c>
-      <c r="F20" s="6">
-        <v>10</v>
-      </c>
-      <c r="G20" s="10">
+      <c r="G24" s="13">
         <v>1</v>
       </c>
-      <c r="H20" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" s="9">
-        <v>250</v>
-      </c>
-      <c r="E21" s="10">
-        <v>0</v>
-      </c>
-      <c r="F21" s="6">
-        <v>12</v>
-      </c>
-      <c r="G21" s="10">
+      <c r="H24" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="H21" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22" s="9">
-        <v>7000</v>
-      </c>
-      <c r="E22" s="10">
-        <v>0</v>
-      </c>
-      <c r="F22" s="6">
-        <v>12</v>
-      </c>
-      <c r="G22" s="10">
+      <c r="E28" s="12">
+        <v>55000</v>
+      </c>
+      <c r="F28" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="G28" s="13">
+        <v>0.0765</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" s="14">
         <v>1</v>
       </c>
-      <c r="H22" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D23" s="9">
-        <v>5000</v>
-      </c>
-      <c r="E23" s="10">
-        <v>0</v>
-      </c>
-      <c r="F23" s="6">
-        <v>12</v>
-      </c>
-      <c r="G23" s="10">
-        <v>1</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" s="9">
-        <v>10</v>
-      </c>
-      <c r="E24" s="10">
-        <v>0</v>
-      </c>
-      <c r="F24" s="6">
-        <v>12</v>
-      </c>
-      <c r="G24" s="10">
-        <v>1</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D27" s="3" t="s">
+      <c r="E29" s="12">
+        <v>45000</v>
+      </c>
+      <c r="F29" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="G29" s="13">
+        <v>0.0765</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="E30" s="12">
+        <v>28000</v>
+      </c>
+      <c r="F30" s="13">
+        <v>0</v>
+      </c>
+      <c r="G30" s="13">
+        <v>0.0765</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" s="6"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" s="12">
+        <v>2500</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="C37" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="D37" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="E37" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+      <c r="F37" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D28" s="11">
-        <v>1</v>
-      </c>
-      <c r="E28" s="9">
-        <v>55000</v>
-      </c>
-      <c r="F28" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="G28" s="10">
-        <v>0.0765</v>
-      </c>
-      <c r="H28" s="4" t="s">
+      <c r="G37" s="6"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D38" s="12">
+        <v>2500</v>
+      </c>
+      <c r="E38" s="13">
+        <v>0.03</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D39" s="12">
+        <v>300</v>
+      </c>
+      <c r="E39" s="13">
+        <v>0</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" s="12">
+        <v>2400</v>
+      </c>
+      <c r="E40" s="13">
+        <v>0</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C41" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="I28" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D29" s="11">
-        <v>1</v>
-      </c>
-      <c r="E29" s="9">
-        <v>45000</v>
-      </c>
-      <c r="F29" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="G29" s="10">
-        <v>0.0765</v>
-      </c>
-      <c r="H29" s="4" t="s">
+      <c r="D41" s="12">
+        <v>500</v>
+      </c>
+      <c r="E41" s="13">
+        <v>0</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C42" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="I29" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D30" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="E30" s="9">
-        <v>28000</v>
-      </c>
-      <c r="F30" s="10">
-        <v>0</v>
-      </c>
-      <c r="G30" s="10">
-        <v>0.0765</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
+      <c r="D42" s="12">
+        <v>300</v>
+      </c>
+      <c r="E42" s="13">
+        <v>0</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C43" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D32" s="3"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B34" s="9">
-        <v>2500</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B35" s="10">
+      <c r="D43" s="12">
+        <v>3000</v>
+      </c>
+      <c r="E43" s="13">
+        <v>0</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C46" s="15">
+        <v>0</v>
+      </c>
+      <c r="D46" s="12">
+        <v>30000</v>
+      </c>
+      <c r="E46" s="16">
+        <v>0.06</v>
+      </c>
+      <c r="F46" s="9">
+        <v>5</v>
+      </c>
+      <c r="G46" s="15">
+        <v>6960</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B49" s="13">
         <v>0.03</v>
       </c>
     </row>
-    <row r="37" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G37" s="3"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D38" s="9">
-        <v>2500</v>
-      </c>
-      <c r="E38" s="10">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B50" s="13">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B51" s="14">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="C51" s="17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B52" s="13">
         <v>0.03</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D39" s="9">
-        <v>300</v>
-      </c>
-      <c r="E39" s="10">
-        <v>0</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" s="9">
-        <v>2400</v>
-      </c>
-      <c r="E40" s="10">
-        <v>0</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D41" s="9">
-        <v>500</v>
-      </c>
-      <c r="E41" s="10">
-        <v>0</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D42" s="9">
-        <v>300</v>
-      </c>
-      <c r="E42" s="10">
-        <v>0</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D43" s="9">
-        <v>3000</v>
-      </c>
-      <c r="E43" s="10">
-        <v>0</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="45" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C46" s="12">
-        <v>0</v>
-      </c>
-      <c r="D46" s="9">
-        <v>30000</v>
-      </c>
-      <c r="E46" s="13">
-        <v>0.06</v>
-      </c>
-      <c r="F46" s="6">
-        <v>5</v>
-      </c>
-      <c r="G46" s="12">
-        <v>6960</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="48" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B49" s="10">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B50" s="10">
-        <v>0.025</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B51" s="11">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="C51" s="14" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B52" s="10">
-        <v>0.03</v>
-      </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B53" s="10">
+      <c r="A53" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B53" s="13">
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B54" s="9">
+      <c r="A54" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B54" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="B56" s="15"/>
-      <c r="C56" s="15"/>
-      <c r="D56" s="15"/>
-      <c r="E56" s="15"/>
-      <c r="F56" s="15"/>
-      <c r="G56" s="15"/>
+      <c r="A56" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="B56" s="18"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1823,7 +2235,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -1836,1324 +2248,1324 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>27</v>
+      <c r="A2" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="18">
+      <c r="A3" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="21">
         <f>Assumptions!B17</f>
         <v>12</v>
       </c>
-      <c r="C3" s="18">
+      <c r="C3" s="21">
         <f>Assumptions!C17</f>
         <v>18</v>
       </c>
-      <c r="D3" s="18">
+      <c r="D3" s="21">
         <f>Assumptions!D17</f>
         <v>22</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="21">
         <f>Assumptions!E17</f>
         <v>25</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="21">
         <f>Assumptions!F17</f>
         <v>25</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="A5" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="12">
+      <c r="A6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="15">
         <v>120000</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="15">
         <v>221400</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="15">
         <v>277365</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="15">
         <v>323067</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="15">
         <v>331144</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="12">
+      <c r="A7" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="15">
         <v>2500</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="15">
         <v>4613</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="15">
         <v>5778</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="15">
         <v>6731</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="15">
         <v>6899</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="12">
+      <c r="A8" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="15">
         <v>70000</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="15">
         <v>129150</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="15">
         <v>161796</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="15">
         <v>188456</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="15">
         <v>193167</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="12">
+      <c r="A9" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="15">
         <v>4167</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="15">
         <v>5125</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="15">
         <v>5253</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="15">
         <v>5384</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="15">
         <v>5519</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="12">
+      <c r="A10" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="15">
         <v>-12000</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="15">
         <v>-22140</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="15">
         <v>-27736</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="15">
         <v>-32307</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="15">
         <v>-33114</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B11" s="19">
+      <c r="A11" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" s="22">
         <f>SUM(B6:B10)</f>
         <v>184667</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="22">
         <f>SUM(C6:C10)</f>
         <v>338147</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="22">
         <f>SUM(D6:D10)</f>
         <v>422456</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="22">
         <f>SUM(E6:E10)</f>
         <v>491331</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="22">
         <f>SUM(F6:F10)</f>
         <v>503615</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+      <c r="A13" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B14" s="12">
+      <c r="A14" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="15">
         <v>58506</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="15">
         <v>72314</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="15">
         <v>74483</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="15">
         <v>76718</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="15">
         <v>79019</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B15" s="12">
+      <c r="A15" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B15" s="15">
         <v>47869</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="15">
         <v>59166</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="15">
         <v>60941</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="15">
         <v>62769</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="15">
         <v>64652</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B16" s="12">
+      <c r="A16" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B16" s="15">
         <v>12559</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="15">
         <v>15523</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="15">
         <v>15989</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="15">
         <v>16468</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="15">
         <v>16963</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B17" s="19">
+      <c r="A17" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B17" s="22">
         <f>SUM(B14:B16)</f>
         <v>118934</v>
       </c>
-      <c r="C17" s="19">
+      <c r="C17" s="22">
         <f>SUM(C14:C16)</f>
         <v>147003</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="22">
         <f>SUM(D14:D16)</f>
         <v>151413</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="22">
         <f>SUM(E14:E16)</f>
         <v>155955</v>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="22">
         <f>SUM(F14:F16)</f>
         <v>160634</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
+      <c r="A19" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
+      <c r="A20" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B21" s="12">
+      <c r="A21" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B21" s="15">
         <v>5000</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="15">
         <v>9225</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="15">
         <v>11557</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="15">
         <v>13461</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="15">
         <v>13798</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="B22" s="21">
+      <c r="A22" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="B22" s="24">
         <v>5000</v>
       </c>
-      <c r="C22" s="21">
+      <c r="C22" s="24">
         <v>9225</v>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="24">
         <v>11557</v>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="24">
         <v>13461</v>
       </c>
-      <c r="F22" s="21">
+      <c r="F22" s="24">
         <v>13798</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
+      <c r="A23" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B24" s="12">
+      <c r="A24" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B24" s="15">
         <v>3000</v>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="15">
         <v>5535</v>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="15">
         <v>6934</v>
       </c>
-      <c r="E24" s="12">
+      <c r="E24" s="15">
         <v>8077</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="15">
         <v>8279</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="B25" s="21">
+      <c r="A25" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25" s="24">
         <v>3000</v>
       </c>
-      <c r="C25" s="21">
+      <c r="C25" s="24">
         <v>5535</v>
       </c>
-      <c r="D25" s="21">
+      <c r="D25" s="24">
         <v>6934</v>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="24">
         <v>8077</v>
       </c>
-      <c r="F25" s="21">
+      <c r="F25" s="24">
         <v>8279</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
+      <c r="A26" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B27" s="12">
+      <c r="A27" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B27" s="15">
         <v>25000</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="15">
         <v>30900</v>
       </c>
-      <c r="D27" s="12">
+      <c r="D27" s="15">
         <v>31827</v>
       </c>
-      <c r="E27" s="12">
+      <c r="E27" s="15">
         <v>32782</v>
       </c>
-      <c r="F27" s="12">
+      <c r="F27" s="15">
         <v>33765</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B28" s="12">
+      <c r="A28" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B28" s="15">
         <v>3000</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="15">
         <v>3690</v>
       </c>
-      <c r="D28" s="12">
+      <c r="D28" s="15">
         <v>3782</v>
       </c>
-      <c r="E28" s="12">
+      <c r="E28" s="15">
         <v>3877</v>
       </c>
-      <c r="F28" s="12">
+      <c r="F28" s="15">
         <v>3974</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B29" s="12">
+      <c r="A29" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B29" s="15">
         <v>2000</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="15">
         <v>2460</v>
       </c>
-      <c r="D29" s="12">
+      <c r="D29" s="15">
         <v>2522</v>
       </c>
-      <c r="E29" s="12">
+      <c r="E29" s="15">
         <v>2585</v>
       </c>
-      <c r="F29" s="12">
+      <c r="F29" s="15">
         <v>2649</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="B30" s="21">
+      <c r="A30" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="B30" s="24">
         <v>30000</v>
       </c>
-      <c r="C30" s="21">
+      <c r="C30" s="24">
         <v>37050</v>
       </c>
-      <c r="D30" s="21">
+      <c r="D30" s="24">
         <v>38131</v>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="24">
         <v>39244</v>
       </c>
-      <c r="F30" s="21">
+      <c r="F30" s="24">
         <v>40388</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
+      <c r="A31" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B32" s="12">
+      <c r="A32" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B32" s="15">
         <v>2500</v>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="15">
         <v>3075</v>
       </c>
-      <c r="D32" s="12">
+      <c r="D32" s="15">
         <v>3152</v>
       </c>
-      <c r="E32" s="12">
+      <c r="E32" s="15">
         <v>3231</v>
       </c>
-      <c r="F32" s="12">
+      <c r="F32" s="15">
         <v>3311</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="B33" s="21">
+      <c r="A33" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="B33" s="24">
         <v>2500</v>
       </c>
-      <c r="C33" s="21">
+      <c r="C33" s="24">
         <v>3075</v>
       </c>
-      <c r="D33" s="21">
+      <c r="D33" s="24">
         <v>3152</v>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="24">
         <v>3231</v>
       </c>
-      <c r="F33" s="21">
+      <c r="F33" s="24">
         <v>3311</v>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B34" s="19">
+      <c r="A34" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B34" s="22">
         <f>B22+B25+B30+B33</f>
         <v>40500</v>
       </c>
-      <c r="C34" s="19">
+      <c r="C34" s="22">
         <f>C22+C25+C30+C33</f>
         <v>54885</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="22">
         <f>D22+D25+D30+D33</f>
         <v>59774</v>
       </c>
-      <c r="E34" s="19">
+      <c r="E34" s="22">
         <f>E22+E25+E30+E33</f>
         <v>64012</v>
       </c>
-      <c r="F34" s="19">
+      <c r="F34" s="22">
         <f>F22+F25+F30+F33</f>
         <v>65776</v>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
+      <c r="A36" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B37" s="12">
+      <c r="A37" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B37" s="15">
         <v>6960</v>
       </c>
-      <c r="C37" s="12">
+      <c r="C37" s="15">
         <v>6960</v>
       </c>
-      <c r="D37" s="12">
+      <c r="D37" s="15">
         <v>6960</v>
       </c>
-      <c r="E37" s="12">
+      <c r="E37" s="15">
         <v>6960</v>
       </c>
-      <c r="F37" s="12">
+      <c r="F37" s="15">
         <v>6960</v>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B38" s="19">
+      <c r="A38" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B38" s="22">
         <f>SUM(B37:B37)</f>
         <v>6960</v>
       </c>
-      <c r="C38" s="19">
+      <c r="C38" s="22">
         <f>SUM(C37:C37)</f>
         <v>6960</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="22">
         <f>SUM(D37:D37)</f>
         <v>6960</v>
       </c>
-      <c r="E38" s="19">
+      <c r="E38" s="22">
         <f>SUM(E37:E37)</f>
         <v>6960</v>
       </c>
-      <c r="F38" s="19">
+      <c r="F38" s="22">
         <f>SUM(F37:F37)</f>
         <v>6960</v>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
+      <c r="A40" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="B41" s="21">
+      <c r="A41" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="B41" s="24">
         <f>B11</f>
         <v>184667</v>
       </c>
-      <c r="C41" s="21">
+      <c r="C41" s="24">
         <f>C11</f>
         <v>338147</v>
       </c>
-      <c r="D41" s="21">
+      <c r="D41" s="24">
         <f>D11</f>
         <v>422456</v>
       </c>
-      <c r="E41" s="21">
+      <c r="E41" s="24">
         <f>E11</f>
         <v>491331</v>
       </c>
-      <c r="F41" s="21">
+      <c r="F41" s="24">
         <f>F11</f>
         <v>503615</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B42" s="12">
+      <c r="A42" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B42" s="15">
         <f>B17</f>
         <v>118934</v>
       </c>
-      <c r="C42" s="12">
+      <c r="C42" s="15">
         <f>C17</f>
         <v>147003</v>
       </c>
-      <c r="D42" s="12">
+      <c r="D42" s="15">
         <f>D17</f>
         <v>151413</v>
       </c>
-      <c r="E42" s="12">
+      <c r="E42" s="15">
         <f>E17</f>
         <v>155955</v>
       </c>
-      <c r="F42" s="12">
+      <c r="F42" s="15">
         <f>F17</f>
         <v>160634</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B43" s="12">
+      <c r="A43" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B43" s="15">
         <f>B34</f>
         <v>40500</v>
       </c>
-      <c r="C43" s="12">
+      <c r="C43" s="15">
         <f>C34</f>
         <v>54885</v>
       </c>
-      <c r="D43" s="12">
+      <c r="D43" s="15">
         <f>D34</f>
         <v>59774</v>
       </c>
-      <c r="E43" s="12">
+      <c r="E43" s="15">
         <f>E34</f>
         <v>64012</v>
       </c>
-      <c r="F43" s="12">
+      <c r="F43" s="15">
         <f>F34</f>
         <v>65776</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B44" s="12">
+      <c r="A44" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B44" s="15">
         <f>B38</f>
         <v>6960</v>
       </c>
-      <c r="C44" s="12">
+      <c r="C44" s="15">
         <f>C38</f>
         <v>6960</v>
       </c>
-      <c r="D44" s="12">
+      <c r="D44" s="15">
         <f>D38</f>
         <v>6960</v>
       </c>
-      <c r="E44" s="12">
+      <c r="E44" s="15">
         <f>E38</f>
         <v>6960</v>
       </c>
-      <c r="F44" s="12">
+      <c r="F44" s="15">
         <f>F38</f>
         <v>6960</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="B45" s="21">
+      <c r="A45" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="B45" s="24">
         <f>B42+B43+B44</f>
         <v>166394</v>
       </c>
-      <c r="C45" s="21">
+      <c r="C45" s="24">
         <f>C42+C43+C44</f>
         <v>208848</v>
       </c>
-      <c r="D45" s="21">
+      <c r="D45" s="24">
         <f>D42+D43+D44</f>
         <v>218147</v>
       </c>
-      <c r="E45" s="21">
+      <c r="E45" s="24">
         <f>E42+E43+E44</f>
         <v>226927</v>
       </c>
-      <c r="F45" s="21">
+      <c r="F45" s="24">
         <f>F42+F43+F44</f>
         <v>233370</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="B47" s="23">
+      <c r="A47" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="B47" s="26">
         <f>B41-B45</f>
         <v>18273</v>
       </c>
-      <c r="C47" s="23">
+      <c r="C47" s="26">
         <f>C41-C45</f>
         <v>129299</v>
       </c>
-      <c r="D47" s="23">
+      <c r="D47" s="26">
         <f>D41-D45</f>
         <v>204309</v>
       </c>
-      <c r="E47" s="23">
+      <c r="E47" s="26">
         <f>E41-E45</f>
         <v>264404</v>
       </c>
-      <c r="F47" s="23">
+      <c r="F47" s="26">
         <f>F41-F45</f>
         <v>270245</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B48" s="24">
+      <c r="A48" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B48" s="27">
         <f>IF(B41=0,"",B47/B41)</f>
         <v>0.1</v>
       </c>
-      <c r="C48" s="24">
+      <c r="C48" s="27">
         <f>IF(C41=0,"",C47/C41)</f>
         <v>0.38</v>
       </c>
-      <c r="D48" s="24">
+      <c r="D48" s="27">
         <f>IF(D41=0,"",D47/D41)</f>
         <v>0.48</v>
       </c>
-      <c r="E48" s="24">
+      <c r="E48" s="27">
         <f>IF(E41=0,"",E47/E41)</f>
         <v>0.54</v>
       </c>
-      <c r="F48" s="24">
+      <c r="F48" s="27">
         <f>IF(F41=0,"",F47/F41)</f>
         <v>0.54</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B49" s="12">
+      <c r="A49" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B49" s="15">
         <f>B47</f>
         <v>18273</v>
       </c>
-      <c r="C49" s="12">
+      <c r="C49" s="15">
         <f>B49+C47</f>
         <v>147572</v>
       </c>
-      <c r="D49" s="12">
+      <c r="D49" s="15">
         <f>C49+D47</f>
         <v>351881</v>
       </c>
-      <c r="E49" s="12">
+      <c r="E49" s="15">
         <f>D49+E47</f>
         <v>616285</v>
       </c>
-      <c r="F49" s="12">
+      <c r="F49" s="15">
         <f>E49+F47</f>
         <v>886530</v>
       </c>
     </row>
     <row r="51" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
+      <c r="A51" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="B52" s="21">
+      <c r="A52" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="B52" s="24">
         <f>B41-B42-B43</f>
         <v>25233</v>
       </c>
-      <c r="C52" s="21">
+      <c r="C52" s="24">
         <f>C41-C42-C43</f>
         <v>136259</v>
       </c>
-      <c r="D52" s="21">
+      <c r="D52" s="24">
         <f>D41-D42-D43</f>
         <v>211269</v>
       </c>
-      <c r="E52" s="21">
+      <c r="E52" s="24">
         <f>E41-E42-E43</f>
         <v>271364</v>
       </c>
-      <c r="F52" s="21">
+      <c r="F52" s="24">
         <f>F41-F42-F43</f>
         <v>277205</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B53" s="12">
+      <c r="A53" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="B53" s="15">
         <f>B44</f>
         <v>6960</v>
       </c>
-      <c r="C53" s="12">
+      <c r="C53" s="15">
         <f>C44</f>
         <v>6960</v>
       </c>
-      <c r="D53" s="12">
+      <c r="D53" s="15">
         <f>D44</f>
         <v>6960</v>
       </c>
-      <c r="E53" s="12">
+      <c r="E53" s="15">
         <f>E44</f>
         <v>6960</v>
       </c>
-      <c r="F53" s="12">
+      <c r="F53" s="15">
         <f>F44</f>
         <v>6960</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="B54" s="25">
+      <c r="A54" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="B54" s="28">
         <f>IF(B53=0,"N/A",B52/B53)</f>
         <v>3.63</v>
       </c>
-      <c r="C54" s="25">
+      <c r="C54" s="28">
         <f>IF(C53=0,"N/A",C52/C53)</f>
         <v>19.58</v>
       </c>
-      <c r="D54" s="25">
+      <c r="D54" s="28">
         <f>IF(D53=0,"N/A",D52/D53)</f>
         <v>30.35</v>
       </c>
-      <c r="E54" s="25">
+      <c r="E54" s="28">
         <f>IF(E53=0,"N/A",E52/E53)</f>
         <v>38.99</v>
       </c>
-      <c r="F54" s="25">
+      <c r="F54" s="28">
         <f>IF(F53=0,"N/A",F52/F53)</f>
         <v>39.83</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B55" s="12" t="str">
+      <c r="A55" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B55" s="15" t="str">
         <f>Assumptions!B54</f>
         <v>0</v>
       </c>
-      <c r="C55" s="12">
+      <c r="C55" s="15">
         <f>B56</f>
         <v>18273</v>
       </c>
-      <c r="D55" s="12">
+      <c r="D55" s="15">
         <f>C56</f>
         <v>147572</v>
       </c>
-      <c r="E55" s="12">
+      <c r="E55" s="15">
         <f>D56</f>
         <v>351881</v>
       </c>
-      <c r="F55" s="12">
+      <c r="F55" s="15">
         <f>E56</f>
         <v>616285</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="B56" s="21">
+      <c r="A56" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="B56" s="24">
         <f>B55+B47</f>
         <v>18273</v>
       </c>
-      <c r="C56" s="21">
+      <c r="C56" s="24">
         <f>C55+C47</f>
         <v>147572</v>
       </c>
-      <c r="D56" s="21">
+      <c r="D56" s="24">
         <f>D55+D47</f>
         <v>351881</v>
       </c>
-      <c r="E56" s="21">
+      <c r="E56" s="24">
         <f>E55+E47</f>
         <v>616285</v>
       </c>
-      <c r="F56" s="21">
+      <c r="F56" s="24">
         <f>F55+F47</f>
         <v>886530</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B57" s="26">
+      <c r="A57" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B57" s="29">
         <f>IF(B45=0,"",B56/B45*365)</f>
         <v>40</v>
       </c>
-      <c r="C57" s="26">
+      <c r="C57" s="29">
         <f>IF(C45=0,"",C56/C45*365)</f>
         <v>258</v>
       </c>
-      <c r="D57" s="26">
+      <c r="D57" s="29">
         <f>IF(D45=0,"",D56/D45*365)</f>
         <v>589</v>
       </c>
-      <c r="E57" s="26">
+      <c r="E57" s="29">
         <f>IF(E45=0,"",E56/E45*365)</f>
         <v>991</v>
       </c>
-      <c r="F57" s="26">
+      <c r="F57" s="29">
         <f>IF(F45=0,"",F56/F45*365)</f>
         <v>1387</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B58" s="27">
+      <c r="A58" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="B58" s="30">
         <f>IF(B45=0,"",B56/(B45/12))</f>
         <v>1.3</v>
       </c>
-      <c r="C58" s="27">
+      <c r="C58" s="30">
         <f>IF(C45=0,"",C56/(C45/12))</f>
         <v>8.5</v>
       </c>
-      <c r="D58" s="27">
+      <c r="D58" s="30">
         <f>IF(D45=0,"",D56/(D45/12))</f>
         <v>19.4</v>
       </c>
-      <c r="E58" s="27">
+      <c r="E58" s="30">
         <f>IF(E45=0,"",E56/(E45/12))</f>
         <v>32.6</v>
       </c>
-      <c r="F58" s="27">
+      <c r="F58" s="30">
         <f>IF(F45=0,"",F56/(F45/12))</f>
         <v>45.6</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B59" s="24">
+      <c r="A59" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="B59" s="27">
         <f>IF(Assumptions!B12=0,"",B3/Assumptions!B12)</f>
         <v>0.48</v>
       </c>
-      <c r="C59" s="24">
+      <c r="C59" s="27">
         <f>IF(Assumptions!B12=0,"",C3/Assumptions!B12)</f>
         <v>0.72</v>
       </c>
-      <c r="D59" s="24">
+      <c r="D59" s="27">
         <f>IF(Assumptions!B12=0,"",D3/Assumptions!B12)</f>
         <v>0.88</v>
       </c>
-      <c r="E59" s="24">
+      <c r="E59" s="27">
         <f>IF(Assumptions!B12=0,"",E3/Assumptions!B12)</f>
         <v>1</v>
       </c>
-      <c r="F59" s="24">
+      <c r="F59" s="27">
         <f>IF(Assumptions!B12=0,"",F3/Assumptions!B12)</f>
         <v>1</v>
       </c>
     </row>
     <row r="61" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
+      <c r="A61" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B62" s="4" t="str">
+      <c r="A62" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B62" s="7" t="str">
         <f>IF(B53=0,"N/A",IF(B54&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="C62" s="4" t="str">
+      <c r="C62" s="7" t="str">
         <f>IF(C53=0,"N/A",IF(C54&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="D62" s="4" t="str">
+      <c r="D62" s="7" t="str">
         <f>IF(D53=0,"N/A",IF(D54&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E62" s="4" t="str">
+      <c r="E62" s="7" t="str">
         <f>IF(E53=0,"N/A",IF(E54&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F62" s="4" t="str">
+      <c r="F62" s="7" t="str">
         <f>IF(F53=0,"N/A",IF(F54&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B63" s="4" t="str">
+      <c r="A63" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B63" s="7" t="str">
         <f>IF(B47&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="C63" s="4" t="str">
+      <c r="C63" s="7" t="str">
         <f>IF(C47&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="D63" s="4" t="str">
+      <c r="D63" s="7" t="str">
         <f>IF(D47&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E63" s="4" t="str">
+      <c r="E63" s="7" t="str">
         <f>IF(E47&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="F63" s="4" t="str">
+      <c r="F63" s="7" t="str">
         <f>IF(F47&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B64" s="4" t="str">
+      <c r="A64" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B64" s="7" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(B3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C64" s="4" t="str">
+      <c r="C64" s="7" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(C3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="D64" s="4" t="str">
+      <c r="D64" s="7" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(D3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E64" s="4" t="str">
+      <c r="E64" s="7" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(E3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F64" s="4" t="str">
+      <c r="F64" s="7" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(F3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B65" s="4" t="str">
+      <c r="A65" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B65" s="7" t="str">
         <f>IF(B45=0,"N/A",IF(B56/(B45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C65" s="4" t="str">
+      <c r="C65" s="7" t="str">
         <f>IF(C45=0,"N/A",IF(C56/(C45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="D65" s="4" t="str">
+      <c r="D65" s="7" t="str">
         <f>IF(D45=0,"N/A",IF(D56/(D45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E65" s="4" t="str">
+      <c r="E65" s="7" t="str">
         <f>IF(E45=0,"N/A",IF(E56/(E45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F65" s="4" t="str">
+      <c r="F65" s="7" t="str">
         <f>IF(F45=0,"N/A",IF(F56/(F45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="67" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
+      <c r="A67" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B67" s="6"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B68" s="12">
+      <c r="A68" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="B68" s="15">
         <f>IF(B3=0,"",B11/B3)</f>
         <v>15389</v>
       </c>
-      <c r="C68" s="12">
+      <c r="C68" s="15">
         <f>IF(C3=0,"",C11/C3)</f>
         <v>18786</v>
       </c>
-      <c r="D68" s="12">
+      <c r="D68" s="15">
         <f>IF(D3=0,"",D11/D3)</f>
         <v>19203</v>
       </c>
-      <c r="E68" s="12">
+      <c r="E68" s="15">
         <f>IF(E3=0,"",E11/E3)</f>
         <v>19653</v>
       </c>
-      <c r="F68" s="12">
+      <c r="F68" s="15">
         <f>IF(F3=0,"",F11/F3)</f>
         <v>20145</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B69" s="12">
+      <c r="A69" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B69" s="15">
         <f>IF(B3=0,"",B45/B3)</f>
         <v>13866</v>
       </c>
-      <c r="C69" s="12">
+      <c r="C69" s="15">
         <f>IF(C3=0,"",C45/C3)</f>
         <v>11603</v>
       </c>
-      <c r="D69" s="12">
+      <c r="D69" s="15">
         <f>IF(D3=0,"",D45/D3)</f>
         <v>9916</v>
       </c>
-      <c r="E69" s="12">
+      <c r="E69" s="15">
         <f>IF(E3=0,"",E45/E3)</f>
         <v>9077</v>
       </c>
-      <c r="F69" s="12">
+      <c r="F69" s="15">
         <f>IF(F3=0,"",F45/F3)</f>
         <v>9335</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B70" s="12">
+      <c r="A70" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B70" s="15">
         <f>B42+B44</f>
         <v>125894</v>
       </c>
-      <c r="C70" s="12">
+      <c r="C70" s="15">
         <f>C42+C44</f>
         <v>153963</v>
       </c>
-      <c r="D70" s="12">
+      <c r="D70" s="15">
         <f>D42+D44</f>
         <v>158373</v>
       </c>
-      <c r="E70" s="12">
+      <c r="E70" s="15">
         <f>E42+E44</f>
         <v>162915</v>
       </c>
-      <c r="F70" s="12">
+      <c r="F70" s="15">
         <f>F42+F44</f>
         <v>167594</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="B71" s="12">
+      <c r="A71" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B71" s="15">
         <f>IF(B3=0,"",B43/B3)</f>
         <v>3375</v>
       </c>
-      <c r="C71" s="12">
+      <c r="C71" s="15">
         <f>IF(C3=0,"",C43/C3)</f>
         <v>3049</v>
       </c>
-      <c r="D71" s="12">
+      <c r="D71" s="15">
         <f>IF(D3=0,"",D43/D3)</f>
         <v>2717</v>
       </c>
-      <c r="E71" s="12">
+      <c r="E71" s="15">
         <f>IF(E3=0,"",E43/E3)</f>
         <v>2560</v>
       </c>
-      <c r="F71" s="12">
+      <c r="F71" s="15">
         <f>IF(F3=0,"",F43/F3)</f>
         <v>2631</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="B72" s="12">
+      <c r="A72" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B72" s="15">
         <f>IF(B3=0,"",B68-B71)</f>
         <v>12014</v>
       </c>
-      <c r="C72" s="12">
+      <c r="C72" s="15">
         <f>IF(C3=0,"",C68-C71)</f>
         <v>15737</v>
       </c>
-      <c r="D72" s="12">
+      <c r="D72" s="15">
         <f>IF(D3=0,"",D68-D71)</f>
         <v>16486</v>
       </c>
-      <c r="E72" s="12">
+      <c r="E72" s="15">
         <f>IF(E3=0,"",E68-E71)</f>
         <v>17093</v>
       </c>
-      <c r="F72" s="12">
+      <c r="F72" s="15">
         <f>IF(F3=0,"",F68-F71)</f>
         <v>17514</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="28" t="s">
-        <v>150</v>
-      </c>
-      <c r="B73" s="29">
+      <c r="A73" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="B73" s="32">
         <f>IF(B72&lt;=0,"N/A",ROUNDUP(B70/B72,0))</f>
         <v>11</v>
       </c>
-      <c r="C73" s="29">
+      <c r="C73" s="32">
         <f>IF(C72&lt;=0,"N/A",ROUNDUP(C70/C72,0))</f>
         <v>10</v>
       </c>
-      <c r="D73" s="29">
+      <c r="D73" s="32">
         <f>IF(D72&lt;=0,"N/A",ROUNDUP(D70/D72,0))</f>
         <v>10</v>
       </c>
-      <c r="E73" s="29">
+      <c r="E73" s="32">
         <f>IF(E72&lt;=0,"N/A",ROUNDUP(E70/E72,0))</f>
         <v>10</v>
       </c>
-      <c r="F73" s="29">
+      <c r="F73" s="32">
         <f>IF(F72&lt;=0,"N/A",ROUNDUP(F70/F72,0))</f>
         <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="B75" s="15"/>
-      <c r="C75" s="15"/>
-      <c r="D75" s="15"/>
-      <c r="E75" s="15"/>
-      <c r="F75" s="15"/>
+      <c r="A75" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="B75" s="18"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="18"/>
+      <c r="E75" s="18"/>
+      <c r="F75" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3169,7 +3581,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3183,1478 +3595,1478 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="A1" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="I2" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="J2" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="K2" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="L2" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="M2" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="N2" s="16" t="s">
-        <v>163</v>
+      <c r="A2" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
+      <c r="A3" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="12">
+      <c r="A4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="15">
         <v>14400</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="15">
         <v>14400</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="15">
         <v>14400</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="15">
         <v>14400</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="15">
         <v>14400</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="15">
         <v>14400</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="15">
         <v>14400</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="15">
         <v>14400</v>
       </c>
-      <c r="J4" s="12">
+      <c r="J4" s="15">
         <v>14400</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="15">
         <v>14400</v>
       </c>
-      <c r="L4" s="12">
-        <v>0</v>
-      </c>
-      <c r="M4" s="12">
-        <v>0</v>
-      </c>
-      <c r="N4" s="12">
+      <c r="L4" s="15">
+        <v>0</v>
+      </c>
+      <c r="M4" s="15">
+        <v>0</v>
+      </c>
+      <c r="N4" s="15">
         <f>SUM(B4:M4)</f>
         <v>120000</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="12">
+      <c r="A5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="15">
         <v>300</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="15">
         <v>300</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="15">
         <v>300</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="15">
         <v>300</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="15">
         <v>300</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="15">
         <v>300</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="15">
         <v>300</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="15">
         <v>300</v>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="15">
         <v>300</v>
       </c>
-      <c r="K5" s="12">
+      <c r="K5" s="15">
         <v>300</v>
       </c>
-      <c r="L5" s="12">
-        <v>0</v>
-      </c>
-      <c r="M5" s="12">
-        <v>0</v>
-      </c>
-      <c r="N5" s="12">
+      <c r="L5" s="15">
+        <v>0</v>
+      </c>
+      <c r="M5" s="15">
+        <v>0</v>
+      </c>
+      <c r="N5" s="15">
         <f>SUM(B5:M5)</f>
         <v>2500</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="12">
+      <c r="A6" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="15">
         <v>8400</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="15">
         <v>8400</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="15">
         <v>8400</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="15">
         <v>8400</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="15">
         <v>8400</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="15">
         <v>8400</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="15">
         <v>8400</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="15">
         <v>8400</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="15">
         <v>8400</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="15">
         <v>8400</v>
       </c>
-      <c r="L6" s="12">
-        <v>0</v>
-      </c>
-      <c r="M6" s="12">
-        <v>0</v>
-      </c>
-      <c r="N6" s="12">
+      <c r="L6" s="15">
+        <v>0</v>
+      </c>
+      <c r="M6" s="15">
+        <v>0</v>
+      </c>
+      <c r="N6" s="15">
         <f>SUM(B6:M6)</f>
         <v>70000</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="12">
+      <c r="A7" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="15">
         <v>500</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="15">
         <v>500</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="15">
         <v>500</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="15">
         <v>500</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="15">
         <v>500</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="15">
         <v>500</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="15">
         <v>500</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="15">
         <v>500</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="15">
         <v>500</v>
       </c>
-      <c r="K7" s="12">
+      <c r="K7" s="15">
         <v>500</v>
       </c>
-      <c r="L7" s="12">
-        <v>0</v>
-      </c>
-      <c r="M7" s="12">
-        <v>0</v>
-      </c>
-      <c r="N7" s="12">
+      <c r="L7" s="15">
+        <v>0</v>
+      </c>
+      <c r="M7" s="15">
+        <v>0</v>
+      </c>
+      <c r="N7" s="15">
         <f>SUM(B7:M7)</f>
         <v>4167</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="12">
-        <v>0</v>
-      </c>
-      <c r="C8" s="12">
-        <v>0</v>
-      </c>
-      <c r="D8" s="12">
-        <v>0</v>
-      </c>
-      <c r="E8" s="12">
-        <v>0</v>
-      </c>
-      <c r="F8" s="12">
-        <v>0</v>
-      </c>
-      <c r="G8" s="12">
-        <v>0</v>
-      </c>
-      <c r="H8" s="12">
-        <v>0</v>
-      </c>
-      <c r="I8" s="12">
-        <v>0</v>
-      </c>
-      <c r="J8" s="12">
-        <v>0</v>
-      </c>
-      <c r="K8" s="12">
-        <v>0</v>
-      </c>
-      <c r="L8" s="12">
-        <v>0</v>
-      </c>
-      <c r="M8" s="12">
-        <v>0</v>
-      </c>
-      <c r="N8" s="12" t="str">
+      <c r="A8" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="15">
+        <v>0</v>
+      </c>
+      <c r="C8" s="15">
+        <v>0</v>
+      </c>
+      <c r="D8" s="15">
+        <v>0</v>
+      </c>
+      <c r="E8" s="15">
+        <v>0</v>
+      </c>
+      <c r="F8" s="15">
+        <v>0</v>
+      </c>
+      <c r="G8" s="15">
+        <v>0</v>
+      </c>
+      <c r="H8" s="15">
+        <v>0</v>
+      </c>
+      <c r="I8" s="15">
+        <v>0</v>
+      </c>
+      <c r="J8" s="15">
+        <v>0</v>
+      </c>
+      <c r="K8" s="15">
+        <v>0</v>
+      </c>
+      <c r="L8" s="15">
+        <v>0</v>
+      </c>
+      <c r="M8" s="15">
+        <v>0</v>
+      </c>
+      <c r="N8" s="15" t="str">
         <f>SUM(B8:M8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B9" s="19">
+      <c r="A9" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B9" s="22">
         <f>SUM(B4:B8)</f>
         <v>155900</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="22">
         <f>SUM(C4:C8)</f>
         <v>7460</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="22">
         <f>SUM(D4:D8)</f>
         <v>7460</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="22">
         <f>SUM(E4:E8)</f>
         <v>7460</v>
       </c>
-      <c r="F9" s="19">
+      <c r="F9" s="22">
         <f>SUM(F4:F8)</f>
         <v>7460</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="22">
         <f>SUM(G4:G8)</f>
         <v>7460</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="22">
         <f>SUM(H4:H8)</f>
         <v>7460</v>
       </c>
-      <c r="I9" s="19">
+      <c r="I9" s="22">
         <f>SUM(I4:I8)</f>
         <v>7460</v>
       </c>
-      <c r="J9" s="19">
+      <c r="J9" s="22">
         <f>SUM(J4:J8)</f>
         <v>7460</v>
       </c>
-      <c r="K9" s="19">
+      <c r="K9" s="22">
         <f>SUM(K4:K8)</f>
         <v>7460</v>
       </c>
-      <c r="L9" s="19">
+      <c r="L9" s="22">
         <f>SUM(L4:L8)</f>
         <v>-1440</v>
       </c>
-      <c r="M9" s="19" t="str">
+      <c r="M9" s="22" t="str">
         <f>SUM(M4:M8)</f>
         <v>0</v>
       </c>
-      <c r="N9" s="19">
+      <c r="N9" s="22">
         <f>SUM(B9:M9)</f>
         <v>221600</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
+      <c r="A11" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="12">
+      <c r="A12" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="15">
         <v>5851</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="15">
         <v>5851</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="15">
         <v>5851</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="15">
         <v>5851</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="15">
         <v>5851</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="15">
         <v>5851</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="15">
         <v>5851</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="15">
         <v>5851</v>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="15">
         <v>5851</v>
       </c>
-      <c r="K12" s="12">
+      <c r="K12" s="15">
         <v>5851</v>
       </c>
-      <c r="L12" s="12">
-        <v>0</v>
-      </c>
-      <c r="M12" s="12">
-        <v>0</v>
-      </c>
-      <c r="N12" s="12">
+      <c r="L12" s="15">
+        <v>0</v>
+      </c>
+      <c r="M12" s="15">
+        <v>0</v>
+      </c>
+      <c r="N12" s="15">
         <f>SUM(B12:M12)</f>
         <v>58506</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B13" s="12">
+      <c r="A13" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="15">
         <v>4787</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="15">
         <v>4787</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="15">
         <v>4787</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="15">
         <v>4787</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="15">
         <v>4787</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="15">
         <v>4787</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="15">
         <v>4787</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="15">
         <v>4787</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="15">
         <v>4787</v>
       </c>
-      <c r="K13" s="12">
+      <c r="K13" s="15">
         <v>4787</v>
       </c>
-      <c r="L13" s="12">
-        <v>0</v>
-      </c>
-      <c r="M13" s="12">
-        <v>0</v>
-      </c>
-      <c r="N13" s="12">
+      <c r="L13" s="15">
+        <v>0</v>
+      </c>
+      <c r="M13" s="15">
+        <v>0</v>
+      </c>
+      <c r="N13" s="15">
         <f>SUM(B13:M13)</f>
         <v>47869</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B14" s="12">
+      <c r="A14" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="15">
         <v>1256</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="15">
         <v>1256</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="15">
         <v>1256</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="15">
         <v>1256</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="15">
         <v>1256</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="15">
         <v>1256</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="15">
         <v>1256</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="15">
         <v>1256</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="15">
         <v>1256</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="15">
         <v>1256</v>
       </c>
-      <c r="L14" s="12">
-        <v>0</v>
-      </c>
-      <c r="M14" s="12">
-        <v>0</v>
-      </c>
-      <c r="N14" s="12">
+      <c r="L14" s="15">
+        <v>0</v>
+      </c>
+      <c r="M14" s="15">
+        <v>0</v>
+      </c>
+      <c r="N14" s="15">
         <f>SUM(B14:M14)</f>
         <v>12559</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B15" s="19">
+      <c r="A15" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B15" s="22">
         <f>SUM(B12:B14)</f>
         <v>11893</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="22">
         <f>SUM(C12:C14)</f>
         <v>11893</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="22">
         <f>SUM(D12:D14)</f>
         <v>11893</v>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="22">
         <f>SUM(E12:E14)</f>
         <v>11893</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="22">
         <f>SUM(F12:F14)</f>
         <v>11893</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="22">
         <f>SUM(G12:G14)</f>
         <v>11893</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="22">
         <f>SUM(H12:H14)</f>
         <v>11893</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="22">
         <f>SUM(I12:I14)</f>
         <v>11893</v>
       </c>
-      <c r="J15" s="19">
+      <c r="J15" s="22">
         <f>SUM(J12:J14)</f>
         <v>11893</v>
       </c>
-      <c r="K15" s="19">
+      <c r="K15" s="22">
         <f>SUM(K12:K14)</f>
         <v>11893</v>
       </c>
-      <c r="L15" s="19" t="str">
+      <c r="L15" s="22" t="str">
         <f>SUM(L12:L14)</f>
         <v>0</v>
       </c>
-      <c r="M15" s="19" t="str">
+      <c r="M15" s="22" t="str">
         <f>SUM(M12:M14)</f>
         <v>0</v>
       </c>
-      <c r="N15" s="19">
+      <c r="N15" s="22">
         <f>SUM(B15:M15)</f>
         <v>118934</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
+      <c r="A17" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
+      <c r="A18" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="B19" s="12">
+      <c r="A19" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="B19" s="15">
         <v>500</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="15">
         <v>500</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="15">
         <v>500</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="15">
         <v>500</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="15">
         <v>500</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="15">
         <v>500</v>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="15">
         <v>500</v>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="15">
         <v>500</v>
       </c>
-      <c r="J19" s="12">
+      <c r="J19" s="15">
         <v>500</v>
       </c>
-      <c r="K19" s="12">
+      <c r="K19" s="15">
         <v>500</v>
       </c>
-      <c r="L19" s="12">
-        <v>0</v>
-      </c>
-      <c r="M19" s="12">
-        <v>0</v>
-      </c>
-      <c r="N19" s="12">
+      <c r="L19" s="15">
+        <v>0</v>
+      </c>
+      <c r="M19" s="15">
+        <v>0</v>
+      </c>
+      <c r="N19" s="15">
         <f>SUM(B19:M19)</f>
         <v>5000</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="B20" s="21">
+      <c r="A20" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="B20" s="24">
         <v>500</v>
       </c>
-      <c r="C20" s="21">
+      <c r="C20" s="24">
         <v>500</v>
       </c>
-      <c r="D20" s="21">
+      <c r="D20" s="24">
         <v>500</v>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="24">
         <v>500</v>
       </c>
-      <c r="F20" s="21">
+      <c r="F20" s="24">
         <v>500</v>
       </c>
-      <c r="G20" s="21">
+      <c r="G20" s="24">
         <v>500</v>
       </c>
-      <c r="H20" s="21">
+      <c r="H20" s="24">
         <v>500</v>
       </c>
-      <c r="I20" s="21">
+      <c r="I20" s="24">
         <v>500</v>
       </c>
-      <c r="J20" s="21">
+      <c r="J20" s="24">
         <v>500</v>
       </c>
-      <c r="K20" s="21">
+      <c r="K20" s="24">
         <v>500</v>
       </c>
-      <c r="L20" s="21">
-        <v>0</v>
-      </c>
-      <c r="M20" s="21">
-        <v>0</v>
-      </c>
-      <c r="N20" s="21">
+      <c r="L20" s="24">
+        <v>0</v>
+      </c>
+      <c r="M20" s="24">
+        <v>0</v>
+      </c>
+      <c r="N20" s="24">
         <f>SUM(B20:M20)</f>
         <v>5000</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
+      <c r="A21" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="B22" s="12">
+      <c r="A22" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B22" s="15">
         <v>300</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="15">
         <v>300</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="15">
         <v>300</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="15">
         <v>300</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="15">
         <v>300</v>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="15">
         <v>300</v>
       </c>
-      <c r="H22" s="12">
+      <c r="H22" s="15">
         <v>300</v>
       </c>
-      <c r="I22" s="12">
+      <c r="I22" s="15">
         <v>300</v>
       </c>
-      <c r="J22" s="12">
+      <c r="J22" s="15">
         <v>300</v>
       </c>
-      <c r="K22" s="12">
+      <c r="K22" s="15">
         <v>300</v>
       </c>
-      <c r="L22" s="12">
-        <v>0</v>
-      </c>
-      <c r="M22" s="12">
-        <v>0</v>
-      </c>
-      <c r="N22" s="12">
+      <c r="L22" s="15">
+        <v>0</v>
+      </c>
+      <c r="M22" s="15">
+        <v>0</v>
+      </c>
+      <c r="N22" s="15">
         <f>SUM(B22:M22)</f>
         <v>3000</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="B23" s="21">
+      <c r="A23" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="B23" s="24">
         <v>300</v>
       </c>
-      <c r="C23" s="21">
+      <c r="C23" s="24">
         <v>300</v>
       </c>
-      <c r="D23" s="21">
+      <c r="D23" s="24">
         <v>300</v>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="24">
         <v>300</v>
       </c>
-      <c r="F23" s="21">
+      <c r="F23" s="24">
         <v>300</v>
       </c>
-      <c r="G23" s="21">
+      <c r="G23" s="24">
         <v>300</v>
       </c>
-      <c r="H23" s="21">
+      <c r="H23" s="24">
         <v>300</v>
       </c>
-      <c r="I23" s="21">
+      <c r="I23" s="24">
         <v>300</v>
       </c>
-      <c r="J23" s="21">
+      <c r="J23" s="24">
         <v>300</v>
       </c>
-      <c r="K23" s="21">
+      <c r="K23" s="24">
         <v>300</v>
       </c>
-      <c r="L23" s="21">
-        <v>0</v>
-      </c>
-      <c r="M23" s="21">
-        <v>0</v>
-      </c>
-      <c r="N23" s="21">
+      <c r="L23" s="24">
+        <v>0</v>
+      </c>
+      <c r="M23" s="24">
+        <v>0</v>
+      </c>
+      <c r="N23" s="24">
         <f>SUM(B23:M23)</f>
         <v>3000</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4"/>
+      <c r="A24" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="B25" s="12">
+      <c r="A25" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="B25" s="15">
         <v>2500</v>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="15">
         <v>2500</v>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" s="15">
         <v>2500</v>
       </c>
-      <c r="E25" s="12">
+      <c r="E25" s="15">
         <v>2500</v>
       </c>
-      <c r="F25" s="12">
+      <c r="F25" s="15">
         <v>2500</v>
       </c>
-      <c r="G25" s="12">
+      <c r="G25" s="15">
         <v>2500</v>
       </c>
-      <c r="H25" s="12">
+      <c r="H25" s="15">
         <v>2500</v>
       </c>
-      <c r="I25" s="12">
+      <c r="I25" s="15">
         <v>2500</v>
       </c>
-      <c r="J25" s="12">
+      <c r="J25" s="15">
         <v>2500</v>
       </c>
-      <c r="K25" s="12">
+      <c r="K25" s="15">
         <v>2500</v>
       </c>
-      <c r="L25" s="12">
-        <v>0</v>
-      </c>
-      <c r="M25" s="12">
-        <v>0</v>
-      </c>
-      <c r="N25" s="12">
+      <c r="L25" s="15">
+        <v>0</v>
+      </c>
+      <c r="M25" s="15">
+        <v>0</v>
+      </c>
+      <c r="N25" s="15">
         <f>SUM(B25:M25)</f>
         <v>25000</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B26" s="12">
+      <c r="A26" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B26" s="15">
         <v>300</v>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="15">
         <v>300</v>
       </c>
-      <c r="D26" s="12">
+      <c r="D26" s="15">
         <v>300</v>
       </c>
-      <c r="E26" s="12">
+      <c r="E26" s="15">
         <v>300</v>
       </c>
-      <c r="F26" s="12">
+      <c r="F26" s="15">
         <v>300</v>
       </c>
-      <c r="G26" s="12">
+      <c r="G26" s="15">
         <v>300</v>
       </c>
-      <c r="H26" s="12">
+      <c r="H26" s="15">
         <v>300</v>
       </c>
-      <c r="I26" s="12">
+      <c r="I26" s="15">
         <v>300</v>
       </c>
-      <c r="J26" s="12">
+      <c r="J26" s="15">
         <v>300</v>
       </c>
-      <c r="K26" s="12">
+      <c r="K26" s="15">
         <v>300</v>
       </c>
-      <c r="L26" s="12">
-        <v>0</v>
-      </c>
-      <c r="M26" s="12">
-        <v>0</v>
-      </c>
-      <c r="N26" s="12">
+      <c r="L26" s="15">
+        <v>0</v>
+      </c>
+      <c r="M26" s="15">
+        <v>0</v>
+      </c>
+      <c r="N26" s="15">
         <f>SUM(B26:M26)</f>
         <v>3000</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B27" s="12">
+      <c r="A27" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="B27" s="15">
         <v>200</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="15">
         <v>200</v>
       </c>
-      <c r="D27" s="12">
+      <c r="D27" s="15">
         <v>200</v>
       </c>
-      <c r="E27" s="12">
+      <c r="E27" s="15">
         <v>200</v>
       </c>
-      <c r="F27" s="12">
+      <c r="F27" s="15">
         <v>200</v>
       </c>
-      <c r="G27" s="12">
+      <c r="G27" s="15">
         <v>200</v>
       </c>
-      <c r="H27" s="12">
+      <c r="H27" s="15">
         <v>200</v>
       </c>
-      <c r="I27" s="12">
+      <c r="I27" s="15">
         <v>200</v>
       </c>
-      <c r="J27" s="12">
+      <c r="J27" s="15">
         <v>200</v>
       </c>
-      <c r="K27" s="12">
+      <c r="K27" s="15">
         <v>200</v>
       </c>
-      <c r="L27" s="12">
-        <v>0</v>
-      </c>
-      <c r="M27" s="12">
-        <v>0</v>
-      </c>
-      <c r="N27" s="12">
+      <c r="L27" s="15">
+        <v>0</v>
+      </c>
+      <c r="M27" s="15">
+        <v>0</v>
+      </c>
+      <c r="N27" s="15">
         <f>SUM(B27:M27)</f>
         <v>2000</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="B28" s="21">
+      <c r="A28" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="B28" s="24">
         <v>3000</v>
       </c>
-      <c r="C28" s="21">
+      <c r="C28" s="24">
         <v>3000</v>
       </c>
-      <c r="D28" s="21">
+      <c r="D28" s="24">
         <v>3000</v>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="24">
         <v>3000</v>
       </c>
-      <c r="F28" s="21">
+      <c r="F28" s="24">
         <v>3000</v>
       </c>
-      <c r="G28" s="21">
+      <c r="G28" s="24">
         <v>3000</v>
       </c>
-      <c r="H28" s="21">
+      <c r="H28" s="24">
         <v>3000</v>
       </c>
-      <c r="I28" s="21">
+      <c r="I28" s="24">
         <v>3000</v>
       </c>
-      <c r="J28" s="21">
+      <c r="J28" s="24">
         <v>3000</v>
       </c>
-      <c r="K28" s="21">
+      <c r="K28" s="24">
         <v>3000</v>
       </c>
-      <c r="L28" s="21">
-        <v>0</v>
-      </c>
-      <c r="M28" s="21">
-        <v>0</v>
-      </c>
-      <c r="N28" s="21">
+      <c r="L28" s="24">
+        <v>0</v>
+      </c>
+      <c r="M28" s="24">
+        <v>0</v>
+      </c>
+      <c r="N28" s="24">
         <f>SUM(B28:M28)</f>
         <v>30000</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
+      <c r="A29" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B30" s="12">
+      <c r="A30" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="B30" s="15">
         <v>250</v>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="15">
         <v>250</v>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="15">
         <v>250</v>
       </c>
-      <c r="E30" s="12">
+      <c r="E30" s="15">
         <v>250</v>
       </c>
-      <c r="F30" s="12">
+      <c r="F30" s="15">
         <v>250</v>
       </c>
-      <c r="G30" s="12">
+      <c r="G30" s="15">
         <v>250</v>
       </c>
-      <c r="H30" s="12">
+      <c r="H30" s="15">
         <v>250</v>
       </c>
-      <c r="I30" s="12">
+      <c r="I30" s="15">
         <v>250</v>
       </c>
-      <c r="J30" s="12">
+      <c r="J30" s="15">
         <v>250</v>
       </c>
-      <c r="K30" s="12">
+      <c r="K30" s="15">
         <v>250</v>
       </c>
-      <c r="L30" s="12">
-        <v>0</v>
-      </c>
-      <c r="M30" s="12">
-        <v>0</v>
-      </c>
-      <c r="N30" s="12">
+      <c r="L30" s="15">
+        <v>0</v>
+      </c>
+      <c r="M30" s="15">
+        <v>0</v>
+      </c>
+      <c r="N30" s="15">
         <f>SUM(B30:M30)</f>
         <v>2500</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="B31" s="21">
+      <c r="A31" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="B31" s="24">
         <v>250</v>
       </c>
-      <c r="C31" s="21">
+      <c r="C31" s="24">
         <v>250</v>
       </c>
-      <c r="D31" s="21">
+      <c r="D31" s="24">
         <v>250</v>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="24">
         <v>250</v>
       </c>
-      <c r="F31" s="21">
+      <c r="F31" s="24">
         <v>250</v>
       </c>
-      <c r="G31" s="21">
+      <c r="G31" s="24">
         <v>250</v>
       </c>
-      <c r="H31" s="21">
+      <c r="H31" s="24">
         <v>250</v>
       </c>
-      <c r="I31" s="21">
+      <c r="I31" s="24">
         <v>250</v>
       </c>
-      <c r="J31" s="21">
+      <c r="J31" s="24">
         <v>250</v>
       </c>
-      <c r="K31" s="21">
+      <c r="K31" s="24">
         <v>250</v>
       </c>
-      <c r="L31" s="21">
-        <v>0</v>
-      </c>
-      <c r="M31" s="21">
-        <v>0</v>
-      </c>
-      <c r="N31" s="21">
+      <c r="L31" s="24">
+        <v>0</v>
+      </c>
+      <c r="M31" s="24">
+        <v>0</v>
+      </c>
+      <c r="N31" s="24">
         <f>SUM(B31:M31)</f>
         <v>2500</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B32" s="19">
+      <c r="A32" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B32" s="22">
         <f>B20+B23+B28+B31</f>
         <v>4050</v>
       </c>
-      <c r="C32" s="19">
+      <c r="C32" s="22">
         <f>C20+C23+C28+C31</f>
         <v>4050</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="22">
         <f>D20+D23+D28+D31</f>
         <v>4050</v>
       </c>
-      <c r="E32" s="19">
+      <c r="E32" s="22">
         <f>E20+E23+E28+E31</f>
         <v>4050</v>
       </c>
-      <c r="F32" s="19">
+      <c r="F32" s="22">
         <f>F20+F23+F28+F31</f>
         <v>4050</v>
       </c>
-      <c r="G32" s="19">
+      <c r="G32" s="22">
         <f>G20+G23+G28+G31</f>
         <v>4050</v>
       </c>
-      <c r="H32" s="19">
+      <c r="H32" s="22">
         <f>H20+H23+H28+H31</f>
         <v>4050</v>
       </c>
-      <c r="I32" s="19">
+      <c r="I32" s="22">
         <f>I20+I23+I28+I31</f>
         <v>4050</v>
       </c>
-      <c r="J32" s="19">
+      <c r="J32" s="22">
         <f>J20+J23+J28+J31</f>
         <v>4050</v>
       </c>
-      <c r="K32" s="19">
+      <c r="K32" s="22">
         <f>K20+K23+K28+K31</f>
         <v>4050</v>
       </c>
-      <c r="L32" s="19" t="str">
+      <c r="L32" s="22" t="str">
         <f>L20+L23+L28+L31</f>
         <v>0</v>
       </c>
-      <c r="M32" s="19" t="str">
+      <c r="M32" s="22" t="str">
         <f>M20+M23+M28+M31</f>
         <v>0</v>
       </c>
-      <c r="N32" s="19">
+      <c r="N32" s="22">
         <f>SUM(B32:M32)</f>
         <v>40500</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="B34" s="12">
+      <c r="A34" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="B34" s="15">
         <v>580</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="15">
         <v>580</v>
       </c>
-      <c r="D34" s="12">
+      <c r="D34" s="15">
         <v>580</v>
       </c>
-      <c r="E34" s="12">
+      <c r="E34" s="15">
         <v>580</v>
       </c>
-      <c r="F34" s="12">
+      <c r="F34" s="15">
         <v>580</v>
       </c>
-      <c r="G34" s="12">
+      <c r="G34" s="15">
         <v>580</v>
       </c>
-      <c r="H34" s="12">
+      <c r="H34" s="15">
         <v>580</v>
       </c>
-      <c r="I34" s="12">
+      <c r="I34" s="15">
         <v>580</v>
       </c>
-      <c r="J34" s="12">
+      <c r="J34" s="15">
         <v>580</v>
       </c>
-      <c r="K34" s="12">
+      <c r="K34" s="15">
         <v>580</v>
       </c>
-      <c r="L34" s="12">
+      <c r="L34" s="15">
         <v>580</v>
       </c>
-      <c r="M34" s="12">
+      <c r="M34" s="15">
         <v>580</v>
       </c>
-      <c r="N34" s="12">
+      <c r="N34" s="15">
         <f>SUM(B34:M34)</f>
         <v>6960</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="3"/>
+      <c r="A36" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="B37" s="21">
+      <c r="A37" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="B37" s="24">
         <f>B15+B32+B34</f>
         <v>16523</v>
       </c>
-      <c r="C37" s="21">
+      <c r="C37" s="24">
         <f>C15+C32+C34</f>
         <v>16523</v>
       </c>
-      <c r="D37" s="21">
+      <c r="D37" s="24">
         <f>D15+D32+D34</f>
         <v>16523</v>
       </c>
-      <c r="E37" s="21">
+      <c r="E37" s="24">
         <f>E15+E32+E34</f>
         <v>16523</v>
       </c>
-      <c r="F37" s="21">
+      <c r="F37" s="24">
         <f>F15+F32+F34</f>
         <v>16523</v>
       </c>
-      <c r="G37" s="21">
+      <c r="G37" s="24">
         <f>G15+G32+G34</f>
         <v>16523</v>
       </c>
-      <c r="H37" s="21">
+      <c r="H37" s="24">
         <f>H15+H32+H34</f>
         <v>16523</v>
       </c>
-      <c r="I37" s="21">
+      <c r="I37" s="24">
         <f>I15+I32+I34</f>
         <v>16523</v>
       </c>
-      <c r="J37" s="21">
+      <c r="J37" s="24">
         <f>J15+J32+J34</f>
         <v>16523</v>
       </c>
-      <c r="K37" s="21">
+      <c r="K37" s="24">
         <f>K15+K32+K34</f>
         <v>16523</v>
       </c>
-      <c r="L37" s="21">
+      <c r="L37" s="24">
         <f>L15+L32+L34</f>
         <v>580</v>
       </c>
-      <c r="M37" s="21">
+      <c r="M37" s="24">
         <f>M15+M32+M34</f>
         <v>580</v>
       </c>
-      <c r="N37" s="21">
+      <c r="N37" s="24">
         <f>SUM(B37:M37)</f>
         <v>166390</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="B38" s="21">
+      <c r="A38" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="B38" s="24">
         <f>B9-B37</f>
         <v>139377</v>
       </c>
-      <c r="C38" s="21">
+      <c r="C38" s="24">
         <f>C9-C37</f>
         <v>-9063</v>
       </c>
-      <c r="D38" s="21">
+      <c r="D38" s="24">
         <f>D9-D37</f>
         <v>-9063</v>
       </c>
-      <c r="E38" s="21">
+      <c r="E38" s="24">
         <f>E9-E37</f>
         <v>-9063</v>
       </c>
-      <c r="F38" s="21">
+      <c r="F38" s="24">
         <f>F9-F37</f>
         <v>-9063</v>
       </c>
-      <c r="G38" s="21">
+      <c r="G38" s="24">
         <f>G9-G37</f>
         <v>-9063</v>
       </c>
-      <c r="H38" s="21">
+      <c r="H38" s="24">
         <f>H9-H37</f>
         <v>-9063</v>
       </c>
-      <c r="I38" s="21">
+      <c r="I38" s="24">
         <f>I9-I37</f>
         <v>-9063</v>
       </c>
-      <c r="J38" s="21">
+      <c r="J38" s="24">
         <f>J9-J37</f>
         <v>-9063</v>
       </c>
-      <c r="K38" s="21">
+      <c r="K38" s="24">
         <f>K9-K37</f>
         <v>-9063</v>
       </c>
-      <c r="L38" s="21">
+      <c r="L38" s="24">
         <f>L9-L37</f>
         <v>-2020</v>
       </c>
-      <c r="M38" s="21">
+      <c r="M38" s="24">
         <f>M9-M37</f>
         <v>-580</v>
       </c>
-      <c r="N38" s="21">
+      <c r="N38" s="24">
         <f>SUM(B38:M38)</f>
         <v>55210</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="B39" s="21">
+      <c r="A39" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="B39" s="24">
         <f>0+B38</f>
         <v>139377</v>
       </c>
-      <c r="C39" s="21">
+      <c r="C39" s="24">
         <f>B39+C38</f>
         <v>130314</v>
       </c>
-      <c r="D39" s="21">
+      <c r="D39" s="24">
         <f>C39+D38</f>
         <v>121251</v>
       </c>
-      <c r="E39" s="21">
+      <c r="E39" s="24">
         <f>D39+E38</f>
         <v>112188</v>
       </c>
-      <c r="F39" s="21">
+      <c r="F39" s="24">
         <f>E39+F38</f>
         <v>103125</v>
       </c>
-      <c r="G39" s="21">
+      <c r="G39" s="24">
         <f>F39+G38</f>
         <v>94062</v>
       </c>
-      <c r="H39" s="21">
+      <c r="H39" s="24">
         <f>G39+H38</f>
         <v>84999</v>
       </c>
-      <c r="I39" s="21">
+      <c r="I39" s="24">
         <f>H39+I38</f>
         <v>75936</v>
       </c>
-      <c r="J39" s="21">
+      <c r="J39" s="24">
         <f>I39+J38</f>
         <v>66873</v>
       </c>
-      <c r="K39" s="21">
+      <c r="K39" s="24">
         <f>J39+K38</f>
         <v>57810</v>
       </c>
-      <c r="L39" s="21">
+      <c r="L39" s="24">
         <f>K39+L38</f>
         <v>55790</v>
       </c>
-      <c r="M39" s="21">
+      <c r="M39" s="24">
         <f>L39+M38</f>
         <v>55210</v>
       </c>
-      <c r="N39" s="21">
+      <c r="N39" s="24">
         <f>M39</f>
         <v>55210</v>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
+      <c r="A41" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B42" s="12">
+      <c r="A42" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B42" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B43" s="21">
+      <c r="A43" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="B43" s="24">
         <f>M39</f>
         <v>55210</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="B44" s="12">
+      <c r="A44" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="B44" s="15">
         <f>MIN(B39:M39)</f>
         <v>55210</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="B46" s="15"/>
-      <c r="C46" s="15"/>
-      <c r="D46" s="15"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="15"/>
-      <c r="G46" s="15"/>
-      <c r="H46" s="15"/>
-      <c r="I46" s="15"/>
-      <c r="J46" s="15"/>
-      <c r="K46" s="15"/>
-      <c r="L46" s="15"/>
-      <c r="M46" s="15"/>
-      <c r="N46" s="15"/>
+      <c r="A46" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="B46" s="18"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
+      <c r="J46" s="18"/>
+      <c r="K46" s="18"/>
+      <c r="L46" s="18"/>
+      <c r="M46" s="18"/>
+      <c r="N46" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4668,4 +5080,398 @@
     <oddFooter>&amp;L&amp;8Built by SchoolStack Budget  •  budget.schoolstack.ai&amp;C&amp;8Page &amp;P of &amp;N&amp;R&amp;8&amp;D</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:G26"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C6" s="34">
+        <v>12</v>
+      </c>
+      <c r="D6" s="34">
+        <v>18</v>
+      </c>
+      <c r="E6" s="34">
+        <v>22</v>
+      </c>
+      <c r="F6" s="34">
+        <v>25</v>
+      </c>
+      <c r="G6" s="34">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="C7" s="35">
+        <v>221600</v>
+      </c>
+      <c r="D7" s="35">
+        <v>338147.49999999994</v>
+      </c>
+      <c r="E7" s="35">
+        <v>422456.3124999999</v>
+      </c>
+      <c r="F7" s="35">
+        <v>491331.3476562498</v>
+      </c>
+      <c r="G7" s="35">
+        <v>503614.631347656</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C8" s="35">
+        <v>118934.16666666667</v>
+      </c>
+      <c r="D8" s="35">
+        <v>147002.63</v>
+      </c>
+      <c r="E8" s="35">
+        <v>151412.7089</v>
+      </c>
+      <c r="F8" s="35">
+        <v>155955.090167</v>
+      </c>
+      <c r="G8" s="35">
+        <v>160633.74287201</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="C9" s="35">
+        <v>48600</v>
+      </c>
+      <c r="D9" s="35">
+        <v>54885</v>
+      </c>
+      <c r="E9" s="35">
+        <v>59773.625</v>
+      </c>
+      <c r="F9" s="35">
+        <v>64011.63812499999</v>
+      </c>
+      <c r="G9" s="35">
+        <v>65775.83812812499</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" s="35">
+        <v>6959.808550594178</v>
+      </c>
+      <c r="D10" s="35">
+        <v>6959.808550594178</v>
+      </c>
+      <c r="E10" s="35">
+        <v>6959.808550594178</v>
+      </c>
+      <c r="F10" s="35">
+        <v>6959.808550594178</v>
+      </c>
+      <c r="G10" s="35">
+        <v>6959.808550594178</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="C11" s="36">
+        <v>47106.02478273915</v>
+      </c>
+      <c r="D11" s="36">
+        <v>129300.06144940577</v>
+      </c>
+      <c r="E11" s="36">
+        <v>204310.17004940574</v>
+      </c>
+      <c r="F11" s="36">
+        <v>264404.8108136556</v>
+      </c>
+      <c r="G11" s="36">
+        <v>270245.2417969268</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="C12" s="36">
+        <v>47106.02478273915</v>
+      </c>
+      <c r="D12" s="36">
+        <v>176406.0862321449</v>
+      </c>
+      <c r="E12" s="36">
+        <v>380716.2562815506</v>
+      </c>
+      <c r="F12" s="36">
+        <v>645121.0670952062</v>
+      </c>
+      <c r="G12" s="36">
+        <v>915366.3088921331</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="C13" s="37">
+        <v>0.21257231400153045</v>
+      </c>
+      <c r="D13" s="37">
+        <v>0.3823776944954666</v>
+      </c>
+      <c r="E13" s="37">
+        <v>0.4836243748858784</v>
+      </c>
+      <c r="F13" s="37">
+        <v>0.5381395102814428</v>
+      </c>
+      <c r="G13" s="37">
+        <v>0.5366111804054611</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="G15" s="6"/>
+    </row>
+    <row r="16" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="38" t="s">
+        <v>217</v>
+      </c>
+      <c r="C16" s="39" t="s">
+        <v>218</v>
+      </c>
+      <c r="D16" s="40" t="s">
+        <v>219</v>
+      </c>
+      <c r="E16" s="40"/>
+      <c r="F16" s="41" t="s">
+        <v>220</v>
+      </c>
+      <c r="G16" s="41"/>
+    </row>
+    <row r="17" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="38" t="s">
+        <v>221</v>
+      </c>
+      <c r="C17" s="39" t="s">
+        <v>218</v>
+      </c>
+      <c r="D17" s="40" t="s">
+        <v>222</v>
+      </c>
+      <c r="E17" s="40"/>
+      <c r="F17" s="41" t="s">
+        <v>223</v>
+      </c>
+      <c r="G17" s="41"/>
+    </row>
+    <row r="18" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="38" t="s">
+        <v>224</v>
+      </c>
+      <c r="C18" s="39" t="s">
+        <v>218</v>
+      </c>
+      <c r="D18" s="40" t="s">
+        <v>225</v>
+      </c>
+      <c r="E18" s="40"/>
+      <c r="F18" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="G18" s="41"/>
+    </row>
+    <row r="19" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="C19" s="39" t="s">
+        <v>218</v>
+      </c>
+      <c r="D19" s="40" t="s">
+        <v>228</v>
+      </c>
+      <c r="E19" s="40"/>
+      <c r="F19" s="41" t="s">
+        <v>229</v>
+      </c>
+      <c r="G19" s="41"/>
+    </row>
+    <row r="20" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="C20" s="39" t="s">
+        <v>218</v>
+      </c>
+      <c r="D20" s="40" t="s">
+        <v>231</v>
+      </c>
+      <c r="E20" s="40"/>
+      <c r="F20" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="G20" s="41"/>
+    </row>
+    <row r="21" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="38" t="s">
+        <v>233</v>
+      </c>
+      <c r="C21" s="39" t="s">
+        <v>218</v>
+      </c>
+      <c r="D21" s="40" t="s">
+        <v>234</v>
+      </c>
+      <c r="E21" s="40"/>
+      <c r="F21" s="41" t="s">
+        <v>235</v>
+      </c>
+      <c r="G21" s="41"/>
+    </row>
+    <row r="22" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="38" t="s">
+        <v>236</v>
+      </c>
+      <c r="C22" s="39" t="s">
+        <v>218</v>
+      </c>
+      <c r="D22" s="40" t="s">
+        <v>237</v>
+      </c>
+      <c r="E22" s="40"/>
+      <c r="F22" s="41" t="s">
+        <v>238</v>
+      </c>
+      <c r="G22" s="41"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="38" t="s">
+        <v>239</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="42" t="s">
+        <v>122</v>
+      </c>
+      <c r="C26" s="42"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="42"/>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="B26:G26"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;10&amp;BBright Horizons Microschool&amp;R&amp;8&amp;IFinancial Health</oddHeader>
+    <oddFooter>&amp;L&amp;8Built by SchoolStack Budget  •  budget.schoolstack.ai&amp;C&amp;8Page &amp;P of &amp;N&amp;R&amp;8&amp;D</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N46</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$G26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$G33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="249">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -666,6 +666,30 @@
   </si>
   <si>
     <t>Net Margin</t>
+  </si>
+  <si>
+    <t>Revenue per Student</t>
+  </si>
+  <si>
+    <t>Payroll %</t>
+  </si>
+  <si>
+    <t>Facility %</t>
+  </si>
+  <si>
+    <t>Operating Margin</t>
+  </si>
+  <si>
+    <t>DSCR</t>
+  </si>
+  <si>
+    <t>Break-even Year</t>
+  </si>
+  <si>
+    <t>Cash Runway</t>
+  </si>
+  <si>
+    <t>60+ months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -916,7 +940,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -971,6 +995,10 @@
     <xf numFmtId="166" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5087,7 +5115,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G26"/>
+  <dimension ref="B2:G33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -5296,176 +5324,302 @@
         <v>0.5366111804054611</v>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C14" s="35">
+        <v>18466.666666666668</v>
+      </c>
+      <c r="D14" s="35">
+        <v>18785.97222222222</v>
+      </c>
+      <c r="E14" s="35">
+        <v>19202.559659090904</v>
+      </c>
+      <c r="F14" s="35">
+        <v>19653.253906249993</v>
+      </c>
+      <c r="G14" s="35">
+        <v>20144.58525390624</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="C15" s="37">
+        <v>0.5367065282791817</v>
+      </c>
+      <c r="D15" s="37">
+        <v>0.4347293119127009</v>
+      </c>
+      <c r="E15" s="37">
+        <v>0.3584103359800075</v>
+      </c>
+      <c r="F15" s="37">
+        <v>0.31741327092386307</v>
+      </c>
+      <c r="G15" s="37">
+        <v>0.31896162834300396</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6" t="s">
+      <c r="C16" s="37">
+        <v>0.0657942238267148</v>
+      </c>
+      <c r="D16" s="37">
+        <v>0.04869324776909486</v>
+      </c>
+      <c r="E16" s="37">
+        <v>0.0424471997918128</v>
+      </c>
+      <c r="F16" s="37">
+        <v>0.03908460457307385</v>
+      </c>
+      <c r="G16" s="37">
+        <v>0.03918224414098794</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="38" t="s">
+      <c r="C17" s="37">
+        <v>0.2439793922984356</v>
+      </c>
+      <c r="D17" s="37">
+        <v>0.40295986219031626</v>
+      </c>
+      <c r="E17" s="37">
+        <v>0.5000989980472832</v>
+      </c>
+      <c r="F17" s="37">
+        <v>0.5523047138325573</v>
+      </c>
+      <c r="G17" s="37">
+        <v>0.5504308911870363</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="C18" s="38">
+        <v>7.768293185121821</v>
+      </c>
+      <c r="D18" s="38">
+        <v>19.57810606562835</v>
+      </c>
+      <c r="E18" s="38">
+        <v>30.35571698045677</v>
+      </c>
+      <c r="F18" s="38">
+        <v>38.99024195731399</v>
+      </c>
+      <c r="G18" s="38">
+        <v>39.82940742297506</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="20" t="s">
         <v>218</v>
       </c>
-      <c r="D16" s="40" t="s">
+      <c r="C19" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="E16" s="40"/>
-      <c r="F16" s="41" t="s">
+      <c r="C20" s="39" t="s">
         <v>220</v>
       </c>
-      <c r="G16" s="41"/>
-    </row>
-    <row r="17" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="38" t="s">
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="C17" s="39" t="s">
-        <v>218</v>
-      </c>
-      <c r="D17" s="40" t="s">
+      <c r="C22" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="E17" s="40"/>
-      <c r="F17" s="41" t="s">
+      <c r="D22" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="G17" s="41"/>
-    </row>
-    <row r="18" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="38" t="s">
+      <c r="E22" s="6"/>
+      <c r="F22" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="C18" s="39" t="s">
-        <v>218</v>
-      </c>
-      <c r="D18" s="40" t="s">
+      <c r="G22" s="6"/>
+    </row>
+    <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="40" t="s">
         <v>225</v>
       </c>
-      <c r="E18" s="40"/>
-      <c r="F18" s="41" t="s">
+      <c r="C23" s="41" t="s">
         <v>226</v>
       </c>
-      <c r="G18" s="41"/>
-    </row>
-    <row r="19" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="38" t="s">
+      <c r="D23" s="42" t="s">
         <v>227</v>
       </c>
-      <c r="C19" s="39" t="s">
-        <v>218</v>
-      </c>
-      <c r="D19" s="40" t="s">
+      <c r="E23" s="42"/>
+      <c r="F23" s="43" t="s">
         <v>228</v>
       </c>
-      <c r="E19" s="40"/>
-      <c r="F19" s="41" t="s">
+      <c r="G23" s="43"/>
+    </row>
+    <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="40" t="s">
         <v>229</v>
       </c>
-      <c r="G19" s="41"/>
-    </row>
-    <row r="20" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="38" t="s">
+      <c r="C24" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="D24" s="42" t="s">
         <v>230</v>
       </c>
-      <c r="C20" s="39" t="s">
-        <v>218</v>
-      </c>
-      <c r="D20" s="40" t="s">
+      <c r="E24" s="42"/>
+      <c r="F24" s="43" t="s">
         <v>231</v>
       </c>
-      <c r="E20" s="40"/>
-      <c r="F20" s="41" t="s">
+      <c r="G24" s="43"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="40" t="s">
         <v>232</v>
       </c>
-      <c r="G20" s="41"/>
-    </row>
-    <row r="21" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="38" t="s">
+      <c r="C25" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="D25" s="42" t="s">
         <v>233</v>
       </c>
-      <c r="C21" s="39" t="s">
-        <v>218</v>
-      </c>
-      <c r="D21" s="40" t="s">
+      <c r="E25" s="42"/>
+      <c r="F25" s="43" t="s">
         <v>234</v>
       </c>
-      <c r="E21" s="40"/>
-      <c r="F21" s="41" t="s">
+      <c r="G25" s="43"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="40" t="s">
         <v>235</v>
       </c>
-      <c r="G21" s="41"/>
-    </row>
-    <row r="22" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="38" t="s">
+      <c r="C26" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="D26" s="42" t="s">
         <v>236</v>
       </c>
-      <c r="C22" s="39" t="s">
-        <v>218</v>
-      </c>
-      <c r="D22" s="40" t="s">
+      <c r="E26" s="42"/>
+      <c r="F26" s="43" t="s">
         <v>237</v>
       </c>
-      <c r="E22" s="40"/>
-      <c r="F22" s="41" t="s">
+      <c r="G26" s="43"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="40" t="s">
         <v>238</v>
       </c>
-      <c r="G22" s="41"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="38" t="s">
+      <c r="C27" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="D27" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="E27" s="42"/>
+      <c r="F27" s="43" t="s">
         <v>240</v>
       </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="42" t="s">
+      <c r="G27" s="43"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="C28" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="D28" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="E28" s="42"/>
+      <c r="F28" s="43" t="s">
+        <v>243</v>
+      </c>
+      <c r="G28" s="43"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="40" t="s">
+        <v>244</v>
+      </c>
+      <c r="C29" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="D29" s="42" t="s">
+        <v>245</v>
+      </c>
+      <c r="E29" s="42"/>
+      <c r="F29" s="43" t="s">
+        <v>246</v>
+      </c>
+      <c r="G29" s="43"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="40" t="s">
+        <v>247</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B33" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="42"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="44"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="22">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C20:G20"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="F22:G22"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="B33:G33"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
@@ -11,7 +11,7 @@
     <sheet sheetId="5" name="Financial Health" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instructions'!$A1:$B29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instructions'!$A1:$B37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Instructions'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$J56</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$3</definedName>
@@ -27,21 +27,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="255">
   <si>
     <t>How to Use This Workbook</t>
   </si>
   <si>
+    <t>Bright Horizons Microschool</t>
+  </si>
+  <si>
+    <t>Generated March 26, 2026 · llc_single</t>
+  </si>
+  <si>
     <t>Cell Color Legend</t>
   </si>
   <si>
-    <t>Blue cells are editable inputs — change these to update your model.</t>
-  </si>
-  <si>
-    <t>White cells contain formulas — do not edit (they recalculate automatically).</t>
-  </si>
-  <si>
-    <t>Green cells are key outputs and summary metrics.</t>
+    <t xml:space="preserve">  Blue cells are editable inputs — change these to update your model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  White cells contain formulas — do not edit (they recalculate automatically).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Green cells are key outputs and summary metrics.</t>
   </si>
   <si>
     <t/>
@@ -89,6 +95,21 @@
     <t>Review key metrics: net margin, cash runway, and DSCR.</t>
   </si>
   <si>
+    <t>Next Steps</t>
+  </si>
+  <si>
+    <t>2. Verify enrollment and revenue projections match your plan.</t>
+  </si>
+  <si>
+    <t>3. Check the Financial Health dashboard for risk signals.</t>
+  </si>
+  <si>
+    <t>4. Share this workbook with your lender or financial advisor.</t>
+  </si>
+  <si>
+    <t>5. Update inputs as your school's plan evolves.</t>
+  </si>
+  <si>
     <t>Disclaimer</t>
   </si>
   <si>
@@ -108,9 +129,6 @@
   </si>
   <si>
     <t>School Name</t>
-  </si>
-  <si>
-    <t>Bright Horizons Microschool</t>
   </si>
   <si>
     <t>State</t>
@@ -787,7 +805,7 @@
     <numFmt numFmtId="167" formatCode="0.00x"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -802,8 +820,24 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF1E293B"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FF1E293B"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF1E3A5F"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -820,11 +854,6 @@
     <font>
       <i/>
       <color rgb="FF666666"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF1E3A5F"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -879,22 +908,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE8EDF2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDBEAFE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -940,83 +969,235 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="21">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1352,9 +1533,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B29"/>
+  <dimension ref="B2:B37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1366,134 +1548,174 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
+      <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
-        <v>5</v>
+      <c r="B11" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="2" t="s">
-        <v>8</v>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="3" t="s">
-        <v>9</v>
+      <c r="B13" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="3" t="s">
-        <v>5</v>
+      <c r="B17" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
-        <v>13</v>
+      <c r="B18" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="3" t="s">
-        <v>14</v>
+      <c r="B19" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="3" t="s">
-        <v>5</v>
+      <c r="B22" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="2" t="s">
-        <v>17</v>
+      <c r="B23" s="6" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="3" t="s">
-        <v>18</v>
+      <c r="B24" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="3" t="s">
-        <v>5</v>
+      <c r="B26" s="6" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="2" t="s">
-        <v>20</v>
+      <c r="B27" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B28" s="3" t="s">
-        <v>21</v>
+      <c r="B28" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="4" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1521,731 +1743,731 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
+      <c r="A1" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>24</v>
+      <c r="A2" s="9" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="13">
         <v>25</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="9">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="G16" s="10"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="15">
+        <v>12</v>
+      </c>
+      <c r="C17" s="15">
+        <v>18</v>
+      </c>
+      <c r="D17" s="15">
+        <v>22</v>
+      </c>
+      <c r="E17" s="15">
         <v>25</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="G16" s="6"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B17" s="11">
+      <c r="F17" s="15">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="16">
+        <v>12000</v>
+      </c>
+      <c r="E20" s="17">
+        <v>0</v>
+      </c>
+      <c r="F20" s="13">
+        <v>10</v>
+      </c>
+      <c r="G20" s="17">
+        <v>1</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="16">
+        <v>250</v>
+      </c>
+      <c r="E21" s="17">
+        <v>0</v>
+      </c>
+      <c r="F21" s="13">
         <v>12</v>
       </c>
-      <c r="C17" s="11">
-        <v>18</v>
-      </c>
-      <c r="D17" s="11">
-        <v>22</v>
-      </c>
-      <c r="E17" s="11">
-        <v>25</v>
-      </c>
-      <c r="F17" s="11">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H19" s="6" t="s">
+      <c r="G21" s="17">
+        <v>1</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="16">
+        <v>7000</v>
+      </c>
+      <c r="E22" s="17">
+        <v>0</v>
+      </c>
+      <c r="F22" s="13">
+        <v>12</v>
+      </c>
+      <c r="G22" s="17">
+        <v>1</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" s="16">
+        <v>5000</v>
+      </c>
+      <c r="E23" s="17">
+        <v>0</v>
+      </c>
+      <c r="F23" s="13">
+        <v>12</v>
+      </c>
+      <c r="G23" s="17">
+        <v>1</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="16">
+        <v>10</v>
+      </c>
+      <c r="E24" s="17">
+        <v>0</v>
+      </c>
+      <c r="F24" s="13">
+        <v>12</v>
+      </c>
+      <c r="G24" s="17">
+        <v>1</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="18">
+        <v>1</v>
+      </c>
+      <c r="E28" s="16">
+        <v>55000</v>
+      </c>
+      <c r="F28" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="G28" s="17">
+        <v>0.0765</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" s="18">
+        <v>1</v>
+      </c>
+      <c r="E29" s="16">
+        <v>45000</v>
+      </c>
+      <c r="F29" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="G29" s="17">
+        <v>0.0765</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="E30" s="16">
+        <v>28000</v>
+      </c>
+      <c r="F30" s="17">
+        <v>0</v>
+      </c>
+      <c r="G30" s="17">
+        <v>0.0765</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32" s="10"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" s="16">
+        <v>2500</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" s="17">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B37" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+      <c r="C37" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="D37" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="E37" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="12">
-        <v>12000</v>
-      </c>
-      <c r="E20" s="13">
-        <v>0</v>
-      </c>
-      <c r="F20" s="9">
-        <v>10</v>
-      </c>
-      <c r="G20" s="13">
-        <v>1</v>
-      </c>
-      <c r="H20" s="7" t="s">
+      <c r="F37" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G37" s="10"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D38" s="16">
+        <v>2500</v>
+      </c>
+      <c r="E38" s="17">
+        <v>0.03</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D39" s="16">
+        <v>300</v>
+      </c>
+      <c r="E39" s="17">
+        <v>0</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D40" s="16">
+        <v>2400</v>
+      </c>
+      <c r="E40" s="17">
+        <v>0</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" s="16">
+        <v>500</v>
+      </c>
+      <c r="E41" s="17">
+        <v>0</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" s="16">
+        <v>300</v>
+      </c>
+      <c r="E42" s="17">
+        <v>0</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D43" s="16">
+        <v>3000</v>
+      </c>
+      <c r="E43" s="17">
+        <v>0</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" s="19">
+        <v>0</v>
+      </c>
+      <c r="D46" s="16">
+        <v>30000</v>
+      </c>
+      <c r="E46" s="20">
+        <v>0.06</v>
+      </c>
+      <c r="F46" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D21" s="12">
-        <v>250</v>
-      </c>
-      <c r="E21" s="13">
-        <v>0</v>
-      </c>
-      <c r="F21" s="9">
-        <v>12</v>
-      </c>
-      <c r="G21" s="13">
-        <v>1</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" s="12">
-        <v>7000</v>
-      </c>
-      <c r="E22" s="13">
-        <v>0</v>
-      </c>
-      <c r="F22" s="9">
-        <v>12</v>
-      </c>
-      <c r="G22" s="13">
-        <v>1</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" s="12">
-        <v>5000</v>
-      </c>
-      <c r="E23" s="13">
-        <v>0</v>
-      </c>
-      <c r="F23" s="9">
-        <v>12</v>
-      </c>
-      <c r="G23" s="13">
-        <v>1</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D24" s="12">
-        <v>10</v>
-      </c>
-      <c r="E24" s="13">
-        <v>0</v>
-      </c>
-      <c r="F24" s="9">
-        <v>12</v>
-      </c>
-      <c r="G24" s="13">
-        <v>1</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="12">
-        <v>55000</v>
-      </c>
-      <c r="F28" s="13">
-        <v>0.2</v>
-      </c>
-      <c r="G28" s="13">
-        <v>0.0765</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="12">
-        <v>45000</v>
-      </c>
-      <c r="F29" s="13">
-        <v>0.2</v>
-      </c>
-      <c r="G29" s="13">
-        <v>0.0765</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D30" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="E30" s="12">
-        <v>28000</v>
-      </c>
-      <c r="F30" s="13">
-        <v>0</v>
-      </c>
-      <c r="G30" s="13">
-        <v>0.0765</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D32" s="6"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="B34" s="12">
-        <v>2500</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="B35" s="13">
+      <c r="G46" s="19">
+        <v>6960</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B48" s="10"/>
+      <c r="C48" s="10"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="B49" s="17">
         <v>0.03</v>
       </c>
     </row>
-    <row r="37" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G37" s="6"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="D38" s="12">
-        <v>2500</v>
-      </c>
-      <c r="E38" s="13">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B50" s="17">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="B51" s="18">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="C51" s="21" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="B52" s="17">
         <v>0.03</v>
       </c>
-      <c r="F38" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="D39" s="12">
-        <v>300</v>
-      </c>
-      <c r="E39" s="13">
-        <v>0</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D40" s="12">
-        <v>2400</v>
-      </c>
-      <c r="E40" s="13">
-        <v>0</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D41" s="12">
-        <v>500</v>
-      </c>
-      <c r="E41" s="13">
-        <v>0</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D42" s="12">
-        <v>300</v>
-      </c>
-      <c r="E42" s="13">
-        <v>0</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D43" s="12">
-        <v>3000</v>
-      </c>
-      <c r="E43" s="13">
-        <v>0</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C46" s="15">
-        <v>0</v>
-      </c>
-      <c r="D46" s="12">
-        <v>30000</v>
-      </c>
-      <c r="E46" s="16">
-        <v>0.06</v>
-      </c>
-      <c r="F46" s="9">
-        <v>5</v>
-      </c>
-      <c r="G46" s="15">
-        <v>6960</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="B49" s="13">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="B50" s="13">
-        <v>0.025</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="B51" s="14">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="C51" s="17" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="B52" s="13">
-        <v>0.03</v>
-      </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B53" s="13">
+      <c r="A53" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="B53" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="B54" s="12">
+      <c r="A54" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B54" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="B56" s="18"/>
-      <c r="C56" s="18"/>
-      <c r="D56" s="18"/>
-      <c r="E56" s="18"/>
-      <c r="F56" s="18"/>
-      <c r="G56" s="18"/>
+      <c r="A56" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="B56" s="22"/>
+      <c r="C56" s="22"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="22"/>
+      <c r="G56" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2276,1324 +2498,1324 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
+      <c r="A1" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>50</v>
+      <c r="A2" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="21">
+      <c r="A3" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="25">
         <f>Assumptions!B17</f>
         <v>12</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="25">
         <f>Assumptions!C17</f>
         <v>18</v>
       </c>
-      <c r="D3" s="21">
+      <c r="D3" s="25">
         <f>Assumptions!D17</f>
         <v>22</v>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="25">
         <f>Assumptions!E17</f>
         <v>25</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="25">
         <f>Assumptions!F17</f>
         <v>25</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
+      <c r="A5" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="15">
+      <c r="A6" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="19">
         <v>120000</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="19">
         <v>221400</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="19">
         <v>277365</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="19">
         <v>323067</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="19">
         <v>331144</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" s="15">
+      <c r="A7" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="19">
         <v>2500</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="19">
         <v>4613</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="19">
         <v>5778</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="19">
         <v>6731</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="19">
         <v>6899</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" s="15">
+      <c r="A8" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="19">
         <v>70000</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="19">
         <v>129150</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="19">
         <v>161796</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="19">
         <v>188456</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="19">
         <v>193167</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" s="15">
+      <c r="A9" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="19">
         <v>4167</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="19">
         <v>5125</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="19">
         <v>5253</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="19">
         <v>5384</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="19">
         <v>5519</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B10" s="15">
+      <c r="A10" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B10" s="19">
         <v>-12000</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="19">
         <v>-22140</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="19">
         <v>-27736</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="19">
         <v>-32307</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="19">
         <v>-33114</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B11" s="22">
+      <c r="A11" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11" s="26">
         <f>SUM(B6:B10)</f>
         <v>184667</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="26">
         <f>SUM(C6:C10)</f>
         <v>338147</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="26">
         <f>SUM(D6:D10)</f>
         <v>422456</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="26">
         <f>SUM(E6:E10)</f>
         <v>491331</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="26">
         <f>SUM(F6:F10)</f>
         <v>503615</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
+      <c r="A13" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="B14" s="15">
+      <c r="A14" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" s="19">
         <v>58506</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="19">
         <v>72314</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="19">
         <v>74483</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="19">
         <v>76718</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="19">
         <v>79019</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="B15" s="15">
+      <c r="A15" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="B15" s="19">
         <v>47869</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="19">
         <v>59166</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="19">
         <v>60941</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="19">
         <v>62769</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="19">
         <v>64652</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="B16" s="15">
+      <c r="A16" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="B16" s="19">
         <v>12559</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="19">
         <v>15523</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="19">
         <v>15989</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="19">
         <v>16468</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="19">
         <v>16963</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B17" s="22">
+      <c r="A17" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B17" s="26">
         <f>SUM(B14:B16)</f>
         <v>118934</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="26">
         <f>SUM(C14:C16)</f>
         <v>147003</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="26">
         <f>SUM(D14:D16)</f>
         <v>151413</v>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="26">
         <f>SUM(E14:E16)</f>
         <v>155955</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="26">
         <f>SUM(F14:F16)</f>
         <v>160634</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
+      <c r="A19" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
+      <c r="A20" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="B21" s="15">
+      <c r="A21" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21" s="19">
         <v>5000</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="19">
         <v>9225</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="19">
         <v>11557</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="19">
         <v>13461</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="19">
         <v>13798</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="B22" s="24">
+      <c r="A22" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="B22" s="28">
         <v>5000</v>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="28">
         <v>9225</v>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="28">
         <v>11557</v>
       </c>
-      <c r="E22" s="24">
+      <c r="E22" s="28">
         <v>13461</v>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="28">
         <v>13798</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
+      <c r="A23" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="B24" s="15">
+      <c r="A24" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="B24" s="19">
         <v>3000</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="19">
         <v>5535</v>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="19">
         <v>6934</v>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="19">
         <v>8077</v>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="19">
         <v>8279</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="B25" s="24">
+      <c r="A25" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="B25" s="28">
         <v>3000</v>
       </c>
-      <c r="C25" s="24">
+      <c r="C25" s="28">
         <v>5535</v>
       </c>
-      <c r="D25" s="24">
+      <c r="D25" s="28">
         <v>6934</v>
       </c>
-      <c r="E25" s="24">
+      <c r="E25" s="28">
         <v>8077</v>
       </c>
-      <c r="F25" s="24">
+      <c r="F25" s="28">
         <v>8279</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
+      <c r="A26" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B27" s="15">
+      <c r="A27" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="B27" s="19">
         <v>25000</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="19">
         <v>30900</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="19">
         <v>31827</v>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="19">
         <v>32782</v>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="19">
         <v>33765</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="B28" s="15">
+      <c r="A28" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="B28" s="19">
         <v>3000</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="19">
         <v>3690</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="19">
         <v>3782</v>
       </c>
-      <c r="E28" s="15">
+      <c r="E28" s="19">
         <v>3877</v>
       </c>
-      <c r="F28" s="15">
+      <c r="F28" s="19">
         <v>3974</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="B29" s="15">
+      <c r="A29" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B29" s="19">
         <v>2000</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="19">
         <v>2460</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="19">
         <v>2522</v>
       </c>
-      <c r="E29" s="15">
+      <c r="E29" s="19">
         <v>2585</v>
       </c>
-      <c r="F29" s="15">
+      <c r="F29" s="19">
         <v>2649</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="B30" s="24">
+      <c r="A30" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="B30" s="28">
         <v>30000</v>
       </c>
-      <c r="C30" s="24">
+      <c r="C30" s="28">
         <v>37050</v>
       </c>
-      <c r="D30" s="24">
+      <c r="D30" s="28">
         <v>38131</v>
       </c>
-      <c r="E30" s="24">
+      <c r="E30" s="28">
         <v>39244</v>
       </c>
-      <c r="F30" s="24">
+      <c r="F30" s="28">
         <v>40388</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
+      <c r="A31" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="B32" s="15">
+      <c r="A32" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B32" s="19">
         <v>2500</v>
       </c>
-      <c r="C32" s="15">
+      <c r="C32" s="19">
         <v>3075</v>
       </c>
-      <c r="D32" s="15">
+      <c r="D32" s="19">
         <v>3152</v>
       </c>
-      <c r="E32" s="15">
+      <c r="E32" s="19">
         <v>3231</v>
       </c>
-      <c r="F32" s="15">
+      <c r="F32" s="19">
         <v>3311</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="B33" s="24">
+      <c r="A33" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="B33" s="28">
         <v>2500</v>
       </c>
-      <c r="C33" s="24">
+      <c r="C33" s="28">
         <v>3075</v>
       </c>
-      <c r="D33" s="24">
+      <c r="D33" s="28">
         <v>3152</v>
       </c>
-      <c r="E33" s="24">
+      <c r="E33" s="28">
         <v>3231</v>
       </c>
-      <c r="F33" s="24">
+      <c r="F33" s="28">
         <v>3311</v>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B34" s="22">
+      <c r="A34" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="B34" s="26">
         <f>B22+B25+B30+B33</f>
         <v>40500</v>
       </c>
-      <c r="C34" s="22">
+      <c r="C34" s="26">
         <f>C22+C25+C30+C33</f>
         <v>54885</v>
       </c>
-      <c r="D34" s="22">
+      <c r="D34" s="26">
         <f>D22+D25+D30+D33</f>
         <v>59774</v>
       </c>
-      <c r="E34" s="22">
+      <c r="E34" s="26">
         <f>E22+E25+E30+E33</f>
         <v>64012</v>
       </c>
-      <c r="F34" s="22">
+      <c r="F34" s="26">
         <f>F22+F25+F30+F33</f>
         <v>65776</v>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
+      <c r="A36" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="B37" s="15">
+      <c r="A37" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B37" s="19">
         <v>6960</v>
       </c>
-      <c r="C37" s="15">
+      <c r="C37" s="19">
         <v>6960</v>
       </c>
-      <c r="D37" s="15">
+      <c r="D37" s="19">
         <v>6960</v>
       </c>
-      <c r="E37" s="15">
+      <c r="E37" s="19">
         <v>6960</v>
       </c>
-      <c r="F37" s="15">
+      <c r="F37" s="19">
         <v>6960</v>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B38" s="22">
+      <c r="A38" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B38" s="26">
         <f>SUM(B37:B37)</f>
         <v>6960</v>
       </c>
-      <c r="C38" s="22">
+      <c r="C38" s="26">
         <f>SUM(C37:C37)</f>
         <v>6960</v>
       </c>
-      <c r="D38" s="22">
+      <c r="D38" s="26">
         <f>SUM(D37:D37)</f>
         <v>6960</v>
       </c>
-      <c r="E38" s="22">
+      <c r="E38" s="26">
         <f>SUM(E37:E37)</f>
         <v>6960</v>
       </c>
-      <c r="F38" s="22">
+      <c r="F38" s="26">
         <f>SUM(F37:F37)</f>
         <v>6960</v>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
+      <c r="A40" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="B41" s="24">
+      <c r="A41" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="B41" s="28">
         <f>B11</f>
         <v>184667</v>
       </c>
-      <c r="C41" s="24">
+      <c r="C41" s="28">
         <f>C11</f>
         <v>338147</v>
       </c>
-      <c r="D41" s="24">
+      <c r="D41" s="28">
         <f>D11</f>
         <v>422456</v>
       </c>
-      <c r="E41" s="24">
+      <c r="E41" s="28">
         <f>E11</f>
         <v>491331</v>
       </c>
-      <c r="F41" s="24">
+      <c r="F41" s="28">
         <f>F11</f>
         <v>503615</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B42" s="15">
+      <c r="A42" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="B42" s="19">
         <f>B17</f>
         <v>118934</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="19">
         <f>C17</f>
         <v>147003</v>
       </c>
-      <c r="D42" s="15">
+      <c r="D42" s="19">
         <f>D17</f>
         <v>151413</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="19">
         <f>E17</f>
         <v>155955</v>
       </c>
-      <c r="F42" s="15">
+      <c r="F42" s="19">
         <f>F17</f>
         <v>160634</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="B43" s="15">
+      <c r="A43" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B43" s="19">
         <f>B34</f>
         <v>40500</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="19">
         <f>C34</f>
         <v>54885</v>
       </c>
-      <c r="D43" s="15">
+      <c r="D43" s="19">
         <f>D34</f>
         <v>59774</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="19">
         <f>E34</f>
         <v>64012</v>
       </c>
-      <c r="F43" s="15">
+      <c r="F43" s="19">
         <f>F34</f>
         <v>65776</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="B44" s="15">
+      <c r="A44" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="B44" s="19">
         <f>B38</f>
         <v>6960</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="19">
         <f>C38</f>
         <v>6960</v>
       </c>
-      <c r="D44" s="15">
+      <c r="D44" s="19">
         <f>D38</f>
         <v>6960</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="19">
         <f>E38</f>
         <v>6960</v>
       </c>
-      <c r="F44" s="15">
+      <c r="F44" s="19">
         <f>F38</f>
         <v>6960</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="B45" s="24">
+      <c r="A45" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="B45" s="28">
         <f>B42+B43+B44</f>
         <v>166394</v>
       </c>
-      <c r="C45" s="24">
+      <c r="C45" s="28">
         <f>C42+C43+C44</f>
         <v>208848</v>
       </c>
-      <c r="D45" s="24">
+      <c r="D45" s="28">
         <f>D42+D43+D44</f>
         <v>218147</v>
       </c>
-      <c r="E45" s="24">
+      <c r="E45" s="28">
         <f>E42+E43+E44</f>
         <v>226927</v>
       </c>
-      <c r="F45" s="24">
+      <c r="F45" s="28">
         <f>F42+F43+F44</f>
         <v>233370</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="B47" s="26">
+      <c r="A47" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="B47" s="30">
         <f>B41-B45</f>
         <v>18273</v>
       </c>
-      <c r="C47" s="26">
+      <c r="C47" s="30">
         <f>C41-C45</f>
         <v>129299</v>
       </c>
-      <c r="D47" s="26">
+      <c r="D47" s="30">
         <f>D41-D45</f>
         <v>204309</v>
       </c>
-      <c r="E47" s="26">
+      <c r="E47" s="30">
         <f>E41-E45</f>
         <v>264404</v>
       </c>
-      <c r="F47" s="26">
+      <c r="F47" s="30">
         <f>F41-F45</f>
         <v>270245</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="B48" s="27">
+      <c r="A48" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="B48" s="31">
         <f>IF(B41=0,"",B47/B41)</f>
         <v>0.1</v>
       </c>
-      <c r="C48" s="27">
+      <c r="C48" s="31">
         <f>IF(C41=0,"",C47/C41)</f>
         <v>0.38</v>
       </c>
-      <c r="D48" s="27">
+      <c r="D48" s="31">
         <f>IF(D41=0,"",D47/D41)</f>
         <v>0.48</v>
       </c>
-      <c r="E48" s="27">
+      <c r="E48" s="31">
         <f>IF(E41=0,"",E47/E41)</f>
         <v>0.54</v>
       </c>
-      <c r="F48" s="27">
+      <c r="F48" s="31">
         <f>IF(F41=0,"",F47/F41)</f>
         <v>0.54</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="B49" s="15">
+      <c r="A49" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="B49" s="19">
         <f>B47</f>
         <v>18273</v>
       </c>
-      <c r="C49" s="15">
+      <c r="C49" s="19">
         <f>B49+C47</f>
         <v>147572</v>
       </c>
-      <c r="D49" s="15">
+      <c r="D49" s="19">
         <f>C49+D47</f>
         <v>351881</v>
       </c>
-      <c r="E49" s="15">
+      <c r="E49" s="19">
         <f>D49+E47</f>
         <v>616285</v>
       </c>
-      <c r="F49" s="15">
+      <c r="F49" s="19">
         <f>E49+F47</f>
         <v>886530</v>
       </c>
     </row>
     <row r="51" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
+      <c r="A51" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B51" s="10"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="B52" s="24">
+      <c r="A52" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="B52" s="28">
         <f>B41-B42-B43</f>
         <v>25233</v>
       </c>
-      <c r="C52" s="24">
+      <c r="C52" s="28">
         <f>C41-C42-C43</f>
         <v>136259</v>
       </c>
-      <c r="D52" s="24">
+      <c r="D52" s="28">
         <f>D41-D42-D43</f>
         <v>211269</v>
       </c>
-      <c r="E52" s="24">
+      <c r="E52" s="28">
         <f>E41-E42-E43</f>
         <v>271364</v>
       </c>
-      <c r="F52" s="24">
+      <c r="F52" s="28">
         <f>F41-F42-F43</f>
         <v>277205</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="B53" s="15">
+      <c r="A53" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="B53" s="19">
         <f>B44</f>
         <v>6960</v>
       </c>
-      <c r="C53" s="15">
+      <c r="C53" s="19">
         <f>C44</f>
         <v>6960</v>
       </c>
-      <c r="D53" s="15">
+      <c r="D53" s="19">
         <f>D44</f>
         <v>6960</v>
       </c>
-      <c r="E53" s="15">
+      <c r="E53" s="19">
         <f>E44</f>
         <v>6960</v>
       </c>
-      <c r="F53" s="15">
+      <c r="F53" s="19">
         <f>F44</f>
         <v>6960</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="B54" s="28">
+      <c r="A54" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="B54" s="32">
         <f>IF(B53=0,"N/A",B52/B53)</f>
         <v>3.63</v>
       </c>
-      <c r="C54" s="28">
+      <c r="C54" s="32">
         <f>IF(C53=0,"N/A",C52/C53)</f>
         <v>19.58</v>
       </c>
-      <c r="D54" s="28">
+      <c r="D54" s="32">
         <f>IF(D53=0,"N/A",D52/D53)</f>
         <v>30.35</v>
       </c>
-      <c r="E54" s="28">
+      <c r="E54" s="32">
         <f>IF(E53=0,"N/A",E52/E53)</f>
         <v>38.99</v>
       </c>
-      <c r="F54" s="28">
+      <c r="F54" s="32">
         <f>IF(F53=0,"N/A",F52/F53)</f>
         <v>39.83</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="B55" s="15" t="str">
+      <c r="A55" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B55" s="19" t="str">
         <f>Assumptions!B54</f>
         <v>0</v>
       </c>
-      <c r="C55" s="15">
+      <c r="C55" s="19">
         <f>B56</f>
         <v>18273</v>
       </c>
-      <c r="D55" s="15">
+      <c r="D55" s="19">
         <f>C56</f>
         <v>147572</v>
       </c>
-      <c r="E55" s="15">
+      <c r="E55" s="19">
         <f>D56</f>
         <v>351881</v>
       </c>
-      <c r="F55" s="15">
+      <c r="F55" s="19">
         <f>E56</f>
         <v>616285</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="B56" s="24">
+      <c r="A56" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B56" s="28">
         <f>B55+B47</f>
         <v>18273</v>
       </c>
-      <c r="C56" s="24">
+      <c r="C56" s="28">
         <f>C55+C47</f>
         <v>147572</v>
       </c>
-      <c r="D56" s="24">
+      <c r="D56" s="28">
         <f>D55+D47</f>
         <v>351881</v>
       </c>
-      <c r="E56" s="24">
+      <c r="E56" s="28">
         <f>E55+E47</f>
         <v>616285</v>
       </c>
-      <c r="F56" s="24">
+      <c r="F56" s="28">
         <f>F55+F47</f>
         <v>886530</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="B57" s="29">
+      <c r="A57" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="B57" s="33">
         <f>IF(B45=0,"",B56/B45*365)</f>
         <v>40</v>
       </c>
-      <c r="C57" s="29">
+      <c r="C57" s="33">
         <f>IF(C45=0,"",C56/C45*365)</f>
         <v>258</v>
       </c>
-      <c r="D57" s="29">
+      <c r="D57" s="33">
         <f>IF(D45=0,"",D56/D45*365)</f>
         <v>589</v>
       </c>
-      <c r="E57" s="29">
+      <c r="E57" s="33">
         <f>IF(E45=0,"",E56/E45*365)</f>
         <v>991</v>
       </c>
-      <c r="F57" s="29">
+      <c r="F57" s="33">
         <f>IF(F45=0,"",F56/F45*365)</f>
         <v>1387</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="B58" s="30">
+      <c r="A58" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B58" s="34">
         <f>IF(B45=0,"",B56/(B45/12))</f>
         <v>1.3</v>
       </c>
-      <c r="C58" s="30">
+      <c r="C58" s="34">
         <f>IF(C45=0,"",C56/(C45/12))</f>
         <v>8.5</v>
       </c>
-      <c r="D58" s="30">
+      <c r="D58" s="34">
         <f>IF(D45=0,"",D56/(D45/12))</f>
         <v>19.4</v>
       </c>
-      <c r="E58" s="30">
+      <c r="E58" s="34">
         <f>IF(E45=0,"",E56/(E45/12))</f>
         <v>32.6</v>
       </c>
-      <c r="F58" s="30">
+      <c r="F58" s="34">
         <f>IF(F45=0,"",F56/(F45/12))</f>
         <v>45.6</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="B59" s="27">
+      <c r="A59" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B59" s="31">
         <f>IF(Assumptions!B12=0,"",B3/Assumptions!B12)</f>
         <v>0.48</v>
       </c>
-      <c r="C59" s="27">
+      <c r="C59" s="31">
         <f>IF(Assumptions!B12=0,"",C3/Assumptions!B12)</f>
         <v>0.72</v>
       </c>
-      <c r="D59" s="27">
+      <c r="D59" s="31">
         <f>IF(Assumptions!B12=0,"",D3/Assumptions!B12)</f>
         <v>0.88</v>
       </c>
-      <c r="E59" s="27">
+      <c r="E59" s="31">
         <f>IF(Assumptions!B12=0,"",E3/Assumptions!B12)</f>
         <v>1</v>
       </c>
-      <c r="F59" s="27">
+      <c r="F59" s="31">
         <f>IF(Assumptions!B12=0,"",F3/Assumptions!B12)</f>
         <v>1</v>
       </c>
     </row>
     <row r="61" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6"/>
+      <c r="A61" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B61" s="10"/>
+      <c r="C61" s="10"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="10"/>
+      <c r="F61" s="10"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="B62" s="7" t="str">
+      <c r="A62" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="B62" s="11" t="str">
         <f>IF(B53=0,"N/A",IF(B54&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="C62" s="7" t="str">
+      <c r="C62" s="11" t="str">
         <f>IF(C53=0,"N/A",IF(C54&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="D62" s="7" t="str">
+      <c r="D62" s="11" t="str">
         <f>IF(D53=0,"N/A",IF(D54&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E62" s="7" t="str">
+      <c r="E62" s="11" t="str">
         <f>IF(E53=0,"N/A",IF(E54&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F62" s="7" t="str">
+      <c r="F62" s="11" t="str">
         <f>IF(F53=0,"N/A",IF(F54&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="B63" s="7" t="str">
+      <c r="A63" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="B63" s="11" t="str">
         <f>IF(B47&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="C63" s="7" t="str">
+      <c r="C63" s="11" t="str">
         <f>IF(C47&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="D63" s="7" t="str">
+      <c r="D63" s="11" t="str">
         <f>IF(D47&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E63" s="7" t="str">
+      <c r="E63" s="11" t="str">
         <f>IF(E47&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="F63" s="7" t="str">
+      <c r="F63" s="11" t="str">
         <f>IF(F47&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="B64" s="7" t="str">
+      <c r="A64" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="B64" s="11" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(B3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C64" s="7" t="str">
+      <c r="C64" s="11" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(C3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="D64" s="7" t="str">
+      <c r="D64" s="11" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(D3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E64" s="7" t="str">
+      <c r="E64" s="11" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(E3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F64" s="7" t="str">
+      <c r="F64" s="11" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(F3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="B65" s="7" t="str">
+      <c r="A65" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="B65" s="11" t="str">
         <f>IF(B45=0,"N/A",IF(B56/(B45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C65" s="7" t="str">
+      <c r="C65" s="11" t="str">
         <f>IF(C45=0,"N/A",IF(C56/(C45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="D65" s="7" t="str">
+      <c r="D65" s="11" t="str">
         <f>IF(D45=0,"N/A",IF(D56/(D45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E65" s="7" t="str">
+      <c r="E65" s="11" t="str">
         <f>IF(E45=0,"N/A",IF(E56/(E45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F65" s="7" t="str">
+      <c r="F65" s="11" t="str">
         <f>IF(F45=0,"N/A",IF(F56/(F45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="67" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="B67" s="6"/>
-      <c r="C67" s="6"/>
-      <c r="D67" s="6"/>
-      <c r="E67" s="6"/>
-      <c r="F67" s="6"/>
+      <c r="A67" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="B67" s="10"/>
+      <c r="C67" s="10"/>
+      <c r="D67" s="10"/>
+      <c r="E67" s="10"/>
+      <c r="F67" s="10"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="B68" s="15">
+      <c r="A68" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="B68" s="19">
         <f>IF(B3=0,"",B11/B3)</f>
         <v>15389</v>
       </c>
-      <c r="C68" s="15">
+      <c r="C68" s="19">
         <f>IF(C3=0,"",C11/C3)</f>
         <v>18786</v>
       </c>
-      <c r="D68" s="15">
+      <c r="D68" s="19">
         <f>IF(D3=0,"",D11/D3)</f>
         <v>19203</v>
       </c>
-      <c r="E68" s="15">
+      <c r="E68" s="19">
         <f>IF(E3=0,"",E11/E3)</f>
         <v>19653</v>
       </c>
-      <c r="F68" s="15">
+      <c r="F68" s="19">
         <f>IF(F3=0,"",F11/F3)</f>
         <v>20145</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="B69" s="15">
+      <c r="A69" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B69" s="19">
         <f>IF(B3=0,"",B45/B3)</f>
         <v>13866</v>
       </c>
-      <c r="C69" s="15">
+      <c r="C69" s="19">
         <f>IF(C3=0,"",C45/C3)</f>
         <v>11603</v>
       </c>
-      <c r="D69" s="15">
+      <c r="D69" s="19">
         <f>IF(D3=0,"",D45/D3)</f>
         <v>9916</v>
       </c>
-      <c r="E69" s="15">
+      <c r="E69" s="19">
         <f>IF(E3=0,"",E45/E3)</f>
         <v>9077</v>
       </c>
-      <c r="F69" s="15">
+      <c r="F69" s="19">
         <f>IF(F3=0,"",F45/F3)</f>
         <v>9335</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="B70" s="15">
+      <c r="A70" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="B70" s="19">
         <f>B42+B44</f>
         <v>125894</v>
       </c>
-      <c r="C70" s="15">
+      <c r="C70" s="19">
         <f>C42+C44</f>
         <v>153963</v>
       </c>
-      <c r="D70" s="15">
+      <c r="D70" s="19">
         <f>D42+D44</f>
         <v>158373</v>
       </c>
-      <c r="E70" s="15">
+      <c r="E70" s="19">
         <f>E42+E44</f>
         <v>162915</v>
       </c>
-      <c r="F70" s="15">
+      <c r="F70" s="19">
         <f>F42+F44</f>
         <v>167594</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="B71" s="15">
+      <c r="A71" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="B71" s="19">
         <f>IF(B3=0,"",B43/B3)</f>
         <v>3375</v>
       </c>
-      <c r="C71" s="15">
+      <c r="C71" s="19">
         <f>IF(C3=0,"",C43/C3)</f>
         <v>3049</v>
       </c>
-      <c r="D71" s="15">
+      <c r="D71" s="19">
         <f>IF(D3=0,"",D43/D3)</f>
         <v>2717</v>
       </c>
-      <c r="E71" s="15">
+      <c r="E71" s="19">
         <f>IF(E3=0,"",E43/E3)</f>
         <v>2560</v>
       </c>
-      <c r="F71" s="15">
+      <c r="F71" s="19">
         <f>IF(F3=0,"",F43/F3)</f>
         <v>2631</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="B72" s="15">
+      <c r="A72" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="B72" s="19">
         <f>IF(B3=0,"",B68-B71)</f>
         <v>12014</v>
       </c>
-      <c r="C72" s="15">
+      <c r="C72" s="19">
         <f>IF(C3=0,"",C68-C71)</f>
         <v>15737</v>
       </c>
-      <c r="D72" s="15">
+      <c r="D72" s="19">
         <f>IF(D3=0,"",D68-D71)</f>
         <v>16486</v>
       </c>
-      <c r="E72" s="15">
+      <c r="E72" s="19">
         <f>IF(E3=0,"",E68-E71)</f>
         <v>17093</v>
       </c>
-      <c r="F72" s="15">
+      <c r="F72" s="19">
         <f>IF(F3=0,"",F68-F71)</f>
         <v>17514</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="31" t="s">
-        <v>172</v>
-      </c>
-      <c r="B73" s="32">
+      <c r="A73" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="B73" s="36">
         <f>IF(B72&lt;=0,"N/A",ROUNDUP(B70/B72,0))</f>
         <v>11</v>
       </c>
-      <c r="C73" s="32">
+      <c r="C73" s="36">
         <f>IF(C72&lt;=0,"N/A",ROUNDUP(C70/C72,0))</f>
         <v>10</v>
       </c>
-      <c r="D73" s="32">
+      <c r="D73" s="36">
         <f>IF(D72&lt;=0,"N/A",ROUNDUP(D70/D72,0))</f>
         <v>10</v>
       </c>
-      <c r="E73" s="32">
+      <c r="E73" s="36">
         <f>IF(E72&lt;=0,"N/A",ROUNDUP(E70/E72,0))</f>
         <v>10</v>
       </c>
-      <c r="F73" s="32">
+      <c r="F73" s="36">
         <f>IF(F72&lt;=0,"N/A",ROUNDUP(F70/F72,0))</f>
         <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="B75" s="18"/>
-      <c r="C75" s="18"/>
-      <c r="D75" s="18"/>
-      <c r="E75" s="18"/>
-      <c r="F75" s="18"/>
+      <c r="A75" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="B75" s="22"/>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3623,1478 +3845,1478 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
+      <c r="A1" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="G2" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="H2" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="I2" s="19" t="s">
+      <c r="A2" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="D2" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="E2" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="F2" s="23" t="s">
         <v>183</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="G2" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="H2" s="23" t="s">
         <v>185</v>
       </c>
+      <c r="I2" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="J2" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="K2" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="L2" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="M2" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="N2" s="23" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
+      <c r="A3" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" s="15">
+      <c r="A4" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="19">
         <v>14400</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="19">
         <v>14400</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="19">
         <v>14400</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="19">
         <v>14400</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="19">
         <v>14400</v>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="19">
         <v>14400</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="19">
         <v>14400</v>
       </c>
-      <c r="I4" s="15">
+      <c r="I4" s="19">
         <v>14400</v>
       </c>
-      <c r="J4" s="15">
+      <c r="J4" s="19">
         <v>14400</v>
       </c>
-      <c r="K4" s="15">
+      <c r="K4" s="19">
         <v>14400</v>
       </c>
-      <c r="L4" s="15">
-        <v>0</v>
-      </c>
-      <c r="M4" s="15">
-        <v>0</v>
-      </c>
-      <c r="N4" s="15">
+      <c r="L4" s="19">
+        <v>0</v>
+      </c>
+      <c r="M4" s="19">
+        <v>0</v>
+      </c>
+      <c r="N4" s="19">
         <f>SUM(B4:M4)</f>
         <v>120000</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="15">
+      <c r="A5" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="19">
         <v>300</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="19">
         <v>300</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="19">
         <v>300</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="19">
         <v>300</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="19">
         <v>300</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="19">
         <v>300</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="19">
         <v>300</v>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="19">
         <v>300</v>
       </c>
-      <c r="J5" s="15">
+      <c r="J5" s="19">
         <v>300</v>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="19">
         <v>300</v>
       </c>
-      <c r="L5" s="15">
-        <v>0</v>
-      </c>
-      <c r="M5" s="15">
-        <v>0</v>
-      </c>
-      <c r="N5" s="15">
+      <c r="L5" s="19">
+        <v>0</v>
+      </c>
+      <c r="M5" s="19">
+        <v>0</v>
+      </c>
+      <c r="N5" s="19">
         <f>SUM(B5:M5)</f>
         <v>2500</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="15">
+      <c r="A6" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="19">
         <v>8400</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="19">
         <v>8400</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="19">
         <v>8400</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="19">
         <v>8400</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="19">
         <v>8400</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="19">
         <v>8400</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="19">
         <v>8400</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="19">
         <v>8400</v>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="19">
         <v>8400</v>
       </c>
-      <c r="K6" s="15">
+      <c r="K6" s="19">
         <v>8400</v>
       </c>
-      <c r="L6" s="15">
-        <v>0</v>
-      </c>
-      <c r="M6" s="15">
-        <v>0</v>
-      </c>
-      <c r="N6" s="15">
+      <c r="L6" s="19">
+        <v>0</v>
+      </c>
+      <c r="M6" s="19">
+        <v>0</v>
+      </c>
+      <c r="N6" s="19">
         <f>SUM(B6:M6)</f>
         <v>70000</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B7" s="15">
+      <c r="A7" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="19">
         <v>500</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="19">
         <v>500</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="19">
         <v>500</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="19">
         <v>500</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="19">
         <v>500</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="19">
         <v>500</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="19">
         <v>500</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="19">
         <v>500</v>
       </c>
-      <c r="J7" s="15">
+      <c r="J7" s="19">
         <v>500</v>
       </c>
-      <c r="K7" s="15">
+      <c r="K7" s="19">
         <v>500</v>
       </c>
-      <c r="L7" s="15">
-        <v>0</v>
-      </c>
-      <c r="M7" s="15">
-        <v>0</v>
-      </c>
-      <c r="N7" s="15">
+      <c r="L7" s="19">
+        <v>0</v>
+      </c>
+      <c r="M7" s="19">
+        <v>0</v>
+      </c>
+      <c r="N7" s="19">
         <f>SUM(B7:M7)</f>
         <v>4167</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B8" s="15">
-        <v>0</v>
-      </c>
-      <c r="C8" s="15">
-        <v>0</v>
-      </c>
-      <c r="D8" s="15">
-        <v>0</v>
-      </c>
-      <c r="E8" s="15">
-        <v>0</v>
-      </c>
-      <c r="F8" s="15">
-        <v>0</v>
-      </c>
-      <c r="G8" s="15">
-        <v>0</v>
-      </c>
-      <c r="H8" s="15">
-        <v>0</v>
-      </c>
-      <c r="I8" s="15">
-        <v>0</v>
-      </c>
-      <c r="J8" s="15">
-        <v>0</v>
-      </c>
-      <c r="K8" s="15">
-        <v>0</v>
-      </c>
-      <c r="L8" s="15">
-        <v>0</v>
-      </c>
-      <c r="M8" s="15">
-        <v>0</v>
-      </c>
-      <c r="N8" s="15" t="str">
+      <c r="A8" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="19">
+        <v>0</v>
+      </c>
+      <c r="C8" s="19">
+        <v>0</v>
+      </c>
+      <c r="D8" s="19">
+        <v>0</v>
+      </c>
+      <c r="E8" s="19">
+        <v>0</v>
+      </c>
+      <c r="F8" s="19">
+        <v>0</v>
+      </c>
+      <c r="G8" s="19">
+        <v>0</v>
+      </c>
+      <c r="H8" s="19">
+        <v>0</v>
+      </c>
+      <c r="I8" s="19">
+        <v>0</v>
+      </c>
+      <c r="J8" s="19">
+        <v>0</v>
+      </c>
+      <c r="K8" s="19">
+        <v>0</v>
+      </c>
+      <c r="L8" s="19">
+        <v>0</v>
+      </c>
+      <c r="M8" s="19">
+        <v>0</v>
+      </c>
+      <c r="N8" s="19" t="str">
         <f>SUM(B8:M8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B9" s="22">
+      <c r="A9" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B9" s="26">
         <f>SUM(B4:B8)</f>
         <v>155900</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="26">
         <f>SUM(C4:C8)</f>
         <v>7460</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="26">
         <f>SUM(D4:D8)</f>
         <v>7460</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="26">
         <f>SUM(E4:E8)</f>
         <v>7460</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="26">
         <f>SUM(F4:F8)</f>
         <v>7460</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="26">
         <f>SUM(G4:G8)</f>
         <v>7460</v>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="26">
         <f>SUM(H4:H8)</f>
         <v>7460</v>
       </c>
-      <c r="I9" s="22">
+      <c r="I9" s="26">
         <f>SUM(I4:I8)</f>
         <v>7460</v>
       </c>
-      <c r="J9" s="22">
+      <c r="J9" s="26">
         <f>SUM(J4:J8)</f>
         <v>7460</v>
       </c>
-      <c r="K9" s="22">
+      <c r="K9" s="26">
         <f>SUM(K4:K8)</f>
         <v>7460</v>
       </c>
-      <c r="L9" s="22">
+      <c r="L9" s="26">
         <f>SUM(L4:L8)</f>
         <v>-1440</v>
       </c>
-      <c r="M9" s="22" t="str">
+      <c r="M9" s="26" t="str">
         <f>SUM(M4:M8)</f>
         <v>0</v>
       </c>
-      <c r="N9" s="22">
+      <c r="N9" s="26">
         <f>SUM(B9:M9)</f>
         <v>221600</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
+      <c r="A11" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B12" s="15">
+      <c r="A12" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" s="19">
         <v>5851</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="19">
         <v>5851</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="19">
         <v>5851</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="19">
         <v>5851</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="19">
         <v>5851</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="19">
         <v>5851</v>
       </c>
-      <c r="H12" s="15">
+      <c r="H12" s="19">
         <v>5851</v>
       </c>
-      <c r="I12" s="15">
+      <c r="I12" s="19">
         <v>5851</v>
       </c>
-      <c r="J12" s="15">
+      <c r="J12" s="19">
         <v>5851</v>
       </c>
-      <c r="K12" s="15">
+      <c r="K12" s="19">
         <v>5851</v>
       </c>
-      <c r="L12" s="15">
-        <v>0</v>
-      </c>
-      <c r="M12" s="15">
-        <v>0</v>
-      </c>
-      <c r="N12" s="15">
+      <c r="L12" s="19">
+        <v>0</v>
+      </c>
+      <c r="M12" s="19">
+        <v>0</v>
+      </c>
+      <c r="N12" s="19">
         <f>SUM(B12:M12)</f>
         <v>58506</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B13" s="15">
+      <c r="A13" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" s="19">
         <v>4787</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="19">
         <v>4787</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="19">
         <v>4787</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="19">
         <v>4787</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="19">
         <v>4787</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="19">
         <v>4787</v>
       </c>
-      <c r="H13" s="15">
+      <c r="H13" s="19">
         <v>4787</v>
       </c>
-      <c r="I13" s="15">
+      <c r="I13" s="19">
         <v>4787</v>
       </c>
-      <c r="J13" s="15">
+      <c r="J13" s="19">
         <v>4787</v>
       </c>
-      <c r="K13" s="15">
+      <c r="K13" s="19">
         <v>4787</v>
       </c>
-      <c r="L13" s="15">
-        <v>0</v>
-      </c>
-      <c r="M13" s="15">
-        <v>0</v>
-      </c>
-      <c r="N13" s="15">
+      <c r="L13" s="19">
+        <v>0</v>
+      </c>
+      <c r="M13" s="19">
+        <v>0</v>
+      </c>
+      <c r="N13" s="19">
         <f>SUM(B13:M13)</f>
         <v>47869</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B14" s="15">
+      <c r="A14" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" s="19">
         <v>1256</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="19">
         <v>1256</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="19">
         <v>1256</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="19">
         <v>1256</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="19">
         <v>1256</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="19">
         <v>1256</v>
       </c>
-      <c r="H14" s="15">
+      <c r="H14" s="19">
         <v>1256</v>
       </c>
-      <c r="I14" s="15">
+      <c r="I14" s="19">
         <v>1256</v>
       </c>
-      <c r="J14" s="15">
+      <c r="J14" s="19">
         <v>1256</v>
       </c>
-      <c r="K14" s="15">
+      <c r="K14" s="19">
         <v>1256</v>
       </c>
-      <c r="L14" s="15">
-        <v>0</v>
-      </c>
-      <c r="M14" s="15">
-        <v>0</v>
-      </c>
-      <c r="N14" s="15">
+      <c r="L14" s="19">
+        <v>0</v>
+      </c>
+      <c r="M14" s="19">
+        <v>0</v>
+      </c>
+      <c r="N14" s="19">
         <f>SUM(B14:M14)</f>
         <v>12559</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B15" s="22">
+      <c r="A15" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B15" s="26">
         <f>SUM(B12:B14)</f>
         <v>11893</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="26">
         <f>SUM(C12:C14)</f>
         <v>11893</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="26">
         <f>SUM(D12:D14)</f>
         <v>11893</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="26">
         <f>SUM(E12:E14)</f>
         <v>11893</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="26">
         <f>SUM(F12:F14)</f>
         <v>11893</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="26">
         <f>SUM(G12:G14)</f>
         <v>11893</v>
       </c>
-      <c r="H15" s="22">
+      <c r="H15" s="26">
         <f>SUM(H12:H14)</f>
         <v>11893</v>
       </c>
-      <c r="I15" s="22">
+      <c r="I15" s="26">
         <f>SUM(I12:I14)</f>
         <v>11893</v>
       </c>
-      <c r="J15" s="22">
+      <c r="J15" s="26">
         <f>SUM(J12:J14)</f>
         <v>11893</v>
       </c>
-      <c r="K15" s="22">
+      <c r="K15" s="26">
         <f>SUM(K12:K14)</f>
         <v>11893</v>
       </c>
-      <c r="L15" s="22" t="str">
+      <c r="L15" s="26" t="str">
         <f>SUM(L12:L14)</f>
         <v>0</v>
       </c>
-      <c r="M15" s="22" t="str">
+      <c r="M15" s="26" t="str">
         <f>SUM(M12:M14)</f>
         <v>0</v>
       </c>
-      <c r="N15" s="22">
+      <c r="N15" s="26">
         <f>SUM(B15:M15)</f>
         <v>118934</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
+      <c r="A17" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
+      <c r="A18" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="B19" s="15">
+      <c r="A19" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="B19" s="19">
         <v>500</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="19">
         <v>500</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="19">
         <v>500</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="19">
         <v>500</v>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="19">
         <v>500</v>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="19">
         <v>500</v>
       </c>
-      <c r="H19" s="15">
+      <c r="H19" s="19">
         <v>500</v>
       </c>
-      <c r="I19" s="15">
+      <c r="I19" s="19">
         <v>500</v>
       </c>
-      <c r="J19" s="15">
+      <c r="J19" s="19">
         <v>500</v>
       </c>
-      <c r="K19" s="15">
+      <c r="K19" s="19">
         <v>500</v>
       </c>
-      <c r="L19" s="15">
-        <v>0</v>
-      </c>
-      <c r="M19" s="15">
-        <v>0</v>
-      </c>
-      <c r="N19" s="15">
+      <c r="L19" s="19">
+        <v>0</v>
+      </c>
+      <c r="M19" s="19">
+        <v>0</v>
+      </c>
+      <c r="N19" s="19">
         <f>SUM(B19:M19)</f>
         <v>5000</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="B20" s="24">
+      <c r="A20" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" s="28">
         <v>500</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="28">
         <v>500</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="28">
         <v>500</v>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="28">
         <v>500</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="28">
         <v>500</v>
       </c>
-      <c r="G20" s="24">
+      <c r="G20" s="28">
         <v>500</v>
       </c>
-      <c r="H20" s="24">
+      <c r="H20" s="28">
         <v>500</v>
       </c>
-      <c r="I20" s="24">
+      <c r="I20" s="28">
         <v>500</v>
       </c>
-      <c r="J20" s="24">
+      <c r="J20" s="28">
         <v>500</v>
       </c>
-      <c r="K20" s="24">
+      <c r="K20" s="28">
         <v>500</v>
       </c>
-      <c r="L20" s="24">
-        <v>0</v>
-      </c>
-      <c r="M20" s="24">
-        <v>0</v>
-      </c>
-      <c r="N20" s="24">
+      <c r="L20" s="28">
+        <v>0</v>
+      </c>
+      <c r="M20" s="28">
+        <v>0</v>
+      </c>
+      <c r="N20" s="28">
         <f>SUM(B20:M20)</f>
         <v>5000</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
+      <c r="A21" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="B22" s="15">
+      <c r="A22" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="B22" s="19">
         <v>300</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="19">
         <v>300</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="19">
         <v>300</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="19">
         <v>300</v>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="19">
         <v>300</v>
       </c>
-      <c r="G22" s="15">
+      <c r="G22" s="19">
         <v>300</v>
       </c>
-      <c r="H22" s="15">
+      <c r="H22" s="19">
         <v>300</v>
       </c>
-      <c r="I22" s="15">
+      <c r="I22" s="19">
         <v>300</v>
       </c>
-      <c r="J22" s="15">
+      <c r="J22" s="19">
         <v>300</v>
       </c>
-      <c r="K22" s="15">
+      <c r="K22" s="19">
         <v>300</v>
       </c>
-      <c r="L22" s="15">
-        <v>0</v>
-      </c>
-      <c r="M22" s="15">
-        <v>0</v>
-      </c>
-      <c r="N22" s="15">
+      <c r="L22" s="19">
+        <v>0</v>
+      </c>
+      <c r="M22" s="19">
+        <v>0</v>
+      </c>
+      <c r="N22" s="19">
         <f>SUM(B22:M22)</f>
         <v>3000</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="B23" s="24">
+      <c r="A23" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" s="28">
         <v>300</v>
       </c>
-      <c r="C23" s="24">
+      <c r="C23" s="28">
         <v>300</v>
       </c>
-      <c r="D23" s="24">
+      <c r="D23" s="28">
         <v>300</v>
       </c>
-      <c r="E23" s="24">
+      <c r="E23" s="28">
         <v>300</v>
       </c>
-      <c r="F23" s="24">
+      <c r="F23" s="28">
         <v>300</v>
       </c>
-      <c r="G23" s="24">
+      <c r="G23" s="28">
         <v>300</v>
       </c>
-      <c r="H23" s="24">
+      <c r="H23" s="28">
         <v>300</v>
       </c>
-      <c r="I23" s="24">
+      <c r="I23" s="28">
         <v>300</v>
       </c>
-      <c r="J23" s="24">
+      <c r="J23" s="28">
         <v>300</v>
       </c>
-      <c r="K23" s="24">
+      <c r="K23" s="28">
         <v>300</v>
       </c>
-      <c r="L23" s="24">
-        <v>0</v>
-      </c>
-      <c r="M23" s="24">
-        <v>0</v>
-      </c>
-      <c r="N23" s="24">
+      <c r="L23" s="28">
+        <v>0</v>
+      </c>
+      <c r="M23" s="28">
+        <v>0</v>
+      </c>
+      <c r="N23" s="28">
         <f>SUM(B23:M23)</f>
         <v>3000</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
+      <c r="A24" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="B25" s="15">
+      <c r="A25" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="B25" s="19">
         <v>2500</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="19">
         <v>2500</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="19">
         <v>2500</v>
       </c>
-      <c r="E25" s="15">
+      <c r="E25" s="19">
         <v>2500</v>
       </c>
-      <c r="F25" s="15">
+      <c r="F25" s="19">
         <v>2500</v>
       </c>
-      <c r="G25" s="15">
+      <c r="G25" s="19">
         <v>2500</v>
       </c>
-      <c r="H25" s="15">
+      <c r="H25" s="19">
         <v>2500</v>
       </c>
-      <c r="I25" s="15">
+      <c r="I25" s="19">
         <v>2500</v>
       </c>
-      <c r="J25" s="15">
+      <c r="J25" s="19">
         <v>2500</v>
       </c>
-      <c r="K25" s="15">
+      <c r="K25" s="19">
         <v>2500</v>
       </c>
-      <c r="L25" s="15">
-        <v>0</v>
-      </c>
-      <c r="M25" s="15">
-        <v>0</v>
-      </c>
-      <c r="N25" s="15">
+      <c r="L25" s="19">
+        <v>0</v>
+      </c>
+      <c r="M25" s="19">
+        <v>0</v>
+      </c>
+      <c r="N25" s="19">
         <f>SUM(B25:M25)</f>
         <v>25000</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B26" s="15">
+      <c r="A26" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="B26" s="19">
         <v>300</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="19">
         <v>300</v>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="19">
         <v>300</v>
       </c>
-      <c r="E26" s="15">
+      <c r="E26" s="19">
         <v>300</v>
       </c>
-      <c r="F26" s="15">
+      <c r="F26" s="19">
         <v>300</v>
       </c>
-      <c r="G26" s="15">
+      <c r="G26" s="19">
         <v>300</v>
       </c>
-      <c r="H26" s="15">
+      <c r="H26" s="19">
         <v>300</v>
       </c>
-      <c r="I26" s="15">
+      <c r="I26" s="19">
         <v>300</v>
       </c>
-      <c r="J26" s="15">
+      <c r="J26" s="19">
         <v>300</v>
       </c>
-      <c r="K26" s="15">
+      <c r="K26" s="19">
         <v>300</v>
       </c>
-      <c r="L26" s="15">
-        <v>0</v>
-      </c>
-      <c r="M26" s="15">
-        <v>0</v>
-      </c>
-      <c r="N26" s="15">
+      <c r="L26" s="19">
+        <v>0</v>
+      </c>
+      <c r="M26" s="19">
+        <v>0</v>
+      </c>
+      <c r="N26" s="19">
         <f>SUM(B26:M26)</f>
         <v>3000</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="B27" s="15">
+      <c r="A27" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="B27" s="19">
         <v>200</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="19">
         <v>200</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="19">
         <v>200</v>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="19">
         <v>200</v>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="19">
         <v>200</v>
       </c>
-      <c r="G27" s="15">
+      <c r="G27" s="19">
         <v>200</v>
       </c>
-      <c r="H27" s="15">
+      <c r="H27" s="19">
         <v>200</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="19">
         <v>200</v>
       </c>
-      <c r="J27" s="15">
+      <c r="J27" s="19">
         <v>200</v>
       </c>
-      <c r="K27" s="15">
+      <c r="K27" s="19">
         <v>200</v>
       </c>
-      <c r="L27" s="15">
-        <v>0</v>
-      </c>
-      <c r="M27" s="15">
-        <v>0</v>
-      </c>
-      <c r="N27" s="15">
+      <c r="L27" s="19">
+        <v>0</v>
+      </c>
+      <c r="M27" s="19">
+        <v>0</v>
+      </c>
+      <c r="N27" s="19">
         <f>SUM(B27:M27)</f>
         <v>2000</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="B28" s="24">
+      <c r="A28" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="B28" s="28">
         <v>3000</v>
       </c>
-      <c r="C28" s="24">
+      <c r="C28" s="28">
         <v>3000</v>
       </c>
-      <c r="D28" s="24">
+      <c r="D28" s="28">
         <v>3000</v>
       </c>
-      <c r="E28" s="24">
+      <c r="E28" s="28">
         <v>3000</v>
       </c>
-      <c r="F28" s="24">
+      <c r="F28" s="28">
         <v>3000</v>
       </c>
-      <c r="G28" s="24">
+      <c r="G28" s="28">
         <v>3000</v>
       </c>
-      <c r="H28" s="24">
+      <c r="H28" s="28">
         <v>3000</v>
       </c>
-      <c r="I28" s="24">
+      <c r="I28" s="28">
         <v>3000</v>
       </c>
-      <c r="J28" s="24">
+      <c r="J28" s="28">
         <v>3000</v>
       </c>
-      <c r="K28" s="24">
+      <c r="K28" s="28">
         <v>3000</v>
       </c>
-      <c r="L28" s="24">
-        <v>0</v>
-      </c>
-      <c r="M28" s="24">
-        <v>0</v>
-      </c>
-      <c r="N28" s="24">
+      <c r="L28" s="28">
+        <v>0</v>
+      </c>
+      <c r="M28" s="28">
+        <v>0</v>
+      </c>
+      <c r="N28" s="28">
         <f>SUM(B28:M28)</f>
         <v>30000</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
+      <c r="A29" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="B30" s="15">
+      <c r="A30" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="B30" s="19">
         <v>250</v>
       </c>
-      <c r="C30" s="15">
+      <c r="C30" s="19">
         <v>250</v>
       </c>
-      <c r="D30" s="15">
+      <c r="D30" s="19">
         <v>250</v>
       </c>
-      <c r="E30" s="15">
+      <c r="E30" s="19">
         <v>250</v>
       </c>
-      <c r="F30" s="15">
+      <c r="F30" s="19">
         <v>250</v>
       </c>
-      <c r="G30" s="15">
+      <c r="G30" s="19">
         <v>250</v>
       </c>
-      <c r="H30" s="15">
+      <c r="H30" s="19">
         <v>250</v>
       </c>
-      <c r="I30" s="15">
+      <c r="I30" s="19">
         <v>250</v>
       </c>
-      <c r="J30" s="15">
+      <c r="J30" s="19">
         <v>250</v>
       </c>
-      <c r="K30" s="15">
+      <c r="K30" s="19">
         <v>250</v>
       </c>
-      <c r="L30" s="15">
-        <v>0</v>
-      </c>
-      <c r="M30" s="15">
-        <v>0</v>
-      </c>
-      <c r="N30" s="15">
+      <c r="L30" s="19">
+        <v>0</v>
+      </c>
+      <c r="M30" s="19">
+        <v>0</v>
+      </c>
+      <c r="N30" s="19">
         <f>SUM(B30:M30)</f>
         <v>2500</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="B31" s="24">
+      <c r="A31" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="B31" s="28">
         <v>250</v>
       </c>
-      <c r="C31" s="24">
+      <c r="C31" s="28">
         <v>250</v>
       </c>
-      <c r="D31" s="24">
+      <c r="D31" s="28">
         <v>250</v>
       </c>
-      <c r="E31" s="24">
+      <c r="E31" s="28">
         <v>250</v>
       </c>
-      <c r="F31" s="24">
+      <c r="F31" s="28">
         <v>250</v>
       </c>
-      <c r="G31" s="24">
+      <c r="G31" s="28">
         <v>250</v>
       </c>
-      <c r="H31" s="24">
+      <c r="H31" s="28">
         <v>250</v>
       </c>
-      <c r="I31" s="24">
+      <c r="I31" s="28">
         <v>250</v>
       </c>
-      <c r="J31" s="24">
+      <c r="J31" s="28">
         <v>250</v>
       </c>
-      <c r="K31" s="24">
+      <c r="K31" s="28">
         <v>250</v>
       </c>
-      <c r="L31" s="24">
-        <v>0</v>
-      </c>
-      <c r="M31" s="24">
-        <v>0</v>
-      </c>
-      <c r="N31" s="24">
+      <c r="L31" s="28">
+        <v>0</v>
+      </c>
+      <c r="M31" s="28">
+        <v>0</v>
+      </c>
+      <c r="N31" s="28">
         <f>SUM(B31:M31)</f>
         <v>2500</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B32" s="22">
+      <c r="A32" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="B32" s="26">
         <f>B20+B23+B28+B31</f>
         <v>4050</v>
       </c>
-      <c r="C32" s="22">
+      <c r="C32" s="26">
         <f>C20+C23+C28+C31</f>
         <v>4050</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="26">
         <f>D20+D23+D28+D31</f>
         <v>4050</v>
       </c>
-      <c r="E32" s="22">
+      <c r="E32" s="26">
         <f>E20+E23+E28+E31</f>
         <v>4050</v>
       </c>
-      <c r="F32" s="22">
+      <c r="F32" s="26">
         <f>F20+F23+F28+F31</f>
         <v>4050</v>
       </c>
-      <c r="G32" s="22">
+      <c r="G32" s="26">
         <f>G20+G23+G28+G31</f>
         <v>4050</v>
       </c>
-      <c r="H32" s="22">
+      <c r="H32" s="26">
         <f>H20+H23+H28+H31</f>
         <v>4050</v>
       </c>
-      <c r="I32" s="22">
+      <c r="I32" s="26">
         <f>I20+I23+I28+I31</f>
         <v>4050</v>
       </c>
-      <c r="J32" s="22">
+      <c r="J32" s="26">
         <f>J20+J23+J28+J31</f>
         <v>4050</v>
       </c>
-      <c r="K32" s="22">
+      <c r="K32" s="26">
         <f>K20+K23+K28+K31</f>
         <v>4050</v>
       </c>
-      <c r="L32" s="22" t="str">
+      <c r="L32" s="26" t="str">
         <f>L20+L23+L28+L31</f>
         <v>0</v>
       </c>
-      <c r="M32" s="22" t="str">
+      <c r="M32" s="26" t="str">
         <f>M20+M23+M28+M31</f>
         <v>0</v>
       </c>
-      <c r="N32" s="22">
+      <c r="N32" s="26">
         <f>SUM(B32:M32)</f>
         <v>40500</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="B34" s="15">
+      <c r="A34" s="24" t="s">
+        <v>198</v>
+      </c>
+      <c r="B34" s="19">
         <v>580</v>
       </c>
-      <c r="C34" s="15">
+      <c r="C34" s="19">
         <v>580</v>
       </c>
-      <c r="D34" s="15">
+      <c r="D34" s="19">
         <v>580</v>
       </c>
-      <c r="E34" s="15">
+      <c r="E34" s="19">
         <v>580</v>
       </c>
-      <c r="F34" s="15">
+      <c r="F34" s="19">
         <v>580</v>
       </c>
-      <c r="G34" s="15">
+      <c r="G34" s="19">
         <v>580</v>
       </c>
-      <c r="H34" s="15">
+      <c r="H34" s="19">
         <v>580</v>
       </c>
-      <c r="I34" s="15">
+      <c r="I34" s="19">
         <v>580</v>
       </c>
-      <c r="J34" s="15">
+      <c r="J34" s="19">
         <v>580</v>
       </c>
-      <c r="K34" s="15">
+      <c r="K34" s="19">
         <v>580</v>
       </c>
-      <c r="L34" s="15">
+      <c r="L34" s="19">
         <v>580</v>
       </c>
-      <c r="M34" s="15">
+      <c r="M34" s="19">
         <v>580</v>
       </c>
-      <c r="N34" s="15">
+      <c r="N34" s="19">
         <f>SUM(B34:M34)</f>
         <v>6960</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="6"/>
-      <c r="M36" s="6"/>
-      <c r="N36" s="6"/>
+      <c r="A36" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="10"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="B37" s="24">
+      <c r="A37" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="B37" s="28">
         <f>B15+B32+B34</f>
         <v>16523</v>
       </c>
-      <c r="C37" s="24">
+      <c r="C37" s="28">
         <f>C15+C32+C34</f>
         <v>16523</v>
       </c>
-      <c r="D37" s="24">
+      <c r="D37" s="28">
         <f>D15+D32+D34</f>
         <v>16523</v>
       </c>
-      <c r="E37" s="24">
+      <c r="E37" s="28">
         <f>E15+E32+E34</f>
         <v>16523</v>
       </c>
-      <c r="F37" s="24">
+      <c r="F37" s="28">
         <f>F15+F32+F34</f>
         <v>16523</v>
       </c>
-      <c r="G37" s="24">
+      <c r="G37" s="28">
         <f>G15+G32+G34</f>
         <v>16523</v>
       </c>
-      <c r="H37" s="24">
+      <c r="H37" s="28">
         <f>H15+H32+H34</f>
         <v>16523</v>
       </c>
-      <c r="I37" s="24">
+      <c r="I37" s="28">
         <f>I15+I32+I34</f>
         <v>16523</v>
       </c>
-      <c r="J37" s="24">
+      <c r="J37" s="28">
         <f>J15+J32+J34</f>
         <v>16523</v>
       </c>
-      <c r="K37" s="24">
+      <c r="K37" s="28">
         <f>K15+K32+K34</f>
         <v>16523</v>
       </c>
-      <c r="L37" s="24">
+      <c r="L37" s="28">
         <f>L15+L32+L34</f>
         <v>580</v>
       </c>
-      <c r="M37" s="24">
+      <c r="M37" s="28">
         <f>M15+M32+M34</f>
         <v>580</v>
       </c>
-      <c r="N37" s="24">
+      <c r="N37" s="28">
         <f>SUM(B37:M37)</f>
         <v>166390</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="B38" s="24">
+      <c r="A38" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="B38" s="28">
         <f>B9-B37</f>
         <v>139377</v>
       </c>
-      <c r="C38" s="24">
+      <c r="C38" s="28">
         <f>C9-C37</f>
         <v>-9063</v>
       </c>
-      <c r="D38" s="24">
+      <c r="D38" s="28">
         <f>D9-D37</f>
         <v>-9063</v>
       </c>
-      <c r="E38" s="24">
+      <c r="E38" s="28">
         <f>E9-E37</f>
         <v>-9063</v>
       </c>
-      <c r="F38" s="24">
+      <c r="F38" s="28">
         <f>F9-F37</f>
         <v>-9063</v>
       </c>
-      <c r="G38" s="24">
+      <c r="G38" s="28">
         <f>G9-G37</f>
         <v>-9063</v>
       </c>
-      <c r="H38" s="24">
+      <c r="H38" s="28">
         <f>H9-H37</f>
         <v>-9063</v>
       </c>
-      <c r="I38" s="24">
+      <c r="I38" s="28">
         <f>I9-I37</f>
         <v>-9063</v>
       </c>
-      <c r="J38" s="24">
+      <c r="J38" s="28">
         <f>J9-J37</f>
         <v>-9063</v>
       </c>
-      <c r="K38" s="24">
+      <c r="K38" s="28">
         <f>K9-K37</f>
         <v>-9063</v>
       </c>
-      <c r="L38" s="24">
+      <c r="L38" s="28">
         <f>L9-L37</f>
         <v>-2020</v>
       </c>
-      <c r="M38" s="24">
+      <c r="M38" s="28">
         <f>M9-M37</f>
         <v>-580</v>
       </c>
-      <c r="N38" s="24">
+      <c r="N38" s="28">
         <f>SUM(B38:M38)</f>
         <v>55210</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="B39" s="24">
+      <c r="A39" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="B39" s="28">
         <f>0+B38</f>
         <v>139377</v>
       </c>
-      <c r="C39" s="24">
+      <c r="C39" s="28">
         <f>B39+C38</f>
         <v>130314</v>
       </c>
-      <c r="D39" s="24">
+      <c r="D39" s="28">
         <f>C39+D38</f>
         <v>121251</v>
       </c>
-      <c r="E39" s="24">
+      <c r="E39" s="28">
         <f>D39+E38</f>
         <v>112188</v>
       </c>
-      <c r="F39" s="24">
+      <c r="F39" s="28">
         <f>E39+F38</f>
         <v>103125</v>
       </c>
-      <c r="G39" s="24">
+      <c r="G39" s="28">
         <f>F39+G38</f>
         <v>94062</v>
       </c>
-      <c r="H39" s="24">
+      <c r="H39" s="28">
         <f>G39+H38</f>
         <v>84999</v>
       </c>
-      <c r="I39" s="24">
+      <c r="I39" s="28">
         <f>H39+I38</f>
         <v>75936</v>
       </c>
-      <c r="J39" s="24">
+      <c r="J39" s="28">
         <f>I39+J38</f>
         <v>66873</v>
       </c>
-      <c r="K39" s="24">
+      <c r="K39" s="28">
         <f>J39+K38</f>
         <v>57810</v>
       </c>
-      <c r="L39" s="24">
+      <c r="L39" s="28">
         <f>K39+L38</f>
         <v>55790</v>
       </c>
-      <c r="M39" s="24">
+      <c r="M39" s="28">
         <f>L39+M38</f>
         <v>55210</v>
       </c>
-      <c r="N39" s="24">
+      <c r="N39" s="28">
         <f>M39</f>
         <v>55210</v>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
+      <c r="A41" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="B41" s="10"/>
+      <c r="C41" s="10"/>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="B42" s="15">
+      <c r="A42" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B42" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="B43" s="24">
+      <c r="A43" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="B43" s="28">
         <f>M39</f>
         <v>55210</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="B44" s="15">
+      <c r="A44" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="B44" s="19">
         <f>MIN(B39:M39)</f>
         <v>55210</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="B46" s="18"/>
-      <c r="C46" s="18"/>
-      <c r="D46" s="18"/>
-      <c r="E46" s="18"/>
-      <c r="F46" s="18"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="18"/>
-      <c r="I46" s="18"/>
-      <c r="J46" s="18"/>
-      <c r="K46" s="18"/>
-      <c r="L46" s="18"/>
-      <c r="M46" s="18"/>
-      <c r="N46" s="18"/>
+      <c r="A46" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="B46" s="22"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="22"/>
+      <c r="G46" s="22"/>
+      <c r="H46" s="22"/>
+      <c r="I46" s="22"/>
+      <c r="J46" s="22"/>
+      <c r="K46" s="22"/>
+      <c r="L46" s="22"/>
+      <c r="M46" s="22"/>
+      <c r="N46" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5113,6 +5335,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF0D9488"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:G33"/>
@@ -5126,7 +5349,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -5135,466 +5358,466 @@
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
+      <c r="B3" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>206</v>
+      <c r="B5" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="C6" s="34">
+      <c r="B6" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="C6" s="38">
         <v>12</v>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="38">
         <v>18</v>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="38">
         <v>22</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="38">
         <v>25</v>
       </c>
-      <c r="G6" s="34">
+      <c r="G6" s="38">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="C7" s="39">
+        <v>221600</v>
+      </c>
+      <c r="D7" s="39">
+        <v>338147.49999999994</v>
+      </c>
+      <c r="E7" s="39">
+        <v>422456.3124999999</v>
+      </c>
+      <c r="F7" s="39">
+        <v>491331.3476562498</v>
+      </c>
+      <c r="G7" s="39">
+        <v>503614.631347656</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C8" s="39">
+        <v>118934.16666666667</v>
+      </c>
+      <c r="D8" s="39">
+        <v>147002.63</v>
+      </c>
+      <c r="E8" s="39">
+        <v>151412.7089</v>
+      </c>
+      <c r="F8" s="39">
+        <v>155955.090167</v>
+      </c>
+      <c r="G8" s="39">
+        <v>160633.74287201</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C9" s="39">
+        <v>48600</v>
+      </c>
+      <c r="D9" s="39">
+        <v>54885</v>
+      </c>
+      <c r="E9" s="39">
+        <v>59773.625</v>
+      </c>
+      <c r="F9" s="39">
+        <v>64011.63812499999</v>
+      </c>
+      <c r="G9" s="39">
+        <v>65775.83812812499</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="C10" s="39">
+        <v>6959.808550594178</v>
+      </c>
+      <c r="D10" s="39">
+        <v>6959.808550594178</v>
+      </c>
+      <c r="E10" s="39">
+        <v>6959.808550594178</v>
+      </c>
+      <c r="F10" s="39">
+        <v>6959.808550594178</v>
+      </c>
+      <c r="G10" s="39">
+        <v>6959.808550594178</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C11" s="40">
+        <v>47106.02478273915</v>
+      </c>
+      <c r="D11" s="40">
+        <v>129300.06144940577</v>
+      </c>
+      <c r="E11" s="40">
+        <v>204310.17004940574</v>
+      </c>
+      <c r="F11" s="40">
+        <v>264404.8108136556</v>
+      </c>
+      <c r="G11" s="40">
+        <v>270245.2417969268</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="C12" s="40">
+        <v>47106.02478273915</v>
+      </c>
+      <c r="D12" s="40">
+        <v>176406.0862321449</v>
+      </c>
+      <c r="E12" s="40">
+        <v>380716.2562815506</v>
+      </c>
+      <c r="F12" s="40">
+        <v>645121.0670952062</v>
+      </c>
+      <c r="G12" s="40">
+        <v>915366.3088921331</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="C13" s="41">
+        <v>0.21257231400153045</v>
+      </c>
+      <c r="D13" s="41">
+        <v>0.3823776944954666</v>
+      </c>
+      <c r="E13" s="41">
+        <v>0.4836243748858784</v>
+      </c>
+      <c r="F13" s="41">
+        <v>0.5381395102814428</v>
+      </c>
+      <c r="G13" s="41">
+        <v>0.5366111804054611</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="C14" s="39">
+        <v>18466.666666666668</v>
+      </c>
+      <c r="D14" s="39">
+        <v>18785.97222222222</v>
+      </c>
+      <c r="E14" s="39">
+        <v>19202.559659090904</v>
+      </c>
+      <c r="F14" s="39">
+        <v>19653.253906249993</v>
+      </c>
+      <c r="G14" s="39">
+        <v>20144.58525390624</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="C15" s="41">
+        <v>0.5367065282791817</v>
+      </c>
+      <c r="D15" s="41">
+        <v>0.4347293119127009</v>
+      </c>
+      <c r="E15" s="41">
+        <v>0.3584103359800075</v>
+      </c>
+      <c r="F15" s="41">
+        <v>0.31741327092386307</v>
+      </c>
+      <c r="G15" s="41">
+        <v>0.31896162834300396</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="C16" s="41">
+        <v>0.0657942238267148</v>
+      </c>
+      <c r="D16" s="41">
+        <v>0.04869324776909486</v>
+      </c>
+      <c r="E16" s="41">
+        <v>0.0424471997918128</v>
+      </c>
+      <c r="F16" s="41">
+        <v>0.03908460457307385</v>
+      </c>
+      <c r="G16" s="41">
+        <v>0.03918224414098794</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="24" t="s">
+        <v>222</v>
+      </c>
+      <c r="C17" s="41">
+        <v>0.2439793922984356</v>
+      </c>
+      <c r="D17" s="41">
+        <v>0.40295986219031626</v>
+      </c>
+      <c r="E17" s="41">
+        <v>0.5000989980472832</v>
+      </c>
+      <c r="F17" s="41">
+        <v>0.5523047138325573</v>
+      </c>
+      <c r="G17" s="41">
+        <v>0.5504308911870363</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="C18" s="42">
+        <v>7.768293185121821</v>
+      </c>
+      <c r="D18" s="42">
+        <v>19.57810606562835</v>
+      </c>
+      <c r="E18" s="42">
+        <v>30.35571698045677</v>
+      </c>
+      <c r="F18" s="42">
+        <v>38.99024195731399</v>
+      </c>
+      <c r="G18" s="42">
+        <v>39.82940742297506</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="C19" s="43" t="s">
         <v>208</v>
       </c>
-      <c r="C7" s="35">
-        <v>221600</v>
-      </c>
-      <c r="D7" s="35">
-        <v>338147.49999999994</v>
-      </c>
-      <c r="E7" s="35">
-        <v>422456.3124999999</v>
-      </c>
-      <c r="F7" s="35">
-        <v>491331.3476562498</v>
-      </c>
-      <c r="G7" s="35">
-        <v>503614.631347656</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C8" s="35">
-        <v>118934.16666666667</v>
-      </c>
-      <c r="D8" s="35">
-        <v>147002.63</v>
-      </c>
-      <c r="E8" s="35">
-        <v>151412.7089</v>
-      </c>
-      <c r="F8" s="35">
-        <v>155955.090167</v>
-      </c>
-      <c r="G8" s="35">
-        <v>160633.74287201</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="C9" s="35">
-        <v>48600</v>
-      </c>
-      <c r="D9" s="35">
-        <v>54885</v>
-      </c>
-      <c r="E9" s="35">
-        <v>59773.625</v>
-      </c>
-      <c r="F9" s="35">
-        <v>64011.63812499999</v>
-      </c>
-      <c r="G9" s="35">
-        <v>65775.83812812499</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" s="35">
-        <v>6959.808550594178</v>
-      </c>
-      <c r="D10" s="35">
-        <v>6959.808550594178</v>
-      </c>
-      <c r="E10" s="35">
-        <v>6959.808550594178</v>
-      </c>
-      <c r="F10" s="35">
-        <v>6959.808550594178</v>
-      </c>
-      <c r="G10" s="35">
-        <v>6959.808550594178</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="C11" s="36">
-        <v>47106.02478273915</v>
-      </c>
-      <c r="D11" s="36">
-        <v>129300.06144940577</v>
-      </c>
-      <c r="E11" s="36">
-        <v>204310.17004940574</v>
-      </c>
-      <c r="F11" s="36">
-        <v>264404.8108136556</v>
-      </c>
-      <c r="G11" s="36">
-        <v>270245.2417969268</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="C12" s="36">
-        <v>47106.02478273915</v>
-      </c>
-      <c r="D12" s="36">
-        <v>176406.0862321449</v>
-      </c>
-      <c r="E12" s="36">
-        <v>380716.2562815506</v>
-      </c>
-      <c r="F12" s="36">
-        <v>645121.0670952062</v>
-      </c>
-      <c r="G12" s="36">
-        <v>915366.3088921331</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="C13" s="37">
-        <v>0.21257231400153045</v>
-      </c>
-      <c r="D13" s="37">
-        <v>0.3823776944954666</v>
-      </c>
-      <c r="E13" s="37">
-        <v>0.4836243748858784</v>
-      </c>
-      <c r="F13" s="37">
-        <v>0.5381395102814428</v>
-      </c>
-      <c r="G13" s="37">
-        <v>0.5366111804054611</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="C14" s="35">
-        <v>18466.666666666668</v>
-      </c>
-      <c r="D14" s="35">
-        <v>18785.97222222222</v>
-      </c>
-      <c r="E14" s="35">
-        <v>19202.559659090904</v>
-      </c>
-      <c r="F14" s="35">
-        <v>19653.253906249993</v>
-      </c>
-      <c r="G14" s="35">
-        <v>20144.58525390624</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="C15" s="37">
-        <v>0.5367065282791817</v>
-      </c>
-      <c r="D15" s="37">
-        <v>0.4347293119127009</v>
-      </c>
-      <c r="E15" s="37">
-        <v>0.3584103359800075</v>
-      </c>
-      <c r="F15" s="37">
-        <v>0.31741327092386307</v>
-      </c>
-      <c r="G15" s="37">
-        <v>0.31896162834300396</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="C16" s="37">
-        <v>0.0657942238267148</v>
-      </c>
-      <c r="D16" s="37">
-        <v>0.04869324776909486</v>
-      </c>
-      <c r="E16" s="37">
-        <v>0.0424471997918128</v>
-      </c>
-      <c r="F16" s="37">
-        <v>0.03908460457307385</v>
-      </c>
-      <c r="G16" s="37">
-        <v>0.03918224414098794</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="C17" s="37">
-        <v>0.2439793922984356</v>
-      </c>
-      <c r="D17" s="37">
-        <v>0.40295986219031626</v>
-      </c>
-      <c r="E17" s="37">
-        <v>0.5000989980472832</v>
-      </c>
-      <c r="F17" s="37">
-        <v>0.5523047138325573</v>
-      </c>
-      <c r="G17" s="37">
-        <v>0.5504308911870363</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="C18" s="38">
-        <v>7.768293185121821</v>
-      </c>
-      <c r="D18" s="38">
-        <v>19.57810606562835</v>
-      </c>
-      <c r="E18" s="38">
-        <v>30.35571698045677</v>
-      </c>
-      <c r="F18" s="38">
-        <v>38.99024195731399</v>
-      </c>
-      <c r="G18" s="38">
-        <v>39.82940742297506</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="C19" s="39" t="s">
-        <v>202</v>
-      </c>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="C20" s="39" t="s">
-        <v>220</v>
-      </c>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
+      <c r="B20" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="C20" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="G22" s="6"/>
+      <c r="B22" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="G22" s="10"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="40" t="s">
-        <v>225</v>
-      </c>
-      <c r="C23" s="41" t="s">
-        <v>226</v>
-      </c>
-      <c r="D23" s="42" t="s">
-        <v>227</v>
-      </c>
-      <c r="E23" s="42"/>
-      <c r="F23" s="43" t="s">
-        <v>228</v>
-      </c>
-      <c r="G23" s="43"/>
+      <c r="B23" s="44" t="s">
+        <v>231</v>
+      </c>
+      <c r="C23" s="45" t="s">
+        <v>232</v>
+      </c>
+      <c r="D23" s="46" t="s">
+        <v>233</v>
+      </c>
+      <c r="E23" s="46"/>
+      <c r="F23" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="G23" s="47"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="40" t="s">
-        <v>229</v>
-      </c>
-      <c r="C24" s="41" t="s">
-        <v>226</v>
-      </c>
-      <c r="D24" s="42" t="s">
-        <v>230</v>
-      </c>
-      <c r="E24" s="42"/>
-      <c r="F24" s="43" t="s">
-        <v>231</v>
-      </c>
-      <c r="G24" s="43"/>
+      <c r="B24" s="44" t="s">
+        <v>235</v>
+      </c>
+      <c r="C24" s="45" t="s">
+        <v>232</v>
+      </c>
+      <c r="D24" s="46" t="s">
+        <v>236</v>
+      </c>
+      <c r="E24" s="46"/>
+      <c r="F24" s="47" t="s">
+        <v>237</v>
+      </c>
+      <c r="G24" s="47"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="40" t="s">
+      <c r="B25" s="44" t="s">
+        <v>238</v>
+      </c>
+      <c r="C25" s="45" t="s">
         <v>232</v>
       </c>
-      <c r="C25" s="41" t="s">
-        <v>226</v>
-      </c>
-      <c r="D25" s="42" t="s">
-        <v>233</v>
-      </c>
-      <c r="E25" s="42"/>
-      <c r="F25" s="43" t="s">
-        <v>234</v>
-      </c>
-      <c r="G25" s="43"/>
+      <c r="D25" s="46" t="s">
+        <v>239</v>
+      </c>
+      <c r="E25" s="46"/>
+      <c r="F25" s="47" t="s">
+        <v>240</v>
+      </c>
+      <c r="G25" s="47"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="40" t="s">
-        <v>235</v>
-      </c>
-      <c r="C26" s="41" t="s">
-        <v>226</v>
-      </c>
-      <c r="D26" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="E26" s="42"/>
-      <c r="F26" s="43" t="s">
-        <v>237</v>
-      </c>
-      <c r="G26" s="43"/>
+      <c r="B26" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="C26" s="45" t="s">
+        <v>232</v>
+      </c>
+      <c r="D26" s="46" t="s">
+        <v>242</v>
+      </c>
+      <c r="E26" s="46"/>
+      <c r="F26" s="47" t="s">
+        <v>243</v>
+      </c>
+      <c r="G26" s="47"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="40" t="s">
-        <v>238</v>
-      </c>
-      <c r="C27" s="41" t="s">
-        <v>226</v>
-      </c>
-      <c r="D27" s="42" t="s">
-        <v>239</v>
-      </c>
-      <c r="E27" s="42"/>
-      <c r="F27" s="43" t="s">
-        <v>240</v>
-      </c>
-      <c r="G27" s="43"/>
+      <c r="B27" s="44" t="s">
+        <v>244</v>
+      </c>
+      <c r="C27" s="45" t="s">
+        <v>232</v>
+      </c>
+      <c r="D27" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="E27" s="46"/>
+      <c r="F27" s="47" t="s">
+        <v>246</v>
+      </c>
+      <c r="G27" s="47"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="40" t="s">
-        <v>241</v>
-      </c>
-      <c r="C28" s="41" t="s">
-        <v>226</v>
-      </c>
-      <c r="D28" s="42" t="s">
-        <v>242</v>
-      </c>
-      <c r="E28" s="42"/>
-      <c r="F28" s="43" t="s">
-        <v>243</v>
-      </c>
-      <c r="G28" s="43"/>
+      <c r="B28" s="44" t="s">
+        <v>247</v>
+      </c>
+      <c r="C28" s="45" t="s">
+        <v>232</v>
+      </c>
+      <c r="D28" s="46" t="s">
+        <v>248</v>
+      </c>
+      <c r="E28" s="46"/>
+      <c r="F28" s="47" t="s">
+        <v>249</v>
+      </c>
+      <c r="G28" s="47"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="40" t="s">
-        <v>244</v>
-      </c>
-      <c r="C29" s="41" t="s">
-        <v>226</v>
-      </c>
-      <c r="D29" s="42" t="s">
-        <v>245</v>
-      </c>
-      <c r="E29" s="42"/>
-      <c r="F29" s="43" t="s">
-        <v>246</v>
-      </c>
-      <c r="G29" s="43"/>
+      <c r="B29" s="44" t="s">
+        <v>250</v>
+      </c>
+      <c r="C29" s="45" t="s">
+        <v>232</v>
+      </c>
+      <c r="D29" s="46" t="s">
+        <v>251</v>
+      </c>
+      <c r="E29" s="46"/>
+      <c r="F29" s="47" t="s">
+        <v>252</v>
+      </c>
+      <c r="G29" s="47"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="40" t="s">
-        <v>247</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>248</v>
-      </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
+      <c r="B31" s="44" t="s">
+        <v>253</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="44" t="s">
-        <v>122</v>
-      </c>
-      <c r="C33" s="44"/>
-      <c r="D33" s="44"/>
-      <c r="E33" s="44"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="44"/>
+      <c r="B33" s="48" t="s">
+        <v>128</v>
+      </c>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -5621,6 +5844,83 @@
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="B33:G33"/>
   </mergeCells>
+  <conditionalFormatting sqref="C11:G11">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>C11&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>C11&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>C11&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12:G12">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>C12&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C12&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C12&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13:G13">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>C13&gt;=0.05</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>C13&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="3">
+      <formula>C13&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C15:G15">
+    <cfRule type="expression" dxfId="9" priority="1">
+      <formula>C15&lt;=0.55</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>C15&lt;=0.65</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="3">
+      <formula>C15&gt;0.65</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G16">
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>C16&lt;=0.15</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>C16&lt;=0.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="3">
+      <formula>C16&gt;0.25</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17:G17">
+    <cfRule type="expression" dxfId="15" priority="1">
+      <formula>C17&gt;=0.10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>C17&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="3">
+      <formula>C17&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18:G18">
+    <cfRule type="expression" dxfId="18" priority="1">
+      <formula>C18&gt;=1.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="2">
+      <formula>C18&gt;=1.0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="3">
+      <formula>C18&lt;1.0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>

--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="255">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -969,7 +969,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -981,6 +981,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1753,721 +1754,724 @@
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="13" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="13" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="13" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="14">
         <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="12" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="12" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="10"/>
+      <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="16">
         <v>12</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="16">
         <v>18</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="16">
         <v>22</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="16">
         <v>25</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="16">
         <v>25</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="17">
         <v>12000</v>
       </c>
-      <c r="E20" s="17">
-        <v>0</v>
-      </c>
-      <c r="F20" s="13">
+      <c r="E20" s="18">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
         <v>10</v>
       </c>
-      <c r="G20" s="17">
+      <c r="G20" s="18">
         <v>1</v>
       </c>
-      <c r="H20" s="11" t="s">
+      <c r="H20" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="17">
         <v>250</v>
       </c>
-      <c r="E21" s="17">
-        <v>0</v>
-      </c>
-      <c r="F21" s="13">
+      <c r="E21" s="18">
+        <v>0</v>
+      </c>
+      <c r="F21" s="14">
         <v>12</v>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="18">
         <v>1</v>
       </c>
-      <c r="H21" s="11" t="s">
+      <c r="H21" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="17">
         <v>7000</v>
       </c>
-      <c r="E22" s="17">
-        <v>0</v>
-      </c>
-      <c r="F22" s="13">
+      <c r="E22" s="18">
+        <v>0</v>
+      </c>
+      <c r="F22" s="14">
         <v>12</v>
       </c>
-      <c r="G22" s="17">
+      <c r="G22" s="18">
         <v>1</v>
       </c>
-      <c r="H22" s="11" t="s">
+      <c r="H22" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="17">
         <v>5000</v>
       </c>
-      <c r="E23" s="17">
-        <v>0</v>
-      </c>
-      <c r="F23" s="13">
+      <c r="E23" s="18">
+        <v>0</v>
+      </c>
+      <c r="F23" s="14">
         <v>12</v>
       </c>
-      <c r="G23" s="17">
+      <c r="G23" s="18">
         <v>1</v>
       </c>
-      <c r="H23" s="11" t="s">
+      <c r="H23" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="17">
         <v>10</v>
       </c>
-      <c r="E24" s="17">
-        <v>0</v>
-      </c>
-      <c r="F24" s="13">
+      <c r="E24" s="18">
+        <v>0</v>
+      </c>
+      <c r="F24" s="14">
         <v>12</v>
       </c>
-      <c r="G24" s="17">
+      <c r="G24" s="18">
         <v>1</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="H24" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="G27" s="10" t="s">
+      <c r="G27" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="H27" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="I27" s="10" t="s">
+      <c r="I27" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="D28" s="18">
+      <c r="D28" s="19">
         <v>1</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="17">
         <v>55000</v>
       </c>
-      <c r="F28" s="17">
+      <c r="F28" s="18">
         <v>0.2</v>
       </c>
-      <c r="G28" s="17">
+      <c r="G28" s="18">
         <v>0.0765</v>
       </c>
-      <c r="H28" s="11" t="s">
+      <c r="H28" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="I28" s="11" t="s">
+      <c r="I28" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="D29" s="18">
+      <c r="D29" s="19">
         <v>1</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="17">
         <v>45000</v>
       </c>
-      <c r="F29" s="17">
+      <c r="F29" s="18">
         <v>0.2</v>
       </c>
-      <c r="G29" s="17">
+      <c r="G29" s="18">
         <v>0.0765</v>
       </c>
-      <c r="H29" s="11" t="s">
+      <c r="H29" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="I29" s="11" t="s">
+      <c r="I29" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="D30" s="18">
+      <c r="D30" s="19">
         <v>0.5</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="17">
         <v>28000</v>
       </c>
-      <c r="F30" s="17">
-        <v>0</v>
-      </c>
-      <c r="G30" s="17">
+      <c r="F30" s="18">
+        <v>0</v>
+      </c>
+      <c r="G30" s="18">
         <v>0.0765</v>
       </c>
-      <c r="H30" s="11" t="s">
+      <c r="H30" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="I30" s="11" t="s">
+      <c r="I30" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="D32" s="10"/>
+      <c r="D32" s="11"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="13" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="B34" s="16">
+      <c r="B34" s="17">
         <v>2500</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="12" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="B35" s="17">
+      <c r="B35" s="18">
         <v>0.03</v>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C37" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="D37" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E37" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="F37" s="10" t="s">
+      <c r="F37" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="G37" s="10"/>
+      <c r="G37" s="11"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="11" t="s">
+      <c r="A38" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="D38" s="16">
+      <c r="D38" s="17">
         <v>2500</v>
       </c>
-      <c r="E38" s="17">
+      <c r="E38" s="18">
         <v>0.03</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="F38" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="11" t="s">
+      <c r="A39" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="D39" s="16">
+      <c r="D39" s="17">
         <v>300</v>
       </c>
-      <c r="E39" s="17">
-        <v>0</v>
-      </c>
-      <c r="F39" s="11" t="s">
+      <c r="E39" s="18">
+        <v>0</v>
+      </c>
+      <c r="F39" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="11" t="s">
+      <c r="A40" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="B40" s="11" t="s">
+      <c r="B40" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C40" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D40" s="16">
+      <c r="D40" s="17">
         <v>2400</v>
       </c>
-      <c r="E40" s="17">
-        <v>0</v>
-      </c>
-      <c r="F40" s="11" t="s">
+      <c r="E40" s="18">
+        <v>0</v>
+      </c>
+      <c r="F40" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="11" t="s">
+      <c r="A41" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B41" s="11" t="s">
+      <c r="B41" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="C41" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D41" s="16">
+      <c r="D41" s="17">
         <v>500</v>
       </c>
-      <c r="E41" s="17">
-        <v>0</v>
-      </c>
-      <c r="F41" s="11" t="s">
+      <c r="E41" s="18">
+        <v>0</v>
+      </c>
+      <c r="F41" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="11" t="s">
+      <c r="A42" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="B42" s="11" t="s">
+      <c r="B42" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="C42" s="11" t="s">
+      <c r="C42" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D42" s="16">
+      <c r="D42" s="17">
         <v>300</v>
       </c>
-      <c r="E42" s="17">
-        <v>0</v>
-      </c>
-      <c r="F42" s="11" t="s">
+      <c r="E42" s="18">
+        <v>0</v>
+      </c>
+      <c r="F42" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="11" t="s">
+      <c r="A43" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="B43" s="11" t="s">
+      <c r="B43" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C43" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D43" s="16">
+      <c r="D43" s="17">
         <v>3000</v>
       </c>
-      <c r="E43" s="17">
-        <v>0</v>
-      </c>
-      <c r="F43" s="11" t="s">
+      <c r="E43" s="18">
+        <v>0</v>
+      </c>
+      <c r="F43" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="45" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C45" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="D45" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="E45" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="F45" s="10" t="s">
+      <c r="F45" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="G45" s="10" t="s">
+      <c r="G45" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="H45" s="10" t="s">
+      <c r="H45" s="11" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="11" t="s">
+      <c r="A46" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="C46" s="19">
-        <v>0</v>
-      </c>
-      <c r="D46" s="16">
+      <c r="C46" s="20">
+        <v>0</v>
+      </c>
+      <c r="D46" s="17">
         <v>30000</v>
       </c>
-      <c r="E46" s="20">
+      <c r="E46" s="21">
         <v>0.06</v>
       </c>
-      <c r="F46" s="13">
+      <c r="F46" s="14">
         <v>5</v>
       </c>
-      <c r="G46" s="19">
+      <c r="G46" s="20">
         <v>6960</v>
       </c>
-      <c r="H46" s="11" t="s">
+      <c r="H46" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="10" t="s">
+      <c r="A48" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="11" t="s">
+      <c r="A49" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="B49" s="17">
+      <c r="B49" s="18">
         <v>0.03</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="B50" s="17">
+      <c r="B50" s="18">
         <v>0.025</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B51" s="18">
+      <c r="B51" s="19">
         <v>0.8333333333333334</v>
       </c>
-      <c r="C51" s="21" t="s">
+      <c r="C51" s="22" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="11" t="s">
+      <c r="A52" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="B52" s="17">
+      <c r="B52" s="18">
         <v>0.03</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="11" t="s">
+      <c r="A53" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="B53" s="17">
+      <c r="B53" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="11" t="s">
+      <c r="A54" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="B54" s="16">
+      <c r="B54" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="22" t="s">
+      <c r="A56" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="B56" s="22"/>
-      <c r="C56" s="22"/>
-      <c r="D56" s="22"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="22"/>
-      <c r="G56" s="22"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="23"/>
+      <c r="G56" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2508,741 +2512,741 @@
       <c r="F1" s="8"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="24" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B3" s="26">
         <f>Assumptions!B17</f>
         <v>12</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="26">
         <f>Assumptions!C17</f>
         <v>18</v>
       </c>
-      <c r="D3" s="25">
+      <c r="D3" s="26">
         <f>Assumptions!D17</f>
         <v>22</v>
       </c>
-      <c r="E3" s="25">
+      <c r="E3" s="26">
         <f>Assumptions!E17</f>
         <v>25</v>
       </c>
-      <c r="F3" s="25">
+      <c r="F3" s="26">
         <f>Assumptions!F17</f>
         <v>25</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="20">
         <v>120000</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="20">
         <v>221400</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="20">
         <v>277365</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="20">
         <v>323067</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="20">
         <v>331144</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="20">
         <v>2500</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="20">
         <v>4613</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="20">
         <v>5778</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="20">
         <v>6731</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="20">
         <v>6899</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="20">
         <v>70000</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="20">
         <v>129150</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="20">
         <v>161796</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="20">
         <v>188456</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="20">
         <v>193167</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="20">
         <v>4167</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="20">
         <v>5125</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="20">
         <v>5253</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="20">
         <v>5384</v>
       </c>
-      <c r="F9" s="19">
+      <c r="F9" s="20">
         <v>5519</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="20">
         <v>-12000</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="20">
         <v>-22140</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="20">
         <v>-27736</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="20">
         <v>-32307</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="20">
         <v>-33114</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="27">
         <f>SUM(B6:B10)</f>
         <v>184667</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="27">
         <f>SUM(C6:C10)</f>
         <v>338147</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="27">
         <f>SUM(D6:D10)</f>
         <v>422456</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="27">
         <f>SUM(E6:E10)</f>
         <v>491331</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="27">
         <f>SUM(F6:F10)</f>
         <v>503615</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="20">
         <v>58506</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="20">
         <v>72314</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="20">
         <v>74483</v>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="20">
         <v>76718</v>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="20">
         <v>79019</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="20">
         <v>47869</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="20">
         <v>59166</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="20">
         <v>60941</v>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="20">
         <v>62769</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="20">
         <v>64652</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="20">
         <v>12559</v>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="20">
         <v>15523</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="20">
         <v>15989</v>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="20">
         <v>16468</v>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="20">
         <v>16963</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="27">
         <f>SUM(B14:B16)</f>
         <v>118934</v>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="27">
         <f>SUM(C14:C16)</f>
         <v>147003</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="27">
         <f>SUM(D14:D16)</f>
         <v>151413</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="27">
         <f>SUM(E14:E16)</f>
         <v>155955</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="27">
         <f>SUM(F14:F16)</f>
         <v>160634</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="20">
         <v>5000</v>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="20">
         <v>9225</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="20">
         <v>11557</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="20">
         <v>13461</v>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="20">
         <v>13798</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="27" t="s">
+      <c r="A22" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="29">
         <v>5000</v>
       </c>
-      <c r="C22" s="28">
+      <c r="C22" s="29">
         <v>9225</v>
       </c>
-      <c r="D22" s="28">
+      <c r="D22" s="29">
         <v>11557</v>
       </c>
-      <c r="E22" s="28">
+      <c r="E22" s="29">
         <v>13461</v>
       </c>
-      <c r="F22" s="28">
+      <c r="F22" s="29">
         <v>13798</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B24" s="19">
+      <c r="B24" s="20">
         <v>3000</v>
       </c>
-      <c r="C24" s="19">
+      <c r="C24" s="20">
         <v>5535</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="20">
         <v>6934</v>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="20">
         <v>8077</v>
       </c>
-      <c r="F24" s="19">
+      <c r="F24" s="20">
         <v>8279</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="27" t="s">
+      <c r="A25" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="29">
         <v>3000</v>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="29">
         <v>5535</v>
       </c>
-      <c r="D25" s="28">
+      <c r="D25" s="29">
         <v>6934</v>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="29">
         <v>8077</v>
       </c>
-      <c r="F25" s="28">
+      <c r="F25" s="29">
         <v>8279</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B27" s="19">
+      <c r="B27" s="20">
         <v>25000</v>
       </c>
-      <c r="C27" s="19">
+      <c r="C27" s="20">
         <v>30900</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="20">
         <v>31827</v>
       </c>
-      <c r="E27" s="19">
+      <c r="E27" s="20">
         <v>32782</v>
       </c>
-      <c r="F27" s="19">
+      <c r="F27" s="20">
         <v>33765</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B28" s="19">
+      <c r="B28" s="20">
         <v>3000</v>
       </c>
-      <c r="C28" s="19">
+      <c r="C28" s="20">
         <v>3690</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="20">
         <v>3782</v>
       </c>
-      <c r="E28" s="19">
+      <c r="E28" s="20">
         <v>3877</v>
       </c>
-      <c r="F28" s="19">
+      <c r="F28" s="20">
         <v>3974</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="B29" s="19">
+      <c r="B29" s="20">
         <v>2000</v>
       </c>
-      <c r="C29" s="19">
+      <c r="C29" s="20">
         <v>2460</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="20">
         <v>2522</v>
       </c>
-      <c r="E29" s="19">
+      <c r="E29" s="20">
         <v>2585</v>
       </c>
-      <c r="F29" s="19">
+      <c r="F29" s="20">
         <v>2649</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="27" t="s">
+      <c r="A30" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="B30" s="28">
+      <c r="B30" s="29">
         <v>30000</v>
       </c>
-      <c r="C30" s="28">
+      <c r="C30" s="29">
         <v>37050</v>
       </c>
-      <c r="D30" s="28">
+      <c r="D30" s="29">
         <v>38131</v>
       </c>
-      <c r="E30" s="28">
+      <c r="E30" s="29">
         <v>39244</v>
       </c>
-      <c r="F30" s="28">
+      <c r="F30" s="29">
         <v>40388</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B32" s="19">
+      <c r="B32" s="20">
         <v>2500</v>
       </c>
-      <c r="C32" s="19">
+      <c r="C32" s="20">
         <v>3075</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="20">
         <v>3152</v>
       </c>
-      <c r="E32" s="19">
+      <c r="E32" s="20">
         <v>3231</v>
       </c>
-      <c r="F32" s="19">
+      <c r="F32" s="20">
         <v>3311</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="27" t="s">
+      <c r="A33" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="B33" s="28">
+      <c r="B33" s="29">
         <v>2500</v>
       </c>
-      <c r="C33" s="28">
+      <c r="C33" s="29">
         <v>3075</v>
       </c>
-      <c r="D33" s="28">
+      <c r="D33" s="29">
         <v>3152</v>
       </c>
-      <c r="E33" s="28">
+      <c r="E33" s="29">
         <v>3231</v>
       </c>
-      <c r="F33" s="28">
+      <c r="F33" s="29">
         <v>3311</v>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B34" s="26">
+      <c r="B34" s="27">
         <f>B22+B25+B30+B33</f>
         <v>40500</v>
       </c>
-      <c r="C34" s="26">
+      <c r="C34" s="27">
         <f>C22+C25+C30+C33</f>
         <v>54885</v>
       </c>
-      <c r="D34" s="26">
+      <c r="D34" s="27">
         <f>D22+D25+D30+D33</f>
         <v>59774</v>
       </c>
-      <c r="E34" s="26">
+      <c r="E34" s="27">
         <f>E22+E25+E30+E33</f>
         <v>64012</v>
       </c>
-      <c r="F34" s="26">
+      <c r="F34" s="27">
         <f>F22+F25+F30+F33</f>
         <v>65776</v>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="B37" s="19">
+      <c r="B37" s="20">
         <v>6960</v>
       </c>
-      <c r="C37" s="19">
+      <c r="C37" s="20">
         <v>6960</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="20">
         <v>6960</v>
       </c>
-      <c r="E37" s="19">
+      <c r="E37" s="20">
         <v>6960</v>
       </c>
-      <c r="F37" s="19">
+      <c r="F37" s="20">
         <v>6960</v>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B38" s="26">
+      <c r="B38" s="27">
         <f>SUM(B37:B37)</f>
         <v>6960</v>
       </c>
-      <c r="C38" s="26">
+      <c r="C38" s="27">
         <f>SUM(C37:C37)</f>
         <v>6960</v>
       </c>
-      <c r="D38" s="26">
+      <c r="D38" s="27">
         <f>SUM(D37:D37)</f>
         <v>6960</v>
       </c>
-      <c r="E38" s="26">
+      <c r="E38" s="27">
         <f>SUM(E37:E37)</f>
         <v>6960</v>
       </c>
-      <c r="F38" s="26">
+      <c r="F38" s="27">
         <f>SUM(F37:F37)</f>
         <v>6960</v>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="24" t="s">
+      <c r="A41" s="25" t="s">
         <v>151</v>
       </c>
-      <c r="B41" s="28">
+      <c r="B41" s="29">
         <f>B11</f>
         <v>184667</v>
       </c>
-      <c r="C41" s="28">
+      <c r="C41" s="29">
         <f>C11</f>
         <v>338147</v>
       </c>
-      <c r="D41" s="28">
+      <c r="D41" s="29">
         <f>D11</f>
         <v>422456</v>
       </c>
-      <c r="E41" s="28">
+      <c r="E41" s="29">
         <f>E11</f>
         <v>491331</v>
       </c>
-      <c r="F41" s="28">
+      <c r="F41" s="29">
         <f>F11</f>
         <v>503615</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="11" t="s">
+      <c r="A42" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="B42" s="19">
+      <c r="B42" s="20">
         <f>B17</f>
         <v>118934</v>
       </c>
-      <c r="C42" s="19">
+      <c r="C42" s="20">
         <f>C17</f>
         <v>147003</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="20">
         <f>D17</f>
         <v>151413</v>
       </c>
-      <c r="E42" s="19">
+      <c r="E42" s="20">
         <f>E17</f>
         <v>155955</v>
       </c>
-      <c r="F42" s="19">
+      <c r="F42" s="20">
         <f>F17</f>
         <v>160634</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="11" t="s">
+      <c r="A43" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="B43" s="19">
+      <c r="B43" s="20">
         <f>B34</f>
         <v>40500</v>
       </c>
-      <c r="C43" s="19">
+      <c r="C43" s="20">
         <f>C34</f>
         <v>54885</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="20">
         <f>D34</f>
         <v>59774</v>
       </c>
-      <c r="E43" s="19">
+      <c r="E43" s="20">
         <f>E34</f>
         <v>64012</v>
       </c>
-      <c r="F43" s="19">
+      <c r="F43" s="20">
         <f>F34</f>
         <v>65776</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="11" t="s">
+      <c r="A44" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="B44" s="19">
+      <c r="B44" s="20">
         <f>B38</f>
         <v>6960</v>
       </c>
-      <c r="C44" s="19">
+      <c r="C44" s="20">
         <f>C38</f>
         <v>6960</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="20">
         <f>D38</f>
         <v>6960</v>
       </c>
-      <c r="E44" s="19">
+      <c r="E44" s="20">
         <f>E38</f>
         <v>6960</v>
       </c>
-      <c r="F44" s="19">
+      <c r="F44" s="20">
         <f>F38</f>
         <v>6960</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="24" t="s">
+      <c r="A45" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="B45" s="28">
+      <c r="B45" s="29">
         <f>B42+B43+B44</f>
         <v>166394</v>
       </c>
-      <c r="C45" s="28">
+      <c r="C45" s="29">
         <f>C42+C43+C44</f>
         <v>208848</v>
       </c>
-      <c r="D45" s="28">
+      <c r="D45" s="29">
         <f>D42+D43+D44</f>
         <v>218147</v>
       </c>
-      <c r="E45" s="28">
+      <c r="E45" s="29">
         <f>E42+E43+E44</f>
         <v>226927</v>
       </c>
-      <c r="F45" s="28">
+      <c r="F45" s="29">
         <f>F42+F43+F44</f>
         <v>233370</v>
       </c>
@@ -3253,569 +3257,569 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="29" t="s">
+      <c r="A47" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="B47" s="30">
+      <c r="B47" s="31">
         <f>B41-B45</f>
         <v>18273</v>
       </c>
-      <c r="C47" s="30">
+      <c r="C47" s="31">
         <f>C41-C45</f>
         <v>129299</v>
       </c>
-      <c r="D47" s="30">
+      <c r="D47" s="31">
         <f>D41-D45</f>
         <v>204309</v>
       </c>
-      <c r="E47" s="30">
+      <c r="E47" s="31">
         <f>E41-E45</f>
         <v>264404</v>
       </c>
-      <c r="F47" s="30">
+      <c r="F47" s="31">
         <f>F41-F45</f>
         <v>270245</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="11" t="s">
+      <c r="A48" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="B48" s="31">
+      <c r="B48" s="32">
         <f>IF(B41=0,"",B47/B41)</f>
         <v>0.1</v>
       </c>
-      <c r="C48" s="31">
+      <c r="C48" s="32">
         <f>IF(C41=0,"",C47/C41)</f>
         <v>0.38</v>
       </c>
-      <c r="D48" s="31">
+      <c r="D48" s="32">
         <f>IF(D41=0,"",D47/D41)</f>
         <v>0.48</v>
       </c>
-      <c r="E48" s="31">
+      <c r="E48" s="32">
         <f>IF(E41=0,"",E47/E41)</f>
         <v>0.54</v>
       </c>
-      <c r="F48" s="31">
+      <c r="F48" s="32">
         <f>IF(F41=0,"",F47/F41)</f>
         <v>0.54</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="11" t="s">
+      <c r="A49" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="B49" s="19">
+      <c r="B49" s="20">
         <f>B47</f>
         <v>18273</v>
       </c>
-      <c r="C49" s="19">
+      <c r="C49" s="20">
         <f>B49+C47</f>
         <v>147572</v>
       </c>
-      <c r="D49" s="19">
+      <c r="D49" s="20">
         <f>C49+D47</f>
         <v>351881</v>
       </c>
-      <c r="E49" s="19">
+      <c r="E49" s="20">
         <f>D49+E47</f>
         <v>616285</v>
       </c>
-      <c r="F49" s="19">
+      <c r="F49" s="20">
         <f>E49+F47</f>
         <v>886530</v>
       </c>
     </row>
     <row r="51" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="10" t="s">
+      <c r="A51" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="24" t="s">
+      <c r="A52" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="B52" s="28">
+      <c r="B52" s="29">
         <f>B41-B42-B43</f>
         <v>25233</v>
       </c>
-      <c r="C52" s="28">
+      <c r="C52" s="29">
         <f>C41-C42-C43</f>
         <v>136259</v>
       </c>
-      <c r="D52" s="28">
+      <c r="D52" s="29">
         <f>D41-D42-D43</f>
         <v>211269</v>
       </c>
-      <c r="E52" s="28">
+      <c r="E52" s="29">
         <f>E41-E42-E43</f>
         <v>271364</v>
       </c>
-      <c r="F52" s="28">
+      <c r="F52" s="29">
         <f>F41-F42-F43</f>
         <v>277205</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="11" t="s">
+      <c r="A53" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="B53" s="19">
+      <c r="B53" s="20">
         <f>B44</f>
         <v>6960</v>
       </c>
-      <c r="C53" s="19">
+      <c r="C53" s="20">
         <f>C44</f>
         <v>6960</v>
       </c>
-      <c r="D53" s="19">
+      <c r="D53" s="20">
         <f>D44</f>
         <v>6960</v>
       </c>
-      <c r="E53" s="19">
+      <c r="E53" s="20">
         <f>E44</f>
         <v>6960</v>
       </c>
-      <c r="F53" s="19">
+      <c r="F53" s="20">
         <f>F44</f>
         <v>6960</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="24" t="s">
+      <c r="A54" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="B54" s="32">
+      <c r="B54" s="33">
         <f>IF(B53=0,"N/A",B52/B53)</f>
         <v>3.63</v>
       </c>
-      <c r="C54" s="32">
+      <c r="C54" s="33">
         <f>IF(C53=0,"N/A",C52/C53)</f>
         <v>19.58</v>
       </c>
-      <c r="D54" s="32">
+      <c r="D54" s="33">
         <f>IF(D53=0,"N/A",D52/D53)</f>
         <v>30.35</v>
       </c>
-      <c r="E54" s="32">
+      <c r="E54" s="33">
         <f>IF(E53=0,"N/A",E52/E53)</f>
         <v>38.99</v>
       </c>
-      <c r="F54" s="32">
+      <c r="F54" s="33">
         <f>IF(F53=0,"N/A",F52/F53)</f>
         <v>39.83</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="11" t="s">
+      <c r="A55" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="B55" s="19" t="str">
+      <c r="B55" s="20" t="str">
         <f>Assumptions!B54</f>
         <v>0</v>
       </c>
-      <c r="C55" s="19">
+      <c r="C55" s="20">
         <f>B56</f>
         <v>18273</v>
       </c>
-      <c r="D55" s="19">
+      <c r="D55" s="20">
         <f>C56</f>
         <v>147572</v>
       </c>
-      <c r="E55" s="19">
+      <c r="E55" s="20">
         <f>D56</f>
         <v>351881</v>
       </c>
-      <c r="F55" s="19">
+      <c r="F55" s="20">
         <f>E56</f>
         <v>616285</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="24" t="s">
+      <c r="A56" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="B56" s="28">
+      <c r="B56" s="29">
         <f>B55+B47</f>
         <v>18273</v>
       </c>
-      <c r="C56" s="28">
+      <c r="C56" s="29">
         <f>C55+C47</f>
         <v>147572</v>
       </c>
-      <c r="D56" s="28">
+      <c r="D56" s="29">
         <f>D55+D47</f>
         <v>351881</v>
       </c>
-      <c r="E56" s="28">
+      <c r="E56" s="29">
         <f>E55+E47</f>
         <v>616285</v>
       </c>
-      <c r="F56" s="28">
+      <c r="F56" s="29">
         <f>F55+F47</f>
         <v>886530</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="11" t="s">
+      <c r="A57" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="B57" s="33">
+      <c r="B57" s="34">
         <f>IF(B45=0,"",B56/B45*365)</f>
         <v>40</v>
       </c>
-      <c r="C57" s="33">
+      <c r="C57" s="34">
         <f>IF(C45=0,"",C56/C45*365)</f>
         <v>258</v>
       </c>
-      <c r="D57" s="33">
+      <c r="D57" s="34">
         <f>IF(D45=0,"",D56/D45*365)</f>
         <v>589</v>
       </c>
-      <c r="E57" s="33">
+      <c r="E57" s="34">
         <f>IF(E45=0,"",E56/E45*365)</f>
         <v>991</v>
       </c>
-      <c r="F57" s="33">
+      <c r="F57" s="34">
         <f>IF(F45=0,"",F56/F45*365)</f>
         <v>1387</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="11" t="s">
+      <c r="A58" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="B58" s="34">
+      <c r="B58" s="35">
         <f>IF(B45=0,"",B56/(B45/12))</f>
         <v>1.3</v>
       </c>
-      <c r="C58" s="34">
+      <c r="C58" s="35">
         <f>IF(C45=0,"",C56/(C45/12))</f>
         <v>8.5</v>
       </c>
-      <c r="D58" s="34">
+      <c r="D58" s="35">
         <f>IF(D45=0,"",D56/(D45/12))</f>
         <v>19.4</v>
       </c>
-      <c r="E58" s="34">
+      <c r="E58" s="35">
         <f>IF(E45=0,"",E56/(E45/12))</f>
         <v>32.6</v>
       </c>
-      <c r="F58" s="34">
+      <c r="F58" s="35">
         <f>IF(F45=0,"",F56/(F45/12))</f>
         <v>45.6</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="11" t="s">
+      <c r="A59" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="B59" s="31">
+      <c r="B59" s="32">
         <f>IF(Assumptions!B12=0,"",B3/Assumptions!B12)</f>
         <v>0.48</v>
       </c>
-      <c r="C59" s="31">
+      <c r="C59" s="32">
         <f>IF(Assumptions!B12=0,"",C3/Assumptions!B12)</f>
         <v>0.72</v>
       </c>
-      <c r="D59" s="31">
+      <c r="D59" s="32">
         <f>IF(Assumptions!B12=0,"",D3/Assumptions!B12)</f>
         <v>0.88</v>
       </c>
-      <c r="E59" s="31">
+      <c r="E59" s="32">
         <f>IF(Assumptions!B12=0,"",E3/Assumptions!B12)</f>
         <v>1</v>
       </c>
-      <c r="F59" s="31">
+      <c r="F59" s="32">
         <f>IF(Assumptions!B12=0,"",F3/Assumptions!B12)</f>
         <v>1</v>
       </c>
     </row>
     <row r="61" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="10" t="s">
+      <c r="A61" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="B61" s="10"/>
-      <c r="C61" s="10"/>
-      <c r="D61" s="10"/>
-      <c r="E61" s="10"/>
-      <c r="F61" s="10"/>
+      <c r="B61" s="11"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="11"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="11" t="s">
+      <c r="A62" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="B62" s="11" t="str">
+      <c r="B62" s="12" t="str">
         <f>IF(B53=0,"N/A",IF(B54&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="C62" s="11" t="str">
+      <c r="C62" s="12" t="str">
         <f>IF(C53=0,"N/A",IF(C54&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="D62" s="11" t="str">
+      <c r="D62" s="12" t="str">
         <f>IF(D53=0,"N/A",IF(D54&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E62" s="11" t="str">
+      <c r="E62" s="12" t="str">
         <f>IF(E53=0,"N/A",IF(E54&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F62" s="11" t="str">
+      <c r="F62" s="12" t="str">
         <f>IF(F53=0,"N/A",IF(F54&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="11" t="s">
+      <c r="A63" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="B63" s="11" t="str">
+      <c r="B63" s="12" t="str">
         <f>IF(B47&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="C63" s="11" t="str">
+      <c r="C63" s="12" t="str">
         <f>IF(C47&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="D63" s="11" t="str">
+      <c r="D63" s="12" t="str">
         <f>IF(D47&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E63" s="11" t="str">
+      <c r="E63" s="12" t="str">
         <f>IF(E47&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="F63" s="11" t="str">
+      <c r="F63" s="12" t="str">
         <f>IF(F47&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="11" t="s">
+      <c r="A64" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="B64" s="11" t="str">
+      <c r="B64" s="12" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(B3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C64" s="11" t="str">
+      <c r="C64" s="12" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(C3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="D64" s="11" t="str">
+      <c r="D64" s="12" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(D3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E64" s="11" t="str">
+      <c r="E64" s="12" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(E3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F64" s="11" t="str">
+      <c r="F64" s="12" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(F3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="11" t="s">
+      <c r="A65" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="B65" s="11" t="str">
+      <c r="B65" s="12" t="str">
         <f>IF(B45=0,"N/A",IF(B56/(B45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C65" s="11" t="str">
+      <c r="C65" s="12" t="str">
         <f>IF(C45=0,"N/A",IF(C56/(C45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="D65" s="11" t="str">
+      <c r="D65" s="12" t="str">
         <f>IF(D45=0,"N/A",IF(D56/(D45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E65" s="11" t="str">
+      <c r="E65" s="12" t="str">
         <f>IF(E45=0,"N/A",IF(E56/(E45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F65" s="11" t="str">
+      <c r="F65" s="12" t="str">
         <f>IF(F45=0,"N/A",IF(F56/(F45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="67" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="10" t="s">
+      <c r="A67" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="B67" s="10"/>
-      <c r="C67" s="10"/>
-      <c r="D67" s="10"/>
-      <c r="E67" s="10"/>
-      <c r="F67" s="10"/>
+      <c r="B67" s="11"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="11"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="11" t="s">
+      <c r="A68" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="B68" s="19">
+      <c r="B68" s="20">
         <f>IF(B3=0,"",B11/B3)</f>
         <v>15389</v>
       </c>
-      <c r="C68" s="19">
+      <c r="C68" s="20">
         <f>IF(C3=0,"",C11/C3)</f>
         <v>18786</v>
       </c>
-      <c r="D68" s="19">
+      <c r="D68" s="20">
         <f>IF(D3=0,"",D11/D3)</f>
         <v>19203</v>
       </c>
-      <c r="E68" s="19">
+      <c r="E68" s="20">
         <f>IF(E3=0,"",E11/E3)</f>
         <v>19653</v>
       </c>
-      <c r="F68" s="19">
+      <c r="F68" s="20">
         <f>IF(F3=0,"",F11/F3)</f>
         <v>20145</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="11" t="s">
+      <c r="A69" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="B69" s="19">
+      <c r="B69" s="20">
         <f>IF(B3=0,"",B45/B3)</f>
         <v>13866</v>
       </c>
-      <c r="C69" s="19">
+      <c r="C69" s="20">
         <f>IF(C3=0,"",C45/C3)</f>
         <v>11603</v>
       </c>
-      <c r="D69" s="19">
+      <c r="D69" s="20">
         <f>IF(D3=0,"",D45/D3)</f>
         <v>9916</v>
       </c>
-      <c r="E69" s="19">
+      <c r="E69" s="20">
         <f>IF(E3=0,"",E45/E3)</f>
         <v>9077</v>
       </c>
-      <c r="F69" s="19">
+      <c r="F69" s="20">
         <f>IF(F3=0,"",F45/F3)</f>
         <v>9335</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="11" t="s">
+      <c r="A70" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="B70" s="19">
+      <c r="B70" s="20">
         <f>B42+B44</f>
         <v>125894</v>
       </c>
-      <c r="C70" s="19">
+      <c r="C70" s="20">
         <f>C42+C44</f>
         <v>153963</v>
       </c>
-      <c r="D70" s="19">
+      <c r="D70" s="20">
         <f>D42+D44</f>
         <v>158373</v>
       </c>
-      <c r="E70" s="19">
+      <c r="E70" s="20">
         <f>E42+E44</f>
         <v>162915</v>
       </c>
-      <c r="F70" s="19">
+      <c r="F70" s="20">
         <f>F42+F44</f>
         <v>167594</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="11" t="s">
+      <c r="A71" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="B71" s="19">
+      <c r="B71" s="20">
         <f>IF(B3=0,"",B43/B3)</f>
         <v>3375</v>
       </c>
-      <c r="C71" s="19">
+      <c r="C71" s="20">
         <f>IF(C3=0,"",C43/C3)</f>
         <v>3049</v>
       </c>
-      <c r="D71" s="19">
+      <c r="D71" s="20">
         <f>IF(D3=0,"",D43/D3)</f>
         <v>2717</v>
       </c>
-      <c r="E71" s="19">
+      <c r="E71" s="20">
         <f>IF(E3=0,"",E43/E3)</f>
         <v>2560</v>
       </c>
-      <c r="F71" s="19">
+      <c r="F71" s="20">
         <f>IF(F3=0,"",F43/F3)</f>
         <v>2631</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="11" t="s">
+      <c r="A72" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="B72" s="19">
+      <c r="B72" s="20">
         <f>IF(B3=0,"",B68-B71)</f>
         <v>12014</v>
       </c>
-      <c r="C72" s="19">
+      <c r="C72" s="20">
         <f>IF(C3=0,"",C68-C71)</f>
         <v>15737</v>
       </c>
-      <c r="D72" s="19">
+      <c r="D72" s="20">
         <f>IF(D3=0,"",D68-D71)</f>
         <v>16486</v>
       </c>
-      <c r="E72" s="19">
+      <c r="E72" s="20">
         <f>IF(E3=0,"",E68-E71)</f>
         <v>17093</v>
       </c>
-      <c r="F72" s="19">
+      <c r="F72" s="20">
         <f>IF(F3=0,"",F68-F71)</f>
         <v>17514</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="35" t="s">
+      <c r="A73" s="36" t="s">
         <v>178</v>
       </c>
-      <c r="B73" s="36">
+      <c r="B73" s="37">
         <f>IF(B72&lt;=0,"N/A",ROUNDUP(B70/B72,0))</f>
         <v>11</v>
       </c>
-      <c r="C73" s="36">
+      <c r="C73" s="37">
         <f>IF(C72&lt;=0,"N/A",ROUNDUP(C70/C72,0))</f>
         <v>10</v>
       </c>
-      <c r="D73" s="36">
+      <c r="D73" s="37">
         <f>IF(D72&lt;=0,"N/A",ROUNDUP(D70/D72,0))</f>
         <v>10</v>
       </c>
-      <c r="E73" s="36">
+      <c r="E73" s="37">
         <f>IF(E72&lt;=0,"N/A",ROUNDUP(E70/E72,0))</f>
         <v>10</v>
       </c>
-      <c r="F73" s="36">
+      <c r="F73" s="37">
         <f>IF(F72&lt;=0,"N/A",ROUNDUP(F70/F72,0))</f>
         <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="22" t="s">
+      <c r="A75" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="B75" s="22"/>
-      <c r="C75" s="22"/>
-      <c r="D75" s="22"/>
-      <c r="E75" s="22"/>
-      <c r="F75" s="22"/>
+      <c r="B75" s="23"/>
+      <c r="C75" s="23"/>
+      <c r="D75" s="23"/>
+      <c r="E75" s="23"/>
+      <c r="F75" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3863,345 +3867,345 @@
       <c r="N1" s="8"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="24" t="s">
         <v>182</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="24" t="s">
         <v>183</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="24" t="s">
         <v>185</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="J2" s="24" t="s">
         <v>187</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="K2" s="24" t="s">
         <v>188</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="L2" s="24" t="s">
         <v>189</v>
       </c>
-      <c r="M2" s="23" t="s">
+      <c r="M2" s="24" t="s">
         <v>190</v>
       </c>
-      <c r="N2" s="23" t="s">
+      <c r="N2" s="24" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="20">
         <v>14400</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="20">
         <v>14400</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="20">
         <v>14400</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="20">
         <v>14400</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="20">
         <v>14400</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="20">
         <v>14400</v>
       </c>
-      <c r="H4" s="19">
+      <c r="H4" s="20">
         <v>14400</v>
       </c>
-      <c r="I4" s="19">
+      <c r="I4" s="20">
         <v>14400</v>
       </c>
-      <c r="J4" s="19">
+      <c r="J4" s="20">
         <v>14400</v>
       </c>
-      <c r="K4" s="19">
+      <c r="K4" s="20">
         <v>14400</v>
       </c>
-      <c r="L4" s="19">
-        <v>0</v>
-      </c>
-      <c r="M4" s="19">
-        <v>0</v>
-      </c>
-      <c r="N4" s="19">
+      <c r="L4" s="20">
+        <v>0</v>
+      </c>
+      <c r="M4" s="20">
+        <v>0</v>
+      </c>
+      <c r="N4" s="20">
         <f>SUM(B4:M4)</f>
         <v>120000</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="20">
         <v>300</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="20">
         <v>300</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="20">
         <v>300</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="20">
         <v>300</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="20">
         <v>300</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="20">
         <v>300</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="20">
         <v>300</v>
       </c>
-      <c r="I5" s="19">
+      <c r="I5" s="20">
         <v>300</v>
       </c>
-      <c r="J5" s="19">
+      <c r="J5" s="20">
         <v>300</v>
       </c>
-      <c r="K5" s="19">
+      <c r="K5" s="20">
         <v>300</v>
       </c>
-      <c r="L5" s="19">
-        <v>0</v>
-      </c>
-      <c r="M5" s="19">
-        <v>0</v>
-      </c>
-      <c r="N5" s="19">
+      <c r="L5" s="20">
+        <v>0</v>
+      </c>
+      <c r="M5" s="20">
+        <v>0</v>
+      </c>
+      <c r="N5" s="20">
         <f>SUM(B5:M5)</f>
         <v>2500</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="20">
         <v>8400</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="20">
         <v>8400</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="20">
         <v>8400</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="20">
         <v>8400</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="20">
         <v>8400</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="20">
         <v>8400</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="20">
         <v>8400</v>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="20">
         <v>8400</v>
       </c>
-      <c r="J6" s="19">
+      <c r="J6" s="20">
         <v>8400</v>
       </c>
-      <c r="K6" s="19">
+      <c r="K6" s="20">
         <v>8400</v>
       </c>
-      <c r="L6" s="19">
-        <v>0</v>
-      </c>
-      <c r="M6" s="19">
-        <v>0</v>
-      </c>
-      <c r="N6" s="19">
+      <c r="L6" s="20">
+        <v>0</v>
+      </c>
+      <c r="M6" s="20">
+        <v>0</v>
+      </c>
+      <c r="N6" s="20">
         <f>SUM(B6:M6)</f>
         <v>70000</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="20">
         <v>500</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="20">
         <v>500</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="20">
         <v>500</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="20">
         <v>500</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="20">
         <v>500</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="20">
         <v>500</v>
       </c>
-      <c r="H7" s="19">
+      <c r="H7" s="20">
         <v>500</v>
       </c>
-      <c r="I7" s="19">
+      <c r="I7" s="20">
         <v>500</v>
       </c>
-      <c r="J7" s="19">
+      <c r="J7" s="20">
         <v>500</v>
       </c>
-      <c r="K7" s="19">
+      <c r="K7" s="20">
         <v>500</v>
       </c>
-      <c r="L7" s="19">
-        <v>0</v>
-      </c>
-      <c r="M7" s="19">
-        <v>0</v>
-      </c>
-      <c r="N7" s="19">
+      <c r="L7" s="20">
+        <v>0</v>
+      </c>
+      <c r="M7" s="20">
+        <v>0</v>
+      </c>
+      <c r="N7" s="20">
         <f>SUM(B7:M7)</f>
         <v>4167</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="19">
-        <v>0</v>
-      </c>
-      <c r="C8" s="19">
-        <v>0</v>
-      </c>
-      <c r="D8" s="19">
-        <v>0</v>
-      </c>
-      <c r="E8" s="19">
-        <v>0</v>
-      </c>
-      <c r="F8" s="19">
-        <v>0</v>
-      </c>
-      <c r="G8" s="19">
-        <v>0</v>
-      </c>
-      <c r="H8" s="19">
-        <v>0</v>
-      </c>
-      <c r="I8" s="19">
-        <v>0</v>
-      </c>
-      <c r="J8" s="19">
-        <v>0</v>
-      </c>
-      <c r="K8" s="19">
-        <v>0</v>
-      </c>
-      <c r="L8" s="19">
-        <v>0</v>
-      </c>
-      <c r="M8" s="19">
-        <v>0</v>
-      </c>
-      <c r="N8" s="19" t="str">
+      <c r="B8" s="20">
+        <v>0</v>
+      </c>
+      <c r="C8" s="20">
+        <v>0</v>
+      </c>
+      <c r="D8" s="20">
+        <v>0</v>
+      </c>
+      <c r="E8" s="20">
+        <v>0</v>
+      </c>
+      <c r="F8" s="20">
+        <v>0</v>
+      </c>
+      <c r="G8" s="20">
+        <v>0</v>
+      </c>
+      <c r="H8" s="20">
+        <v>0</v>
+      </c>
+      <c r="I8" s="20">
+        <v>0</v>
+      </c>
+      <c r="J8" s="20">
+        <v>0</v>
+      </c>
+      <c r="K8" s="20">
+        <v>0</v>
+      </c>
+      <c r="L8" s="20">
+        <v>0</v>
+      </c>
+      <c r="M8" s="20">
+        <v>0</v>
+      </c>
+      <c r="N8" s="20" t="str">
         <f>SUM(B8:M8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="27">
         <f>SUM(B4:B8)</f>
         <v>155900</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="27">
         <f>SUM(C4:C8)</f>
         <v>7460</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="27">
         <f>SUM(D4:D8)</f>
         <v>7460</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="27">
         <f>SUM(E4:E8)</f>
         <v>7460</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="27">
         <f>SUM(F4:F8)</f>
         <v>7460</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="27">
         <f>SUM(G4:G8)</f>
         <v>7460</v>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="27">
         <f>SUM(H4:H8)</f>
         <v>7460</v>
       </c>
-      <c r="I9" s="26">
+      <c r="I9" s="27">
         <f>SUM(I4:I8)</f>
         <v>7460</v>
       </c>
-      <c r="J9" s="26">
+      <c r="J9" s="27">
         <f>SUM(J4:J8)</f>
         <v>7460</v>
       </c>
-      <c r="K9" s="26">
+      <c r="K9" s="27">
         <f>SUM(K4:K8)</f>
         <v>7460</v>
       </c>
-      <c r="L9" s="26">
+      <c r="L9" s="27">
         <f>SUM(L4:L8)</f>
         <v>-1440</v>
       </c>
-      <c r="M9" s="26" t="str">
+      <c r="M9" s="27" t="str">
         <f>SUM(M4:M8)</f>
         <v>0</v>
       </c>
-      <c r="N9" s="26">
+      <c r="N9" s="27">
         <f>SUM(B9:M9)</f>
         <v>221600</v>
       </c>
@@ -4212,211 +4216,211 @@
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="20">
         <v>5851</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="20">
         <v>5851</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="20">
         <v>5851</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="20">
         <v>5851</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="20">
         <v>5851</v>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="20">
         <v>5851</v>
       </c>
-      <c r="H12" s="19">
+      <c r="H12" s="20">
         <v>5851</v>
       </c>
-      <c r="I12" s="19">
+      <c r="I12" s="20">
         <v>5851</v>
       </c>
-      <c r="J12" s="19">
+      <c r="J12" s="20">
         <v>5851</v>
       </c>
-      <c r="K12" s="19">
+      <c r="K12" s="20">
         <v>5851</v>
       </c>
-      <c r="L12" s="19">
-        <v>0</v>
-      </c>
-      <c r="M12" s="19">
-        <v>0</v>
-      </c>
-      <c r="N12" s="19">
+      <c r="L12" s="20">
+        <v>0</v>
+      </c>
+      <c r="M12" s="20">
+        <v>0</v>
+      </c>
+      <c r="N12" s="20">
         <f>SUM(B12:M12)</f>
         <v>58506</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="20">
         <v>4787</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="20">
         <v>4787</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="20">
         <v>4787</v>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="20">
         <v>4787</v>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="20">
         <v>4787</v>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="20">
         <v>4787</v>
       </c>
-      <c r="H13" s="19">
+      <c r="H13" s="20">
         <v>4787</v>
       </c>
-      <c r="I13" s="19">
+      <c r="I13" s="20">
         <v>4787</v>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="20">
         <v>4787</v>
       </c>
-      <c r="K13" s="19">
+      <c r="K13" s="20">
         <v>4787</v>
       </c>
-      <c r="L13" s="19">
-        <v>0</v>
-      </c>
-      <c r="M13" s="19">
-        <v>0</v>
-      </c>
-      <c r="N13" s="19">
+      <c r="L13" s="20">
+        <v>0</v>
+      </c>
+      <c r="M13" s="20">
+        <v>0</v>
+      </c>
+      <c r="N13" s="20">
         <f>SUM(B13:M13)</f>
         <v>47869</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="20">
         <v>1256</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="20">
         <v>1256</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="20">
         <v>1256</v>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="20">
         <v>1256</v>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="20">
         <v>1256</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="20">
         <v>1256</v>
       </c>
-      <c r="H14" s="19">
+      <c r="H14" s="20">
         <v>1256</v>
       </c>
-      <c r="I14" s="19">
+      <c r="I14" s="20">
         <v>1256</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="20">
         <v>1256</v>
       </c>
-      <c r="K14" s="19">
+      <c r="K14" s="20">
         <v>1256</v>
       </c>
-      <c r="L14" s="19">
-        <v>0</v>
-      </c>
-      <c r="M14" s="19">
-        <v>0</v>
-      </c>
-      <c r="N14" s="19">
+      <c r="L14" s="20">
+        <v>0</v>
+      </c>
+      <c r="M14" s="20">
+        <v>0</v>
+      </c>
+      <c r="N14" s="20">
         <f>SUM(B14:M14)</f>
         <v>12559</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="27">
         <f>SUM(B12:B14)</f>
         <v>11893</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="27">
         <f>SUM(C12:C14)</f>
         <v>11893</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="27">
         <f>SUM(D12:D14)</f>
         <v>11893</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="27">
         <f>SUM(E12:E14)</f>
         <v>11893</v>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="27">
         <f>SUM(F12:F14)</f>
         <v>11893</v>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="27">
         <f>SUM(G12:G14)</f>
         <v>11893</v>
       </c>
-      <c r="H15" s="26">
+      <c r="H15" s="27">
         <f>SUM(H12:H14)</f>
         <v>11893</v>
       </c>
-      <c r="I15" s="26">
+      <c r="I15" s="27">
         <f>SUM(I12:I14)</f>
         <v>11893</v>
       </c>
-      <c r="J15" s="26">
+      <c r="J15" s="27">
         <f>SUM(J12:J14)</f>
         <v>11893</v>
       </c>
-      <c r="K15" s="26">
+      <c r="K15" s="27">
         <f>SUM(K12:K14)</f>
         <v>11893</v>
       </c>
-      <c r="L15" s="26" t="str">
+      <c r="L15" s="27" t="str">
         <f>SUM(L12:L14)</f>
         <v>0</v>
       </c>
-      <c r="M15" s="26" t="str">
+      <c r="M15" s="27" t="str">
         <f>SUM(M12:M14)</f>
         <v>0</v>
       </c>
-      <c r="N15" s="26">
+      <c r="N15" s="27">
         <f>SUM(B15:M15)</f>
         <v>118934</v>
       </c>
@@ -4427,598 +4431,598 @@
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="20">
         <v>500</v>
       </c>
-      <c r="C19" s="19">
+      <c r="C19" s="20">
         <v>500</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="20">
         <v>500</v>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="20">
         <v>500</v>
       </c>
-      <c r="F19" s="19">
+      <c r="F19" s="20">
         <v>500</v>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="20">
         <v>500</v>
       </c>
-      <c r="H19" s="19">
+      <c r="H19" s="20">
         <v>500</v>
       </c>
-      <c r="I19" s="19">
+      <c r="I19" s="20">
         <v>500</v>
       </c>
-      <c r="J19" s="19">
+      <c r="J19" s="20">
         <v>500</v>
       </c>
-      <c r="K19" s="19">
+      <c r="K19" s="20">
         <v>500</v>
       </c>
-      <c r="L19" s="19">
-        <v>0</v>
-      </c>
-      <c r="M19" s="19">
-        <v>0</v>
-      </c>
-      <c r="N19" s="19">
+      <c r="L19" s="20">
+        <v>0</v>
+      </c>
+      <c r="M19" s="20">
+        <v>0</v>
+      </c>
+      <c r="N19" s="20">
         <f>SUM(B19:M19)</f>
         <v>5000</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="29">
         <v>500</v>
       </c>
-      <c r="C20" s="28">
+      <c r="C20" s="29">
         <v>500</v>
       </c>
-      <c r="D20" s="28">
+      <c r="D20" s="29">
         <v>500</v>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="29">
         <v>500</v>
       </c>
-      <c r="F20" s="28">
+      <c r="F20" s="29">
         <v>500</v>
       </c>
-      <c r="G20" s="28">
+      <c r="G20" s="29">
         <v>500</v>
       </c>
-      <c r="H20" s="28">
+      <c r="H20" s="29">
         <v>500</v>
       </c>
-      <c r="I20" s="28">
+      <c r="I20" s="29">
         <v>500</v>
       </c>
-      <c r="J20" s="28">
+      <c r="J20" s="29">
         <v>500</v>
       </c>
-      <c r="K20" s="28">
+      <c r="K20" s="29">
         <v>500</v>
       </c>
-      <c r="L20" s="28">
-        <v>0</v>
-      </c>
-      <c r="M20" s="28">
-        <v>0</v>
-      </c>
-      <c r="N20" s="28">
+      <c r="L20" s="29">
+        <v>0</v>
+      </c>
+      <c r="M20" s="29">
+        <v>0</v>
+      </c>
+      <c r="N20" s="29">
         <f>SUM(B20:M20)</f>
         <v>5000</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="20">
         <v>300</v>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="20">
         <v>300</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="20">
         <v>300</v>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="20">
         <v>300</v>
       </c>
-      <c r="F22" s="19">
+      <c r="F22" s="20">
         <v>300</v>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="20">
         <v>300</v>
       </c>
-      <c r="H22" s="19">
+      <c r="H22" s="20">
         <v>300</v>
       </c>
-      <c r="I22" s="19">
+      <c r="I22" s="20">
         <v>300</v>
       </c>
-      <c r="J22" s="19">
+      <c r="J22" s="20">
         <v>300</v>
       </c>
-      <c r="K22" s="19">
+      <c r="K22" s="20">
         <v>300</v>
       </c>
-      <c r="L22" s="19">
-        <v>0</v>
-      </c>
-      <c r="M22" s="19">
-        <v>0</v>
-      </c>
-      <c r="N22" s="19">
+      <c r="L22" s="20">
+        <v>0</v>
+      </c>
+      <c r="M22" s="20">
+        <v>0</v>
+      </c>
+      <c r="N22" s="20">
         <f>SUM(B22:M22)</f>
         <v>3000</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="29">
         <v>300</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="29">
         <v>300</v>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="29">
         <v>300</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="29">
         <v>300</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="29">
         <v>300</v>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="29">
         <v>300</v>
       </c>
-      <c r="H23" s="28">
+      <c r="H23" s="29">
         <v>300</v>
       </c>
-      <c r="I23" s="28">
+      <c r="I23" s="29">
         <v>300</v>
       </c>
-      <c r="J23" s="28">
+      <c r="J23" s="29">
         <v>300</v>
       </c>
-      <c r="K23" s="28">
+      <c r="K23" s="29">
         <v>300</v>
       </c>
-      <c r="L23" s="28">
-        <v>0</v>
-      </c>
-      <c r="M23" s="28">
-        <v>0</v>
-      </c>
-      <c r="N23" s="28">
+      <c r="L23" s="29">
+        <v>0</v>
+      </c>
+      <c r="M23" s="29">
+        <v>0</v>
+      </c>
+      <c r="N23" s="29">
         <f>SUM(B23:M23)</f>
         <v>3000</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="B25" s="19">
+      <c r="B25" s="20">
         <v>2500</v>
       </c>
-      <c r="C25" s="19">
+      <c r="C25" s="20">
         <v>2500</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="20">
         <v>2500</v>
       </c>
-      <c r="E25" s="19">
+      <c r="E25" s="20">
         <v>2500</v>
       </c>
-      <c r="F25" s="19">
+      <c r="F25" s="20">
         <v>2500</v>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="20">
         <v>2500</v>
       </c>
-      <c r="H25" s="19">
+      <c r="H25" s="20">
         <v>2500</v>
       </c>
-      <c r="I25" s="19">
+      <c r="I25" s="20">
         <v>2500</v>
       </c>
-      <c r="J25" s="19">
+      <c r="J25" s="20">
         <v>2500</v>
       </c>
-      <c r="K25" s="19">
+      <c r="K25" s="20">
         <v>2500</v>
       </c>
-      <c r="L25" s="19">
-        <v>0</v>
-      </c>
-      <c r="M25" s="19">
-        <v>0</v>
-      </c>
-      <c r="N25" s="19">
+      <c r="L25" s="20">
+        <v>0</v>
+      </c>
+      <c r="M25" s="20">
+        <v>0</v>
+      </c>
+      <c r="N25" s="20">
         <f>SUM(B25:M25)</f>
         <v>25000</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="B26" s="19">
+      <c r="B26" s="20">
         <v>300</v>
       </c>
-      <c r="C26" s="19">
+      <c r="C26" s="20">
         <v>300</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="20">
         <v>300</v>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="20">
         <v>300</v>
       </c>
-      <c r="F26" s="19">
+      <c r="F26" s="20">
         <v>300</v>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="20">
         <v>300</v>
       </c>
-      <c r="H26" s="19">
+      <c r="H26" s="20">
         <v>300</v>
       </c>
-      <c r="I26" s="19">
+      <c r="I26" s="20">
         <v>300</v>
       </c>
-      <c r="J26" s="19">
+      <c r="J26" s="20">
         <v>300</v>
       </c>
-      <c r="K26" s="19">
+      <c r="K26" s="20">
         <v>300</v>
       </c>
-      <c r="L26" s="19">
-        <v>0</v>
-      </c>
-      <c r="M26" s="19">
-        <v>0</v>
-      </c>
-      <c r="N26" s="19">
+      <c r="L26" s="20">
+        <v>0</v>
+      </c>
+      <c r="M26" s="20">
+        <v>0</v>
+      </c>
+      <c r="N26" s="20">
         <f>SUM(B26:M26)</f>
         <v>3000</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="B27" s="19">
+      <c r="B27" s="20">
         <v>200</v>
       </c>
-      <c r="C27" s="19">
+      <c r="C27" s="20">
         <v>200</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="20">
         <v>200</v>
       </c>
-      <c r="E27" s="19">
+      <c r="E27" s="20">
         <v>200</v>
       </c>
-      <c r="F27" s="19">
+      <c r="F27" s="20">
         <v>200</v>
       </c>
-      <c r="G27" s="19">
+      <c r="G27" s="20">
         <v>200</v>
       </c>
-      <c r="H27" s="19">
+      <c r="H27" s="20">
         <v>200</v>
       </c>
-      <c r="I27" s="19">
+      <c r="I27" s="20">
         <v>200</v>
       </c>
-      <c r="J27" s="19">
+      <c r="J27" s="20">
         <v>200</v>
       </c>
-      <c r="K27" s="19">
+      <c r="K27" s="20">
         <v>200</v>
       </c>
-      <c r="L27" s="19">
-        <v>0</v>
-      </c>
-      <c r="M27" s="19">
-        <v>0</v>
-      </c>
-      <c r="N27" s="19">
+      <c r="L27" s="20">
+        <v>0</v>
+      </c>
+      <c r="M27" s="20">
+        <v>0</v>
+      </c>
+      <c r="N27" s="20">
         <f>SUM(B27:M27)</f>
         <v>2000</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="27" t="s">
+      <c r="A28" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="B28" s="28">
+      <c r="B28" s="29">
         <v>3000</v>
       </c>
-      <c r="C28" s="28">
+      <c r="C28" s="29">
         <v>3000</v>
       </c>
-      <c r="D28" s="28">
+      <c r="D28" s="29">
         <v>3000</v>
       </c>
-      <c r="E28" s="28">
+      <c r="E28" s="29">
         <v>3000</v>
       </c>
-      <c r="F28" s="28">
+      <c r="F28" s="29">
         <v>3000</v>
       </c>
-      <c r="G28" s="28">
+      <c r="G28" s="29">
         <v>3000</v>
       </c>
-      <c r="H28" s="28">
+      <c r="H28" s="29">
         <v>3000</v>
       </c>
-      <c r="I28" s="28">
+      <c r="I28" s="29">
         <v>3000</v>
       </c>
-      <c r="J28" s="28">
+      <c r="J28" s="29">
         <v>3000</v>
       </c>
-      <c r="K28" s="28">
+      <c r="K28" s="29">
         <v>3000</v>
       </c>
-      <c r="L28" s="28">
-        <v>0</v>
-      </c>
-      <c r="M28" s="28">
-        <v>0</v>
-      </c>
-      <c r="N28" s="28">
+      <c r="L28" s="29">
+        <v>0</v>
+      </c>
+      <c r="M28" s="29">
+        <v>0</v>
+      </c>
+      <c r="N28" s="29">
         <f>SUM(B28:M28)</f>
         <v>30000</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="11"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="B30" s="19">
+      <c r="B30" s="20">
         <v>250</v>
       </c>
-      <c r="C30" s="19">
+      <c r="C30" s="20">
         <v>250</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="20">
         <v>250</v>
       </c>
-      <c r="E30" s="19">
+      <c r="E30" s="20">
         <v>250</v>
       </c>
-      <c r="F30" s="19">
+      <c r="F30" s="20">
         <v>250</v>
       </c>
-      <c r="G30" s="19">
+      <c r="G30" s="20">
         <v>250</v>
       </c>
-      <c r="H30" s="19">
+      <c r="H30" s="20">
         <v>250</v>
       </c>
-      <c r="I30" s="19">
+      <c r="I30" s="20">
         <v>250</v>
       </c>
-      <c r="J30" s="19">
+      <c r="J30" s="20">
         <v>250</v>
       </c>
-      <c r="K30" s="19">
+      <c r="K30" s="20">
         <v>250</v>
       </c>
-      <c r="L30" s="19">
-        <v>0</v>
-      </c>
-      <c r="M30" s="19">
-        <v>0</v>
-      </c>
-      <c r="N30" s="19">
+      <c r="L30" s="20">
+        <v>0</v>
+      </c>
+      <c r="M30" s="20">
+        <v>0</v>
+      </c>
+      <c r="N30" s="20">
         <f>SUM(B30:M30)</f>
         <v>2500</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="27" t="s">
+      <c r="A31" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="29">
         <v>250</v>
       </c>
-      <c r="C31" s="28">
+      <c r="C31" s="29">
         <v>250</v>
       </c>
-      <c r="D31" s="28">
+      <c r="D31" s="29">
         <v>250</v>
       </c>
-      <c r="E31" s="28">
+      <c r="E31" s="29">
         <v>250</v>
       </c>
-      <c r="F31" s="28">
+      <c r="F31" s="29">
         <v>250</v>
       </c>
-      <c r="G31" s="28">
+      <c r="G31" s="29">
         <v>250</v>
       </c>
-      <c r="H31" s="28">
+      <c r="H31" s="29">
         <v>250</v>
       </c>
-      <c r="I31" s="28">
+      <c r="I31" s="29">
         <v>250</v>
       </c>
-      <c r="J31" s="28">
+      <c r="J31" s="29">
         <v>250</v>
       </c>
-      <c r="K31" s="28">
+      <c r="K31" s="29">
         <v>250</v>
       </c>
-      <c r="L31" s="28">
-        <v>0</v>
-      </c>
-      <c r="M31" s="28">
-        <v>0</v>
-      </c>
-      <c r="N31" s="28">
+      <c r="L31" s="29">
+        <v>0</v>
+      </c>
+      <c r="M31" s="29">
+        <v>0</v>
+      </c>
+      <c r="N31" s="29">
         <f>SUM(B31:M31)</f>
         <v>2500</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B32" s="26">
+      <c r="B32" s="27">
         <f>B20+B23+B28+B31</f>
         <v>4050</v>
       </c>
-      <c r="C32" s="26">
+      <c r="C32" s="27">
         <f>C20+C23+C28+C31</f>
         <v>4050</v>
       </c>
-      <c r="D32" s="26">
+      <c r="D32" s="27">
         <f>D20+D23+D28+D31</f>
         <v>4050</v>
       </c>
-      <c r="E32" s="26">
+      <c r="E32" s="27">
         <f>E20+E23+E28+E31</f>
         <v>4050</v>
       </c>
-      <c r="F32" s="26">
+      <c r="F32" s="27">
         <f>F20+F23+F28+F31</f>
         <v>4050</v>
       </c>
-      <c r="G32" s="26">
+      <c r="G32" s="27">
         <f>G20+G23+G28+G31</f>
         <v>4050</v>
       </c>
-      <c r="H32" s="26">
+      <c r="H32" s="27">
         <f>H20+H23+H28+H31</f>
         <v>4050</v>
       </c>
-      <c r="I32" s="26">
+      <c r="I32" s="27">
         <f>I20+I23+I28+I31</f>
         <v>4050</v>
       </c>
-      <c r="J32" s="26">
+      <c r="J32" s="27">
         <f>J20+J23+J28+J31</f>
         <v>4050</v>
       </c>
-      <c r="K32" s="26">
+      <c r="K32" s="27">
         <f>K20+K23+K28+K31</f>
         <v>4050</v>
       </c>
-      <c r="L32" s="26" t="str">
+      <c r="L32" s="27" t="str">
         <f>L20+L23+L28+L31</f>
         <v>0</v>
       </c>
-      <c r="M32" s="26" t="str">
+      <c r="M32" s="27" t="str">
         <f>M20+M23+M28+M31</f>
         <v>0</v>
       </c>
-      <c r="N32" s="26">
+      <c r="N32" s="27">
         <f>SUM(B32:M32)</f>
         <v>40500</v>
       </c>
@@ -5029,46 +5033,46 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
+      <c r="A34" s="25" t="s">
         <v>198</v>
       </c>
-      <c r="B34" s="19">
+      <c r="B34" s="20">
         <v>580</v>
       </c>
-      <c r="C34" s="19">
+      <c r="C34" s="20">
         <v>580</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="20">
         <v>580</v>
       </c>
-      <c r="E34" s="19">
+      <c r="E34" s="20">
         <v>580</v>
       </c>
-      <c r="F34" s="19">
+      <c r="F34" s="20">
         <v>580</v>
       </c>
-      <c r="G34" s="19">
+      <c r="G34" s="20">
         <v>580</v>
       </c>
-      <c r="H34" s="19">
+      <c r="H34" s="20">
         <v>580</v>
       </c>
-      <c r="I34" s="19">
+      <c r="I34" s="20">
         <v>580</v>
       </c>
-      <c r="J34" s="19">
+      <c r="J34" s="20">
         <v>580</v>
       </c>
-      <c r="K34" s="19">
+      <c r="K34" s="20">
         <v>580</v>
       </c>
-      <c r="L34" s="19">
+      <c r="L34" s="20">
         <v>580</v>
       </c>
-      <c r="M34" s="19">
+      <c r="M34" s="20">
         <v>580</v>
       </c>
-      <c r="N34" s="19">
+      <c r="N34" s="20">
         <f>SUM(B34:M34)</f>
         <v>6960</v>
       </c>
@@ -5079,244 +5083,244 @@
       </c>
     </row>
     <row r="36" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
-      <c r="N36" s="10"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="11"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="24" t="s">
+      <c r="A37" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="B37" s="28">
+      <c r="B37" s="29">
         <f>B15+B32+B34</f>
         <v>16523</v>
       </c>
-      <c r="C37" s="28">
+      <c r="C37" s="29">
         <f>C15+C32+C34</f>
         <v>16523</v>
       </c>
-      <c r="D37" s="28">
+      <c r="D37" s="29">
         <f>D15+D32+D34</f>
         <v>16523</v>
       </c>
-      <c r="E37" s="28">
+      <c r="E37" s="29">
         <f>E15+E32+E34</f>
         <v>16523</v>
       </c>
-      <c r="F37" s="28">
+      <c r="F37" s="29">
         <f>F15+F32+F34</f>
         <v>16523</v>
       </c>
-      <c r="G37" s="28">
+      <c r="G37" s="29">
         <f>G15+G32+G34</f>
         <v>16523</v>
       </c>
-      <c r="H37" s="28">
+      <c r="H37" s="29">
         <f>H15+H32+H34</f>
         <v>16523</v>
       </c>
-      <c r="I37" s="28">
+      <c r="I37" s="29">
         <f>I15+I32+I34</f>
         <v>16523</v>
       </c>
-      <c r="J37" s="28">
+      <c r="J37" s="29">
         <f>J15+J32+J34</f>
         <v>16523</v>
       </c>
-      <c r="K37" s="28">
+      <c r="K37" s="29">
         <f>K15+K32+K34</f>
         <v>16523</v>
       </c>
-      <c r="L37" s="28">
+      <c r="L37" s="29">
         <f>L15+L32+L34</f>
         <v>580</v>
       </c>
-      <c r="M37" s="28">
+      <c r="M37" s="29">
         <f>M15+M32+M34</f>
         <v>580</v>
       </c>
-      <c r="N37" s="28">
+      <c r="N37" s="29">
         <f>SUM(B37:M37)</f>
         <v>166390</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="24" t="s">
+      <c r="A38" s="25" t="s">
         <v>200</v>
       </c>
-      <c r="B38" s="28">
+      <c r="B38" s="29">
         <f>B9-B37</f>
         <v>139377</v>
       </c>
-      <c r="C38" s="28">
+      <c r="C38" s="29">
         <f>C9-C37</f>
         <v>-9063</v>
       </c>
-      <c r="D38" s="28">
+      <c r="D38" s="29">
         <f>D9-D37</f>
         <v>-9063</v>
       </c>
-      <c r="E38" s="28">
+      <c r="E38" s="29">
         <f>E9-E37</f>
         <v>-9063</v>
       </c>
-      <c r="F38" s="28">
+      <c r="F38" s="29">
         <f>F9-F37</f>
         <v>-9063</v>
       </c>
-      <c r="G38" s="28">
+      <c r="G38" s="29">
         <f>G9-G37</f>
         <v>-9063</v>
       </c>
-      <c r="H38" s="28">
+      <c r="H38" s="29">
         <f>H9-H37</f>
         <v>-9063</v>
       </c>
-      <c r="I38" s="28">
+      <c r="I38" s="29">
         <f>I9-I37</f>
         <v>-9063</v>
       </c>
-      <c r="J38" s="28">
+      <c r="J38" s="29">
         <f>J9-J37</f>
         <v>-9063</v>
       </c>
-      <c r="K38" s="28">
+      <c r="K38" s="29">
         <f>K9-K37</f>
         <v>-9063</v>
       </c>
-      <c r="L38" s="28">
+      <c r="L38" s="29">
         <f>L9-L37</f>
         <v>-2020</v>
       </c>
-      <c r="M38" s="28">
+      <c r="M38" s="29">
         <f>M9-M37</f>
         <v>-580</v>
       </c>
-      <c r="N38" s="28">
+      <c r="N38" s="29">
         <f>SUM(B38:M38)</f>
         <v>55210</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="24" t="s">
+      <c r="A39" s="25" t="s">
         <v>201</v>
       </c>
-      <c r="B39" s="28">
+      <c r="B39" s="29">
         <f>0+B38</f>
         <v>139377</v>
       </c>
-      <c r="C39" s="28">
+      <c r="C39" s="29">
         <f>B39+C38</f>
         <v>130314</v>
       </c>
-      <c r="D39" s="28">
+      <c r="D39" s="29">
         <f>C39+D38</f>
         <v>121251</v>
       </c>
-      <c r="E39" s="28">
+      <c r="E39" s="29">
         <f>D39+E38</f>
         <v>112188</v>
       </c>
-      <c r="F39" s="28">
+      <c r="F39" s="29">
         <f>E39+F38</f>
         <v>103125</v>
       </c>
-      <c r="G39" s="28">
+      <c r="G39" s="29">
         <f>F39+G38</f>
         <v>94062</v>
       </c>
-      <c r="H39" s="28">
+      <c r="H39" s="29">
         <f>G39+H38</f>
         <v>84999</v>
       </c>
-      <c r="I39" s="28">
+      <c r="I39" s="29">
         <f>H39+I38</f>
         <v>75936</v>
       </c>
-      <c r="J39" s="28">
+      <c r="J39" s="29">
         <f>I39+J38</f>
         <v>66873</v>
       </c>
-      <c r="K39" s="28">
+      <c r="K39" s="29">
         <f>J39+K38</f>
         <v>57810</v>
       </c>
-      <c r="L39" s="28">
+      <c r="L39" s="29">
         <f>K39+L38</f>
         <v>55790</v>
       </c>
-      <c r="M39" s="28">
+      <c r="M39" s="29">
         <f>L39+M38</f>
         <v>55210</v>
       </c>
-      <c r="N39" s="28">
+      <c r="N39" s="29">
         <f>M39</f>
         <v>55210</v>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="10" t="s">
+      <c r="A41" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="11" t="s">
+      <c r="A42" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="B42" s="19">
+      <c r="B42" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="11" t="s">
+      <c r="A43" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="B43" s="28">
+      <c r="B43" s="29">
         <f>M39</f>
         <v>55210</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="11" t="s">
+      <c r="A44" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="B44" s="19">
+      <c r="B44" s="20">
         <f>MIN(B39:M39)</f>
         <v>55210</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="22" t="s">
+      <c r="A46" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="B46" s="22"/>
-      <c r="C46" s="22"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="22"/>
-      <c r="F46" s="22"/>
-      <c r="G46" s="22"/>
-      <c r="H46" s="22"/>
-      <c r="I46" s="22"/>
-      <c r="J46" s="22"/>
-      <c r="K46" s="22"/>
-      <c r="L46" s="22"/>
-      <c r="M46" s="22"/>
-      <c r="N46" s="22"/>
+      <c r="B46" s="23"/>
+      <c r="C46" s="23"/>
+      <c r="D46" s="23"/>
+      <c r="E46" s="23"/>
+      <c r="F46" s="23"/>
+      <c r="G46" s="23"/>
+      <c r="H46" s="23"/>
+      <c r="I46" s="23"/>
+      <c r="J46" s="23"/>
+      <c r="K46" s="23"/>
+      <c r="L46" s="23"/>
+      <c r="M46" s="23"/>
+      <c r="N46" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5358,466 +5362,466 @@
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="38" t="s">
         <v>206</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="15" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="C6" s="38">
+      <c r="C6" s="39">
         <v>12</v>
       </c>
-      <c r="D6" s="38">
+      <c r="D6" s="39">
         <v>18</v>
       </c>
-      <c r="E6" s="38">
+      <c r="E6" s="39">
         <v>22</v>
       </c>
-      <c r="F6" s="38">
+      <c r="F6" s="39">
         <v>25</v>
       </c>
-      <c r="G6" s="38">
+      <c r="G6" s="39">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="C7" s="39">
+      <c r="C7" s="40">
         <v>221600</v>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="40">
         <v>338147.49999999994</v>
       </c>
-      <c r="E7" s="39">
+      <c r="E7" s="40">
         <v>422456.3124999999</v>
       </c>
-      <c r="F7" s="39">
+      <c r="F7" s="40">
         <v>491331.3476562498</v>
       </c>
-      <c r="G7" s="39">
+      <c r="G7" s="40">
         <v>503614.631347656</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="C8" s="39">
+      <c r="C8" s="40">
         <v>118934.16666666667</v>
       </c>
-      <c r="D8" s="39">
+      <c r="D8" s="40">
         <v>147002.63</v>
       </c>
-      <c r="E8" s="39">
+      <c r="E8" s="40">
         <v>151412.7089</v>
       </c>
-      <c r="F8" s="39">
+      <c r="F8" s="40">
         <v>155955.090167</v>
       </c>
-      <c r="G8" s="39">
+      <c r="G8" s="40">
         <v>160633.74287201</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="C9" s="39">
+      <c r="C9" s="40">
         <v>48600</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="40">
         <v>54885</v>
       </c>
-      <c r="E9" s="39">
+      <c r="E9" s="40">
         <v>59773.625</v>
       </c>
-      <c r="F9" s="39">
+      <c r="F9" s="40">
         <v>64011.63812499999</v>
       </c>
-      <c r="G9" s="39">
+      <c r="G9" s="40">
         <v>65775.83812812499</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="C10" s="39">
+      <c r="C10" s="40">
         <v>6959.808550594178</v>
       </c>
-      <c r="D10" s="39">
+      <c r="D10" s="40">
         <v>6959.808550594178</v>
       </c>
-      <c r="E10" s="39">
+      <c r="E10" s="40">
         <v>6959.808550594178</v>
       </c>
-      <c r="F10" s="39">
+      <c r="F10" s="40">
         <v>6959.808550594178</v>
       </c>
-      <c r="G10" s="39">
+      <c r="G10" s="40">
         <v>6959.808550594178</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="25" t="s">
         <v>217</v>
       </c>
-      <c r="C11" s="40">
+      <c r="C11" s="41">
         <v>47106.02478273915</v>
       </c>
-      <c r="D11" s="40">
+      <c r="D11" s="41">
         <v>129300.06144940577</v>
       </c>
-      <c r="E11" s="40">
+      <c r="E11" s="41">
         <v>204310.17004940574</v>
       </c>
-      <c r="F11" s="40">
+      <c r="F11" s="41">
         <v>264404.8108136556</v>
       </c>
-      <c r="G11" s="40">
+      <c r="G11" s="41">
         <v>270245.2417969268</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="C12" s="40">
+      <c r="C12" s="41">
         <v>47106.02478273915</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="41">
         <v>176406.0862321449</v>
       </c>
-      <c r="E12" s="40">
+      <c r="E12" s="41">
         <v>380716.2562815506</v>
       </c>
-      <c r="F12" s="40">
+      <c r="F12" s="41">
         <v>645121.0670952062</v>
       </c>
-      <c r="G12" s="40">
+      <c r="G12" s="41">
         <v>915366.3088921331</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="25" t="s">
         <v>218</v>
       </c>
-      <c r="C13" s="41">
+      <c r="C13" s="42">
         <v>0.21257231400153045</v>
       </c>
-      <c r="D13" s="41">
+      <c r="D13" s="42">
         <v>0.3823776944954666</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="42">
         <v>0.4836243748858784</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="42">
         <v>0.5381395102814428</v>
       </c>
-      <c r="G13" s="41">
+      <c r="G13" s="42">
         <v>0.5366111804054611</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="C14" s="39">
+      <c r="C14" s="40">
         <v>18466.666666666668</v>
       </c>
-      <c r="D14" s="39">
+      <c r="D14" s="40">
         <v>18785.97222222222</v>
       </c>
-      <c r="E14" s="39">
+      <c r="E14" s="40">
         <v>19202.559659090904</v>
       </c>
-      <c r="F14" s="39">
+      <c r="F14" s="40">
         <v>19653.253906249993</v>
       </c>
-      <c r="G14" s="39">
+      <c r="G14" s="40">
         <v>20144.58525390624</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="C15" s="41">
+      <c r="C15" s="42">
         <v>0.5367065282791817</v>
       </c>
-      <c r="D15" s="41">
+      <c r="D15" s="42">
         <v>0.4347293119127009</v>
       </c>
-      <c r="E15" s="41">
+      <c r="E15" s="42">
         <v>0.3584103359800075</v>
       </c>
-      <c r="F15" s="41">
+      <c r="F15" s="42">
         <v>0.31741327092386307</v>
       </c>
-      <c r="G15" s="41">
+      <c r="G15" s="42">
         <v>0.31896162834300396</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="C16" s="41">
+      <c r="C16" s="42">
         <v>0.0657942238267148</v>
       </c>
-      <c r="D16" s="41">
+      <c r="D16" s="42">
         <v>0.04869324776909486</v>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="42">
         <v>0.0424471997918128</v>
       </c>
-      <c r="F16" s="41">
+      <c r="F16" s="42">
         <v>0.03908460457307385</v>
       </c>
-      <c r="G16" s="41">
+      <c r="G16" s="42">
         <v>0.03918224414098794</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="25" t="s">
         <v>222</v>
       </c>
-      <c r="C17" s="41">
+      <c r="C17" s="42">
         <v>0.2439793922984356</v>
       </c>
-      <c r="D17" s="41">
+      <c r="D17" s="42">
         <v>0.40295986219031626</v>
       </c>
-      <c r="E17" s="41">
+      <c r="E17" s="42">
         <v>0.5000989980472832</v>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="42">
         <v>0.5523047138325573</v>
       </c>
-      <c r="G17" s="41">
+      <c r="G17" s="42">
         <v>0.5504308911870363</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="C18" s="42">
+      <c r="C18" s="43">
         <v>7.768293185121821</v>
       </c>
-      <c r="D18" s="42">
+      <c r="D18" s="43">
         <v>19.57810606562835</v>
       </c>
-      <c r="E18" s="42">
+      <c r="E18" s="43">
         <v>30.35571698045677</v>
       </c>
-      <c r="F18" s="42">
+      <c r="F18" s="43">
         <v>38.99024195731399</v>
       </c>
-      <c r="G18" s="42">
+      <c r="G18" s="43">
         <v>39.82940742297506</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="25" t="s">
         <v>224</v>
       </c>
-      <c r="C19" s="43" t="s">
+      <c r="C19" s="44" t="s">
         <v>208</v>
       </c>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="43"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="25" t="s">
         <v>225</v>
       </c>
-      <c r="C20" s="43" t="s">
+      <c r="C20" s="44" t="s">
         <v>226</v>
       </c>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10" t="s">
+      <c r="E22" s="11"/>
+      <c r="F22" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="G22" s="10"/>
+      <c r="G22" s="11"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="44" t="s">
+      <c r="B23" s="45" t="s">
         <v>231</v>
       </c>
-      <c r="C23" s="45" t="s">
+      <c r="C23" s="46" t="s">
         <v>232</v>
       </c>
-      <c r="D23" s="46" t="s">
+      <c r="D23" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="E23" s="46"/>
-      <c r="F23" s="47" t="s">
+      <c r="E23" s="47"/>
+      <c r="F23" s="48" t="s">
         <v>234</v>
       </c>
-      <c r="G23" s="47"/>
+      <c r="G23" s="48"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="44" t="s">
+      <c r="B24" s="45" t="s">
         <v>235</v>
       </c>
-      <c r="C24" s="45" t="s">
+      <c r="C24" s="46" t="s">
         <v>232</v>
       </c>
-      <c r="D24" s="46" t="s">
+      <c r="D24" s="47" t="s">
         <v>236</v>
       </c>
-      <c r="E24" s="46"/>
-      <c r="F24" s="47" t="s">
+      <c r="E24" s="47"/>
+      <c r="F24" s="48" t="s">
         <v>237</v>
       </c>
-      <c r="G24" s="47"/>
+      <c r="G24" s="48"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="44" t="s">
+      <c r="B25" s="45" t="s">
         <v>238</v>
       </c>
-      <c r="C25" s="45" t="s">
+      <c r="C25" s="46" t="s">
         <v>232</v>
       </c>
-      <c r="D25" s="46" t="s">
+      <c r="D25" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="E25" s="46"/>
-      <c r="F25" s="47" t="s">
+      <c r="E25" s="47"/>
+      <c r="F25" s="48" t="s">
         <v>240</v>
       </c>
-      <c r="G25" s="47"/>
+      <c r="G25" s="48"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="44" t="s">
+      <c r="B26" s="45" t="s">
         <v>241</v>
       </c>
-      <c r="C26" s="45" t="s">
+      <c r="C26" s="46" t="s">
         <v>232</v>
       </c>
-      <c r="D26" s="46" t="s">
+      <c r="D26" s="47" t="s">
         <v>242</v>
       </c>
-      <c r="E26" s="46"/>
-      <c r="F26" s="47" t="s">
+      <c r="E26" s="47"/>
+      <c r="F26" s="48" t="s">
         <v>243</v>
       </c>
-      <c r="G26" s="47"/>
+      <c r="G26" s="48"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="44" t="s">
+      <c r="B27" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="C27" s="45" t="s">
+      <c r="C27" s="46" t="s">
         <v>232</v>
       </c>
-      <c r="D27" s="46" t="s">
+      <c r="D27" s="47" t="s">
         <v>245</v>
       </c>
-      <c r="E27" s="46"/>
-      <c r="F27" s="47" t="s">
+      <c r="E27" s="47"/>
+      <c r="F27" s="48" t="s">
         <v>246</v>
       </c>
-      <c r="G27" s="47"/>
+      <c r="G27" s="48"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="44" t="s">
+      <c r="B28" s="45" t="s">
         <v>247</v>
       </c>
-      <c r="C28" s="45" t="s">
+      <c r="C28" s="46" t="s">
         <v>232</v>
       </c>
-      <c r="D28" s="46" t="s">
+      <c r="D28" s="47" t="s">
         <v>248</v>
       </c>
-      <c r="E28" s="46"/>
-      <c r="F28" s="47" t="s">
+      <c r="E28" s="47"/>
+      <c r="F28" s="48" t="s">
         <v>249</v>
       </c>
-      <c r="G28" s="47"/>
+      <c r="G28" s="48"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="44" t="s">
+      <c r="B29" s="45" t="s">
         <v>250</v>
       </c>
-      <c r="C29" s="45" t="s">
+      <c r="C29" s="46" t="s">
         <v>232</v>
       </c>
-      <c r="D29" s="46" t="s">
+      <c r="D29" s="47" t="s">
         <v>251</v>
       </c>
-      <c r="E29" s="46"/>
-      <c r="F29" s="47" t="s">
+      <c r="E29" s="47"/>
+      <c r="F29" s="48" t="s">
         <v>252</v>
       </c>
-      <c r="G29" s="47"/>
+      <c r="G29" s="48"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="44" t="s">
+      <c r="B31" s="45" t="s">
         <v>253</v>
       </c>
-      <c r="C31" s="24" t="s">
+      <c r="C31" s="25" t="s">
         <v>254</v>
       </c>
-      <c r="D31" s="24"/>
-      <c r="E31" s="24"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="48" t="s">
+      <c r="B33" s="49" t="s">
         <v>128</v>
       </c>
-      <c r="C33" s="48"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="48"/>
+      <c r="C33" s="49"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="49"/>
+      <c r="G33" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="22">

--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="256">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -122,7 +122,10 @@
     <t>Bright Horizons Microschool - Financial Model Assumptions</t>
   </si>
   <si>
-    <t>Blue cells are editable inputs. All other cells in this workbook are formulas.</t>
+    <t>Editable assumption — change this value</t>
+  </si>
+  <si>
+    <t>Calculated — driven by formula</t>
   </si>
   <si>
     <t>SCHOOL PROFILE</t>
@@ -899,7 +902,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -918,6 +921,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE8EDF2"/>
       </patternFill>
     </fill>
@@ -927,12 +935,21 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -969,7 +986,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -983,64 +1000,65 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1754,724 +1772,730 @@
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>31</v>
       </c>
+      <c r="D2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
+      <c r="A4" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="13" t="s">
+      <c r="A5" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="13" t="s">
+      <c r="A6" s="13" t="s">
         <v>35</v>
       </c>
+      <c r="B6" s="14" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="13" t="s">
+      <c r="A7" s="13" t="s">
         <v>37</v>
       </c>
+      <c r="B7" s="14" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="13" t="s">
+      <c r="A8" s="13" t="s">
         <v>39</v>
       </c>
+      <c r="B8" s="14" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="13" t="s">
+      <c r="A9" s="13" t="s">
         <v>41</v>
       </c>
+      <c r="B9" s="14" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="13" t="s">
+      <c r="A10" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
+      <c r="B10" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="13" t="s">
+      <c r="A11" s="13" t="s">
         <v>45</v>
       </c>
+      <c r="B11" s="14" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="14">
+      <c r="A12" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="15">
         <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="12" t="s">
+      <c r="A13" s="13" t="s">
         <v>48</v>
       </c>
+      <c r="B13" s="13" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="12" t="s">
+      <c r="A14" s="13" t="s">
         <v>50</v>
       </c>
+      <c r="B14" s="13" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="15" t="s">
+      <c r="A16" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="B16" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="C16" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="D16" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="E16" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="11"/>
+      <c r="F16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16" s="12"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B17" s="16">
+      <c r="A17" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="17">
         <v>12</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="17">
         <v>18</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="17">
         <v>22</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="17">
         <v>25</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="17">
         <v>25</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19" s="11" t="s">
+      <c r="A19" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="B19" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="C19" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="D19" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="E19" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="F19" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="H19" s="11" t="s">
+      <c r="G19" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
+      <c r="H19" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D20" s="18">
+        <v>12000</v>
+      </c>
+      <c r="E20" s="19">
+        <v>0</v>
+      </c>
+      <c r="F20" s="15">
+        <v>10</v>
+      </c>
+      <c r="G20" s="19">
+        <v>1</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="18">
+        <v>250</v>
+      </c>
+      <c r="E21" s="19">
+        <v>0</v>
+      </c>
+      <c r="F21" s="15">
+        <v>12</v>
+      </c>
+      <c r="G21" s="19">
+        <v>1</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" s="18">
+        <v>7000</v>
+      </c>
+      <c r="E22" s="19">
+        <v>0</v>
+      </c>
+      <c r="F22" s="15">
+        <v>12</v>
+      </c>
+      <c r="G22" s="19">
+        <v>1</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="18">
+        <v>5000</v>
+      </c>
+      <c r="E23" s="19">
+        <v>0</v>
+      </c>
+      <c r="F23" s="15">
+        <v>12</v>
+      </c>
+      <c r="G23" s="19">
+        <v>1</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="18">
+        <v>10</v>
+      </c>
+      <c r="E24" s="19">
+        <v>0</v>
+      </c>
+      <c r="F24" s="15">
+        <v>12</v>
+      </c>
+      <c r="G24" s="19">
+        <v>1</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D28" s="20">
+        <v>1</v>
+      </c>
+      <c r="E28" s="18">
+        <v>55000</v>
+      </c>
+      <c r="F28" s="19">
+        <v>0.2</v>
+      </c>
+      <c r="G28" s="19">
+        <v>0.0765</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" s="20">
+        <v>1</v>
+      </c>
+      <c r="E29" s="18">
+        <v>45000</v>
+      </c>
+      <c r="F29" s="19">
+        <v>0.2</v>
+      </c>
+      <c r="G29" s="19">
+        <v>0.0765</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D30" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="E30" s="18">
+        <v>28000</v>
+      </c>
+      <c r="F30" s="19">
+        <v>0</v>
+      </c>
+      <c r="G30" s="19">
+        <v>0.0765</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D32" s="12"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" s="18">
+        <v>2500</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B35" s="19">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F37" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" s="17">
-        <v>12000</v>
-      </c>
-      <c r="E20" s="18">
-        <v>0</v>
-      </c>
-      <c r="F20" s="14">
-        <v>10</v>
-      </c>
-      <c r="G20" s="18">
-        <v>1</v>
-      </c>
-      <c r="H20" s="12" t="s">
+      <c r="G37" s="12"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D38" s="18">
+        <v>2500</v>
+      </c>
+      <c r="E38" s="19">
+        <v>0.03</v>
+      </c>
+      <c r="F38" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D39" s="18">
+        <v>300</v>
+      </c>
+      <c r="E39" s="19">
+        <v>0</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40" s="18">
+        <v>2400</v>
+      </c>
+      <c r="E40" s="19">
+        <v>0</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C41" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="B21" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D21" s="17">
-        <v>250</v>
-      </c>
-      <c r="E21" s="18">
-        <v>0</v>
-      </c>
-      <c r="F21" s="14">
-        <v>12</v>
-      </c>
-      <c r="G21" s="18">
-        <v>1</v>
-      </c>
-      <c r="H21" s="12" t="s">
+      <c r="D41" s="18">
+        <v>500</v>
+      </c>
+      <c r="E41" s="19">
+        <v>0</v>
+      </c>
+      <c r="F41" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="17">
-        <v>7000</v>
-      </c>
-      <c r="E22" s="18">
-        <v>0</v>
-      </c>
-      <c r="F22" s="14">
-        <v>12</v>
-      </c>
-      <c r="G22" s="18">
-        <v>1</v>
-      </c>
-      <c r="H22" s="12" t="s">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D42" s="18">
+        <v>300</v>
+      </c>
+      <c r="E42" s="19">
+        <v>0</v>
+      </c>
+      <c r="F42" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D23" s="17">
-        <v>5000</v>
-      </c>
-      <c r="E23" s="18">
-        <v>0</v>
-      </c>
-      <c r="F23" s="14">
-        <v>12</v>
-      </c>
-      <c r="G23" s="18">
-        <v>1</v>
-      </c>
-      <c r="H23" s="12" t="s">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D43" s="18">
+        <v>3000</v>
+      </c>
+      <c r="E43" s="19">
+        <v>0</v>
+      </c>
+      <c r="F43" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D24" s="17">
-        <v>10</v>
-      </c>
-      <c r="E24" s="18">
-        <v>0</v>
-      </c>
-      <c r="F24" s="14">
-        <v>12</v>
-      </c>
-      <c r="G24" s="18">
-        <v>1</v>
-      </c>
-      <c r="H24" s="12" t="s">
+    <row r="45" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="H45" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C46" s="21">
+        <v>0</v>
+      </c>
+      <c r="D46" s="18">
+        <v>30000</v>
+      </c>
+      <c r="E46" s="22">
+        <v>0.06</v>
+      </c>
+      <c r="F46" s="15">
+        <v>5</v>
+      </c>
+      <c r="G46" s="21">
+        <v>6960</v>
+      </c>
+      <c r="H46" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="G27" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="H27" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D28" s="19">
-        <v>1</v>
-      </c>
-      <c r="E28" s="17">
-        <v>55000</v>
-      </c>
-      <c r="F28" s="18">
-        <v>0.2</v>
-      </c>
-      <c r="G28" s="18">
-        <v>0.0765</v>
-      </c>
-      <c r="H28" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="I28" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D29" s="19">
-        <v>1</v>
-      </c>
-      <c r="E29" s="17">
-        <v>45000</v>
-      </c>
-      <c r="F29" s="18">
-        <v>0.2</v>
-      </c>
-      <c r="G29" s="18">
-        <v>0.0765</v>
-      </c>
-      <c r="H29" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="I29" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" s="19">
-        <v>0.5</v>
-      </c>
-      <c r="E30" s="17">
-        <v>28000</v>
-      </c>
-      <c r="F30" s="18">
-        <v>0</v>
-      </c>
-      <c r="G30" s="18">
-        <v>0.0765</v>
-      </c>
-      <c r="H30" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="I30" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="D32" s="11"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="B34" s="17">
-        <v>2500</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="B35" s="18">
+    <row r="48" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B48" s="12"/>
+      <c r="C48" s="12"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B49" s="19">
         <v>0.03</v>
       </c>
     </row>
-    <row r="37" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="G37" s="11"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="D38" s="17">
-        <v>2500</v>
-      </c>
-      <c r="E38" s="18">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="B50" s="19">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B51" s="20">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="C51" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="B52" s="19">
         <v>0.03</v>
       </c>
-      <c r="F38" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="D39" s="17">
-        <v>300</v>
-      </c>
-      <c r="E39" s="18">
-        <v>0</v>
-      </c>
-      <c r="F39" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D40" s="17">
-        <v>2400</v>
-      </c>
-      <c r="E40" s="18">
-        <v>0</v>
-      </c>
-      <c r="F40" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D41" s="17">
-        <v>500</v>
-      </c>
-      <c r="E41" s="18">
-        <v>0</v>
-      </c>
-      <c r="F41" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D42" s="17">
-        <v>300</v>
-      </c>
-      <c r="E42" s="18">
-        <v>0</v>
-      </c>
-      <c r="F42" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D43" s="17">
-        <v>3000</v>
-      </c>
-      <c r="E43" s="18">
-        <v>0</v>
-      </c>
-      <c r="F43" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="B45" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C45" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="E45" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="F45" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="G45" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="H45" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="C46" s="20">
-        <v>0</v>
-      </c>
-      <c r="D46" s="17">
-        <v>30000</v>
-      </c>
-      <c r="E46" s="21">
-        <v>0.06</v>
-      </c>
-      <c r="F46" s="14">
-        <v>5</v>
-      </c>
-      <c r="G46" s="20">
-        <v>6960</v>
-      </c>
-      <c r="H46" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="B49" s="18">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="B50" s="18">
-        <v>0.025</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="B51" s="19">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="C51" s="22" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="B52" s="18">
-        <v>0.03</v>
-      </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="B53" s="18">
+      <c r="A53" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="B53" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="B54" s="17">
+      <c r="A54" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B54" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="B56" s="23"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="23"/>
-      <c r="G56" s="23"/>
+      <c r="A56" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="B56" s="24"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="24"/>
+      <c r="E56" s="24"/>
+      <c r="F56" s="24"/>
+      <c r="G56" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2503,7 +2527,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -2512,741 +2536,741 @@
       <c r="F1" s="8"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="24" t="s">
+      <c r="B2" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="C2" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="D2" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="E2" s="25" t="s">
         <v>56</v>
       </c>
+      <c r="F2" s="25" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" s="26">
+      <c r="A3" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="27">
         <f>Assumptions!B17</f>
         <v>12</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="27">
         <f>Assumptions!C17</f>
         <v>18</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="27">
         <f>Assumptions!D17</f>
         <v>22</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="27">
         <f>Assumptions!E17</f>
         <v>25</v>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="27">
         <f>Assumptions!F17</f>
         <v>25</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
+      <c r="A5" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6" s="20">
+      <c r="A6" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="21">
         <v>120000</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="21">
         <v>221400</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="21">
         <v>277365</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="21">
         <v>323067</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="21">
         <v>331144</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="20">
+      <c r="A7" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="21">
         <v>2500</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="21">
         <v>4613</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="21">
         <v>5778</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="21">
         <v>6731</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="21">
         <v>6899</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8" s="20">
+      <c r="A8" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="21">
         <v>70000</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="21">
         <v>129150</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="21">
         <v>161796</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="21">
         <v>188456</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="21">
         <v>193167</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="B9" s="20">
+      <c r="A9" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="21">
         <v>4167</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="21">
         <v>5125</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="21">
         <v>5253</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="21">
         <v>5384</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="21">
         <v>5519</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B10" s="20">
+      <c r="A10" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="21">
         <v>-12000</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="21">
         <v>-22140</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="21">
         <v>-27736</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="21">
         <v>-32307</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="21">
         <v>-33114</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B11" s="27">
+      <c r="A11" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B11" s="28">
         <f>SUM(B6:B10)</f>
         <v>184667</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="28">
         <f>SUM(C6:C10)</f>
         <v>338147</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="28">
         <f>SUM(D6:D10)</f>
         <v>422456</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="28">
         <f>SUM(E6:E10)</f>
         <v>491331</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="28">
         <f>SUM(F6:F10)</f>
         <v>503615</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
+      <c r="A13" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="B14" s="20">
+      <c r="A14" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B14" s="21">
         <v>58506</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="21">
         <v>72314</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="21">
         <v>74483</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="21">
         <v>76718</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="21">
         <v>79019</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="B15" s="20">
+      <c r="A15" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B15" s="21">
         <v>47869</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="21">
         <v>59166</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="21">
         <v>60941</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="21">
         <v>62769</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="21">
         <v>64652</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="B16" s="20">
+      <c r="A16" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="B16" s="21">
         <v>12559</v>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="21">
         <v>15523</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="21">
         <v>15989</v>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="21">
         <v>16468</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="21">
         <v>16963</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="B17" s="27">
+      <c r="A17" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B17" s="28">
         <f>SUM(B14:B16)</f>
         <v>118934</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="28">
         <f>SUM(C14:C16)</f>
         <v>147003</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="28">
         <f>SUM(D14:D16)</f>
         <v>151413</v>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="28">
         <f>SUM(E14:E16)</f>
         <v>155955</v>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="28">
         <f>SUM(F14:F16)</f>
         <v>160634</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
+      <c r="A19" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
+      <c r="A20" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="B21" s="20">
+      <c r="A21" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B21" s="21">
         <v>5000</v>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="21">
         <v>9225</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="21">
         <v>11557</v>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="21">
         <v>13461</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="21">
         <v>13798</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="B22" s="29">
+      <c r="A22" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="B22" s="30">
         <v>5000</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="30">
         <v>9225</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="30">
         <v>11557</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="30">
         <v>13461</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="30">
         <v>13798</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
+      <c r="A23" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="B24" s="20">
+      <c r="A24" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="B24" s="21">
         <v>3000</v>
       </c>
-      <c r="C24" s="20">
+      <c r="C24" s="21">
         <v>5535</v>
       </c>
-      <c r="D24" s="20">
+      <c r="D24" s="21">
         <v>6934</v>
       </c>
-      <c r="E24" s="20">
+      <c r="E24" s="21">
         <v>8077</v>
       </c>
-      <c r="F24" s="20">
+      <c r="F24" s="21">
         <v>8279</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="28" t="s">
-        <v>140</v>
-      </c>
-      <c r="B25" s="29">
+      <c r="A25" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="B25" s="30">
         <v>3000</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="30">
         <v>5535</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="30">
         <v>6934</v>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="30">
         <v>8077</v>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="30">
         <v>8279</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
+      <c r="A26" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="B27" s="20">
+      <c r="A27" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="B27" s="21">
         <v>25000</v>
       </c>
-      <c r="C27" s="20">
+      <c r="C27" s="21">
         <v>30900</v>
       </c>
-      <c r="D27" s="20">
+      <c r="D27" s="21">
         <v>31827</v>
       </c>
-      <c r="E27" s="20">
+      <c r="E27" s="21">
         <v>32782</v>
       </c>
-      <c r="F27" s="20">
+      <c r="F27" s="21">
         <v>33765</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="B28" s="20">
+      <c r="A28" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B28" s="21">
         <v>3000</v>
       </c>
-      <c r="C28" s="20">
+      <c r="C28" s="21">
         <v>3690</v>
       </c>
-      <c r="D28" s="20">
+      <c r="D28" s="21">
         <v>3782</v>
       </c>
-      <c r="E28" s="20">
+      <c r="E28" s="21">
         <v>3877</v>
       </c>
-      <c r="F28" s="20">
+      <c r="F28" s="21">
         <v>3974</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="B29" s="20">
+      <c r="A29" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" s="21">
         <v>2000</v>
       </c>
-      <c r="C29" s="20">
+      <c r="C29" s="21">
         <v>2460</v>
       </c>
-      <c r="D29" s="20">
+      <c r="D29" s="21">
         <v>2522</v>
       </c>
-      <c r="E29" s="20">
+      <c r="E29" s="21">
         <v>2585</v>
       </c>
-      <c r="F29" s="20">
+      <c r="F29" s="21">
         <v>2649</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="B30" s="29">
+      <c r="A30" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="B30" s="30">
         <v>30000</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C30" s="30">
         <v>37050</v>
       </c>
-      <c r="D30" s="29">
+      <c r="D30" s="30">
         <v>38131</v>
       </c>
-      <c r="E30" s="29">
+      <c r="E30" s="30">
         <v>39244</v>
       </c>
-      <c r="F30" s="29">
+      <c r="F30" s="30">
         <v>40388</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
+      <c r="A31" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="B32" s="20">
+      <c r="A32" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="B32" s="21">
         <v>2500</v>
       </c>
-      <c r="C32" s="20">
+      <c r="C32" s="21">
         <v>3075</v>
       </c>
-      <c r="D32" s="20">
+      <c r="D32" s="21">
         <v>3152</v>
       </c>
-      <c r="E32" s="20">
+      <c r="E32" s="21">
         <v>3231</v>
       </c>
-      <c r="F32" s="20">
+      <c r="F32" s="21">
         <v>3311</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="28" t="s">
-        <v>146</v>
-      </c>
-      <c r="B33" s="29">
+      <c r="A33" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="B33" s="30">
         <v>2500</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C33" s="30">
         <v>3075</v>
       </c>
-      <c r="D33" s="29">
+      <c r="D33" s="30">
         <v>3152</v>
       </c>
-      <c r="E33" s="29">
+      <c r="E33" s="30">
         <v>3231</v>
       </c>
-      <c r="F33" s="29">
+      <c r="F33" s="30">
         <v>3311</v>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="B34" s="27">
+      <c r="A34" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B34" s="28">
         <f>B22+B25+B30+B33</f>
         <v>40500</v>
       </c>
-      <c r="C34" s="27">
+      <c r="C34" s="28">
         <f>C22+C25+C30+C33</f>
         <v>54885</v>
       </c>
-      <c r="D34" s="27">
+      <c r="D34" s="28">
         <f>D22+D25+D30+D33</f>
         <v>59774</v>
       </c>
-      <c r="E34" s="27">
+      <c r="E34" s="28">
         <f>E22+E25+E30+E33</f>
         <v>64012</v>
       </c>
-      <c r="F34" s="27">
+      <c r="F34" s="28">
         <f>F22+F25+F30+F33</f>
         <v>65776</v>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
+      <c r="A36" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="B37" s="20">
+      <c r="A37" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B37" s="21">
         <v>6960</v>
       </c>
-      <c r="C37" s="20">
+      <c r="C37" s="21">
         <v>6960</v>
       </c>
-      <c r="D37" s="20">
+      <c r="D37" s="21">
         <v>6960</v>
       </c>
-      <c r="E37" s="20">
+      <c r="E37" s="21">
         <v>6960</v>
       </c>
-      <c r="F37" s="20">
+      <c r="F37" s="21">
         <v>6960</v>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="B38" s="27">
+      <c r="A38" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B38" s="28">
         <f>SUM(B37:B37)</f>
         <v>6960</v>
       </c>
-      <c r="C38" s="27">
+      <c r="C38" s="28">
         <f>SUM(C37:C37)</f>
         <v>6960</v>
       </c>
-      <c r="D38" s="27">
+      <c r="D38" s="28">
         <f>SUM(D37:D37)</f>
         <v>6960</v>
       </c>
-      <c r="E38" s="27">
+      <c r="E38" s="28">
         <f>SUM(E37:E37)</f>
         <v>6960</v>
       </c>
-      <c r="F38" s="27">
+      <c r="F38" s="28">
         <f>SUM(F37:F37)</f>
         <v>6960</v>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
+      <c r="A40" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="B41" s="29">
+      <c r="A41" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="B41" s="30">
         <f>B11</f>
         <v>184667</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C41" s="30">
         <f>C11</f>
         <v>338147</v>
       </c>
-      <c r="D41" s="29">
+      <c r="D41" s="30">
         <f>D11</f>
         <v>422456</v>
       </c>
-      <c r="E41" s="29">
+      <c r="E41" s="30">
         <f>E11</f>
         <v>491331</v>
       </c>
-      <c r="F41" s="29">
+      <c r="F41" s="30">
         <f>F11</f>
         <v>503615</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="B42" s="20">
+      <c r="A42" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="B42" s="21">
         <f>B17</f>
         <v>118934</v>
       </c>
-      <c r="C42" s="20">
+      <c r="C42" s="21">
         <f>C17</f>
         <v>147003</v>
       </c>
-      <c r="D42" s="20">
+      <c r="D42" s="21">
         <f>D17</f>
         <v>151413</v>
       </c>
-      <c r="E42" s="20">
+      <c r="E42" s="21">
         <f>E17</f>
         <v>155955</v>
       </c>
-      <c r="F42" s="20">
+      <c r="F42" s="21">
         <f>F17</f>
         <v>160634</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="B43" s="20">
+      <c r="A43" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="B43" s="21">
         <f>B34</f>
         <v>40500</v>
       </c>
-      <c r="C43" s="20">
+      <c r="C43" s="21">
         <f>C34</f>
         <v>54885</v>
       </c>
-      <c r="D43" s="20">
+      <c r="D43" s="21">
         <f>D34</f>
         <v>59774</v>
       </c>
-      <c r="E43" s="20">
+      <c r="E43" s="21">
         <f>E34</f>
         <v>64012</v>
       </c>
-      <c r="F43" s="20">
+      <c r="F43" s="21">
         <f>F34</f>
         <v>65776</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="B44" s="20">
+      <c r="A44" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="B44" s="21">
         <f>B38</f>
         <v>6960</v>
       </c>
-      <c r="C44" s="20">
+      <c r="C44" s="21">
         <f>C38</f>
         <v>6960</v>
       </c>
-      <c r="D44" s="20">
+      <c r="D44" s="21">
         <f>D38</f>
         <v>6960</v>
       </c>
-      <c r="E44" s="20">
+      <c r="E44" s="21">
         <f>E38</f>
         <v>6960</v>
       </c>
-      <c r="F44" s="20">
+      <c r="F44" s="21">
         <f>F38</f>
         <v>6960</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="B45" s="29">
+      <c r="A45" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="B45" s="30">
         <f>B42+B43+B44</f>
         <v>166394</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C45" s="30">
         <f>C42+C43+C44</f>
         <v>208848</v>
       </c>
-      <c r="D45" s="29">
+      <c r="D45" s="30">
         <f>D42+D43+D44</f>
         <v>218147</v>
       </c>
-      <c r="E45" s="29">
+      <c r="E45" s="30">
         <f>E42+E43+E44</f>
         <v>226927</v>
       </c>
-      <c r="F45" s="29">
+      <c r="F45" s="30">
         <f>F42+F43+F44</f>
         <v>233370</v>
       </c>
@@ -3257,569 +3281,569 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="B47" s="31">
+      <c r="A47" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="B47" s="32">
         <f>B41-B45</f>
         <v>18273</v>
       </c>
-      <c r="C47" s="31">
+      <c r="C47" s="32">
         <f>C41-C45</f>
         <v>129299</v>
       </c>
-      <c r="D47" s="31">
+      <c r="D47" s="32">
         <f>D41-D45</f>
         <v>204309</v>
       </c>
-      <c r="E47" s="31">
+      <c r="E47" s="32">
         <f>E41-E45</f>
         <v>264404</v>
       </c>
-      <c r="F47" s="31">
+      <c r="F47" s="32">
         <f>F41-F45</f>
         <v>270245</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="B48" s="32">
+      <c r="A48" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="B48" s="33">
         <f>IF(B41=0,"",B47/B41)</f>
         <v>0.1</v>
       </c>
-      <c r="C48" s="32">
+      <c r="C48" s="33">
         <f>IF(C41=0,"",C47/C41)</f>
         <v>0.38</v>
       </c>
-      <c r="D48" s="32">
+      <c r="D48" s="33">
         <f>IF(D41=0,"",D47/D41)</f>
         <v>0.48</v>
       </c>
-      <c r="E48" s="32">
+      <c r="E48" s="33">
         <f>IF(E41=0,"",E47/E41)</f>
         <v>0.54</v>
       </c>
-      <c r="F48" s="32">
+      <c r="F48" s="33">
         <f>IF(F41=0,"",F47/F41)</f>
         <v>0.54</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="B49" s="20">
+      <c r="A49" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="B49" s="21">
         <f>B47</f>
         <v>18273</v>
       </c>
-      <c r="C49" s="20">
+      <c r="C49" s="21">
         <f>B49+C47</f>
         <v>147572</v>
       </c>
-      <c r="D49" s="20">
+      <c r="D49" s="21">
         <f>C49+D47</f>
         <v>351881</v>
       </c>
-      <c r="E49" s="20">
+      <c r="E49" s="21">
         <f>D49+E47</f>
         <v>616285</v>
       </c>
-      <c r="F49" s="20">
+      <c r="F49" s="21">
         <f>E49+F47</f>
         <v>886530</v>
       </c>
     </row>
     <row r="51" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="11"/>
+      <c r="A51" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="B51" s="12"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="B52" s="29">
+      <c r="A52" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="B52" s="30">
         <f>B41-B42-B43</f>
         <v>25233</v>
       </c>
-      <c r="C52" s="29">
+      <c r="C52" s="30">
         <f>C41-C42-C43</f>
         <v>136259</v>
       </c>
-      <c r="D52" s="29">
+      <c r="D52" s="30">
         <f>D41-D42-D43</f>
         <v>211269</v>
       </c>
-      <c r="E52" s="29">
+      <c r="E52" s="30">
         <f>E41-E42-E43</f>
         <v>271364</v>
       </c>
-      <c r="F52" s="29">
+      <c r="F52" s="30">
         <f>F41-F42-F43</f>
         <v>277205</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="B53" s="20">
+      <c r="A53" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="B53" s="21">
         <f>B44</f>
         <v>6960</v>
       </c>
-      <c r="C53" s="20">
+      <c r="C53" s="21">
         <f>C44</f>
         <v>6960</v>
       </c>
-      <c r="D53" s="20">
+      <c r="D53" s="21">
         <f>D44</f>
         <v>6960</v>
       </c>
-      <c r="E53" s="20">
+      <c r="E53" s="21">
         <f>E44</f>
         <v>6960</v>
       </c>
-      <c r="F53" s="20">
+      <c r="F53" s="21">
         <f>F44</f>
         <v>6960</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="B54" s="33">
+      <c r="A54" s="26" t="s">
+        <v>163</v>
+      </c>
+      <c r="B54" s="34">
         <f>IF(B53=0,"N/A",B52/B53)</f>
         <v>3.63</v>
       </c>
-      <c r="C54" s="33">
+      <c r="C54" s="34">
         <f>IF(C53=0,"N/A",C52/C53)</f>
         <v>19.58</v>
       </c>
-      <c r="D54" s="33">
+      <c r="D54" s="34">
         <f>IF(D53=0,"N/A",D52/D53)</f>
         <v>30.35</v>
       </c>
-      <c r="E54" s="33">
+      <c r="E54" s="34">
         <f>IF(E53=0,"N/A",E52/E53)</f>
         <v>38.99</v>
       </c>
-      <c r="F54" s="33">
+      <c r="F54" s="34">
         <f>IF(F53=0,"N/A",F52/F53)</f>
         <v>39.83</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="B55" s="20" t="str">
+      <c r="A55" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B55" s="21" t="str">
         <f>Assumptions!B54</f>
         <v>0</v>
       </c>
-      <c r="C55" s="20">
+      <c r="C55" s="21">
         <f>B56</f>
         <v>18273</v>
       </c>
-      <c r="D55" s="20">
+      <c r="D55" s="21">
         <f>C56</f>
         <v>147572</v>
       </c>
-      <c r="E55" s="20">
+      <c r="E55" s="21">
         <f>D56</f>
         <v>351881</v>
       </c>
-      <c r="F55" s="20">
+      <c r="F55" s="21">
         <f>E56</f>
         <v>616285</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="25" t="s">
-        <v>163</v>
-      </c>
-      <c r="B56" s="29">
+      <c r="A56" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="B56" s="30">
         <f>B55+B47</f>
         <v>18273</v>
       </c>
-      <c r="C56" s="29">
+      <c r="C56" s="30">
         <f>C55+C47</f>
         <v>147572</v>
       </c>
-      <c r="D56" s="29">
+      <c r="D56" s="30">
         <f>D55+D47</f>
         <v>351881</v>
       </c>
-      <c r="E56" s="29">
+      <c r="E56" s="30">
         <f>E55+E47</f>
         <v>616285</v>
       </c>
-      <c r="F56" s="29">
+      <c r="F56" s="30">
         <f>F55+F47</f>
         <v>886530</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="B57" s="34">
+      <c r="A57" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="B57" s="35">
         <f>IF(B45=0,"",B56/B45*365)</f>
         <v>40</v>
       </c>
-      <c r="C57" s="34">
+      <c r="C57" s="35">
         <f>IF(C45=0,"",C56/C45*365)</f>
         <v>258</v>
       </c>
-      <c r="D57" s="34">
+      <c r="D57" s="35">
         <f>IF(D45=0,"",D56/D45*365)</f>
         <v>589</v>
       </c>
-      <c r="E57" s="34">
+      <c r="E57" s="35">
         <f>IF(E45=0,"",E56/E45*365)</f>
         <v>991</v>
       </c>
-      <c r="F57" s="34">
+      <c r="F57" s="35">
         <f>IF(F45=0,"",F56/F45*365)</f>
         <v>1387</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="B58" s="35">
+      <c r="A58" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="B58" s="36">
         <f>IF(B45=0,"",B56/(B45/12))</f>
         <v>1.3</v>
       </c>
-      <c r="C58" s="35">
+      <c r="C58" s="36">
         <f>IF(C45=0,"",C56/(C45/12))</f>
         <v>8.5</v>
       </c>
-      <c r="D58" s="35">
+      <c r="D58" s="36">
         <f>IF(D45=0,"",D56/(D45/12))</f>
         <v>19.4</v>
       </c>
-      <c r="E58" s="35">
+      <c r="E58" s="36">
         <f>IF(E45=0,"",E56/(E45/12))</f>
         <v>32.6</v>
       </c>
-      <c r="F58" s="35">
+      <c r="F58" s="36">
         <f>IF(F45=0,"",F56/(F45/12))</f>
         <v>45.6</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="B59" s="32">
+      <c r="A59" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="B59" s="33">
         <f>IF(Assumptions!B12=0,"",B3/Assumptions!B12)</f>
         <v>0.48</v>
       </c>
-      <c r="C59" s="32">
+      <c r="C59" s="33">
         <f>IF(Assumptions!B12=0,"",C3/Assumptions!B12)</f>
         <v>0.72</v>
       </c>
-      <c r="D59" s="32">
+      <c r="D59" s="33">
         <f>IF(Assumptions!B12=0,"",D3/Assumptions!B12)</f>
         <v>0.88</v>
       </c>
-      <c r="E59" s="32">
+      <c r="E59" s="33">
         <f>IF(Assumptions!B12=0,"",E3/Assumptions!B12)</f>
         <v>1</v>
       </c>
-      <c r="F59" s="32">
+      <c r="F59" s="33">
         <f>IF(Assumptions!B12=0,"",F3/Assumptions!B12)</f>
         <v>1</v>
       </c>
     </row>
     <row r="61" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B61" s="11"/>
-      <c r="C61" s="11"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
+      <c r="A61" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="B61" s="12"/>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="B62" s="12" t="str">
+      <c r="A62" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="B62" s="13" t="str">
         <f>IF(B53=0,"N/A",IF(B54&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="C62" s="12" t="str">
+      <c r="C62" s="13" t="str">
         <f>IF(C53=0,"N/A",IF(C54&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="D62" s="12" t="str">
+      <c r="D62" s="13" t="str">
         <f>IF(D53=0,"N/A",IF(D54&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E62" s="12" t="str">
+      <c r="E62" s="13" t="str">
         <f>IF(E53=0,"N/A",IF(E54&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F62" s="12" t="str">
+      <c r="F62" s="13" t="str">
         <f>IF(F53=0,"N/A",IF(F54&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="B63" s="12" t="str">
+      <c r="A63" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="B63" s="13" t="str">
         <f>IF(B47&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="C63" s="12" t="str">
+      <c r="C63" s="13" t="str">
         <f>IF(C47&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="D63" s="12" t="str">
+      <c r="D63" s="13" t="str">
         <f>IF(D47&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E63" s="12" t="str">
+      <c r="E63" s="13" t="str">
         <f>IF(E47&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="F63" s="12" t="str">
+      <c r="F63" s="13" t="str">
         <f>IF(F47&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="B64" s="12" t="str">
+      <c r="A64" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="B64" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(B3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C64" s="12" t="str">
+      <c r="C64" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(C3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="D64" s="12" t="str">
+      <c r="D64" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(D3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E64" s="12" t="str">
+      <c r="E64" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(E3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F64" s="12" t="str">
+      <c r="F64" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(F3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="B65" s="12" t="str">
+      <c r="A65" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="B65" s="13" t="str">
         <f>IF(B45=0,"N/A",IF(B56/(B45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C65" s="12" t="str">
+      <c r="C65" s="13" t="str">
         <f>IF(C45=0,"N/A",IF(C56/(C45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="D65" s="12" t="str">
+      <c r="D65" s="13" t="str">
         <f>IF(D45=0,"N/A",IF(D56/(D45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E65" s="12" t="str">
+      <c r="E65" s="13" t="str">
         <f>IF(E45=0,"N/A",IF(E56/(E45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F65" s="12" t="str">
+      <c r="F65" s="13" t="str">
         <f>IF(F45=0,"N/A",IF(F56/(F45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="67" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="B67" s="11"/>
-      <c r="C67" s="11"/>
-      <c r="D67" s="11"/>
-      <c r="E67" s="11"/>
-      <c r="F67" s="11"/>
+      <c r="A67" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="B67" s="12"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="12"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="B68" s="20">
+      <c r="A68" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="B68" s="21">
         <f>IF(B3=0,"",B11/B3)</f>
         <v>15389</v>
       </c>
-      <c r="C68" s="20">
+      <c r="C68" s="21">
         <f>IF(C3=0,"",C11/C3)</f>
         <v>18786</v>
       </c>
-      <c r="D68" s="20">
+      <c r="D68" s="21">
         <f>IF(D3=0,"",D11/D3)</f>
         <v>19203</v>
       </c>
-      <c r="E68" s="20">
+      <c r="E68" s="21">
         <f>IF(E3=0,"",E11/E3)</f>
         <v>19653</v>
       </c>
-      <c r="F68" s="20">
+      <c r="F68" s="21">
         <f>IF(F3=0,"",F11/F3)</f>
         <v>20145</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="B69" s="20">
+      <c r="A69" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="B69" s="21">
         <f>IF(B3=0,"",B45/B3)</f>
         <v>13866</v>
       </c>
-      <c r="C69" s="20">
+      <c r="C69" s="21">
         <f>IF(C3=0,"",C45/C3)</f>
         <v>11603</v>
       </c>
-      <c r="D69" s="20">
+      <c r="D69" s="21">
         <f>IF(D3=0,"",D45/D3)</f>
         <v>9916</v>
       </c>
-      <c r="E69" s="20">
+      <c r="E69" s="21">
         <f>IF(E3=0,"",E45/E3)</f>
         <v>9077</v>
       </c>
-      <c r="F69" s="20">
+      <c r="F69" s="21">
         <f>IF(F3=0,"",F45/F3)</f>
         <v>9335</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="B70" s="20">
+      <c r="A70" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="B70" s="21">
         <f>B42+B44</f>
         <v>125894</v>
       </c>
-      <c r="C70" s="20">
+      <c r="C70" s="21">
         <f>C42+C44</f>
         <v>153963</v>
       </c>
-      <c r="D70" s="20">
+      <c r="D70" s="21">
         <f>D42+D44</f>
         <v>158373</v>
       </c>
-      <c r="E70" s="20">
+      <c r="E70" s="21">
         <f>E42+E44</f>
         <v>162915</v>
       </c>
-      <c r="F70" s="20">
+      <c r="F70" s="21">
         <f>F42+F44</f>
         <v>167594</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="B71" s="20">
+      <c r="A71" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="B71" s="21">
         <f>IF(B3=0,"",B43/B3)</f>
         <v>3375</v>
       </c>
-      <c r="C71" s="20">
+      <c r="C71" s="21">
         <f>IF(C3=0,"",C43/C3)</f>
         <v>3049</v>
       </c>
-      <c r="D71" s="20">
+      <c r="D71" s="21">
         <f>IF(D3=0,"",D43/D3)</f>
         <v>2717</v>
       </c>
-      <c r="E71" s="20">
+      <c r="E71" s="21">
         <f>IF(E3=0,"",E43/E3)</f>
         <v>2560</v>
       </c>
-      <c r="F71" s="20">
+      <c r="F71" s="21">
         <f>IF(F3=0,"",F43/F3)</f>
         <v>2631</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="B72" s="20">
+      <c r="A72" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="B72" s="21">
         <f>IF(B3=0,"",B68-B71)</f>
         <v>12014</v>
       </c>
-      <c r="C72" s="20">
+      <c r="C72" s="21">
         <f>IF(C3=0,"",C68-C71)</f>
         <v>15737</v>
       </c>
-      <c r="D72" s="20">
+      <c r="D72" s="21">
         <f>IF(D3=0,"",D68-D71)</f>
         <v>16486</v>
       </c>
-      <c r="E72" s="20">
+      <c r="E72" s="21">
         <f>IF(E3=0,"",E68-E71)</f>
         <v>17093</v>
       </c>
-      <c r="F72" s="20">
+      <c r="F72" s="21">
         <f>IF(F3=0,"",F68-F71)</f>
         <v>17514</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="36" t="s">
-        <v>178</v>
-      </c>
-      <c r="B73" s="37">
+      <c r="A73" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="B73" s="38">
         <f>IF(B72&lt;=0,"N/A",ROUNDUP(B70/B72,0))</f>
         <v>11</v>
       </c>
-      <c r="C73" s="37">
+      <c r="C73" s="38">
         <f>IF(C72&lt;=0,"N/A",ROUNDUP(C70/C72,0))</f>
         <v>10</v>
       </c>
-      <c r="D73" s="37">
+      <c r="D73" s="38">
         <f>IF(D72&lt;=0,"N/A",ROUNDUP(D70/D72,0))</f>
         <v>10</v>
       </c>
-      <c r="E73" s="37">
+      <c r="E73" s="38">
         <f>IF(E72&lt;=0,"N/A",ROUNDUP(E70/E72,0))</f>
         <v>10</v>
       </c>
-      <c r="F73" s="37">
+      <c r="F73" s="38">
         <f>IF(F72&lt;=0,"N/A",ROUNDUP(F70/F72,0))</f>
         <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="B75" s="23"/>
-      <c r="C75" s="23"/>
-      <c r="D75" s="23"/>
-      <c r="E75" s="23"/>
-      <c r="F75" s="23"/>
+      <c r="A75" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="B75" s="24"/>
+      <c r="C75" s="24"/>
+      <c r="D75" s="24"/>
+      <c r="E75" s="24"/>
+      <c r="F75" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3850,7 +3874,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -3867,345 +3891,345 @@
       <c r="N1" s="8"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>180</v>
-      </c>
-      <c r="D2" s="24" t="s">
+      <c r="B2" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="25" t="s">
         <v>181</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="D2" s="25" t="s">
         <v>182</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="E2" s="25" t="s">
         <v>183</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="F2" s="25" t="s">
         <v>184</v>
       </c>
-      <c r="H2" s="24" t="s">
+      <c r="G2" s="25" t="s">
         <v>185</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="H2" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="J2" s="24" t="s">
+      <c r="I2" s="25" t="s">
         <v>187</v>
       </c>
-      <c r="K2" s="24" t="s">
+      <c r="J2" s="25" t="s">
         <v>188</v>
       </c>
-      <c r="L2" s="24" t="s">
+      <c r="K2" s="25" t="s">
         <v>189</v>
       </c>
-      <c r="M2" s="24" t="s">
+      <c r="L2" s="25" t="s">
         <v>190</v>
       </c>
-      <c r="N2" s="24" t="s">
+      <c r="M2" s="25" t="s">
         <v>191</v>
       </c>
+      <c r="N2" s="25" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
+      <c r="A3" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="B4" s="20">
+      <c r="A4" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="21">
         <v>14400</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="21">
         <v>14400</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="21">
         <v>14400</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="21">
         <v>14400</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="21">
         <v>14400</v>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="21">
         <v>14400</v>
       </c>
-      <c r="H4" s="20">
+      <c r="H4" s="21">
         <v>14400</v>
       </c>
-      <c r="I4" s="20">
+      <c r="I4" s="21">
         <v>14400</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="21">
         <v>14400</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="21">
         <v>14400</v>
       </c>
-      <c r="L4" s="20">
-        <v>0</v>
-      </c>
-      <c r="M4" s="20">
-        <v>0</v>
-      </c>
-      <c r="N4" s="20">
+      <c r="L4" s="21">
+        <v>0</v>
+      </c>
+      <c r="M4" s="21">
+        <v>0</v>
+      </c>
+      <c r="N4" s="21">
         <f>SUM(B4:M4)</f>
         <v>120000</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="20">
+      <c r="A5" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="21">
         <v>300</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="21">
         <v>300</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="21">
         <v>300</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="21">
         <v>300</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="21">
         <v>300</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="21">
         <v>300</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="21">
         <v>300</v>
       </c>
-      <c r="I5" s="20">
+      <c r="I5" s="21">
         <v>300</v>
       </c>
-      <c r="J5" s="20">
+      <c r="J5" s="21">
         <v>300</v>
       </c>
-      <c r="K5" s="20">
+      <c r="K5" s="21">
         <v>300</v>
       </c>
-      <c r="L5" s="20">
-        <v>0</v>
-      </c>
-      <c r="M5" s="20">
-        <v>0</v>
-      </c>
-      <c r="N5" s="20">
+      <c r="L5" s="21">
+        <v>0</v>
+      </c>
+      <c r="M5" s="21">
+        <v>0</v>
+      </c>
+      <c r="N5" s="21">
         <f>SUM(B5:M5)</f>
         <v>2500</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" s="20">
+      <c r="A6" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="21">
         <v>8400</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="21">
         <v>8400</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="21">
         <v>8400</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="21">
         <v>8400</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="21">
         <v>8400</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="21">
         <v>8400</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="21">
         <v>8400</v>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="21">
         <v>8400</v>
       </c>
-      <c r="J6" s="20">
+      <c r="J6" s="21">
         <v>8400</v>
       </c>
-      <c r="K6" s="20">
+      <c r="K6" s="21">
         <v>8400</v>
       </c>
-      <c r="L6" s="20">
-        <v>0</v>
-      </c>
-      <c r="M6" s="20">
-        <v>0</v>
-      </c>
-      <c r="N6" s="20">
+      <c r="L6" s="21">
+        <v>0</v>
+      </c>
+      <c r="M6" s="21">
+        <v>0</v>
+      </c>
+      <c r="N6" s="21">
         <f>SUM(B6:M6)</f>
         <v>70000</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" s="20">
+      <c r="A7" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="21">
         <v>500</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="21">
         <v>500</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="21">
         <v>500</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="21">
         <v>500</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="21">
         <v>500</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="21">
         <v>500</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="21">
         <v>500</v>
       </c>
-      <c r="I7" s="20">
+      <c r="I7" s="21">
         <v>500</v>
       </c>
-      <c r="J7" s="20">
+      <c r="J7" s="21">
         <v>500</v>
       </c>
-      <c r="K7" s="20">
+      <c r="K7" s="21">
         <v>500</v>
       </c>
-      <c r="L7" s="20">
-        <v>0</v>
-      </c>
-      <c r="M7" s="20">
-        <v>0</v>
-      </c>
-      <c r="N7" s="20">
+      <c r="L7" s="21">
+        <v>0</v>
+      </c>
+      <c r="M7" s="21">
+        <v>0</v>
+      </c>
+      <c r="N7" s="21">
         <f>SUM(B7:M7)</f>
         <v>4167</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" s="20">
-        <v>0</v>
-      </c>
-      <c r="C8" s="20">
-        <v>0</v>
-      </c>
-      <c r="D8" s="20">
-        <v>0</v>
-      </c>
-      <c r="E8" s="20">
-        <v>0</v>
-      </c>
-      <c r="F8" s="20">
-        <v>0</v>
-      </c>
-      <c r="G8" s="20">
-        <v>0</v>
-      </c>
-      <c r="H8" s="20">
-        <v>0</v>
-      </c>
-      <c r="I8" s="20">
-        <v>0</v>
-      </c>
-      <c r="J8" s="20">
-        <v>0</v>
-      </c>
-      <c r="K8" s="20">
-        <v>0</v>
-      </c>
-      <c r="L8" s="20">
-        <v>0</v>
-      </c>
-      <c r="M8" s="20">
-        <v>0</v>
-      </c>
-      <c r="N8" s="20" t="str">
+      <c r="A8" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="21">
+        <v>0</v>
+      </c>
+      <c r="C8" s="21">
+        <v>0</v>
+      </c>
+      <c r="D8" s="21">
+        <v>0</v>
+      </c>
+      <c r="E8" s="21">
+        <v>0</v>
+      </c>
+      <c r="F8" s="21">
+        <v>0</v>
+      </c>
+      <c r="G8" s="21">
+        <v>0</v>
+      </c>
+      <c r="H8" s="21">
+        <v>0</v>
+      </c>
+      <c r="I8" s="21">
+        <v>0</v>
+      </c>
+      <c r="J8" s="21">
+        <v>0</v>
+      </c>
+      <c r="K8" s="21">
+        <v>0</v>
+      </c>
+      <c r="L8" s="21">
+        <v>0</v>
+      </c>
+      <c r="M8" s="21">
+        <v>0</v>
+      </c>
+      <c r="N8" s="21" t="str">
         <f>SUM(B8:M8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B9" s="27">
+      <c r="A9" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B9" s="28">
         <f>SUM(B4:B8)</f>
         <v>155900</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="28">
         <f>SUM(C4:C8)</f>
         <v>7460</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="28">
         <f>SUM(D4:D8)</f>
         <v>7460</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="28">
         <f>SUM(E4:E8)</f>
         <v>7460</v>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="28">
         <f>SUM(F4:F8)</f>
         <v>7460</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="28">
         <f>SUM(G4:G8)</f>
         <v>7460</v>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="28">
         <f>SUM(H4:H8)</f>
         <v>7460</v>
       </c>
-      <c r="I9" s="27">
+      <c r="I9" s="28">
         <f>SUM(I4:I8)</f>
         <v>7460</v>
       </c>
-      <c r="J9" s="27">
+      <c r="J9" s="28">
         <f>SUM(J4:J8)</f>
         <v>7460</v>
       </c>
-      <c r="K9" s="27">
+      <c r="K9" s="28">
         <f>SUM(K4:K8)</f>
         <v>7460</v>
       </c>
-      <c r="L9" s="27">
+      <c r="L9" s="28">
         <f>SUM(L4:L8)</f>
         <v>-1440</v>
       </c>
-      <c r="M9" s="27" t="str">
+      <c r="M9" s="28" t="str">
         <f>SUM(M4:M8)</f>
         <v>0</v>
       </c>
-      <c r="N9" s="27">
+      <c r="N9" s="28">
         <f>SUM(B9:M9)</f>
         <v>221600</v>
       </c>
@@ -4216,211 +4240,211 @@
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
+      <c r="A11" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="B12" s="20">
+      <c r="A12" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" s="21">
         <v>5851</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="21">
         <v>5851</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="21">
         <v>5851</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="21">
         <v>5851</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="21">
         <v>5851</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="21">
         <v>5851</v>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="21">
         <v>5851</v>
       </c>
-      <c r="I12" s="20">
+      <c r="I12" s="21">
         <v>5851</v>
       </c>
-      <c r="J12" s="20">
+      <c r="J12" s="21">
         <v>5851</v>
       </c>
-      <c r="K12" s="20">
+      <c r="K12" s="21">
         <v>5851</v>
       </c>
-      <c r="L12" s="20">
-        <v>0</v>
-      </c>
-      <c r="M12" s="20">
-        <v>0</v>
-      </c>
-      <c r="N12" s="20">
+      <c r="L12" s="21">
+        <v>0</v>
+      </c>
+      <c r="M12" s="21">
+        <v>0</v>
+      </c>
+      <c r="N12" s="21">
         <f>SUM(B12:M12)</f>
         <v>58506</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B13" s="20">
+      <c r="A13" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" s="21">
         <v>4787</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="21">
         <v>4787</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="21">
         <v>4787</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="21">
         <v>4787</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="21">
         <v>4787</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="21">
         <v>4787</v>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="21">
         <v>4787</v>
       </c>
-      <c r="I13" s="20">
+      <c r="I13" s="21">
         <v>4787</v>
       </c>
-      <c r="J13" s="20">
+      <c r="J13" s="21">
         <v>4787</v>
       </c>
-      <c r="K13" s="20">
+      <c r="K13" s="21">
         <v>4787</v>
       </c>
-      <c r="L13" s="20">
-        <v>0</v>
-      </c>
-      <c r="M13" s="20">
-        <v>0</v>
-      </c>
-      <c r="N13" s="20">
+      <c r="L13" s="21">
+        <v>0</v>
+      </c>
+      <c r="M13" s="21">
+        <v>0</v>
+      </c>
+      <c r="N13" s="21">
         <f>SUM(B13:M13)</f>
         <v>47869</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="B14" s="20">
+      <c r="A14" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" s="21">
         <v>1256</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="21">
         <v>1256</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="21">
         <v>1256</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="21">
         <v>1256</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="21">
         <v>1256</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="21">
         <v>1256</v>
       </c>
-      <c r="H14" s="20">
+      <c r="H14" s="21">
         <v>1256</v>
       </c>
-      <c r="I14" s="20">
+      <c r="I14" s="21">
         <v>1256</v>
       </c>
-      <c r="J14" s="20">
+      <c r="J14" s="21">
         <v>1256</v>
       </c>
-      <c r="K14" s="20">
+      <c r="K14" s="21">
         <v>1256</v>
       </c>
-      <c r="L14" s="20">
-        <v>0</v>
-      </c>
-      <c r="M14" s="20">
-        <v>0</v>
-      </c>
-      <c r="N14" s="20">
+      <c r="L14" s="21">
+        <v>0</v>
+      </c>
+      <c r="M14" s="21">
+        <v>0</v>
+      </c>
+      <c r="N14" s="21">
         <f>SUM(B14:M14)</f>
         <v>12559</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="B15" s="27">
+      <c r="A15" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B15" s="28">
         <f>SUM(B12:B14)</f>
         <v>11893</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="28">
         <f>SUM(C12:C14)</f>
         <v>11893</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="28">
         <f>SUM(D12:D14)</f>
         <v>11893</v>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="28">
         <f>SUM(E12:E14)</f>
         <v>11893</v>
       </c>
-      <c r="F15" s="27">
+      <c r="F15" s="28">
         <f>SUM(F12:F14)</f>
         <v>11893</v>
       </c>
-      <c r="G15" s="27">
+      <c r="G15" s="28">
         <f>SUM(G12:G14)</f>
         <v>11893</v>
       </c>
-      <c r="H15" s="27">
+      <c r="H15" s="28">
         <f>SUM(H12:H14)</f>
         <v>11893</v>
       </c>
-      <c r="I15" s="27">
+      <c r="I15" s="28">
         <f>SUM(I12:I14)</f>
         <v>11893</v>
       </c>
-      <c r="J15" s="27">
+      <c r="J15" s="28">
         <f>SUM(J12:J14)</f>
         <v>11893</v>
       </c>
-      <c r="K15" s="27">
+      <c r="K15" s="28">
         <f>SUM(K12:K14)</f>
         <v>11893</v>
       </c>
-      <c r="L15" s="27" t="str">
+      <c r="L15" s="28" t="str">
         <f>SUM(L12:L14)</f>
         <v>0</v>
       </c>
-      <c r="M15" s="27" t="str">
+      <c r="M15" s="28" t="str">
         <f>SUM(M12:M14)</f>
         <v>0</v>
       </c>
-      <c r="N15" s="27">
+      <c r="N15" s="28">
         <f>SUM(B15:M15)</f>
         <v>118934</v>
       </c>
@@ -4431,598 +4455,598 @@
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
+      <c r="A17" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
+      <c r="A18" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="B19" s="20">
+      <c r="A19" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="B19" s="21">
         <v>500</v>
       </c>
-      <c r="C19" s="20">
+      <c r="C19" s="21">
         <v>500</v>
       </c>
-      <c r="D19" s="20">
+      <c r="D19" s="21">
         <v>500</v>
       </c>
-      <c r="E19" s="20">
+      <c r="E19" s="21">
         <v>500</v>
       </c>
-      <c r="F19" s="20">
+      <c r="F19" s="21">
         <v>500</v>
       </c>
-      <c r="G19" s="20">
+      <c r="G19" s="21">
         <v>500</v>
       </c>
-      <c r="H19" s="20">
+      <c r="H19" s="21">
         <v>500</v>
       </c>
-      <c r="I19" s="20">
+      <c r="I19" s="21">
         <v>500</v>
       </c>
-      <c r="J19" s="20">
+      <c r="J19" s="21">
         <v>500</v>
       </c>
-      <c r="K19" s="20">
+      <c r="K19" s="21">
         <v>500</v>
       </c>
-      <c r="L19" s="20">
-        <v>0</v>
-      </c>
-      <c r="M19" s="20">
-        <v>0</v>
-      </c>
-      <c r="N19" s="20">
+      <c r="L19" s="21">
+        <v>0</v>
+      </c>
+      <c r="M19" s="21">
+        <v>0</v>
+      </c>
+      <c r="N19" s="21">
         <f>SUM(B19:M19)</f>
         <v>5000</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="B20" s="29">
+      <c r="A20" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="B20" s="30">
         <v>500</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <v>500</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="30">
         <v>500</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="30">
         <v>500</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="30">
         <v>500</v>
       </c>
-      <c r="G20" s="29">
+      <c r="G20" s="30">
         <v>500</v>
       </c>
-      <c r="H20" s="29">
+      <c r="H20" s="30">
         <v>500</v>
       </c>
-      <c r="I20" s="29">
+      <c r="I20" s="30">
         <v>500</v>
       </c>
-      <c r="J20" s="29">
+      <c r="J20" s="30">
         <v>500</v>
       </c>
-      <c r="K20" s="29">
+      <c r="K20" s="30">
         <v>500</v>
       </c>
-      <c r="L20" s="29">
-        <v>0</v>
-      </c>
-      <c r="M20" s="29">
-        <v>0</v>
-      </c>
-      <c r="N20" s="29">
+      <c r="L20" s="30">
+        <v>0</v>
+      </c>
+      <c r="M20" s="30">
+        <v>0</v>
+      </c>
+      <c r="N20" s="30">
         <f>SUM(B20:M20)</f>
         <v>5000</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="12"/>
+      <c r="A21" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="B22" s="20">
+      <c r="A22" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="B22" s="21">
         <v>300</v>
       </c>
-      <c r="C22" s="20">
+      <c r="C22" s="21">
         <v>300</v>
       </c>
-      <c r="D22" s="20">
+      <c r="D22" s="21">
         <v>300</v>
       </c>
-      <c r="E22" s="20">
+      <c r="E22" s="21">
         <v>300</v>
       </c>
-      <c r="F22" s="20">
+      <c r="F22" s="21">
         <v>300</v>
       </c>
-      <c r="G22" s="20">
+      <c r="G22" s="21">
         <v>300</v>
       </c>
-      <c r="H22" s="20">
+      <c r="H22" s="21">
         <v>300</v>
       </c>
-      <c r="I22" s="20">
+      <c r="I22" s="21">
         <v>300</v>
       </c>
-      <c r="J22" s="20">
+      <c r="J22" s="21">
         <v>300</v>
       </c>
-      <c r="K22" s="20">
+      <c r="K22" s="21">
         <v>300</v>
       </c>
-      <c r="L22" s="20">
-        <v>0</v>
-      </c>
-      <c r="M22" s="20">
-        <v>0</v>
-      </c>
-      <c r="N22" s="20">
+      <c r="L22" s="21">
+        <v>0</v>
+      </c>
+      <c r="M22" s="21">
+        <v>0</v>
+      </c>
+      <c r="N22" s="21">
         <f>SUM(B22:M22)</f>
         <v>3000</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="28" t="s">
-        <v>140</v>
-      </c>
-      <c r="B23" s="29">
+      <c r="A23" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="B23" s="30">
         <v>300</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C23" s="30">
         <v>300</v>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="30">
         <v>300</v>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="30">
         <v>300</v>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="30">
         <v>300</v>
       </c>
-      <c r="G23" s="29">
+      <c r="G23" s="30">
         <v>300</v>
       </c>
-      <c r="H23" s="29">
+      <c r="H23" s="30">
         <v>300</v>
       </c>
-      <c r="I23" s="29">
+      <c r="I23" s="30">
         <v>300</v>
       </c>
-      <c r="J23" s="29">
+      <c r="J23" s="30">
         <v>300</v>
       </c>
-      <c r="K23" s="29">
+      <c r="K23" s="30">
         <v>300</v>
       </c>
-      <c r="L23" s="29">
-        <v>0</v>
-      </c>
-      <c r="M23" s="29">
-        <v>0</v>
-      </c>
-      <c r="N23" s="29">
+      <c r="L23" s="30">
+        <v>0</v>
+      </c>
+      <c r="M23" s="30">
+        <v>0</v>
+      </c>
+      <c r="N23" s="30">
         <f>SUM(B23:M23)</f>
         <v>3000</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12"/>
-      <c r="N24" s="12"/>
+      <c r="A24" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="B25" s="20">
+      <c r="A25" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="B25" s="21">
         <v>2500</v>
       </c>
-      <c r="C25" s="20">
+      <c r="C25" s="21">
         <v>2500</v>
       </c>
-      <c r="D25" s="20">
+      <c r="D25" s="21">
         <v>2500</v>
       </c>
-      <c r="E25" s="20">
+      <c r="E25" s="21">
         <v>2500</v>
       </c>
-      <c r="F25" s="20">
+      <c r="F25" s="21">
         <v>2500</v>
       </c>
-      <c r="G25" s="20">
+      <c r="G25" s="21">
         <v>2500</v>
       </c>
-      <c r="H25" s="20">
+      <c r="H25" s="21">
         <v>2500</v>
       </c>
-      <c r="I25" s="20">
+      <c r="I25" s="21">
         <v>2500</v>
       </c>
-      <c r="J25" s="20">
+      <c r="J25" s="21">
         <v>2500</v>
       </c>
-      <c r="K25" s="20">
+      <c r="K25" s="21">
         <v>2500</v>
       </c>
-      <c r="L25" s="20">
-        <v>0</v>
-      </c>
-      <c r="M25" s="20">
-        <v>0</v>
-      </c>
-      <c r="N25" s="20">
+      <c r="L25" s="21">
+        <v>0</v>
+      </c>
+      <c r="M25" s="21">
+        <v>0</v>
+      </c>
+      <c r="N25" s="21">
         <f>SUM(B25:M25)</f>
         <v>25000</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="B26" s="20">
+      <c r="A26" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="B26" s="21">
         <v>300</v>
       </c>
-      <c r="C26" s="20">
+      <c r="C26" s="21">
         <v>300</v>
       </c>
-      <c r="D26" s="20">
+      <c r="D26" s="21">
         <v>300</v>
       </c>
-      <c r="E26" s="20">
+      <c r="E26" s="21">
         <v>300</v>
       </c>
-      <c r="F26" s="20">
+      <c r="F26" s="21">
         <v>300</v>
       </c>
-      <c r="G26" s="20">
+      <c r="G26" s="21">
         <v>300</v>
       </c>
-      <c r="H26" s="20">
+      <c r="H26" s="21">
         <v>300</v>
       </c>
-      <c r="I26" s="20">
+      <c r="I26" s="21">
         <v>300</v>
       </c>
-      <c r="J26" s="20">
+      <c r="J26" s="21">
         <v>300</v>
       </c>
-      <c r="K26" s="20">
+      <c r="K26" s="21">
         <v>300</v>
       </c>
-      <c r="L26" s="20">
-        <v>0</v>
-      </c>
-      <c r="M26" s="20">
-        <v>0</v>
-      </c>
-      <c r="N26" s="20">
+      <c r="L26" s="21">
+        <v>0</v>
+      </c>
+      <c r="M26" s="21">
+        <v>0</v>
+      </c>
+      <c r="N26" s="21">
         <f>SUM(B26:M26)</f>
         <v>3000</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="B27" s="20">
+      <c r="A27" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="B27" s="21">
         <v>200</v>
       </c>
-      <c r="C27" s="20">
+      <c r="C27" s="21">
         <v>200</v>
       </c>
-      <c r="D27" s="20">
+      <c r="D27" s="21">
         <v>200</v>
       </c>
-      <c r="E27" s="20">
+      <c r="E27" s="21">
         <v>200</v>
       </c>
-      <c r="F27" s="20">
+      <c r="F27" s="21">
         <v>200</v>
       </c>
-      <c r="G27" s="20">
+      <c r="G27" s="21">
         <v>200</v>
       </c>
-      <c r="H27" s="20">
+      <c r="H27" s="21">
         <v>200</v>
       </c>
-      <c r="I27" s="20">
+      <c r="I27" s="21">
         <v>200</v>
       </c>
-      <c r="J27" s="20">
+      <c r="J27" s="21">
         <v>200</v>
       </c>
-      <c r="K27" s="20">
+      <c r="K27" s="21">
         <v>200</v>
       </c>
-      <c r="L27" s="20">
-        <v>0</v>
-      </c>
-      <c r="M27" s="20">
-        <v>0</v>
-      </c>
-      <c r="N27" s="20">
+      <c r="L27" s="21">
+        <v>0</v>
+      </c>
+      <c r="M27" s="21">
+        <v>0</v>
+      </c>
+      <c r="N27" s="21">
         <f>SUM(B27:M27)</f>
         <v>2000</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="B28" s="29">
+      <c r="A28" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="B28" s="30">
         <v>3000</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C28" s="30">
         <v>3000</v>
       </c>
-      <c r="D28" s="29">
+      <c r="D28" s="30">
         <v>3000</v>
       </c>
-      <c r="E28" s="29">
+      <c r="E28" s="30">
         <v>3000</v>
       </c>
-      <c r="F28" s="29">
+      <c r="F28" s="30">
         <v>3000</v>
       </c>
-      <c r="G28" s="29">
+      <c r="G28" s="30">
         <v>3000</v>
       </c>
-      <c r="H28" s="29">
+      <c r="H28" s="30">
         <v>3000</v>
       </c>
-      <c r="I28" s="29">
+      <c r="I28" s="30">
         <v>3000</v>
       </c>
-      <c r="J28" s="29">
+      <c r="J28" s="30">
         <v>3000</v>
       </c>
-      <c r="K28" s="29">
+      <c r="K28" s="30">
         <v>3000</v>
       </c>
-      <c r="L28" s="29">
-        <v>0</v>
-      </c>
-      <c r="M28" s="29">
-        <v>0</v>
-      </c>
-      <c r="N28" s="29">
+      <c r="L28" s="30">
+        <v>0</v>
+      </c>
+      <c r="M28" s="30">
+        <v>0</v>
+      </c>
+      <c r="N28" s="30">
         <f>SUM(B28:M28)</f>
         <v>30000</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
+      <c r="A29" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="B30" s="20">
+      <c r="A30" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="B30" s="21">
         <v>250</v>
       </c>
-      <c r="C30" s="20">
+      <c r="C30" s="21">
         <v>250</v>
       </c>
-      <c r="D30" s="20">
+      <c r="D30" s="21">
         <v>250</v>
       </c>
-      <c r="E30" s="20">
+      <c r="E30" s="21">
         <v>250</v>
       </c>
-      <c r="F30" s="20">
+      <c r="F30" s="21">
         <v>250</v>
       </c>
-      <c r="G30" s="20">
+      <c r="G30" s="21">
         <v>250</v>
       </c>
-      <c r="H30" s="20">
+      <c r="H30" s="21">
         <v>250</v>
       </c>
-      <c r="I30" s="20">
+      <c r="I30" s="21">
         <v>250</v>
       </c>
-      <c r="J30" s="20">
+      <c r="J30" s="21">
         <v>250</v>
       </c>
-      <c r="K30" s="20">
+      <c r="K30" s="21">
         <v>250</v>
       </c>
-      <c r="L30" s="20">
-        <v>0</v>
-      </c>
-      <c r="M30" s="20">
-        <v>0</v>
-      </c>
-      <c r="N30" s="20">
+      <c r="L30" s="21">
+        <v>0</v>
+      </c>
+      <c r="M30" s="21">
+        <v>0</v>
+      </c>
+      <c r="N30" s="21">
         <f>SUM(B30:M30)</f>
         <v>2500</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="28" t="s">
-        <v>146</v>
-      </c>
-      <c r="B31" s="29">
+      <c r="A31" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="B31" s="30">
         <v>250</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C31" s="30">
         <v>250</v>
       </c>
-      <c r="D31" s="29">
+      <c r="D31" s="30">
         <v>250</v>
       </c>
-      <c r="E31" s="29">
+      <c r="E31" s="30">
         <v>250</v>
       </c>
-      <c r="F31" s="29">
+      <c r="F31" s="30">
         <v>250</v>
       </c>
-      <c r="G31" s="29">
+      <c r="G31" s="30">
         <v>250</v>
       </c>
-      <c r="H31" s="29">
+      <c r="H31" s="30">
         <v>250</v>
       </c>
-      <c r="I31" s="29">
+      <c r="I31" s="30">
         <v>250</v>
       </c>
-      <c r="J31" s="29">
+      <c r="J31" s="30">
         <v>250</v>
       </c>
-      <c r="K31" s="29">
+      <c r="K31" s="30">
         <v>250</v>
       </c>
-      <c r="L31" s="29">
-        <v>0</v>
-      </c>
-      <c r="M31" s="29">
-        <v>0</v>
-      </c>
-      <c r="N31" s="29">
+      <c r="L31" s="30">
+        <v>0</v>
+      </c>
+      <c r="M31" s="30">
+        <v>0</v>
+      </c>
+      <c r="N31" s="30">
         <f>SUM(B31:M31)</f>
         <v>2500</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="B32" s="27">
+      <c r="A32" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B32" s="28">
         <f>B20+B23+B28+B31</f>
         <v>4050</v>
       </c>
-      <c r="C32" s="27">
+      <c r="C32" s="28">
         <f>C20+C23+C28+C31</f>
         <v>4050</v>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="28">
         <f>D20+D23+D28+D31</f>
         <v>4050</v>
       </c>
-      <c r="E32" s="27">
+      <c r="E32" s="28">
         <f>E20+E23+E28+E31</f>
         <v>4050</v>
       </c>
-      <c r="F32" s="27">
+      <c r="F32" s="28">
         <f>F20+F23+F28+F31</f>
         <v>4050</v>
       </c>
-      <c r="G32" s="27">
+      <c r="G32" s="28">
         <f>G20+G23+G28+G31</f>
         <v>4050</v>
       </c>
-      <c r="H32" s="27">
+      <c r="H32" s="28">
         <f>H20+H23+H28+H31</f>
         <v>4050</v>
       </c>
-      <c r="I32" s="27">
+      <c r="I32" s="28">
         <f>I20+I23+I28+I31</f>
         <v>4050</v>
       </c>
-      <c r="J32" s="27">
+      <c r="J32" s="28">
         <f>J20+J23+J28+J31</f>
         <v>4050</v>
       </c>
-      <c r="K32" s="27">
+      <c r="K32" s="28">
         <f>K20+K23+K28+K31</f>
         <v>4050</v>
       </c>
-      <c r="L32" s="27" t="str">
+      <c r="L32" s="28" t="str">
         <f>L20+L23+L28+L31</f>
         <v>0</v>
       </c>
-      <c r="M32" s="27" t="str">
+      <c r="M32" s="28" t="str">
         <f>M20+M23+M28+M31</f>
         <v>0</v>
       </c>
-      <c r="N32" s="27">
+      <c r="N32" s="28">
         <f>SUM(B32:M32)</f>
         <v>40500</v>
       </c>
@@ -5033,46 +5057,46 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="25" t="s">
-        <v>198</v>
-      </c>
-      <c r="B34" s="20">
+      <c r="A34" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="B34" s="21">
         <v>580</v>
       </c>
-      <c r="C34" s="20">
+      <c r="C34" s="21">
         <v>580</v>
       </c>
-      <c r="D34" s="20">
+      <c r="D34" s="21">
         <v>580</v>
       </c>
-      <c r="E34" s="20">
+      <c r="E34" s="21">
         <v>580</v>
       </c>
-      <c r="F34" s="20">
+      <c r="F34" s="21">
         <v>580</v>
       </c>
-      <c r="G34" s="20">
+      <c r="G34" s="21">
         <v>580</v>
       </c>
-      <c r="H34" s="20">
+      <c r="H34" s="21">
         <v>580</v>
       </c>
-      <c r="I34" s="20">
+      <c r="I34" s="21">
         <v>580</v>
       </c>
-      <c r="J34" s="20">
+      <c r="J34" s="21">
         <v>580</v>
       </c>
-      <c r="K34" s="20">
+      <c r="K34" s="21">
         <v>580</v>
       </c>
-      <c r="L34" s="20">
+      <c r="L34" s="21">
         <v>580</v>
       </c>
-      <c r="M34" s="20">
+      <c r="M34" s="21">
         <v>580</v>
       </c>
-      <c r="N34" s="20">
+      <c r="N34" s="21">
         <f>SUM(B34:M34)</f>
         <v>6960</v>
       </c>
@@ -5083,244 +5107,244 @@
       </c>
     </row>
     <row r="36" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="11"/>
+      <c r="A36" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
+      <c r="M36" s="12"/>
+      <c r="N36" s="12"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="B37" s="29">
+      <c r="A37" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="B37" s="30">
         <f>B15+B32+B34</f>
         <v>16523</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C37" s="30">
         <f>C15+C32+C34</f>
         <v>16523</v>
       </c>
-      <c r="D37" s="29">
+      <c r="D37" s="30">
         <f>D15+D32+D34</f>
         <v>16523</v>
       </c>
-      <c r="E37" s="29">
+      <c r="E37" s="30">
         <f>E15+E32+E34</f>
         <v>16523</v>
       </c>
-      <c r="F37" s="29">
+      <c r="F37" s="30">
         <f>F15+F32+F34</f>
         <v>16523</v>
       </c>
-      <c r="G37" s="29">
+      <c r="G37" s="30">
         <f>G15+G32+G34</f>
         <v>16523</v>
       </c>
-      <c r="H37" s="29">
+      <c r="H37" s="30">
         <f>H15+H32+H34</f>
         <v>16523</v>
       </c>
-      <c r="I37" s="29">
+      <c r="I37" s="30">
         <f>I15+I32+I34</f>
         <v>16523</v>
       </c>
-      <c r="J37" s="29">
+      <c r="J37" s="30">
         <f>J15+J32+J34</f>
         <v>16523</v>
       </c>
-      <c r="K37" s="29">
+      <c r="K37" s="30">
         <f>K15+K32+K34</f>
         <v>16523</v>
       </c>
-      <c r="L37" s="29">
+      <c r="L37" s="30">
         <f>L15+L32+L34</f>
         <v>580</v>
       </c>
-      <c r="M37" s="29">
+      <c r="M37" s="30">
         <f>M15+M32+M34</f>
         <v>580</v>
       </c>
-      <c r="N37" s="29">
+      <c r="N37" s="30">
         <f>SUM(B37:M37)</f>
         <v>166390</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="25" t="s">
-        <v>200</v>
-      </c>
-      <c r="B38" s="29">
+      <c r="A38" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="B38" s="30">
         <f>B9-B37</f>
         <v>139377</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C38" s="30">
         <f>C9-C37</f>
         <v>-9063</v>
       </c>
-      <c r="D38" s="29">
+      <c r="D38" s="30">
         <f>D9-D37</f>
         <v>-9063</v>
       </c>
-      <c r="E38" s="29">
+      <c r="E38" s="30">
         <f>E9-E37</f>
         <v>-9063</v>
       </c>
-      <c r="F38" s="29">
+      <c r="F38" s="30">
         <f>F9-F37</f>
         <v>-9063</v>
       </c>
-      <c r="G38" s="29">
+      <c r="G38" s="30">
         <f>G9-G37</f>
         <v>-9063</v>
       </c>
-      <c r="H38" s="29">
+      <c r="H38" s="30">
         <f>H9-H37</f>
         <v>-9063</v>
       </c>
-      <c r="I38" s="29">
+      <c r="I38" s="30">
         <f>I9-I37</f>
         <v>-9063</v>
       </c>
-      <c r="J38" s="29">
+      <c r="J38" s="30">
         <f>J9-J37</f>
         <v>-9063</v>
       </c>
-      <c r="K38" s="29">
+      <c r="K38" s="30">
         <f>K9-K37</f>
         <v>-9063</v>
       </c>
-      <c r="L38" s="29">
+      <c r="L38" s="30">
         <f>L9-L37</f>
         <v>-2020</v>
       </c>
-      <c r="M38" s="29">
+      <c r="M38" s="30">
         <f>M9-M37</f>
         <v>-580</v>
       </c>
-      <c r="N38" s="29">
+      <c r="N38" s="30">
         <f>SUM(B38:M38)</f>
         <v>55210</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="25" t="s">
-        <v>201</v>
-      </c>
-      <c r="B39" s="29">
+      <c r="A39" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="B39" s="30">
         <f>0+B38</f>
         <v>139377</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C39" s="30">
         <f>B39+C38</f>
         <v>130314</v>
       </c>
-      <c r="D39" s="29">
+      <c r="D39" s="30">
         <f>C39+D38</f>
         <v>121251</v>
       </c>
-      <c r="E39" s="29">
+      <c r="E39" s="30">
         <f>D39+E38</f>
         <v>112188</v>
       </c>
-      <c r="F39" s="29">
+      <c r="F39" s="30">
         <f>E39+F38</f>
         <v>103125</v>
       </c>
-      <c r="G39" s="29">
+      <c r="G39" s="30">
         <f>F39+G38</f>
         <v>94062</v>
       </c>
-      <c r="H39" s="29">
+      <c r="H39" s="30">
         <f>G39+H38</f>
         <v>84999</v>
       </c>
-      <c r="I39" s="29">
+      <c r="I39" s="30">
         <f>H39+I38</f>
         <v>75936</v>
       </c>
-      <c r="J39" s="29">
+      <c r="J39" s="30">
         <f>I39+J38</f>
         <v>66873</v>
       </c>
-      <c r="K39" s="29">
+      <c r="K39" s="30">
         <f>J39+K38</f>
         <v>57810</v>
       </c>
-      <c r="L39" s="29">
+      <c r="L39" s="30">
         <f>K39+L38</f>
         <v>55790</v>
       </c>
-      <c r="M39" s="29">
+      <c r="M39" s="30">
         <f>L39+M38</f>
         <v>55210</v>
       </c>
-      <c r="N39" s="29">
+      <c r="N39" s="30">
         <f>M39</f>
         <v>55210</v>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
+      <c r="A41" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="B42" s="20">
+      <c r="A42" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B42" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="B43" s="29">
+      <c r="A43" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="B43" s="30">
         <f>M39</f>
         <v>55210</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="B44" s="20">
+      <c r="A44" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="B44" s="21">
         <f>MIN(B39:M39)</f>
         <v>55210</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="B46" s="23"/>
-      <c r="C46" s="23"/>
-      <c r="D46" s="23"/>
-      <c r="E46" s="23"/>
-      <c r="F46" s="23"/>
-      <c r="G46" s="23"/>
-      <c r="H46" s="23"/>
-      <c r="I46" s="23"/>
-      <c r="J46" s="23"/>
-      <c r="K46" s="23"/>
-      <c r="L46" s="23"/>
-      <c r="M46" s="23"/>
-      <c r="N46" s="23"/>
+      <c r="A46" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="B46" s="24"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24"/>
+      <c r="H46" s="24"/>
+      <c r="I46" s="24"/>
+      <c r="J46" s="24"/>
+      <c r="K46" s="24"/>
+      <c r="L46" s="24"/>
+      <c r="M46" s="24"/>
+      <c r="N46" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5353,7 +5377,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -5362,466 +5386,466 @@
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="38" t="s">
-        <v>206</v>
-      </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
+      <c r="B3" s="39" t="s">
+        <v>207</v>
+      </c>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="C5" s="15" t="s">
+      <c r="B5" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="C5" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="D5" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="E5" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="16" t="s">
         <v>212</v>
       </c>
+      <c r="G5" s="16" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="C6" s="39">
+      <c r="B6" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="C6" s="40">
         <v>12</v>
       </c>
-      <c r="D6" s="39">
+      <c r="D6" s="40">
         <v>18</v>
       </c>
-      <c r="E6" s="39">
+      <c r="E6" s="40">
         <v>22</v>
       </c>
-      <c r="F6" s="39">
+      <c r="F6" s="40">
         <v>25</v>
       </c>
-      <c r="G6" s="39">
+      <c r="G6" s="40">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="C7" s="40">
+      <c r="B7" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="C7" s="41">
         <v>221600</v>
       </c>
-      <c r="D7" s="40">
+      <c r="D7" s="41">
         <v>338147.49999999994</v>
       </c>
-      <c r="E7" s="40">
+      <c r="E7" s="41">
         <v>422456.3124999999</v>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="41">
         <v>491331.3476562498</v>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="41">
         <v>503614.631347656</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="C8" s="40">
+      <c r="B8" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="C8" s="41">
         <v>118934.16666666667</v>
       </c>
-      <c r="D8" s="40">
+      <c r="D8" s="41">
         <v>147002.63</v>
       </c>
-      <c r="E8" s="40">
+      <c r="E8" s="41">
         <v>151412.7089</v>
       </c>
-      <c r="F8" s="40">
+      <c r="F8" s="41">
         <v>155955.090167</v>
       </c>
-      <c r="G8" s="40">
+      <c r="G8" s="41">
         <v>160633.74287201</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="C9" s="40">
+      <c r="B9" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="C9" s="41">
         <v>48600</v>
       </c>
-      <c r="D9" s="40">
+      <c r="D9" s="41">
         <v>54885</v>
       </c>
-      <c r="E9" s="40">
+      <c r="E9" s="41">
         <v>59773.625</v>
       </c>
-      <c r="F9" s="40">
+      <c r="F9" s="41">
         <v>64011.63812499999</v>
       </c>
-      <c r="G9" s="40">
+      <c r="G9" s="41">
         <v>65775.83812812499</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="C10" s="40">
+      <c r="B10" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="C10" s="41">
         <v>6959.808550594178</v>
       </c>
-      <c r="D10" s="40">
+      <c r="D10" s="41">
         <v>6959.808550594178</v>
       </c>
-      <c r="E10" s="40">
+      <c r="E10" s="41">
         <v>6959.808550594178</v>
       </c>
-      <c r="F10" s="40">
+      <c r="F10" s="41">
         <v>6959.808550594178</v>
       </c>
-      <c r="G10" s="40">
+      <c r="G10" s="41">
         <v>6959.808550594178</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="C11" s="41">
+      <c r="B11" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="C11" s="42">
         <v>47106.02478273915</v>
       </c>
-      <c r="D11" s="41">
+      <c r="D11" s="42">
         <v>129300.06144940577</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="42">
         <v>204310.17004940574</v>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="42">
         <v>264404.8108136556</v>
       </c>
-      <c r="G11" s="41">
+      <c r="G11" s="42">
         <v>270245.2417969268</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="25" t="s">
-        <v>163</v>
-      </c>
-      <c r="C12" s="41">
+      <c r="B12" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="C12" s="42">
         <v>47106.02478273915</v>
       </c>
-      <c r="D12" s="41">
+      <c r="D12" s="42">
         <v>176406.0862321449</v>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="42">
         <v>380716.2562815506</v>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="42">
         <v>645121.0670952062</v>
       </c>
-      <c r="G12" s="41">
+      <c r="G12" s="42">
         <v>915366.3088921331</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="C13" s="42">
+      <c r="B13" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="C13" s="43">
         <v>0.21257231400153045</v>
       </c>
-      <c r="D13" s="42">
+      <c r="D13" s="43">
         <v>0.3823776944954666</v>
       </c>
-      <c r="E13" s="42">
+      <c r="E13" s="43">
         <v>0.4836243748858784</v>
       </c>
-      <c r="F13" s="42">
+      <c r="F13" s="43">
         <v>0.5381395102814428</v>
       </c>
-      <c r="G13" s="42">
+      <c r="G13" s="43">
         <v>0.5366111804054611</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="C14" s="40">
+      <c r="B14" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="C14" s="41">
         <v>18466.666666666668</v>
       </c>
-      <c r="D14" s="40">
+      <c r="D14" s="41">
         <v>18785.97222222222</v>
       </c>
-      <c r="E14" s="40">
+      <c r="E14" s="41">
         <v>19202.559659090904</v>
       </c>
-      <c r="F14" s="40">
+      <c r="F14" s="41">
         <v>19653.253906249993</v>
       </c>
-      <c r="G14" s="40">
+      <c r="G14" s="41">
         <v>20144.58525390624</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="C15" s="42">
+      <c r="B15" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="C15" s="43">
         <v>0.5367065282791817</v>
       </c>
-      <c r="D15" s="42">
+      <c r="D15" s="43">
         <v>0.4347293119127009</v>
       </c>
-      <c r="E15" s="42">
+      <c r="E15" s="43">
         <v>0.3584103359800075</v>
       </c>
-      <c r="F15" s="42">
+      <c r="F15" s="43">
         <v>0.31741327092386307</v>
       </c>
-      <c r="G15" s="42">
+      <c r="G15" s="43">
         <v>0.31896162834300396</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="25" t="s">
-        <v>221</v>
-      </c>
-      <c r="C16" s="42">
+      <c r="B16" s="26" t="s">
+        <v>222</v>
+      </c>
+      <c r="C16" s="43">
         <v>0.0657942238267148</v>
       </c>
-      <c r="D16" s="42">
+      <c r="D16" s="43">
         <v>0.04869324776909486</v>
       </c>
-      <c r="E16" s="42">
+      <c r="E16" s="43">
         <v>0.0424471997918128</v>
       </c>
-      <c r="F16" s="42">
+      <c r="F16" s="43">
         <v>0.03908460457307385</v>
       </c>
-      <c r="G16" s="42">
+      <c r="G16" s="43">
         <v>0.03918224414098794</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="C17" s="42">
+      <c r="B17" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="C17" s="43">
         <v>0.2439793922984356</v>
       </c>
-      <c r="D17" s="42">
+      <c r="D17" s="43">
         <v>0.40295986219031626</v>
       </c>
-      <c r="E17" s="42">
+      <c r="E17" s="43">
         <v>0.5000989980472832</v>
       </c>
-      <c r="F17" s="42">
+      <c r="F17" s="43">
         <v>0.5523047138325573</v>
       </c>
-      <c r="G17" s="42">
+      <c r="G17" s="43">
         <v>0.5504308911870363</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="25" t="s">
-        <v>223</v>
-      </c>
-      <c r="C18" s="43">
+      <c r="B18" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="C18" s="44">
         <v>7.768293185121821</v>
       </c>
-      <c r="D18" s="43">
+      <c r="D18" s="44">
         <v>19.57810606562835</v>
       </c>
-      <c r="E18" s="43">
+      <c r="E18" s="44">
         <v>30.35571698045677</v>
       </c>
-      <c r="F18" s="43">
+      <c r="F18" s="44">
         <v>38.99024195731399</v>
       </c>
-      <c r="G18" s="43">
+      <c r="G18" s="44">
         <v>39.82940742297506</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C19" s="44" t="s">
-        <v>208</v>
-      </c>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
+      <c r="B19" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="C19" s="45" t="s">
+        <v>209</v>
+      </c>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="C20" s="44" t="s">
+      <c r="B20" s="26" t="s">
         <v>226</v>
       </c>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
+      <c r="C20" s="45" t="s">
+        <v>227</v>
+      </c>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="C22" s="11" t="s">
+      <c r="B22" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="C22" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11" t="s">
+      <c r="D22" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="G22" s="11"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="G22" s="12"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="45" t="s">
-        <v>231</v>
-      </c>
-      <c r="C23" s="46" t="s">
+      <c r="B23" s="46" t="s">
         <v>232</v>
       </c>
-      <c r="D23" s="47" t="s">
+      <c r="C23" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="E23" s="47"/>
-      <c r="F23" s="48" t="s">
+      <c r="D23" s="48" t="s">
         <v>234</v>
       </c>
-      <c r="G23" s="48"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="49" t="s">
+        <v>235</v>
+      </c>
+      <c r="G23" s="49"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="45" t="s">
-        <v>235</v>
-      </c>
-      <c r="C24" s="46" t="s">
-        <v>232</v>
-      </c>
-      <c r="D24" s="47" t="s">
+      <c r="B24" s="46" t="s">
         <v>236</v>
       </c>
-      <c r="E24" s="47"/>
-      <c r="F24" s="48" t="s">
+      <c r="C24" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="D24" s="48" t="s">
         <v>237</v>
       </c>
-      <c r="G24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="49" t="s">
+        <v>238</v>
+      </c>
+      <c r="G24" s="49"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="45" t="s">
-        <v>238</v>
-      </c>
-      <c r="C25" s="46" t="s">
-        <v>232</v>
-      </c>
-      <c r="D25" s="47" t="s">
+      <c r="B25" s="46" t="s">
         <v>239</v>
       </c>
-      <c r="E25" s="47"/>
-      <c r="F25" s="48" t="s">
+      <c r="C25" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="D25" s="48" t="s">
         <v>240</v>
       </c>
-      <c r="G25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="49" t="s">
+        <v>241</v>
+      </c>
+      <c r="G25" s="49"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="45" t="s">
-        <v>241</v>
-      </c>
-      <c r="C26" s="46" t="s">
-        <v>232</v>
-      </c>
-      <c r="D26" s="47" t="s">
+      <c r="B26" s="46" t="s">
         <v>242</v>
       </c>
-      <c r="E26" s="47"/>
-      <c r="F26" s="48" t="s">
+      <c r="C26" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="D26" s="48" t="s">
         <v>243</v>
       </c>
-      <c r="G26" s="48"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="49" t="s">
+        <v>244</v>
+      </c>
+      <c r="G26" s="49"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="45" t="s">
-        <v>244</v>
-      </c>
-      <c r="C27" s="46" t="s">
-        <v>232</v>
-      </c>
-      <c r="D27" s="47" t="s">
+      <c r="B27" s="46" t="s">
         <v>245</v>
       </c>
-      <c r="E27" s="47"/>
-      <c r="F27" s="48" t="s">
+      <c r="C27" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="D27" s="48" t="s">
         <v>246</v>
       </c>
-      <c r="G27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="49" t="s">
+        <v>247</v>
+      </c>
+      <c r="G27" s="49"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="45" t="s">
-        <v>247</v>
-      </c>
-      <c r="C28" s="46" t="s">
-        <v>232</v>
-      </c>
-      <c r="D28" s="47" t="s">
+      <c r="B28" s="46" t="s">
         <v>248</v>
       </c>
-      <c r="E28" s="47"/>
-      <c r="F28" s="48" t="s">
+      <c r="C28" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="D28" s="48" t="s">
         <v>249</v>
       </c>
-      <c r="G28" s="48"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="49" t="s">
+        <v>250</v>
+      </c>
+      <c r="G28" s="49"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="45" t="s">
-        <v>250</v>
-      </c>
-      <c r="C29" s="46" t="s">
-        <v>232</v>
-      </c>
-      <c r="D29" s="47" t="s">
+      <c r="B29" s="46" t="s">
         <v>251</v>
       </c>
-      <c r="E29" s="47"/>
-      <c r="F29" s="48" t="s">
+      <c r="C29" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="D29" s="48" t="s">
         <v>252</v>
       </c>
-      <c r="G29" s="48"/>
+      <c r="E29" s="48"/>
+      <c r="F29" s="49" t="s">
+        <v>253</v>
+      </c>
+      <c r="G29" s="49"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="45" t="s">
-        <v>253</v>
-      </c>
-      <c r="C31" s="25" t="s">
+      <c r="B31" s="46" t="s">
         <v>254</v>
       </c>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
+      <c r="C31" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="49" t="s">
-        <v>128</v>
-      </c>
-      <c r="C33" s="49"/>
-      <c r="D33" s="49"/>
-      <c r="E33" s="49"/>
-      <c r="F33" s="49"/>
-      <c r="G33" s="49"/>
+      <c r="B33" s="50" t="s">
+        <v>129</v>
+      </c>
+      <c r="C33" s="50"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="50"/>
+      <c r="G33" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="22">

--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N46</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$G33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="267">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -653,6 +653,15 @@
     <t>Generated March 26, 2026</t>
   </si>
   <si>
+    <t>● Green = healthy</t>
+  </si>
+  <si>
+    <t>◐ Yellow = monitor</t>
+  </si>
+  <si>
+    <t>○ Red = action needed</t>
+  </si>
+  <si>
     <t>Metric</t>
   </si>
   <si>
@@ -671,6 +680,9 @@
     <t>Year 5</t>
   </si>
   <si>
+    <t>Benchmark</t>
+  </si>
+  <si>
     <t>Enrollment</t>
   </si>
   <si>
@@ -692,16 +704,37 @@
     <t>Revenue per Student</t>
   </si>
   <si>
+    <t>≥ $10,000</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
+    <t>≤ 55%</t>
+  </si>
+  <si>
     <t>Facility %</t>
   </si>
   <si>
+    <t>≤ 15%</t>
+  </si>
+  <si>
     <t>Operating Margin</t>
   </si>
   <si>
+    <t>≥ 10%</t>
+  </si>
+  <si>
+    <t>Revenue Sources</t>
+  </si>
+  <si>
+    <t>≥ 3 sources</t>
+  </si>
+  <si>
     <t>DSCR</t>
+  </si>
+  <si>
+    <t>≥ 1.25x</t>
   </si>
   <si>
     <t>Break-even Year</t>
@@ -808,7 +841,7 @@
     <numFmt numFmtId="167" formatCode="0.00x"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -901,6 +934,18 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FFD97706"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFDC2626"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -986,7 +1031,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1035,6 +1080,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1047,6 +1095,11 @@
     <xf numFmtId="166" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1068,7 +1121,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -5363,19 +5437,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF0D9488"/>
+    <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G33"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>206</v>
       </c>
@@ -5384,8 +5459,9 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="39" t="s">
         <v>207</v>
       </c>
@@ -5394,559 +5470,632 @@
       <c r="E3" s="39"/>
       <c r="F3" s="39"/>
       <c r="G3" s="39"/>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="12" t="s">
+      <c r="H3" s="39"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="40" t="s">
         <v>208</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="D4" s="41" t="s">
         <v>209</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="F4" s="42" t="s">
         <v>210</v>
       </c>
-      <c r="E5" s="16" t="s">
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="C6" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="D6" s="16" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="13" t="s">
+      <c r="E6" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="C6" s="40">
-        <v>12</v>
-      </c>
-      <c r="D6" s="40">
-        <v>18</v>
-      </c>
-      <c r="E6" s="40">
-        <v>22</v>
-      </c>
-      <c r="F6" s="40">
-        <v>25</v>
-      </c>
-      <c r="G6" s="40">
-        <v>25</v>
+      <c r="F6" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="C7" s="41">
-        <v>221600</v>
-      </c>
-      <c r="D7" s="41">
-        <v>338147.49999999994</v>
-      </c>
-      <c r="E7" s="41">
-        <v>422456.3124999999</v>
-      </c>
-      <c r="F7" s="41">
-        <v>491331.3476562498</v>
-      </c>
-      <c r="G7" s="41">
-        <v>503614.631347656</v>
+        <v>218</v>
+      </c>
+      <c r="C7" s="43">
+        <v>12</v>
+      </c>
+      <c r="D7" s="43">
+        <v>18</v>
+      </c>
+      <c r="E7" s="43">
+        <v>22</v>
+      </c>
+      <c r="F7" s="43">
+        <v>25</v>
+      </c>
+      <c r="G7" s="43">
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="C8" s="41">
-        <v>118934.16666666667</v>
-      </c>
-      <c r="D8" s="41">
-        <v>147002.63</v>
-      </c>
-      <c r="E8" s="41">
-        <v>151412.7089</v>
-      </c>
-      <c r="F8" s="41">
-        <v>155955.090167</v>
-      </c>
-      <c r="G8" s="41">
-        <v>160633.74287201</v>
+        <v>219</v>
+      </c>
+      <c r="C8" s="44">
+        <v>221600</v>
+      </c>
+      <c r="D8" s="44">
+        <v>338147.49999999994</v>
+      </c>
+      <c r="E8" s="44">
+        <v>422456.3124999999</v>
+      </c>
+      <c r="F8" s="44">
+        <v>491331.3476562498</v>
+      </c>
+      <c r="G8" s="44">
+        <v>503614.631347656</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="C9" s="41">
-        <v>48600</v>
-      </c>
-      <c r="D9" s="41">
-        <v>54885</v>
-      </c>
-      <c r="E9" s="41">
-        <v>59773.625</v>
-      </c>
-      <c r="F9" s="41">
-        <v>64011.63812499999</v>
-      </c>
-      <c r="G9" s="41">
-        <v>65775.83812812499</v>
+        <v>220</v>
+      </c>
+      <c r="C9" s="44">
+        <v>118934.16666666667</v>
+      </c>
+      <c r="D9" s="44">
+        <v>147002.63</v>
+      </c>
+      <c r="E9" s="44">
+        <v>151412.7089</v>
+      </c>
+      <c r="F9" s="44">
+        <v>155955.090167</v>
+      </c>
+      <c r="G9" s="44">
+        <v>160633.74287201</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="C10" s="44">
+        <v>48600</v>
+      </c>
+      <c r="D10" s="44">
+        <v>54885</v>
+      </c>
+      <c r="E10" s="44">
+        <v>59773.625</v>
+      </c>
+      <c r="F10" s="44">
+        <v>64011.63812499999</v>
+      </c>
+      <c r="G10" s="44">
+        <v>65775.83812812499</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="C10" s="41">
+      <c r="C11" s="44">
         <v>6959.808550594178</v>
       </c>
-      <c r="D10" s="41">
+      <c r="D11" s="44">
         <v>6959.808550594178</v>
       </c>
-      <c r="E10" s="41">
+      <c r="E11" s="44">
         <v>6959.808550594178</v>
       </c>
-      <c r="F10" s="41">
+      <c r="F11" s="44">
         <v>6959.808550594178</v>
       </c>
-      <c r="G10" s="41">
+      <c r="G11" s="44">
         <v>6959.808550594178</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="26" t="s">
-        <v>218</v>
-      </c>
-      <c r="C11" s="42">
-        <v>47106.02478273915</v>
-      </c>
-      <c r="D11" s="42">
-        <v>129300.06144940577</v>
-      </c>
-      <c r="E11" s="42">
-        <v>204310.17004940574</v>
-      </c>
-      <c r="F11" s="42">
-        <v>264404.8108136556</v>
-      </c>
-      <c r="G11" s="42">
-        <v>270245.2417969268</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="C12" s="42">
+        <v>222</v>
+      </c>
+      <c r="C12" s="45">
         <v>47106.02478273915</v>
       </c>
-      <c r="D12" s="42">
-        <v>176406.0862321449</v>
-      </c>
-      <c r="E12" s="42">
-        <v>380716.2562815506</v>
-      </c>
-      <c r="F12" s="42">
-        <v>645121.0670952062</v>
-      </c>
-      <c r="G12" s="42">
-        <v>915366.3088921331</v>
+      <c r="D12" s="45">
+        <v>129300.06144940577</v>
+      </c>
+      <c r="E12" s="45">
+        <v>204310.17004940574</v>
+      </c>
+      <c r="F12" s="45">
+        <v>264404.8108136556</v>
+      </c>
+      <c r="G12" s="45">
+        <v>270245.2417969268</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="C13" s="43">
-        <v>0.21257231400153045</v>
-      </c>
-      <c r="D13" s="43">
-        <v>0.3823776944954666</v>
-      </c>
-      <c r="E13" s="43">
-        <v>0.4836243748858784</v>
-      </c>
-      <c r="F13" s="43">
-        <v>0.5381395102814428</v>
-      </c>
-      <c r="G13" s="43">
-        <v>0.5366111804054611</v>
+        <v>164</v>
+      </c>
+      <c r="C13" s="45">
+        <v>47106.02478273915</v>
+      </c>
+      <c r="D13" s="45">
+        <v>176406.0862321449</v>
+      </c>
+      <c r="E13" s="45">
+        <v>380716.2562815506</v>
+      </c>
+      <c r="F13" s="45">
+        <v>645121.0670952062</v>
+      </c>
+      <c r="G13" s="45">
+        <v>915366.3088921331</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="26" t="s">
-        <v>220</v>
-      </c>
-      <c r="C14" s="41">
+        <v>223</v>
+      </c>
+      <c r="C14" s="46">
+        <v>0.21257231400153045</v>
+      </c>
+      <c r="D14" s="46">
+        <v>0.3823776944954666</v>
+      </c>
+      <c r="E14" s="46">
+        <v>0.4836243748858784</v>
+      </c>
+      <c r="F14" s="46">
+        <v>0.5381395102814428</v>
+      </c>
+      <c r="G14" s="46">
+        <v>0.5366111804054611</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="C15" s="47">
         <v>18466.666666666668</v>
       </c>
-      <c r="D14" s="41">
+      <c r="D15" s="47">
         <v>18785.97222222222</v>
       </c>
-      <c r="E14" s="41">
+      <c r="E15" s="47">
         <v>19202.559659090904</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F15" s="47">
         <v>19653.253906249993</v>
       </c>
-      <c r="G14" s="41">
+      <c r="G15" s="47">
         <v>20144.58525390624</v>
       </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="C15" s="43">
+      <c r="H15" s="48" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="C16" s="46">
         <v>0.5367065282791817</v>
       </c>
-      <c r="D15" s="43">
+      <c r="D16" s="46">
         <v>0.4347293119127009</v>
       </c>
-      <c r="E15" s="43">
+      <c r="E16" s="46">
         <v>0.3584103359800075</v>
       </c>
-      <c r="F15" s="43">
+      <c r="F16" s="46">
         <v>0.31741327092386307</v>
       </c>
-      <c r="G15" s="43">
+      <c r="G16" s="46">
         <v>0.31896162834300396</v>
       </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="26" t="s">
-        <v>222</v>
-      </c>
-      <c r="C16" s="43">
+      <c r="H16" s="48" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="C17" s="46">
         <v>0.0657942238267148</v>
       </c>
-      <c r="D16" s="43">
+      <c r="D17" s="46">
         <v>0.04869324776909486</v>
       </c>
-      <c r="E16" s="43">
+      <c r="E17" s="46">
         <v>0.0424471997918128</v>
       </c>
-      <c r="F16" s="43">
+      <c r="F17" s="46">
         <v>0.03908460457307385</v>
       </c>
-      <c r="G16" s="43">
+      <c r="G17" s="46">
         <v>0.03918224414098794</v>
       </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="C17" s="43">
+      <c r="H17" s="48" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="C18" s="46">
         <v>0.2439793922984356</v>
       </c>
-      <c r="D17" s="43">
+      <c r="D18" s="46">
         <v>0.40295986219031626</v>
       </c>
-      <c r="E17" s="43">
+      <c r="E18" s="46">
         <v>0.5000989980472832</v>
       </c>
-      <c r="F17" s="43">
+      <c r="F18" s="46">
         <v>0.5523047138325573</v>
       </c>
-      <c r="G17" s="43">
+      <c r="G18" s="46">
         <v>0.5504308911870363</v>
       </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="C18" s="44">
+      <c r="H18" s="48" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="C19" s="49">
+        <v>1</v>
+      </c>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="49"/>
+      <c r="H19" s="48" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="C20" s="50">
         <v>7.768293185121821</v>
       </c>
-      <c r="D18" s="44">
+      <c r="D20" s="50">
         <v>19.57810606562835</v>
       </c>
-      <c r="E18" s="44">
+      <c r="E20" s="50">
         <v>30.35571698045677</v>
       </c>
-      <c r="F18" s="44">
+      <c r="F20" s="50">
         <v>38.99024195731399</v>
       </c>
-      <c r="G18" s="44">
+      <c r="G20" s="50">
         <v>39.82940742297506</v>
       </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="C19" s="45" t="s">
-        <v>209</v>
-      </c>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="45"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="C20" s="45" t="s">
-        <v>227</v>
-      </c>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="G22" s="12"/>
-    </row>
-    <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="46" t="s">
-        <v>232</v>
-      </c>
-      <c r="C23" s="47" t="s">
-        <v>233</v>
-      </c>
-      <c r="D23" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="E23" s="48"/>
-      <c r="F23" s="49" t="s">
+      <c r="H20" s="48" t="s">
         <v>235</v>
       </c>
-      <c r="G23" s="49"/>
-    </row>
-    <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="46" t="s">
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="26" t="s">
         <v>236</v>
       </c>
-      <c r="C24" s="47" t="s">
-        <v>233</v>
-      </c>
-      <c r="D24" s="48" t="s">
+      <c r="C21" s="51" t="s">
+        <v>212</v>
+      </c>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="48" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="26" t="s">
         <v>237</v>
       </c>
-      <c r="E24" s="48"/>
-      <c r="F24" s="49" t="s">
+      <c r="C22" s="51" t="s">
         <v>238</v>
       </c>
-      <c r="G24" s="49"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="46" t="s">
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="48" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="C25" s="47" t="s">
-        <v>233</v>
-      </c>
-      <c r="D25" s="48" t="s">
+      <c r="C24" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="E25" s="48"/>
-      <c r="F25" s="49" t="s">
+      <c r="D24" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="G25" s="49"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="46" t="s">
+      <c r="E24" s="12"/>
+      <c r="F24" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="C26" s="47" t="s">
-        <v>233</v>
-      </c>
-      <c r="D26" s="48" t="s">
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E26" s="48"/>
-      <c r="F26" s="49" t="s">
+      <c r="C25" s="53" t="s">
         <v>244</v>
       </c>
-      <c r="G26" s="49"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="46" t="s">
+      <c r="D25" s="54" t="s">
         <v>245</v>
       </c>
-      <c r="C27" s="47" t="s">
-        <v>233</v>
-      </c>
-      <c r="D27" s="48" t="s">
+      <c r="E25" s="54"/>
+      <c r="F25" s="55" t="s">
         <v>246</v>
       </c>
-      <c r="E27" s="48"/>
-      <c r="F27" s="49" t="s">
+      <c r="G25" s="55"/>
+      <c r="H25" s="55"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="52" t="s">
         <v>247</v>
       </c>
-      <c r="G27" s="49"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="46" t="s">
+      <c r="C26" s="53" t="s">
+        <v>244</v>
+      </c>
+      <c r="D26" s="54" t="s">
         <v>248</v>
       </c>
-      <c r="C28" s="47" t="s">
-        <v>233</v>
-      </c>
-      <c r="D28" s="48" t="s">
+      <c r="E26" s="54"/>
+      <c r="F26" s="55" t="s">
         <v>249</v>
       </c>
-      <c r="E28" s="48"/>
-      <c r="F28" s="49" t="s">
+      <c r="G26" s="55"/>
+      <c r="H26" s="55"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="52" t="s">
         <v>250</v>
       </c>
-      <c r="G28" s="49"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="46" t="s">
+      <c r="C27" s="53" t="s">
+        <v>244</v>
+      </c>
+      <c r="D27" s="54" t="s">
         <v>251</v>
       </c>
-      <c r="C29" s="47" t="s">
-        <v>233</v>
-      </c>
-      <c r="D29" s="48" t="s">
+      <c r="E27" s="54"/>
+      <c r="F27" s="55" t="s">
         <v>252</v>
       </c>
-      <c r="E29" s="48"/>
-      <c r="F29" s="49" t="s">
+      <c r="G27" s="55"/>
+      <c r="H27" s="55"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="52" t="s">
         <v>253</v>
       </c>
-      <c r="G29" s="49"/>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="46" t="s">
+      <c r="C28" s="53" t="s">
+        <v>244</v>
+      </c>
+      <c r="D28" s="54" t="s">
         <v>254</v>
       </c>
-      <c r="C31" s="26" t="s">
+      <c r="E28" s="54"/>
+      <c r="F28" s="55" t="s">
         <v>255</v>
       </c>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="50" t="s">
+      <c r="G28" s="55"/>
+      <c r="H28" s="55"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="52" t="s">
+        <v>256</v>
+      </c>
+      <c r="C29" s="53" t="s">
+        <v>244</v>
+      </c>
+      <c r="D29" s="54" t="s">
+        <v>257</v>
+      </c>
+      <c r="E29" s="54"/>
+      <c r="F29" s="55" t="s">
+        <v>258</v>
+      </c>
+      <c r="G29" s="55"/>
+      <c r="H29" s="55"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="52" t="s">
+        <v>259</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>244</v>
+      </c>
+      <c r="D30" s="54" t="s">
+        <v>260</v>
+      </c>
+      <c r="E30" s="54"/>
+      <c r="F30" s="55" t="s">
+        <v>261</v>
+      </c>
+      <c r="G30" s="55"/>
+      <c r="H30" s="55"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="52" t="s">
+        <v>262</v>
+      </c>
+      <c r="C31" s="53" t="s">
+        <v>244</v>
+      </c>
+      <c r="D31" s="54" t="s">
+        <v>263</v>
+      </c>
+      <c r="E31" s="54"/>
+      <c r="F31" s="55" t="s">
+        <v>264</v>
+      </c>
+      <c r="G31" s="55"/>
+      <c r="H31" s="55"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="52" t="s">
+        <v>265</v>
+      </c>
+      <c r="C33" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="56" t="s">
         <v>129</v>
       </c>
-      <c r="C33" s="50"/>
-      <c r="D33" s="50"/>
-      <c r="E33" s="50"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="50"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
+  <mergeCells count="23">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F26:H26"/>
     <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F27:H27"/>
     <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
-  <conditionalFormatting sqref="C11:G11">
+  <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>C11&gt;=0</formula>
+      <formula>C12&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>C11&gt;=-1</formula>
+      <formula>C12&gt;=-1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="3">
-      <formula>C11&lt;-1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C12:G12">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>C12&gt;=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
-      <formula>C12&gt;=-1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3">
       <formula>C12&lt;-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:G13">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>C13&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C13&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C13&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:G14">
     <cfRule type="expression" dxfId="6" priority="1">
-      <formula>C13&gt;=0.05</formula>
+      <formula>C14&gt;=0.05</formula>
     </cfRule>
     <cfRule type="expression" dxfId="7" priority="2">
-      <formula>C13&gt;=0</formula>
+      <formula>C14&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="8" priority="3">
-      <formula>C13&lt;0</formula>
+      <formula>C14&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:G15">
     <cfRule type="expression" dxfId="9" priority="1">
-      <formula>C15&lt;=0.55</formula>
+      <formula>C15&gt;=10000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="2">
-      <formula>C15&lt;=0.65</formula>
+      <formula>C15&gt;=7000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="11" priority="3">
-      <formula>C15&gt;0.65</formula>
+      <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.15</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.25</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.25</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&gt;=0.10</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&gt;=0</formula>
+      <formula>C17&lt;=0.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&lt;0</formula>
+      <formula>C17&gt;0.25</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=1.25</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=1.0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;1.0</formula>
+      <formula>C18&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C20:G20">
+    <cfRule type="expression" dxfId="21" priority="1">
+      <formula>C20&gt;=1.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="2">
+      <formula>C20&gt;=1.0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="3">
+      <formula>C20&lt;1.0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
@@ -15,7 +15,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Instructions'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$J56</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'5-Year Model'!$A1:$F75</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'5-Year Model'!$A1:$F76</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N46</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="269">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -507,6 +507,12 @@
   </si>
   <si>
     <t>Cumulative Profit</t>
+  </si>
+  <si>
+    <t>Break-even</t>
+  </si>
+  <si>
+    <t>✓ Break-even</t>
   </si>
   <si>
     <t>CASH FLOW &amp; DEBT COVERAGE</t>
@@ -923,14 +929,14 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <i/>
-      <color rgb="FF6B7280"/>
+      <b/>
+      <color rgb="FF16A34A"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF16A34A"/>
+      <i/>
+      <color rgb="FF6B7280"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1031,7 +1037,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1074,13 +1080,19 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="167" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1098,20 +1110,17 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2592,7 +2601,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -3429,500 +3438,520 @@
         <v>886530</v>
       </c>
     </row>
-    <row r="51" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="12" t="s">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="29" t="s">
         <v>160</v>
       </c>
-      <c r="B51" s="12"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="26" t="s">
+      <c r="B50" s="34" t="s">
         <v>161</v>
       </c>
-      <c r="B52" s="30">
+      <c r="C50" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="E50" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="F50" s="35" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="B52" s="12"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="26" t="s">
+        <v>163</v>
+      </c>
+      <c r="B53" s="30">
         <f>B41-B42-B43</f>
         <v>25233</v>
       </c>
-      <c r="C52" s="30">
+      <c r="C53" s="30">
         <f>C41-C42-C43</f>
         <v>136259</v>
       </c>
-      <c r="D52" s="30">
+      <c r="D53" s="30">
         <f>D41-D42-D43</f>
         <v>211269</v>
       </c>
-      <c r="E52" s="30">
+      <c r="E53" s="30">
         <f>E41-E42-E43</f>
         <v>271364</v>
       </c>
-      <c r="F52" s="30">
+      <c r="F53" s="30">
         <f>F41-F42-F43</f>
         <v>277205</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="B53" s="21">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="B54" s="21">
         <f>B44</f>
         <v>6960</v>
       </c>
-      <c r="C53" s="21">
+      <c r="C54" s="21">
         <f>C44</f>
         <v>6960</v>
       </c>
-      <c r="D53" s="21">
+      <c r="D54" s="21">
         <f>D44</f>
         <v>6960</v>
       </c>
-      <c r="E53" s="21">
+      <c r="E54" s="21">
         <f>E44</f>
         <v>6960</v>
       </c>
-      <c r="F53" s="21">
+      <c r="F54" s="21">
         <f>F44</f>
         <v>6960</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="26" t="s">
-        <v>163</v>
-      </c>
-      <c r="B54" s="34">
-        <f>IF(B53=0,"N/A",B52/B53)</f>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="B55" s="36">
+        <f>IF(B54=0,"N/A",B53/B54)</f>
         <v>3.63</v>
       </c>
-      <c r="C54" s="34">
-        <f>IF(C53=0,"N/A",C52/C53)</f>
+      <c r="C55" s="36">
+        <f>IF(C54=0,"N/A",C53/C54)</f>
         <v>19.58</v>
       </c>
-      <c r="D54" s="34">
-        <f>IF(D53=0,"N/A",D52/D53)</f>
+      <c r="D55" s="36">
+        <f>IF(D54=0,"N/A",D53/D54)</f>
         <v>30.35</v>
       </c>
-      <c r="E54" s="34">
-        <f>IF(E53=0,"N/A",E52/E53)</f>
+      <c r="E55" s="36">
+        <f>IF(E54=0,"N/A",E53/E54)</f>
         <v>38.99</v>
       </c>
-      <c r="F54" s="34">
-        <f>IF(F53=0,"N/A",F52/F53)</f>
+      <c r="F55" s="36">
+        <f>IF(F54=0,"N/A",F53/F54)</f>
         <v>39.83</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="13" t="s">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="B55" s="21" t="str">
+      <c r="B56" s="21" t="str">
         <f>Assumptions!B54</f>
         <v>0</v>
       </c>
-      <c r="C55" s="21">
-        <f>B56</f>
+      <c r="C56" s="21">
+        <f>B57</f>
         <v>18273</v>
       </c>
-      <c r="D55" s="21">
-        <f>C56</f>
+      <c r="D56" s="21">
+        <f>C57</f>
         <v>147572</v>
       </c>
-      <c r="E55" s="21">
-        <f>D56</f>
+      <c r="E56" s="21">
+        <f>D57</f>
         <v>351881</v>
       </c>
-      <c r="F55" s="21">
-        <f>E56</f>
+      <c r="F56" s="21">
+        <f>E57</f>
         <v>616285</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="B56" s="30">
-        <f>B55+B47</f>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="B57" s="30">
+        <f>B56+B47</f>
         <v>18273</v>
       </c>
-      <c r="C56" s="30">
-        <f>C55+C47</f>
+      <c r="C57" s="30">
+        <f>C56+C47</f>
         <v>147572</v>
       </c>
-      <c r="D56" s="30">
-        <f>D55+D47</f>
+      <c r="D57" s="30">
+        <f>D56+D47</f>
         <v>351881</v>
       </c>
-      <c r="E56" s="30">
-        <f>E55+E47</f>
+      <c r="E57" s="30">
+        <f>E56+E47</f>
         <v>616285</v>
       </c>
-      <c r="F56" s="30">
-        <f>F55+F47</f>
+      <c r="F57" s="30">
+        <f>F56+F47</f>
         <v>886530</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="B57" s="35">
-        <f>IF(B45=0,"",B56/B45*365)</f>
-        <v>40</v>
-      </c>
-      <c r="C57" s="35">
-        <f>IF(C45=0,"",C56/C45*365)</f>
-        <v>258</v>
-      </c>
-      <c r="D57" s="35">
-        <f>IF(D45=0,"",D56/D45*365)</f>
-        <v>589</v>
-      </c>
-      <c r="E57" s="35">
-        <f>IF(E45=0,"",E56/E45*365)</f>
-        <v>991</v>
-      </c>
-      <c r="F57" s="35">
-        <f>IF(F45=0,"",F56/F45*365)</f>
-        <v>1387</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="B58" s="36">
-        <f>IF(B45=0,"",B56/(B45/12))</f>
-        <v>1.3</v>
-      </c>
-      <c r="C58" s="36">
-        <f>IF(C45=0,"",C56/(C45/12))</f>
-        <v>8.5</v>
-      </c>
-      <c r="D58" s="36">
-        <f>IF(D45=0,"",D56/(D45/12))</f>
-        <v>19.4</v>
-      </c>
-      <c r="E58" s="36">
-        <f>IF(E45=0,"",E56/(E45/12))</f>
-        <v>32.6</v>
-      </c>
-      <c r="F58" s="36">
-        <f>IF(F45=0,"",F56/(F45/12))</f>
-        <v>45.6</v>
+        <v>167</v>
+      </c>
+      <c r="B58" s="37">
+        <f>IF(B45=0,"",B57/B45*365)</f>
+        <v>40</v>
+      </c>
+      <c r="C58" s="37">
+        <f>IF(C45=0,"",C57/C45*365)</f>
+        <v>258</v>
+      </c>
+      <c r="D58" s="37">
+        <f>IF(D45=0,"",D57/D45*365)</f>
+        <v>589</v>
+      </c>
+      <c r="E58" s="37">
+        <f>IF(E45=0,"",E57/E45*365)</f>
+        <v>991</v>
+      </c>
+      <c r="F58" s="37">
+        <f>IF(F45=0,"",F57/F45*365)</f>
+        <v>1387</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="B59" s="33">
+        <v>168</v>
+      </c>
+      <c r="B59" s="38">
+        <f>IF(B45=0,"",B57/(B45/12))</f>
+        <v>1.3</v>
+      </c>
+      <c r="C59" s="38">
+        <f>IF(C45=0,"",C57/(C45/12))</f>
+        <v>8.5</v>
+      </c>
+      <c r="D59" s="38">
+        <f>IF(D45=0,"",D57/(D45/12))</f>
+        <v>19.4</v>
+      </c>
+      <c r="E59" s="38">
+        <f>IF(E45=0,"",E57/(E45/12))</f>
+        <v>32.6</v>
+      </c>
+      <c r="F59" s="38">
+        <f>IF(F45=0,"",F57/(F45/12))</f>
+        <v>45.6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="B60" s="33">
         <f>IF(Assumptions!B12=0,"",B3/Assumptions!B12)</f>
         <v>0.48</v>
       </c>
-      <c r="C59" s="33">
+      <c r="C60" s="33">
         <f>IF(Assumptions!B12=0,"",C3/Assumptions!B12)</f>
         <v>0.72</v>
       </c>
-      <c r="D59" s="33">
+      <c r="D60" s="33">
         <f>IF(Assumptions!B12=0,"",D3/Assumptions!B12)</f>
         <v>0.88</v>
       </c>
-      <c r="E59" s="33">
+      <c r="E60" s="33">
         <f>IF(Assumptions!B12=0,"",E3/Assumptions!B12)</f>
         <v>1</v>
       </c>
-      <c r="F59" s="33">
+      <c r="F60" s="33">
         <f>IF(Assumptions!B12=0,"",F3/Assumptions!B12)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="61" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="B61" s="12"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="12"/>
-      <c r="E61" s="12"/>
-      <c r="F61" s="12"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="B62" s="13" t="str">
-        <f>IF(B53=0,"N/A",IF(B54&gt;=1.2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="C62" s="13" t="str">
-        <f>IF(C53=0,"N/A",IF(C54&gt;=1.2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="D62" s="13" t="str">
-        <f>IF(D53=0,"N/A",IF(D54&gt;=1.2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="E62" s="13" t="str">
-        <f>IF(E53=0,"N/A",IF(E54&gt;=1.2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="F62" s="13" t="str">
-        <f>IF(F53=0,"N/A",IF(F54&gt;=1.2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
+    <row r="62" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B63" s="13" t="str">
+        <f>IF(B54=0,"N/A",IF(B55&gt;=1.2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+      <c r="C63" s="13" t="str">
+        <f>IF(C54=0,"N/A",IF(C55&gt;=1.2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+      <c r="D63" s="13" t="str">
+        <f>IF(D54=0,"N/A",IF(D55&gt;=1.2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+      <c r="E63" s="13" t="str">
+        <f>IF(E54=0,"N/A",IF(E55&gt;=1.2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+      <c r="F63" s="13" t="str">
+        <f>IF(F54=0,"N/A",IF(F55&gt;=1.2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="B64" s="13" t="str">
         <f>IF(B47&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="C63" s="13" t="str">
+      <c r="C64" s="13" t="str">
         <f>IF(C47&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="D63" s="13" t="str">
+      <c r="D64" s="13" t="str">
         <f>IF(D47&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E63" s="13" t="str">
+      <c r="E64" s="13" t="str">
         <f>IF(E47&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="F63" s="13" t="str">
+      <c r="F64" s="13" t="str">
         <f>IF(F47&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B64" s="13" t="str">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="B65" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(B3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C64" s="13" t="str">
+      <c r="C65" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(C3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="D64" s="13" t="str">
+      <c r="D65" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(D3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E64" s="13" t="str">
+      <c r="E65" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(E3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F64" s="13" t="str">
+      <c r="F65" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(F3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="B65" s="13" t="str">
-        <f>IF(B45=0,"N/A",IF(B56/(B45/12)&gt;=2,"PASS","FAIL"))</f>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="B66" s="13" t="str">
+        <f>IF(B45=0,"N/A",IF(B57/(B45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C65" s="13" t="str">
-        <f>IF(C45=0,"N/A",IF(C56/(C45/12)&gt;=2,"PASS","FAIL"))</f>
+      <c r="C66" s="13" t="str">
+        <f>IF(C45=0,"N/A",IF(C57/(C45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="D65" s="13" t="str">
-        <f>IF(D45=0,"N/A",IF(D56/(D45/12)&gt;=2,"PASS","FAIL"))</f>
+      <c r="D66" s="13" t="str">
+        <f>IF(D45=0,"N/A",IF(D57/(D45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E65" s="13" t="str">
-        <f>IF(E45=0,"N/A",IF(E56/(E45/12)&gt;=2,"PASS","FAIL"))</f>
+      <c r="E66" s="13" t="str">
+        <f>IF(E45=0,"N/A",IF(E57/(E45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F65" s="13" t="str">
-        <f>IF(F45=0,"N/A",IF(F56/(F45/12)&gt;=2,"PASS","FAIL"))</f>
+      <c r="F66" s="13" t="str">
+        <f>IF(F45=0,"N/A",IF(F57/(F45/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="67" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="B67" s="12"/>
-      <c r="C67" s="12"/>
-      <c r="D67" s="12"/>
-      <c r="E67" s="12"/>
-      <c r="F67" s="12"/>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="B68" s="21">
+    <row r="68" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="B68" s="12"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="12"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="B69" s="21">
         <f>IF(B3=0,"",B11/B3)</f>
         <v>15389</v>
       </c>
-      <c r="C68" s="21">
+      <c r="C69" s="21">
         <f>IF(C3=0,"",C11/C3)</f>
         <v>18786</v>
       </c>
-      <c r="D68" s="21">
+      <c r="D69" s="21">
         <f>IF(D3=0,"",D11/D3)</f>
         <v>19203</v>
       </c>
-      <c r="E68" s="21">
+      <c r="E69" s="21">
         <f>IF(E3=0,"",E11/E3)</f>
         <v>19653</v>
       </c>
-      <c r="F68" s="21">
+      <c r="F69" s="21">
         <f>IF(F3=0,"",F11/F3)</f>
         <v>20145</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="B69" s="21">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="B70" s="21">
         <f>IF(B3=0,"",B45/B3)</f>
         <v>13866</v>
       </c>
-      <c r="C69" s="21">
+      <c r="C70" s="21">
         <f>IF(C3=0,"",C45/C3)</f>
         <v>11603</v>
       </c>
-      <c r="D69" s="21">
+      <c r="D70" s="21">
         <f>IF(D3=0,"",D45/D3)</f>
         <v>9916</v>
       </c>
-      <c r="E69" s="21">
+      <c r="E70" s="21">
         <f>IF(E3=0,"",E45/E3)</f>
         <v>9077</v>
       </c>
-      <c r="F69" s="21">
+      <c r="F70" s="21">
         <f>IF(F3=0,"",F45/F3)</f>
         <v>9335</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="B70" s="21">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="B71" s="21">
         <f>B42+B44</f>
         <v>125894</v>
       </c>
-      <c r="C70" s="21">
+      <c r="C71" s="21">
         <f>C42+C44</f>
         <v>153963</v>
       </c>
-      <c r="D70" s="21">
+      <c r="D71" s="21">
         <f>D42+D44</f>
         <v>158373</v>
       </c>
-      <c r="E70" s="21">
+      <c r="E71" s="21">
         <f>E42+E44</f>
         <v>162915</v>
       </c>
-      <c r="F70" s="21">
+      <c r="F71" s="21">
         <f>F42+F44</f>
         <v>167594</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="B71" s="21">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="B72" s="21">
         <f>IF(B3=0,"",B43/B3)</f>
         <v>3375</v>
       </c>
-      <c r="C71" s="21">
+      <c r="C72" s="21">
         <f>IF(C3=0,"",C43/C3)</f>
         <v>3049</v>
       </c>
-      <c r="D71" s="21">
+      <c r="D72" s="21">
         <f>IF(D3=0,"",D43/D3)</f>
         <v>2717</v>
       </c>
-      <c r="E71" s="21">
+      <c r="E72" s="21">
         <f>IF(E3=0,"",E43/E3)</f>
         <v>2560</v>
       </c>
-      <c r="F71" s="21">
+      <c r="F72" s="21">
         <f>IF(F3=0,"",F43/F3)</f>
         <v>2631</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="B72" s="21">
-        <f>IF(B3=0,"",B68-B71)</f>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B73" s="21">
+        <f>IF(B3=0,"",B69-B72)</f>
         <v>12014</v>
       </c>
-      <c r="C72" s="21">
-        <f>IF(C3=0,"",C68-C71)</f>
+      <c r="C73" s="21">
+        <f>IF(C3=0,"",C69-C72)</f>
         <v>15737</v>
       </c>
-      <c r="D72" s="21">
-        <f>IF(D3=0,"",D68-D71)</f>
+      <c r="D73" s="21">
+        <f>IF(D3=0,"",D69-D72)</f>
         <v>16486</v>
       </c>
-      <c r="E72" s="21">
-        <f>IF(E3=0,"",E68-E71)</f>
+      <c r="E73" s="21">
+        <f>IF(E3=0,"",E69-E72)</f>
         <v>17093</v>
       </c>
-      <c r="F72" s="21">
-        <f>IF(F3=0,"",F68-F71)</f>
+      <c r="F73" s="21">
+        <f>IF(F3=0,"",F69-F72)</f>
         <v>17514</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="B73" s="38">
-        <f>IF(B72&lt;=0,"N/A",ROUNDUP(B70/B72,0))</f>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="39" t="s">
+        <v>181</v>
+      </c>
+      <c r="B74" s="40">
+        <f>IF(B73&lt;=0,"N/A",ROUNDUP(B71/B73,0))</f>
         <v>11</v>
       </c>
-      <c r="C73" s="38">
-        <f>IF(C72&lt;=0,"N/A",ROUNDUP(C70/C72,0))</f>
+      <c r="C74" s="40">
+        <f>IF(C73&lt;=0,"N/A",ROUNDUP(C71/C73,0))</f>
         <v>10</v>
       </c>
-      <c r="D73" s="38">
-        <f>IF(D72&lt;=0,"N/A",ROUNDUP(D70/D72,0))</f>
+      <c r="D74" s="40">
+        <f>IF(D73&lt;=0,"N/A",ROUNDUP(D71/D73,0))</f>
         <v>10</v>
       </c>
-      <c r="E73" s="38">
-        <f>IF(E72&lt;=0,"N/A",ROUNDUP(E70/E72,0))</f>
+      <c r="E74" s="40">
+        <f>IF(E73&lt;=0,"N/A",ROUNDUP(E71/E73,0))</f>
         <v>10</v>
       </c>
-      <c r="F73" s="38">
-        <f>IF(F72&lt;=0,"N/A",ROUNDUP(F70/F72,0))</f>
+      <c r="F74" s="40">
+        <f>IF(F73&lt;=0,"N/A",ROUNDUP(F71/F73,0))</f>
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="24" t="s">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="B75" s="24"/>
-      <c r="C75" s="24"/>
-      <c r="D75" s="24"/>
-      <c r="E75" s="24"/>
-      <c r="F75" s="24"/>
+      <c r="B76" s="24"/>
+      <c r="C76" s="24"/>
+      <c r="D76" s="24"/>
+      <c r="E76" s="24"/>
+      <c r="F76" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A76:F76"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
@@ -3948,7 +3977,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -3972,40 +4001,40 @@
         <v>46</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H2" s="25" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="J2" s="25" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K2" s="25" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L2" s="25" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M2" s="25" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="N2" s="25" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -4566,7 +4595,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B19" s="21">
         <v>500</v>
@@ -4674,7 +4703,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B22" s="21">
         <v>300</v>
@@ -4782,7 +4811,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B25" s="21">
         <v>2500</v>
@@ -4827,7 +4856,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B26" s="21">
         <v>300</v>
@@ -4872,7 +4901,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B27" s="21">
         <v>200</v>
@@ -4980,7 +5009,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B30" s="21">
         <v>250</v>
@@ -5132,7 +5161,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="26" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B34" s="21">
         <v>580</v>
@@ -5182,7 +5211,7 @@
     </row>
     <row r="36" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
@@ -5257,7 +5286,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="26" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B38" s="30">
         <f>B9-B37</f>
@@ -5314,7 +5343,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B39" s="30">
         <f>0+B38</f>
@@ -5371,7 +5400,7 @@
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
@@ -5386,7 +5415,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B43" s="30">
         <f>M39</f>
@@ -5395,7 +5424,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B44" s="21">
         <f>MIN(B39:M39)</f>
@@ -5452,7 +5481,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -5462,527 +5491,527 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="39" t="s">
-        <v>207</v>
-      </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
+      <c r="B3" s="41" t="s">
+        <v>209</v>
+      </c>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="40" t="s">
-        <v>208</v>
-      </c>
-      <c r="D4" s="41" t="s">
-        <v>209</v>
-      </c>
-      <c r="F4" s="42" t="s">
+      <c r="B4" s="42" t="s">
         <v>210</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>211</v>
+      </c>
+      <c r="F4" s="44" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="C7" s="43">
+        <v>220</v>
+      </c>
+      <c r="C7" s="45">
         <v>12</v>
       </c>
-      <c r="D7" s="43">
+      <c r="D7" s="45">
         <v>18</v>
       </c>
-      <c r="E7" s="43">
+      <c r="E7" s="45">
         <v>22</v>
       </c>
-      <c r="F7" s="43">
+      <c r="F7" s="45">
         <v>25</v>
       </c>
-      <c r="G7" s="43">
+      <c r="G7" s="45">
         <v>25</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="C8" s="44">
+        <v>221</v>
+      </c>
+      <c r="C8" s="46">
         <v>221600</v>
       </c>
-      <c r="D8" s="44">
+      <c r="D8" s="46">
         <v>338147.49999999994</v>
       </c>
-      <c r="E8" s="44">
+      <c r="E8" s="46">
         <v>422456.3124999999</v>
       </c>
-      <c r="F8" s="44">
+      <c r="F8" s="46">
         <v>491331.3476562498</v>
       </c>
-      <c r="G8" s="44">
+      <c r="G8" s="46">
         <v>503614.631347656</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="C9" s="44">
+        <v>222</v>
+      </c>
+      <c r="C9" s="46">
         <v>118934.16666666667</v>
       </c>
-      <c r="D9" s="44">
+      <c r="D9" s="46">
         <v>147002.63</v>
       </c>
-      <c r="E9" s="44">
+      <c r="E9" s="46">
         <v>151412.7089</v>
       </c>
-      <c r="F9" s="44">
+      <c r="F9" s="46">
         <v>155955.090167</v>
       </c>
-      <c r="G9" s="44">
+      <c r="G9" s="46">
         <v>160633.74287201</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="C10" s="44">
+        <v>223</v>
+      </c>
+      <c r="C10" s="46">
         <v>48600</v>
       </c>
-      <c r="D10" s="44">
+      <c r="D10" s="46">
         <v>54885</v>
       </c>
-      <c r="E10" s="44">
+      <c r="E10" s="46">
         <v>59773.625</v>
       </c>
-      <c r="F10" s="44">
+      <c r="F10" s="46">
         <v>64011.63812499999</v>
       </c>
-      <c r="G10" s="44">
+      <c r="G10" s="46">
         <v>65775.83812812499</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="C11" s="44">
+        <v>164</v>
+      </c>
+      <c r="C11" s="46">
         <v>6959.808550594178</v>
       </c>
-      <c r="D11" s="44">
+      <c r="D11" s="46">
         <v>6959.808550594178</v>
       </c>
-      <c r="E11" s="44">
+      <c r="E11" s="46">
         <v>6959.808550594178</v>
       </c>
-      <c r="F11" s="44">
+      <c r="F11" s="46">
         <v>6959.808550594178</v>
       </c>
-      <c r="G11" s="44">
+      <c r="G11" s="46">
         <v>6959.808550594178</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="26" t="s">
-        <v>222</v>
-      </c>
-      <c r="C12" s="45">
+        <v>224</v>
+      </c>
+      <c r="C12" s="47">
         <v>47106.02478273915</v>
       </c>
-      <c r="D12" s="45">
+      <c r="D12" s="47">
         <v>129300.06144940577</v>
       </c>
-      <c r="E12" s="45">
+      <c r="E12" s="47">
         <v>204310.17004940574</v>
       </c>
-      <c r="F12" s="45">
+      <c r="F12" s="47">
         <v>264404.8108136556</v>
       </c>
-      <c r="G12" s="45">
+      <c r="G12" s="47">
         <v>270245.2417969268</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="C13" s="45">
+        <v>166</v>
+      </c>
+      <c r="C13" s="47">
         <v>47106.02478273915</v>
       </c>
-      <c r="D13" s="45">
+      <c r="D13" s="47">
         <v>176406.0862321449</v>
       </c>
-      <c r="E13" s="45">
+      <c r="E13" s="47">
         <v>380716.2562815506</v>
       </c>
-      <c r="F13" s="45">
+      <c r="F13" s="47">
         <v>645121.0670952062</v>
       </c>
-      <c r="G13" s="45">
+      <c r="G13" s="47">
         <v>915366.3088921331</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="C14" s="46">
+        <v>225</v>
+      </c>
+      <c r="C14" s="48">
         <v>0.21257231400153045</v>
       </c>
-      <c r="D14" s="46">
+      <c r="D14" s="48">
         <v>0.3823776944954666</v>
       </c>
-      <c r="E14" s="46">
+      <c r="E14" s="48">
         <v>0.4836243748858784</v>
       </c>
-      <c r="F14" s="46">
+      <c r="F14" s="48">
         <v>0.5381395102814428</v>
       </c>
-      <c r="G14" s="46">
+      <c r="G14" s="48">
         <v>0.5366111804054611</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="C15" s="47">
+        <v>226</v>
+      </c>
+      <c r="C15" s="49">
         <v>18466.666666666668</v>
       </c>
-      <c r="D15" s="47">
+      <c r="D15" s="49">
         <v>18785.97222222222</v>
       </c>
-      <c r="E15" s="47">
+      <c r="E15" s="49">
         <v>19202.559659090904</v>
       </c>
-      <c r="F15" s="47">
+      <c r="F15" s="49">
         <v>19653.253906249993</v>
       </c>
-      <c r="G15" s="47">
+      <c r="G15" s="49">
         <v>20144.58525390624</v>
       </c>
-      <c r="H15" s="48" t="s">
-        <v>225</v>
+      <c r="H15" s="50" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="C16" s="46">
+        <v>228</v>
+      </c>
+      <c r="C16" s="48">
         <v>0.5367065282791817</v>
       </c>
-      <c r="D16" s="46">
+      <c r="D16" s="48">
         <v>0.4347293119127009</v>
       </c>
-      <c r="E16" s="46">
+      <c r="E16" s="48">
         <v>0.3584103359800075</v>
       </c>
-      <c r="F16" s="46">
+      <c r="F16" s="48">
         <v>0.31741327092386307</v>
       </c>
-      <c r="G16" s="46">
+      <c r="G16" s="48">
         <v>0.31896162834300396</v>
       </c>
-      <c r="H16" s="48" t="s">
-        <v>227</v>
+      <c r="H16" s="50" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="C17" s="46">
+        <v>230</v>
+      </c>
+      <c r="C17" s="48">
         <v>0.0657942238267148</v>
       </c>
-      <c r="D17" s="46">
+      <c r="D17" s="48">
         <v>0.04869324776909486</v>
       </c>
-      <c r="E17" s="46">
+      <c r="E17" s="48">
         <v>0.0424471997918128</v>
       </c>
-      <c r="F17" s="46">
+      <c r="F17" s="48">
         <v>0.03908460457307385</v>
       </c>
-      <c r="G17" s="46">
+      <c r="G17" s="48">
         <v>0.03918224414098794</v>
       </c>
-      <c r="H17" s="48" t="s">
-        <v>229</v>
+      <c r="H17" s="50" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="C18" s="46">
+        <v>232</v>
+      </c>
+      <c r="C18" s="48">
         <v>0.2439793922984356</v>
       </c>
-      <c r="D18" s="46">
+      <c r="D18" s="48">
         <v>0.40295986219031626</v>
       </c>
-      <c r="E18" s="46">
+      <c r="E18" s="48">
         <v>0.5000989980472832</v>
       </c>
-      <c r="F18" s="46">
+      <c r="F18" s="48">
         <v>0.5523047138325573</v>
       </c>
-      <c r="G18" s="46">
+      <c r="G18" s="48">
         <v>0.5504308911870363</v>
       </c>
-      <c r="H18" s="48" t="s">
-        <v>231</v>
+      <c r="H18" s="50" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="26" t="s">
-        <v>232</v>
-      </c>
-      <c r="C19" s="49">
-        <v>1</v>
-      </c>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="48" t="s">
-        <v>233</v>
+        <v>234</v>
+      </c>
+      <c r="C19" s="51">
+        <v>3</v>
+      </c>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="50" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="C20" s="50">
+        <v>236</v>
+      </c>
+      <c r="C20" s="52">
         <v>7.768293185121821</v>
       </c>
-      <c r="D20" s="50">
+      <c r="D20" s="52">
         <v>19.57810606562835</v>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="52">
         <v>30.35571698045677</v>
       </c>
-      <c r="F20" s="50">
+      <c r="F20" s="52">
         <v>38.99024195731399</v>
       </c>
-      <c r="G20" s="50">
+      <c r="G20" s="52">
         <v>39.82940742297506</v>
       </c>
-      <c r="H20" s="48" t="s">
-        <v>235</v>
+      <c r="H20" s="50" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="26" t="s">
-        <v>236</v>
-      </c>
-      <c r="C21" s="51" t="s">
-        <v>212</v>
-      </c>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="48" t="s">
-        <v>212</v>
+        <v>238</v>
+      </c>
+      <c r="C21" s="53" t="s">
+        <v>214</v>
+      </c>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="50" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="C22" s="51" t="s">
-        <v>238</v>
-      </c>
-      <c r="D22" s="51"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="51"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="48" t="s">
-        <v>238</v>
+        <v>239</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>240</v>
+      </c>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="50" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="12" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E24" s="12"/>
       <c r="F24" s="12" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="G24" s="12"/>
       <c r="H24" s="12"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="52" t="s">
-        <v>243</v>
-      </c>
-      <c r="C25" s="53" t="s">
-        <v>244</v>
-      </c>
-      <c r="D25" s="54" t="s">
+      <c r="B25" s="54" t="s">
         <v>245</v>
       </c>
-      <c r="E25" s="54"/>
-      <c r="F25" s="55" t="s">
+      <c r="C25" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="G25" s="55"/>
-      <c r="H25" s="55"/>
+      <c r="D25" s="55" t="s">
+        <v>247</v>
+      </c>
+      <c r="E25" s="55"/>
+      <c r="F25" s="56" t="s">
+        <v>248</v>
+      </c>
+      <c r="G25" s="56"/>
+      <c r="H25" s="56"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="52" t="s">
-        <v>247</v>
-      </c>
-      <c r="C26" s="53" t="s">
-        <v>244</v>
-      </c>
-      <c r="D26" s="54" t="s">
-        <v>248</v>
-      </c>
-      <c r="E26" s="54"/>
-      <c r="F26" s="55" t="s">
+      <c r="B26" s="54" t="s">
         <v>249</v>
       </c>
-      <c r="G26" s="55"/>
-      <c r="H26" s="55"/>
+      <c r="C26" s="34" t="s">
+        <v>246</v>
+      </c>
+      <c r="D26" s="55" t="s">
+        <v>250</v>
+      </c>
+      <c r="E26" s="55"/>
+      <c r="F26" s="56" t="s">
+        <v>251</v>
+      </c>
+      <c r="G26" s="56"/>
+      <c r="H26" s="56"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="52" t="s">
-        <v>250</v>
-      </c>
-      <c r="C27" s="53" t="s">
-        <v>244</v>
-      </c>
-      <c r="D27" s="54" t="s">
-        <v>251</v>
-      </c>
-      <c r="E27" s="54"/>
-      <c r="F27" s="55" t="s">
+      <c r="B27" s="54" t="s">
         <v>252</v>
       </c>
-      <c r="G27" s="55"/>
-      <c r="H27" s="55"/>
+      <c r="C27" s="34" t="s">
+        <v>246</v>
+      </c>
+      <c r="D27" s="55" t="s">
+        <v>253</v>
+      </c>
+      <c r="E27" s="55"/>
+      <c r="F27" s="56" t="s">
+        <v>254</v>
+      </c>
+      <c r="G27" s="56"/>
+      <c r="H27" s="56"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="52" t="s">
-        <v>253</v>
-      </c>
-      <c r="C28" s="53" t="s">
-        <v>244</v>
-      </c>
-      <c r="D28" s="54" t="s">
-        <v>254</v>
-      </c>
-      <c r="E28" s="54"/>
-      <c r="F28" s="55" t="s">
+      <c r="B28" s="54" t="s">
         <v>255</v>
       </c>
-      <c r="G28" s="55"/>
-      <c r="H28" s="55"/>
+      <c r="C28" s="34" t="s">
+        <v>246</v>
+      </c>
+      <c r="D28" s="55" t="s">
+        <v>256</v>
+      </c>
+      <c r="E28" s="55"/>
+      <c r="F28" s="56" t="s">
+        <v>257</v>
+      </c>
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="52" t="s">
-        <v>256</v>
-      </c>
-      <c r="C29" s="53" t="s">
-        <v>244</v>
-      </c>
-      <c r="D29" s="54" t="s">
-        <v>257</v>
-      </c>
-      <c r="E29" s="54"/>
-      <c r="F29" s="55" t="s">
+      <c r="B29" s="54" t="s">
         <v>258</v>
       </c>
-      <c r="G29" s="55"/>
-      <c r="H29" s="55"/>
+      <c r="C29" s="34" t="s">
+        <v>246</v>
+      </c>
+      <c r="D29" s="55" t="s">
+        <v>259</v>
+      </c>
+      <c r="E29" s="55"/>
+      <c r="F29" s="56" t="s">
+        <v>260</v>
+      </c>
+      <c r="G29" s="56"/>
+      <c r="H29" s="56"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="52" t="s">
-        <v>259</v>
-      </c>
-      <c r="C30" s="53" t="s">
-        <v>244</v>
-      </c>
-      <c r="D30" s="54" t="s">
-        <v>260</v>
-      </c>
-      <c r="E30" s="54"/>
-      <c r="F30" s="55" t="s">
+      <c r="B30" s="54" t="s">
         <v>261</v>
       </c>
-      <c r="G30" s="55"/>
-      <c r="H30" s="55"/>
+      <c r="C30" s="34" t="s">
+        <v>246</v>
+      </c>
+      <c r="D30" s="55" t="s">
+        <v>262</v>
+      </c>
+      <c r="E30" s="55"/>
+      <c r="F30" s="56" t="s">
+        <v>263</v>
+      </c>
+      <c r="G30" s="56"/>
+      <c r="H30" s="56"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="52" t="s">
-        <v>262</v>
-      </c>
-      <c r="C31" s="53" t="s">
-        <v>244</v>
-      </c>
-      <c r="D31" s="54" t="s">
-        <v>263</v>
-      </c>
-      <c r="E31" s="54"/>
-      <c r="F31" s="55" t="s">
+      <c r="B31" s="54" t="s">
         <v>264</v>
       </c>
-      <c r="G31" s="55"/>
-      <c r="H31" s="55"/>
+      <c r="C31" s="34" t="s">
+        <v>246</v>
+      </c>
+      <c r="D31" s="55" t="s">
+        <v>265</v>
+      </c>
+      <c r="E31" s="55"/>
+      <c r="F31" s="56" t="s">
+        <v>266</v>
+      </c>
+      <c r="G31" s="56"/>
+      <c r="H31" s="56"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="52" t="s">
-        <v>265</v>
+      <c r="B33" s="54" t="s">
+        <v>267</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D33" s="26"/>
       <c r="E33" s="26"/>
       <c r="F33" s="26"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="56" t="s">
+      <c r="B35" s="57" t="s">
         <v>129</v>
       </c>
-      <c r="C35" s="56"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
+      <c r="C35" s="57"/>
+      <c r="D35" s="57"/>
+      <c r="E35" s="57"/>
+      <c r="F35" s="57"/>
+      <c r="G35" s="57"/>
+      <c r="H35" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="23">

--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
@@ -6121,10 +6121,10 @@
       <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1.0</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1.0</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="269">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1037,7 +1037,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1114,6 +1114,9 @@
     <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -5829,13 +5832,26 @@
       <c r="B21" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="C21" s="53" t="s">
-        <v>214</v>
-      </c>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53"/>
+      <c r="C21" s="34" t="str">
+        <f>IF('5-Year Model'!B49&gt;=0,"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="D21" s="53" t="str">
+        <f>IF('5-Year Model'!C49&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="53" t="str">
+        <f>IF('5-Year Model'!D49&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="53" t="str">
+        <f>IF('5-Year Model'!E49&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="53" t="str">
+        <f>IF('5-Year Model'!F49&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
       <c r="H21" s="50" t="s">
         <v>214</v>
       </c>
@@ -5844,13 +5860,13 @@
       <c r="B22" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="C22" s="53" t="s">
+      <c r="C22" s="54" t="s">
         <v>240</v>
       </c>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="53"/>
-      <c r="G22" s="53"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
       <c r="H22" s="50" t="s">
         <v>240</v>
       </c>
@@ -5873,126 +5889,126 @@
       <c r="H24" s="12"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="54" t="s">
+      <c r="B25" s="55" t="s">
         <v>245</v>
       </c>
       <c r="C25" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="D25" s="55" t="s">
+      <c r="D25" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="E25" s="55"/>
-      <c r="F25" s="56" t="s">
+      <c r="E25" s="56"/>
+      <c r="F25" s="57" t="s">
         <v>248</v>
       </c>
-      <c r="G25" s="56"/>
-      <c r="H25" s="56"/>
+      <c r="G25" s="57"/>
+      <c r="H25" s="57"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="54" t="s">
+      <c r="B26" s="55" t="s">
         <v>249</v>
       </c>
       <c r="C26" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="D26" s="55" t="s">
+      <c r="D26" s="56" t="s">
         <v>250</v>
       </c>
-      <c r="E26" s="55"/>
-      <c r="F26" s="56" t="s">
+      <c r="E26" s="56"/>
+      <c r="F26" s="57" t="s">
         <v>251</v>
       </c>
-      <c r="G26" s="56"/>
-      <c r="H26" s="56"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="54" t="s">
+      <c r="B27" s="55" t="s">
         <v>252</v>
       </c>
       <c r="C27" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="D27" s="55" t="s">
+      <c r="D27" s="56" t="s">
         <v>253</v>
       </c>
-      <c r="E27" s="55"/>
-      <c r="F27" s="56" t="s">
+      <c r="E27" s="56"/>
+      <c r="F27" s="57" t="s">
         <v>254</v>
       </c>
-      <c r="G27" s="56"/>
-      <c r="H27" s="56"/>
+      <c r="G27" s="57"/>
+      <c r="H27" s="57"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="54" t="s">
+      <c r="B28" s="55" t="s">
         <v>255</v>
       </c>
       <c r="C28" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="D28" s="55" t="s">
+      <c r="D28" s="56" t="s">
         <v>256</v>
       </c>
-      <c r="E28" s="55"/>
-      <c r="F28" s="56" t="s">
+      <c r="E28" s="56"/>
+      <c r="F28" s="57" t="s">
         <v>257</v>
       </c>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="57"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="54" t="s">
+      <c r="B29" s="55" t="s">
         <v>258</v>
       </c>
       <c r="C29" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="D29" s="55" t="s">
+      <c r="D29" s="56" t="s">
         <v>259</v>
       </c>
-      <c r="E29" s="55"/>
-      <c r="F29" s="56" t="s">
+      <c r="E29" s="56"/>
+      <c r="F29" s="57" t="s">
         <v>260</v>
       </c>
-      <c r="G29" s="56"/>
-      <c r="H29" s="56"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="54" t="s">
+      <c r="B30" s="55" t="s">
         <v>261</v>
       </c>
       <c r="C30" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="D30" s="55" t="s">
+      <c r="D30" s="56" t="s">
         <v>262</v>
       </c>
-      <c r="E30" s="55"/>
-      <c r="F30" s="56" t="s">
+      <c r="E30" s="56"/>
+      <c r="F30" s="57" t="s">
         <v>263</v>
       </c>
-      <c r="G30" s="56"/>
-      <c r="H30" s="56"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="54" t="s">
+      <c r="B31" s="55" t="s">
         <v>264</v>
       </c>
       <c r="C31" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="D31" s="55" t="s">
+      <c r="D31" s="56" t="s">
         <v>265</v>
       </c>
-      <c r="E31" s="55"/>
-      <c r="F31" s="56" t="s">
+      <c r="E31" s="56"/>
+      <c r="F31" s="57" t="s">
         <v>266</v>
       </c>
-      <c r="G31" s="56"/>
-      <c r="H31" s="56"/>
+      <c r="G31" s="57"/>
+      <c r="H31" s="57"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="54" t="s">
+      <c r="B33" s="55" t="s">
         <v>267</v>
       </c>
       <c r="C33" s="26" t="s">
@@ -6003,22 +6019,21 @@
       <c r="F33" s="26"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="57" t="s">
+      <c r="B35" s="58" t="s">
         <v>129</v>
       </c>
-      <c r="C35" s="57"/>
-      <c r="D35" s="57"/>
-      <c r="E35" s="57"/>
-      <c r="F35" s="57"/>
-      <c r="G35" s="57"/>
-      <c r="H35" s="57"/>
+      <c r="C35" s="58"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="22">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C21:G21"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
@@ -6099,10 +6114,10 @@
       <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.25</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.25</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:G18">

--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="269">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -746,10 +746,10 @@
     <t>Break-even Year</t>
   </si>
   <si>
-    <t>Cash Runway</t>
-  </si>
-  <si>
-    <t>60+ months</t>
+    <t>Cash Runway (Months)</t>
+  </si>
+  <si>
+    <t>≥ 24 months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -953,7 +953,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -983,6 +983,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E1"/>
       </patternFill>
     </fill>
   </fills>
@@ -1037,7 +1047,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1111,14 +1121,21 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="167" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -5797,10 +5814,18 @@
       <c r="C19" s="51">
         <v>3</v>
       </c>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="51"/>
+      <c r="D19" s="51">
+        <v>3</v>
+      </c>
+      <c r="E19" s="51">
+        <v>3</v>
+      </c>
+      <c r="F19" s="51">
+        <v>3</v>
+      </c>
+      <c r="G19" s="51">
+        <v>3</v>
+      </c>
       <c r="H19" s="50" t="s">
         <v>235</v>
       </c>
@@ -5837,19 +5862,19 @@
         <v>✓ Break-even</v>
       </c>
       <c r="D21" s="53" t="str">
-        <f>IF('5-Year Model'!C49&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Model'!C49&gt;=0,'5-Year Model'!B49&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="E21" s="53" t="str">
-        <f>IF('5-Year Model'!D49&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Model'!D49&gt;=0,'5-Year Model'!C49&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="F21" s="53" t="str">
-        <f>IF('5-Year Model'!E49&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Model'!E49&gt;=0,'5-Year Model'!D49&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="G21" s="53" t="str">
-        <f>IF('5-Year Model'!F49&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Model'!F49&gt;=0,'5-Year Model'!E49&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="H21" s="50" t="s">
@@ -5860,13 +5885,21 @@
       <c r="B22" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="C22" s="54" t="s">
-        <v>240</v>
-      </c>
-      <c r="D22" s="54"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="54"/>
+      <c r="C22" s="54">
+        <v>3</v>
+      </c>
+      <c r="D22" s="54">
+        <v>10</v>
+      </c>
+      <c r="E22" s="55">
+        <v>21</v>
+      </c>
+      <c r="F22" s="51">
+        <v>34</v>
+      </c>
+      <c r="G22" s="51">
+        <v>47</v>
+      </c>
       <c r="H22" s="50" t="s">
         <v>240</v>
       </c>
@@ -5889,126 +5922,126 @@
       <c r="H24" s="12"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="55" t="s">
+      <c r="B25" s="56" t="s">
         <v>245</v>
       </c>
       <c r="C25" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="D25" s="56" t="s">
+      <c r="D25" s="57" t="s">
         <v>247</v>
       </c>
-      <c r="E25" s="56"/>
-      <c r="F25" s="57" t="s">
+      <c r="E25" s="57"/>
+      <c r="F25" s="58" t="s">
         <v>248</v>
       </c>
-      <c r="G25" s="57"/>
-      <c r="H25" s="57"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="58"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="55" t="s">
+      <c r="B26" s="56" t="s">
         <v>249</v>
       </c>
       <c r="C26" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="D26" s="56" t="s">
+      <c r="D26" s="57" t="s">
         <v>250</v>
       </c>
-      <c r="E26" s="56"/>
-      <c r="F26" s="57" t="s">
+      <c r="E26" s="57"/>
+      <c r="F26" s="58" t="s">
         <v>251</v>
       </c>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="58"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="55" t="s">
+      <c r="B27" s="56" t="s">
         <v>252</v>
       </c>
       <c r="C27" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="D27" s="56" t="s">
+      <c r="D27" s="57" t="s">
         <v>253</v>
       </c>
-      <c r="E27" s="56"/>
-      <c r="F27" s="57" t="s">
+      <c r="E27" s="57"/>
+      <c r="F27" s="58" t="s">
         <v>254</v>
       </c>
-      <c r="G27" s="57"/>
-      <c r="H27" s="57"/>
+      <c r="G27" s="58"/>
+      <c r="H27" s="58"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="55" t="s">
+      <c r="B28" s="56" t="s">
         <v>255</v>
       </c>
       <c r="C28" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="D28" s="56" t="s">
+      <c r="D28" s="57" t="s">
         <v>256</v>
       </c>
-      <c r="E28" s="56"/>
-      <c r="F28" s="57" t="s">
+      <c r="E28" s="57"/>
+      <c r="F28" s="58" t="s">
         <v>257</v>
       </c>
-      <c r="G28" s="57"/>
-      <c r="H28" s="57"/>
+      <c r="G28" s="58"/>
+      <c r="H28" s="58"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="55" t="s">
+      <c r="B29" s="56" t="s">
         <v>258</v>
       </c>
       <c r="C29" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="D29" s="56" t="s">
+      <c r="D29" s="57" t="s">
         <v>259</v>
       </c>
-      <c r="E29" s="56"/>
-      <c r="F29" s="57" t="s">
+      <c r="E29" s="57"/>
+      <c r="F29" s="58" t="s">
         <v>260</v>
       </c>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
+      <c r="G29" s="58"/>
+      <c r="H29" s="58"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="55" t="s">
+      <c r="B30" s="56" t="s">
         <v>261</v>
       </c>
       <c r="C30" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="D30" s="56" t="s">
+      <c r="D30" s="57" t="s">
         <v>262</v>
       </c>
-      <c r="E30" s="56"/>
-      <c r="F30" s="57" t="s">
+      <c r="E30" s="57"/>
+      <c r="F30" s="58" t="s">
         <v>263</v>
       </c>
-      <c r="G30" s="57"/>
-      <c r="H30" s="57"/>
+      <c r="G30" s="58"/>
+      <c r="H30" s="58"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="55" t="s">
+      <c r="B31" s="56" t="s">
         <v>264</v>
       </c>
       <c r="C31" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="D31" s="56" t="s">
+      <c r="D31" s="57" t="s">
         <v>265</v>
       </c>
-      <c r="E31" s="56"/>
-      <c r="F31" s="57" t="s">
+      <c r="E31" s="57"/>
+      <c r="F31" s="58" t="s">
         <v>266</v>
       </c>
-      <c r="G31" s="57"/>
-      <c r="H31" s="57"/>
+      <c r="G31" s="58"/>
+      <c r="H31" s="58"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="55" t="s">
+      <c r="B33" s="56" t="s">
         <v>267</v>
       </c>
       <c r="C33" s="26" t="s">
@@ -6019,22 +6052,20 @@
       <c r="F33" s="26"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="58" t="s">
+      <c r="B35" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
@@ -797,7 +797,7 @@
     <t>Facility Burden</t>
   </si>
   <si>
-    <t>Facility costs at 4% of revenue are well-managed and leave budget for programs.</t>
+    <t>Facility costs at 8% of revenue are well-managed and leave budget for programs.</t>
   </si>
   <si>
     <t>Watch for rent escalation clauses that could push this higher over time.</t>
@@ -987,12 +987,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4EC"/>
+        <fgColor rgb="FFFFF8E1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF8E1"/>
+        <fgColor rgb="FFFCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -1047,7 +1047,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1121,6 +1121,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="164" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1130,10 +1133,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -5765,20 +5768,20 @@
       <c r="B17" s="26" t="s">
         <v>230</v>
       </c>
-      <c r="C17" s="48">
-        <v>0.0657942238267148</v>
+      <c r="C17" s="51">
+        <v>0.1624548736462094</v>
       </c>
       <c r="D17" s="48">
-        <v>0.04869324776909486</v>
+        <v>0.10956757036500346</v>
       </c>
       <c r="E17" s="48">
-        <v>0.0424471997918128</v>
+        <v>0.09025962891725049</v>
       </c>
       <c r="F17" s="48">
-        <v>0.03908460457307385</v>
+        <v>0.07987105633946989</v>
       </c>
       <c r="G17" s="48">
-        <v>0.03918224414098794</v>
+        <v>0.08019652156585022</v>
       </c>
       <c r="H17" s="50" t="s">
         <v>231</v>
@@ -5811,19 +5814,19 @@
       <c r="B19" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="C19" s="51">
+      <c r="C19" s="52">
         <v>3</v>
       </c>
-      <c r="D19" s="51">
+      <c r="D19" s="52">
         <v>3</v>
       </c>
-      <c r="E19" s="51">
+      <c r="E19" s="52">
         <v>3</v>
       </c>
-      <c r="F19" s="51">
+      <c r="F19" s="52">
         <v>3</v>
       </c>
-      <c r="G19" s="51">
+      <c r="G19" s="52">
         <v>3</v>
       </c>
       <c r="H19" s="50" t="s">
@@ -5834,19 +5837,19 @@
       <c r="B20" s="26" t="s">
         <v>236</v>
       </c>
-      <c r="C20" s="52">
+      <c r="C20" s="53">
         <v>7.768293185121821</v>
       </c>
-      <c r="D20" s="52">
+      <c r="D20" s="53">
         <v>19.57810606562835</v>
       </c>
-      <c r="E20" s="52">
+      <c r="E20" s="53">
         <v>30.35571698045677</v>
       </c>
-      <c r="F20" s="52">
+      <c r="F20" s="53">
         <v>38.99024195731399</v>
       </c>
-      <c r="G20" s="52">
+      <c r="G20" s="53">
         <v>39.82940742297506</v>
       </c>
       <c r="H20" s="50" t="s">
@@ -5861,19 +5864,19 @@
         <f>IF('5-Year Model'!B49&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D21" s="53" t="str">
+      <c r="D21" s="54" t="str">
         <f>IF(AND('5-Year Model'!C49&gt;=0,'5-Year Model'!B49&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="53" t="str">
+      <c r="E21" s="54" t="str">
         <f>IF(AND('5-Year Model'!D49&gt;=0,'5-Year Model'!C49&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="53" t="str">
+      <c r="F21" s="54" t="str">
         <f>IF(AND('5-Year Model'!E49&gt;=0,'5-Year Model'!D49&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="53" t="str">
+      <c r="G21" s="54" t="str">
         <f>IF(AND('5-Year Model'!F49&gt;=0,'5-Year Model'!E49&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
@@ -5885,19 +5888,19 @@
       <c r="B22" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="C22" s="54">
+      <c r="C22" s="55">
         <v>3</v>
       </c>
-      <c r="D22" s="54">
+      <c r="D22" s="55">
         <v>10</v>
       </c>
-      <c r="E22" s="55">
+      <c r="E22" s="56">
         <v>21</v>
       </c>
-      <c r="F22" s="51">
+      <c r="F22" s="52">
         <v>34</v>
       </c>
-      <c r="G22" s="51">
+      <c r="G22" s="52">
         <v>47</v>
       </c>
       <c r="H22" s="50" t="s">
@@ -5922,126 +5925,126 @@
       <c r="H24" s="12"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="56" t="s">
+      <c r="B25" s="57" t="s">
         <v>245</v>
       </c>
       <c r="C25" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="D25" s="57" t="s">
+      <c r="D25" s="58" t="s">
         <v>247</v>
       </c>
-      <c r="E25" s="57"/>
-      <c r="F25" s="58" t="s">
+      <c r="E25" s="58"/>
+      <c r="F25" s="59" t="s">
         <v>248</v>
       </c>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="59"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="56" t="s">
+      <c r="B26" s="57" t="s">
         <v>249</v>
       </c>
       <c r="C26" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="D26" s="57" t="s">
+      <c r="D26" s="58" t="s">
         <v>250</v>
       </c>
-      <c r="E26" s="57"/>
-      <c r="F26" s="58" t="s">
+      <c r="E26" s="58"/>
+      <c r="F26" s="59" t="s">
         <v>251</v>
       </c>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
+      <c r="G26" s="59"/>
+      <c r="H26" s="59"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="56" t="s">
+      <c r="B27" s="57" t="s">
         <v>252</v>
       </c>
       <c r="C27" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="D27" s="57" t="s">
+      <c r="D27" s="58" t="s">
         <v>253</v>
       </c>
-      <c r="E27" s="57"/>
-      <c r="F27" s="58" t="s">
+      <c r="E27" s="58"/>
+      <c r="F27" s="59" t="s">
         <v>254</v>
       </c>
-      <c r="G27" s="58"/>
-      <c r="H27" s="58"/>
+      <c r="G27" s="59"/>
+      <c r="H27" s="59"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="56" t="s">
+      <c r="B28" s="57" t="s">
         <v>255</v>
       </c>
       <c r="C28" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="D28" s="57" t="s">
+      <c r="D28" s="58" t="s">
         <v>256</v>
       </c>
-      <c r="E28" s="57"/>
-      <c r="F28" s="58" t="s">
+      <c r="E28" s="58"/>
+      <c r="F28" s="59" t="s">
         <v>257</v>
       </c>
-      <c r="G28" s="58"/>
-      <c r="H28" s="58"/>
+      <c r="G28" s="59"/>
+      <c r="H28" s="59"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="56" t="s">
+      <c r="B29" s="57" t="s">
         <v>258</v>
       </c>
       <c r="C29" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="D29" s="57" t="s">
+      <c r="D29" s="58" t="s">
         <v>259</v>
       </c>
-      <c r="E29" s="57"/>
-      <c r="F29" s="58" t="s">
+      <c r="E29" s="58"/>
+      <c r="F29" s="59" t="s">
         <v>260</v>
       </c>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="59"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="56" t="s">
+      <c r="B30" s="57" t="s">
         <v>261</v>
       </c>
       <c r="C30" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="D30" s="57" t="s">
+      <c r="D30" s="58" t="s">
         <v>262</v>
       </c>
-      <c r="E30" s="57"/>
-      <c r="F30" s="58" t="s">
+      <c r="E30" s="58"/>
+      <c r="F30" s="59" t="s">
         <v>263</v>
       </c>
-      <c r="G30" s="58"/>
-      <c r="H30" s="58"/>
+      <c r="G30" s="59"/>
+      <c r="H30" s="59"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="56" t="s">
+      <c r="B31" s="57" t="s">
         <v>264</v>
       </c>
       <c r="C31" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="D31" s="57" t="s">
+      <c r="D31" s="58" t="s">
         <v>265</v>
       </c>
-      <c r="E31" s="57"/>
-      <c r="F31" s="58" t="s">
+      <c r="E31" s="58"/>
+      <c r="F31" s="59" t="s">
         <v>266</v>
       </c>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
+      <c r="G31" s="59"/>
+      <c r="H31" s="59"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="56" t="s">
+      <c r="B33" s="57" t="s">
         <v>267</v>
       </c>
       <c r="C33" s="26" t="s">
@@ -6052,15 +6055,15 @@
       <c r="F33" s="26"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="59" t="s">
+      <c r="B35" s="60" t="s">
         <v>129</v>
       </c>
-      <c r="C35" s="59"/>
-      <c r="D35" s="59"/>
-      <c r="E35" s="59"/>
-      <c r="F35" s="59"/>
-      <c r="G35" s="59"/>
-      <c r="H35" s="59"/>
+      <c r="C35" s="60"/>
+      <c r="D35" s="60"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="60"/>
+      <c r="G35" s="60"/>
+      <c r="H35" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
@@ -35,7 +35,7 @@
     <t>Bright Horizons Microschool</t>
   </si>
   <si>
-    <t>Generated March 26, 2026 · llc_single</t>
+    <t>Generated March 27, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -656,7 +656,7 @@
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 26, 2026</t>
+    <t>Generated March 27, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>

--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N46</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="270">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -750,6 +750,9 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -5492,7 +5495,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -5907,170 +5910,191 @@
         <v>240</v>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="12" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="C23" s="52">
+        <v>99</v>
+      </c>
+      <c r="D23" s="52">
+        <v>308</v>
+      </c>
+      <c r="E23" s="52">
+        <v>637</v>
+      </c>
+      <c r="F23" s="52">
+        <v>1038</v>
+      </c>
+      <c r="G23" s="52">
+        <v>1432</v>
+      </c>
+      <c r="H23" s="50" t="s">
         <v>241</v>
       </c>
-      <c r="C24" s="12" t="s">
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="C25" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12" t="s">
+      <c r="D25" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="57" t="s">
+      <c r="E25" s="12"/>
+      <c r="F25" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="C25" s="34" t="s">
-        <v>246</v>
-      </c>
-      <c r="D25" s="58" t="s">
-        <v>247</v>
-      </c>
-      <c r="E25" s="58"/>
-      <c r="F25" s="59" t="s">
-        <v>248</v>
-      </c>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="57" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D26" s="58" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E26" s="58"/>
       <c r="F26" s="59" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G26" s="59"/>
       <c r="H26" s="59"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="57" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C27" s="34" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D27" s="58" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E27" s="58"/>
       <c r="F27" s="59" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G27" s="59"/>
       <c r="H27" s="59"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="57" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D28" s="58" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E28" s="58"/>
       <c r="F28" s="59" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G28" s="59"/>
       <c r="H28" s="59"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="57" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D29" s="58" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E29" s="58"/>
       <c r="F29" s="59" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G29" s="59"/>
       <c r="H29" s="59"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="57" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D30" s="58" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E30" s="58"/>
       <c r="F30" s="59" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G30" s="59"/>
       <c r="H30" s="59"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="57" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C31" s="34" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D31" s="58" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E31" s="58"/>
       <c r="F31" s="59" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G31" s="59"/>
       <c r="H31" s="59"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="57" t="s">
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="57" t="s">
+        <v>265</v>
+      </c>
+      <c r="C32" s="34" t="s">
+        <v>247</v>
+      </c>
+      <c r="D32" s="58" t="s">
+        <v>266</v>
+      </c>
+      <c r="E32" s="58"/>
+      <c r="F32" s="59" t="s">
         <v>267</v>
       </c>
-      <c r="C33" s="26" t="s">
+      <c r="G32" s="59"/>
+      <c r="H32" s="59"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="57" t="s">
         <v>268</v>
       </c>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="60" t="s">
+      <c r="C34" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="60" t="s">
         <v>129</v>
       </c>
-      <c r="C35" s="60"/>
-      <c r="D35" s="60"/>
-      <c r="E35" s="60"/>
-      <c r="F35" s="60"/>
-      <c r="G35" s="60"/>
-      <c r="H35" s="60"/>
+      <c r="C36" s="60"/>
+      <c r="D36" s="60"/>
+      <c r="E36" s="60"/>
+      <c r="F36" s="60"/>
+      <c r="G36" s="60"/>
+      <c r="H36" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
@@ -6085,8 +6109,10 @@
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="B36:H36"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N46</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="275">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -711,6 +711,21 @@
   </si>
   <si>
     <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t>Cost per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
   </si>
   <si>
     <t>Payroll %</t>
@@ -1050,7 +1065,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1124,6 +1139,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="166" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -5495,7 +5519,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H36"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -5744,365 +5768,440 @@
         <v>227</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="26" t="s">
         <v>228</v>
       </c>
-      <c r="C16" s="48">
-        <v>0.5367065282791817</v>
-      </c>
-      <c r="D16" s="48">
-        <v>0.4347293119127009</v>
-      </c>
-      <c r="E16" s="48">
-        <v>0.3584103359800075</v>
-      </c>
-      <c r="F16" s="48">
-        <v>0.31741327092386307</v>
-      </c>
-      <c r="G16" s="48">
-        <v>0.31896162834300396</v>
-      </c>
-      <c r="H16" s="50" t="s">
+      <c r="C16" s="51">
+        <v>14541.164601438404</v>
+      </c>
+      <c r="D16" s="51">
+        <v>11602.63547503301</v>
+      </c>
+      <c r="E16" s="51">
+        <v>9915.73374775428</v>
+      </c>
+      <c r="F16" s="51">
+        <v>9077.061473703767</v>
+      </c>
+      <c r="G16" s="51">
+        <v>9334.775582029166</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="13" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="26" t="s">
+      <c r="C17" s="46">
+        <v>500</v>
+      </c>
+      <c r="D17" s="46">
+        <v>512.5</v>
+      </c>
+      <c r="E17" s="46">
+        <v>525.3125</v>
+      </c>
+      <c r="F17" s="46">
+        <v>538.4453124999998</v>
+      </c>
+      <c r="G17" s="46">
+        <v>551.9064453124997</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="C17" s="51">
-        <v>0.1624548736462094</v>
-      </c>
-      <c r="D17" s="48">
-        <v>0.10956757036500346</v>
-      </c>
-      <c r="E17" s="48">
-        <v>0.09025962891725049</v>
-      </c>
-      <c r="F17" s="48">
-        <v>0.07987105633946989</v>
-      </c>
-      <c r="G17" s="48">
-        <v>0.08019652156585022</v>
-      </c>
-      <c r="H17" s="50" t="s">
+      <c r="C18" s="52">
+        <v>3000</v>
+      </c>
+      <c r="D18" s="52">
+        <v>2058.3333333333335</v>
+      </c>
+      <c r="E18" s="49">
+        <v>1733.215909090909</v>
+      </c>
+      <c r="F18" s="49">
+        <v>1569.72615</v>
+      </c>
+      <c r="G18" s="49">
+        <v>1615.5256657500001</v>
+      </c>
+      <c r="H18" s="50" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="26" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="26" t="s">
         <v>232</v>
       </c>
-      <c r="C18" s="48">
-        <v>0.2439793922984356</v>
-      </c>
-      <c r="D18" s="48">
-        <v>0.40295986219031626</v>
-      </c>
-      <c r="E18" s="48">
-        <v>0.5000989980472832</v>
-      </c>
-      <c r="F18" s="48">
-        <v>0.5523047138325573</v>
-      </c>
-      <c r="G18" s="48">
-        <v>0.5504308911870363</v>
-      </c>
-      <c r="H18" s="50" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="C19" s="52">
-        <v>3</v>
-      </c>
-      <c r="D19" s="52">
-        <v>3</v>
-      </c>
-      <c r="E19" s="52">
-        <v>3</v>
-      </c>
-      <c r="F19" s="52">
-        <v>3</v>
-      </c>
-      <c r="G19" s="52">
-        <v>3</v>
-      </c>
-      <c r="H19" s="50" t="s">
-        <v>235</v>
+      <c r="C19" s="53">
+        <v>3925.5020652282624</v>
+      </c>
+      <c r="D19" s="53">
+        <v>7183.336747189209</v>
+      </c>
+      <c r="E19" s="53">
+        <v>9286.825911336624</v>
+      </c>
+      <c r="F19" s="53">
+        <v>10576.192432546224</v>
+      </c>
+      <c r="G19" s="53">
+        <v>10809.809671877074</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="26" t="s">
-        <v>236</v>
-      </c>
-      <c r="C20" s="53">
-        <v>7.768293185121821</v>
-      </c>
-      <c r="D20" s="53">
-        <v>19.57810606562835</v>
-      </c>
-      <c r="E20" s="53">
-        <v>30.35571698045677</v>
-      </c>
-      <c r="F20" s="53">
-        <v>38.99024195731399</v>
-      </c>
-      <c r="G20" s="53">
-        <v>39.82940742297506</v>
+        <v>233</v>
+      </c>
+      <c r="C20" s="48">
+        <v>0.5367065282791817</v>
+      </c>
+      <c r="D20" s="48">
+        <v>0.4347293119127009</v>
+      </c>
+      <c r="E20" s="48">
+        <v>0.3584103359800075</v>
+      </c>
+      <c r="F20" s="48">
+        <v>0.31741327092386307</v>
+      </c>
+      <c r="G20" s="48">
+        <v>0.31896162834300396</v>
       </c>
       <c r="H20" s="50" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="C21" s="54">
+        <v>0.1624548736462094</v>
+      </c>
+      <c r="D21" s="48">
+        <v>0.10956757036500346</v>
+      </c>
+      <c r="E21" s="48">
+        <v>0.09025962891725049</v>
+      </c>
+      <c r="F21" s="48">
+        <v>0.07987105633946989</v>
+      </c>
+      <c r="G21" s="48">
+        <v>0.08019652156585022</v>
+      </c>
+      <c r="H21" s="50" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="C22" s="48">
+        <v>0.2439793922984356</v>
+      </c>
+      <c r="D22" s="48">
+        <v>0.40295986219031626</v>
+      </c>
+      <c r="E22" s="48">
+        <v>0.5000989980472832</v>
+      </c>
+      <c r="F22" s="48">
+        <v>0.5523047138325573</v>
+      </c>
+      <c r="G22" s="48">
+        <v>0.5504308911870363</v>
+      </c>
+      <c r="H22" s="50" t="s">
         <v>238</v>
       </c>
-      <c r="C21" s="34" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="C23" s="55">
+        <v>3</v>
+      </c>
+      <c r="D23" s="55">
+        <v>3</v>
+      </c>
+      <c r="E23" s="55">
+        <v>3</v>
+      </c>
+      <c r="F23" s="55">
+        <v>3</v>
+      </c>
+      <c r="G23" s="55">
+        <v>3</v>
+      </c>
+      <c r="H23" s="50" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="C24" s="56">
+        <v>7.768293185121821</v>
+      </c>
+      <c r="D24" s="56">
+        <v>19.57810606562835</v>
+      </c>
+      <c r="E24" s="56">
+        <v>30.35571698045677</v>
+      </c>
+      <c r="F24" s="56">
+        <v>38.99024195731399</v>
+      </c>
+      <c r="G24" s="56">
+        <v>39.82940742297506</v>
+      </c>
+      <c r="H24" s="50" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="C25" s="34" t="str">
         <f>IF('5-Year Model'!B49&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D21" s="54" t="str">
+      <c r="D25" s="57" t="str">
         <f>IF(AND('5-Year Model'!C49&gt;=0,'5-Year Model'!B49&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="54" t="str">
+      <c r="E25" s="57" t="str">
         <f>IF(AND('5-Year Model'!D49&gt;=0,'5-Year Model'!C49&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="54" t="str">
+      <c r="F25" s="57" t="str">
         <f>IF(AND('5-Year Model'!E49&gt;=0,'5-Year Model'!D49&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="54" t="str">
+      <c r="G25" s="57" t="str">
         <f>IF(AND('5-Year Model'!F49&gt;=0,'5-Year Model'!E49&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="50" t="s">
+      <c r="H25" s="50" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="26" t="s">
-        <v>239</v>
-      </c>
-      <c r="C22" s="55">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="C26" s="58">
         <v>3</v>
       </c>
-      <c r="D22" s="55">
+      <c r="D26" s="58">
         <v>10</v>
       </c>
-      <c r="E22" s="56">
+      <c r="E26" s="59">
         <v>21</v>
       </c>
-      <c r="F22" s="52">
+      <c r="F26" s="55">
         <v>34</v>
       </c>
-      <c r="G22" s="52">
+      <c r="G26" s="55">
         <v>47</v>
       </c>
-      <c r="H22" s="50" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="26" t="s">
+      <c r="H26" s="50" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="C23" s="52">
+      <c r="C27" s="55">
         <v>99</v>
       </c>
-      <c r="D23" s="52">
+      <c r="D27" s="55">
         <v>308</v>
       </c>
-      <c r="E23" s="52">
+      <c r="E27" s="55">
         <v>637</v>
       </c>
-      <c r="F23" s="52">
+      <c r="F27" s="55">
         <v>1038</v>
       </c>
-      <c r="G23" s="52">
+      <c r="G27" s="55">
         <v>1432</v>
       </c>
-      <c r="H23" s="50" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="57" t="s">
+      <c r="H27" s="50" t="s">
         <v>246</v>
       </c>
-      <c r="C26" s="34" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="D26" s="58" t="s">
+      <c r="C29" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="E26" s="58"/>
-      <c r="F26" s="59" t="s">
+      <c r="D29" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="G26" s="59"/>
-      <c r="H26" s="59"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="57" t="s">
+      <c r="E29" s="12"/>
+      <c r="F29" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="C27" s="34" t="s">
-        <v>247</v>
-      </c>
-      <c r="D27" s="58" t="s">
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="60" t="s">
         <v>251</v>
       </c>
-      <c r="E27" s="58"/>
-      <c r="F27" s="59" t="s">
+      <c r="C30" s="34" t="s">
         <v>252</v>
       </c>
-      <c r="G27" s="59"/>
-      <c r="H27" s="59"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="57" t="s">
+      <c r="D30" s="61" t="s">
         <v>253</v>
       </c>
-      <c r="C28" s="34" t="s">
-        <v>247</v>
-      </c>
-      <c r="D28" s="58" t="s">
+      <c r="E30" s="61"/>
+      <c r="F30" s="62" t="s">
         <v>254</v>
       </c>
-      <c r="E28" s="58"/>
-      <c r="F28" s="59" t="s">
+      <c r="G30" s="62"/>
+      <c r="H30" s="62"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="60" t="s">
         <v>255</v>
       </c>
-      <c r="G28" s="59"/>
-      <c r="H28" s="59"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="57" t="s">
+      <c r="C31" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="D31" s="61" t="s">
         <v>256</v>
       </c>
-      <c r="C29" s="34" t="s">
-        <v>247</v>
-      </c>
-      <c r="D29" s="58" t="s">
+      <c r="E31" s="61"/>
+      <c r="F31" s="62" t="s">
         <v>257</v>
       </c>
-      <c r="E29" s="58"/>
-      <c r="F29" s="59" t="s">
+      <c r="G31" s="62"/>
+      <c r="H31" s="62"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="60" t="s">
         <v>258</v>
       </c>
-      <c r="G29" s="59"/>
-      <c r="H29" s="59"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="57" t="s">
+      <c r="C32" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="D32" s="61" t="s">
         <v>259</v>
       </c>
-      <c r="C30" s="34" t="s">
-        <v>247</v>
-      </c>
-      <c r="D30" s="58" t="s">
+      <c r="E32" s="61"/>
+      <c r="F32" s="62" t="s">
         <v>260</v>
       </c>
-      <c r="E30" s="58"/>
-      <c r="F30" s="59" t="s">
+      <c r="G32" s="62"/>
+      <c r="H32" s="62"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="60" t="s">
         <v>261</v>
       </c>
-      <c r="G30" s="59"/>
-      <c r="H30" s="59"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="57" t="s">
+      <c r="C33" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="D33" s="61" t="s">
         <v>262</v>
       </c>
-      <c r="C31" s="34" t="s">
-        <v>247</v>
-      </c>
-      <c r="D31" s="58" t="s">
+      <c r="E33" s="61"/>
+      <c r="F33" s="62" t="s">
         <v>263</v>
       </c>
-      <c r="E31" s="58"/>
-      <c r="F31" s="59" t="s">
+      <c r="G33" s="62"/>
+      <c r="H33" s="62"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="60" t="s">
         <v>264</v>
       </c>
-      <c r="G31" s="59"/>
-      <c r="H31" s="59"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="57" t="s">
+      <c r="C34" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="D34" s="61" t="s">
         <v>265</v>
       </c>
-      <c r="C32" s="34" t="s">
-        <v>247</v>
-      </c>
-      <c r="D32" s="58" t="s">
+      <c r="E34" s="61"/>
+      <c r="F34" s="62" t="s">
         <v>266</v>
       </c>
-      <c r="E32" s="58"/>
-      <c r="F32" s="59" t="s">
+      <c r="G34" s="62"/>
+      <c r="H34" s="62"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="60" t="s">
         <v>267</v>
       </c>
-      <c r="G32" s="59"/>
-      <c r="H32" s="59"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="57" t="s">
+      <c r="C35" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="D35" s="61" t="s">
         <v>268</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="E35" s="61"/>
+      <c r="F35" s="62" t="s">
         <v>269</v>
       </c>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G35" s="62"/>
+      <c r="H35" s="62"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="60" t="s">
+        <v>270</v>
+      </c>
+      <c r="C36" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="D36" s="61" t="s">
+        <v>271</v>
+      </c>
+      <c r="E36" s="61"/>
+      <c r="F36" s="62" t="s">
+        <v>272</v>
+      </c>
+      <c r="G36" s="62"/>
+      <c r="H36" s="62"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="60" t="s">
+        <v>273</v>
+      </c>
+      <c r="C38" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="63" t="s">
         <v>129</v>
       </c>
-      <c r="C36" s="60"/>
-      <c r="D36" s="60"/>
-      <c r="E36" s="60"/>
-      <c r="F36" s="60"/>
-      <c r="G36" s="60"/>
-      <c r="H36" s="60"/>
+      <c r="C40" s="63"/>
+      <c r="D40" s="63"/>
+      <c r="E40" s="63"/>
+      <c r="F40" s="63"/>
+      <c r="G40" s="63"/>
+      <c r="H40" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
@@ -6111,8 +6210,16 @@
     <mergeCell ref="F31:H31"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="F32:H32"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -6158,48 +6265,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N46</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="269">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -713,21 +713,6 @@
     <t>≥ $10,000</t>
   </si>
   <si>
-    <t>Cost per Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Instructional / Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Facility / Student</t>
-  </si>
-  <si>
-    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
-  </si>
-  <si>
-    <t>Surplus per Student</t>
-  </si>
-  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -765,9 +750,6 @@
   </si>
   <si>
     <t>≥ 24 months</t>
-  </si>
-  <si>
-    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1065,7 +1047,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1139,15 +1121,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="166" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -5519,7 +5492,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -5768,458 +5741,352 @@
         <v>227</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="26" t="s">
         <v>228</v>
       </c>
-      <c r="C16" s="51">
-        <v>14541.164601438404</v>
-      </c>
-      <c r="D16" s="51">
-        <v>11602.63547503301</v>
-      </c>
-      <c r="E16" s="51">
-        <v>9915.73374775428</v>
-      </c>
-      <c r="F16" s="51">
-        <v>9077.061473703767</v>
-      </c>
-      <c r="G16" s="51">
-        <v>9334.775582029166</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="13" t="s">
+      <c r="C16" s="48">
+        <v>0.5367065282791817</v>
+      </c>
+      <c r="D16" s="48">
+        <v>0.4347293119127009</v>
+      </c>
+      <c r="E16" s="48">
+        <v>0.3584103359800075</v>
+      </c>
+      <c r="F16" s="48">
+        <v>0.31741327092386307</v>
+      </c>
+      <c r="G16" s="48">
+        <v>0.31896162834300396</v>
+      </c>
+      <c r="H16" s="50" t="s">
         <v>229</v>
       </c>
-      <c r="C17" s="46">
-        <v>500</v>
-      </c>
-      <c r="D17" s="46">
-        <v>512.5</v>
-      </c>
-      <c r="E17" s="46">
-        <v>525.3125</v>
-      </c>
-      <c r="F17" s="46">
-        <v>538.4453124999998</v>
-      </c>
-      <c r="G17" s="46">
-        <v>551.9064453124997</v>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="C17" s="51">
+        <v>0.1624548736462094</v>
+      </c>
+      <c r="D17" s="48">
+        <v>0.10956757036500346</v>
+      </c>
+      <c r="E17" s="48">
+        <v>0.09025962891725049</v>
+      </c>
+      <c r="F17" s="48">
+        <v>0.07987105633946989</v>
+      </c>
+      <c r="G17" s="48">
+        <v>0.08019652156585022</v>
+      </c>
+      <c r="H17" s="50" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="C18" s="52">
-        <v>3000</v>
-      </c>
-      <c r="D18" s="52">
-        <v>2058.3333333333335</v>
-      </c>
-      <c r="E18" s="49">
-        <v>1733.215909090909</v>
-      </c>
-      <c r="F18" s="49">
-        <v>1569.72615</v>
-      </c>
-      <c r="G18" s="49">
-        <v>1615.5256657500001</v>
+      <c r="B18" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="C18" s="48">
+        <v>0.2439793922984356</v>
+      </c>
+      <c r="D18" s="48">
+        <v>0.40295986219031626</v>
+      </c>
+      <c r="E18" s="48">
+        <v>0.5000989980472832</v>
+      </c>
+      <c r="F18" s="48">
+        <v>0.5523047138325573</v>
+      </c>
+      <c r="G18" s="48">
+        <v>0.5504308911870363</v>
       </c>
       <c r="H18" s="50" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="26" t="s">
-        <v>232</v>
-      </c>
-      <c r="C19" s="53">
-        <v>3925.5020652282624</v>
-      </c>
-      <c r="D19" s="53">
-        <v>7183.336747189209</v>
-      </c>
-      <c r="E19" s="53">
-        <v>9286.825911336624</v>
-      </c>
-      <c r="F19" s="53">
-        <v>10576.192432546224</v>
-      </c>
-      <c r="G19" s="53">
-        <v>10809.809671877074</v>
+        <v>234</v>
+      </c>
+      <c r="C19" s="52">
+        <v>3</v>
+      </c>
+      <c r="D19" s="52">
+        <v>3</v>
+      </c>
+      <c r="E19" s="52">
+        <v>3</v>
+      </c>
+      <c r="F19" s="52">
+        <v>3</v>
+      </c>
+      <c r="G19" s="52">
+        <v>3</v>
+      </c>
+      <c r="H19" s="50" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="26" t="s">
-        <v>233</v>
-      </c>
-      <c r="C20" s="48">
-        <v>0.5367065282791817</v>
-      </c>
-      <c r="D20" s="48">
-        <v>0.4347293119127009</v>
-      </c>
-      <c r="E20" s="48">
-        <v>0.3584103359800075</v>
-      </c>
-      <c r="F20" s="48">
-        <v>0.31741327092386307</v>
-      </c>
-      <c r="G20" s="48">
-        <v>0.31896162834300396</v>
+        <v>236</v>
+      </c>
+      <c r="C20" s="53">
+        <v>7.768293185121821</v>
+      </c>
+      <c r="D20" s="53">
+        <v>19.57810606562835</v>
+      </c>
+      <c r="E20" s="53">
+        <v>30.35571698045677</v>
+      </c>
+      <c r="F20" s="53">
+        <v>38.99024195731399</v>
+      </c>
+      <c r="G20" s="53">
+        <v>39.82940742297506</v>
       </c>
       <c r="H20" s="50" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="26" t="s">
-        <v>235</v>
-      </c>
-      <c r="C21" s="54">
-        <v>0.1624548736462094</v>
-      </c>
-      <c r="D21" s="48">
-        <v>0.10956757036500346</v>
-      </c>
-      <c r="E21" s="48">
-        <v>0.09025962891725049</v>
-      </c>
-      <c r="F21" s="48">
-        <v>0.07987105633946989</v>
-      </c>
-      <c r="G21" s="48">
-        <v>0.08019652156585022</v>
+        <v>238</v>
+      </c>
+      <c r="C21" s="34" t="str">
+        <f>IF('5-Year Model'!B49&gt;=0,"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="D21" s="54" t="str">
+        <f>IF(AND('5-Year Model'!C49&gt;=0,'5-Year Model'!B49&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="54" t="str">
+        <f>IF(AND('5-Year Model'!D49&gt;=0,'5-Year Model'!C49&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="54" t="str">
+        <f>IF(AND('5-Year Model'!E49&gt;=0,'5-Year Model'!D49&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="54" t="str">
+        <f>IF(AND('5-Year Model'!F49&gt;=0,'5-Year Model'!E49&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
       </c>
       <c r="H21" s="50" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="C22" s="48">
-        <v>0.2439793922984356</v>
-      </c>
-      <c r="D22" s="48">
-        <v>0.40295986219031626</v>
-      </c>
-      <c r="E22" s="48">
-        <v>0.5000989980472832</v>
-      </c>
-      <c r="F22" s="48">
-        <v>0.5523047138325573</v>
-      </c>
-      <c r="G22" s="48">
-        <v>0.5504308911870363</v>
+        <v>239</v>
+      </c>
+      <c r="C22" s="55">
+        <v>3</v>
+      </c>
+      <c r="D22" s="55">
+        <v>10</v>
+      </c>
+      <c r="E22" s="56">
+        <v>21</v>
+      </c>
+      <c r="F22" s="52">
+        <v>34</v>
+      </c>
+      <c r="G22" s="52">
+        <v>47</v>
       </c>
       <c r="H22" s="50" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="26" t="s">
-        <v>239</v>
-      </c>
-      <c r="C23" s="55">
-        <v>3</v>
-      </c>
-      <c r="D23" s="55">
-        <v>3</v>
-      </c>
-      <c r="E23" s="55">
-        <v>3</v>
-      </c>
-      <c r="F23" s="55">
-        <v>3</v>
-      </c>
-      <c r="G23" s="55">
-        <v>3</v>
-      </c>
-      <c r="H23" s="50" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="26" t="s">
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="C24" s="56">
-        <v>7.768293185121821</v>
-      </c>
-      <c r="D24" s="56">
-        <v>19.57810606562835</v>
-      </c>
-      <c r="E24" s="56">
-        <v>30.35571698045677</v>
-      </c>
-      <c r="F24" s="56">
-        <v>38.99024195731399</v>
-      </c>
-      <c r="G24" s="56">
-        <v>39.82940742297506</v>
-      </c>
-      <c r="H24" s="50" t="s">
+      <c r="C24" s="12" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="26" t="s">
+      <c r="D24" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="C25" s="34" t="str">
-        <f>IF('5-Year Model'!B49&gt;=0,"✓ Break-even","")</f>
-        <v>✓ Break-even</v>
-      </c>
-      <c r="D25" s="57" t="str">
-        <f>IF(AND('5-Year Model'!C49&gt;=0,'5-Year Model'!B49&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="57" t="str">
-        <f>IF(AND('5-Year Model'!D49&gt;=0,'5-Year Model'!C49&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="57" t="str">
-        <f>IF(AND('5-Year Model'!E49&gt;=0,'5-Year Model'!D49&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="57" t="str">
-        <f>IF(AND('5-Year Model'!F49&gt;=0,'5-Year Model'!E49&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="50" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="26" t="s">
+      <c r="E24" s="12"/>
+      <c r="F24" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="C26" s="58">
-        <v>3</v>
-      </c>
-      <c r="D26" s="58">
-        <v>10</v>
-      </c>
-      <c r="E26" s="59">
-        <v>21</v>
-      </c>
-      <c r="F26" s="55">
-        <v>34</v>
-      </c>
-      <c r="G26" s="55">
-        <v>47</v>
-      </c>
-      <c r="H26" s="50" t="s">
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="57" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="26" t="s">
-        <v>167</v>
-      </c>
-      <c r="C27" s="55">
-        <v>99</v>
-      </c>
-      <c r="D27" s="55">
-        <v>308</v>
-      </c>
-      <c r="E27" s="55">
-        <v>637</v>
-      </c>
-      <c r="F27" s="55">
-        <v>1038</v>
-      </c>
-      <c r="G27" s="55">
-        <v>1432</v>
-      </c>
-      <c r="H27" s="50" t="s">
+      <c r="C25" s="34" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="12" t="s">
+      <c r="D25" s="58" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="E25" s="58"/>
+      <c r="F25" s="59" t="s">
         <v>248</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="G25" s="59"/>
+      <c r="H25" s="59"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="57" t="s">
         <v>249</v>
       </c>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12" t="s">
+      <c r="C26" s="34" t="s">
+        <v>246</v>
+      </c>
+      <c r="D26" s="58" t="s">
         <v>250</v>
       </c>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="59" t="s">
+        <v>251</v>
+      </c>
+      <c r="G26" s="59"/>
+      <c r="H26" s="59"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="57" t="s">
+        <v>252</v>
+      </c>
+      <c r="C27" s="34" t="s">
+        <v>246</v>
+      </c>
+      <c r="D27" s="58" t="s">
+        <v>253</v>
+      </c>
+      <c r="E27" s="58"/>
+      <c r="F27" s="59" t="s">
+        <v>254</v>
+      </c>
+      <c r="G27" s="59"/>
+      <c r="H27" s="59"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="57" t="s">
+        <v>255</v>
+      </c>
+      <c r="C28" s="34" t="s">
+        <v>246</v>
+      </c>
+      <c r="D28" s="58" t="s">
+        <v>256</v>
+      </c>
+      <c r="E28" s="58"/>
+      <c r="F28" s="59" t="s">
+        <v>257</v>
+      </c>
+      <c r="G28" s="59"/>
+      <c r="H28" s="59"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="57" t="s">
+        <v>258</v>
+      </c>
+      <c r="C29" s="34" t="s">
+        <v>246</v>
+      </c>
+      <c r="D29" s="58" t="s">
+        <v>259</v>
+      </c>
+      <c r="E29" s="58"/>
+      <c r="F29" s="59" t="s">
+        <v>260</v>
+      </c>
+      <c r="G29" s="59"/>
+      <c r="H29" s="59"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="60" t="s">
-        <v>251</v>
+      <c r="B30" s="57" t="s">
+        <v>261</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="D30" s="61" t="s">
-        <v>253</v>
-      </c>
-      <c r="E30" s="61"/>
-      <c r="F30" s="62" t="s">
-        <v>254</v>
-      </c>
-      <c r="G30" s="62"/>
-      <c r="H30" s="62"/>
+        <v>246</v>
+      </c>
+      <c r="D30" s="58" t="s">
+        <v>262</v>
+      </c>
+      <c r="E30" s="58"/>
+      <c r="F30" s="59" t="s">
+        <v>263</v>
+      </c>
+      <c r="G30" s="59"/>
+      <c r="H30" s="59"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="60" t="s">
-        <v>255</v>
+      <c r="B31" s="57" t="s">
+        <v>264</v>
       </c>
       <c r="C31" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="D31" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="E31" s="61"/>
-      <c r="F31" s="62" t="s">
-        <v>257</v>
-      </c>
-      <c r="G31" s="62"/>
-      <c r="H31" s="62"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="60" t="s">
-        <v>258</v>
-      </c>
-      <c r="C32" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="D32" s="61" t="s">
-        <v>259</v>
-      </c>
-      <c r="E32" s="61"/>
-      <c r="F32" s="62" t="s">
-        <v>260</v>
-      </c>
-      <c r="G32" s="62"/>
-      <c r="H32" s="62"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="60" t="s">
-        <v>261</v>
-      </c>
-      <c r="C33" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="D33" s="61" t="s">
-        <v>262</v>
-      </c>
-      <c r="E33" s="61"/>
-      <c r="F33" s="62" t="s">
-        <v>263</v>
-      </c>
-      <c r="G33" s="62"/>
-      <c r="H33" s="62"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="60" t="s">
-        <v>264</v>
-      </c>
-      <c r="C34" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="D34" s="61" t="s">
+        <v>246</v>
+      </c>
+      <c r="D31" s="58" t="s">
         <v>265</v>
       </c>
-      <c r="E34" s="61"/>
-      <c r="F34" s="62" t="s">
+      <c r="E31" s="58"/>
+      <c r="F31" s="59" t="s">
         <v>266</v>
       </c>
-      <c r="G34" s="62"/>
-      <c r="H34" s="62"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G31" s="59"/>
+      <c r="H31" s="59"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="57" t="s">
+        <v>267</v>
+      </c>
+      <c r="C33" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="60" t="s">
-        <v>267</v>
-      </c>
-      <c r="C35" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="D35" s="61" t="s">
-        <v>268</v>
-      </c>
-      <c r="E35" s="61"/>
-      <c r="F35" s="62" t="s">
-        <v>269</v>
-      </c>
-      <c r="G35" s="62"/>
-      <c r="H35" s="62"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="60" t="s">
-        <v>270</v>
-      </c>
-      <c r="C36" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="D36" s="61" t="s">
-        <v>271</v>
-      </c>
-      <c r="E36" s="61"/>
-      <c r="F36" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="G36" s="62"/>
-      <c r="H36" s="62"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="60" t="s">
-        <v>273</v>
-      </c>
-      <c r="C38" s="26" t="s">
-        <v>274</v>
-      </c>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="26"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="63" t="s">
         <v>129</v>
       </c>
-      <c r="C40" s="63"/>
-      <c r="D40" s="63"/>
-      <c r="E40" s="63"/>
-      <c r="F40" s="63"/>
-      <c r="G40" s="63"/>
-      <c r="H40" s="63"/>
+      <c r="C35" s="60"/>
+      <c r="D35" s="60"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="60"/>
+      <c r="G35" s="60"/>
+      <c r="H35" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -6265,48 +6132,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:G21">
+  <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:G22">
+  <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C18&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24:G24">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C24&gt;=1.25</formula>
+      <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N46</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="275">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -713,6 +713,21 @@
     <t>≥ $10,000</t>
   </si>
   <si>
+    <t>Cost per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -750,6 +765,9 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1047,7 +1065,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1121,6 +1139,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="166" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -5492,7 +5519,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -5741,352 +5768,458 @@
         <v>227</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="26" t="s">
         <v>228</v>
       </c>
-      <c r="C16" s="48">
-        <v>0.5367065282791817</v>
-      </c>
-      <c r="D16" s="48">
-        <v>0.4347293119127009</v>
-      </c>
-      <c r="E16" s="48">
-        <v>0.3584103359800075</v>
-      </c>
-      <c r="F16" s="48">
-        <v>0.31741327092386307</v>
-      </c>
-      <c r="G16" s="48">
-        <v>0.31896162834300396</v>
-      </c>
-      <c r="H16" s="50" t="s">
+      <c r="C16" s="51">
+        <v>14541.164601438404</v>
+      </c>
+      <c r="D16" s="51">
+        <v>11602.63547503301</v>
+      </c>
+      <c r="E16" s="51">
+        <v>9915.73374775428</v>
+      </c>
+      <c r="F16" s="51">
+        <v>9077.061473703767</v>
+      </c>
+      <c r="G16" s="51">
+        <v>9334.775582029166</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="13" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="26" t="s">
+      <c r="C17" s="46">
+        <v>500</v>
+      </c>
+      <c r="D17" s="46">
+        <v>512.5</v>
+      </c>
+      <c r="E17" s="46">
+        <v>525.3125</v>
+      </c>
+      <c r="F17" s="46">
+        <v>538.4453124999998</v>
+      </c>
+      <c r="G17" s="46">
+        <v>551.9064453124997</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="C17" s="51">
-        <v>0.1624548736462094</v>
-      </c>
-      <c r="D17" s="48">
-        <v>0.10956757036500346</v>
-      </c>
-      <c r="E17" s="48">
-        <v>0.09025962891725049</v>
-      </c>
-      <c r="F17" s="48">
-        <v>0.07987105633946989</v>
-      </c>
-      <c r="G17" s="48">
-        <v>0.08019652156585022</v>
-      </c>
-      <c r="H17" s="50" t="s">
+      <c r="C18" s="52">
+        <v>3000</v>
+      </c>
+      <c r="D18" s="52">
+        <v>2058.3333333333335</v>
+      </c>
+      <c r="E18" s="49">
+        <v>1733.215909090909</v>
+      </c>
+      <c r="F18" s="49">
+        <v>1569.72615</v>
+      </c>
+      <c r="G18" s="49">
+        <v>1615.5256657500001</v>
+      </c>
+      <c r="H18" s="50" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="26" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="26" t="s">
         <v>232</v>
       </c>
-      <c r="C18" s="48">
-        <v>0.2439793922984356</v>
-      </c>
-      <c r="D18" s="48">
-        <v>0.40295986219031626</v>
-      </c>
-      <c r="E18" s="48">
-        <v>0.5000989980472832</v>
-      </c>
-      <c r="F18" s="48">
-        <v>0.5523047138325573</v>
-      </c>
-      <c r="G18" s="48">
-        <v>0.5504308911870363</v>
-      </c>
-      <c r="H18" s="50" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="C19" s="52">
-        <v>3</v>
-      </c>
-      <c r="D19" s="52">
-        <v>3</v>
-      </c>
-      <c r="E19" s="52">
-        <v>3</v>
-      </c>
-      <c r="F19" s="52">
-        <v>3</v>
-      </c>
-      <c r="G19" s="52">
-        <v>3</v>
-      </c>
-      <c r="H19" s="50" t="s">
-        <v>235</v>
+      <c r="C19" s="53">
+        <v>3925.5020652282624</v>
+      </c>
+      <c r="D19" s="53">
+        <v>7183.336747189209</v>
+      </c>
+      <c r="E19" s="53">
+        <v>9286.825911336624</v>
+      </c>
+      <c r="F19" s="53">
+        <v>10576.192432546224</v>
+      </c>
+      <c r="G19" s="53">
+        <v>10809.809671877074</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="26" t="s">
-        <v>236</v>
-      </c>
-      <c r="C20" s="53">
-        <v>7.768293185121821</v>
-      </c>
-      <c r="D20" s="53">
-        <v>19.57810606562835</v>
-      </c>
-      <c r="E20" s="53">
-        <v>30.35571698045677</v>
-      </c>
-      <c r="F20" s="53">
-        <v>38.99024195731399</v>
-      </c>
-      <c r="G20" s="53">
-        <v>39.82940742297506</v>
+        <v>233</v>
+      </c>
+      <c r="C20" s="48">
+        <v>0.5367065282791817</v>
+      </c>
+      <c r="D20" s="48">
+        <v>0.4347293119127009</v>
+      </c>
+      <c r="E20" s="48">
+        <v>0.3584103359800075</v>
+      </c>
+      <c r="F20" s="48">
+        <v>0.31741327092386307</v>
+      </c>
+      <c r="G20" s="48">
+        <v>0.31896162834300396</v>
       </c>
       <c r="H20" s="50" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="C21" s="54">
+        <v>0.1624548736462094</v>
+      </c>
+      <c r="D21" s="48">
+        <v>0.10956757036500346</v>
+      </c>
+      <c r="E21" s="48">
+        <v>0.09025962891725049</v>
+      </c>
+      <c r="F21" s="48">
+        <v>0.07987105633946989</v>
+      </c>
+      <c r="G21" s="48">
+        <v>0.08019652156585022</v>
+      </c>
+      <c r="H21" s="50" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="C22" s="48">
+        <v>0.2439793922984356</v>
+      </c>
+      <c r="D22" s="48">
+        <v>0.40295986219031626</v>
+      </c>
+      <c r="E22" s="48">
+        <v>0.5000989980472832</v>
+      </c>
+      <c r="F22" s="48">
+        <v>0.5523047138325573</v>
+      </c>
+      <c r="G22" s="48">
+        <v>0.5504308911870363</v>
+      </c>
+      <c r="H22" s="50" t="s">
         <v>238</v>
       </c>
-      <c r="C21" s="34" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="C23" s="55">
+        <v>3</v>
+      </c>
+      <c r="D23" s="55">
+        <v>3</v>
+      </c>
+      <c r="E23" s="55">
+        <v>3</v>
+      </c>
+      <c r="F23" s="55">
+        <v>3</v>
+      </c>
+      <c r="G23" s="55">
+        <v>3</v>
+      </c>
+      <c r="H23" s="50" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="C24" s="56">
+        <v>7.768293185121821</v>
+      </c>
+      <c r="D24" s="56">
+        <v>19.57810606562835</v>
+      </c>
+      <c r="E24" s="56">
+        <v>30.35571698045677</v>
+      </c>
+      <c r="F24" s="56">
+        <v>38.99024195731399</v>
+      </c>
+      <c r="G24" s="56">
+        <v>39.82940742297506</v>
+      </c>
+      <c r="H24" s="50" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="C25" s="34" t="str">
         <f>IF('5-Year Model'!B49&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D21" s="54" t="str">
+      <c r="D25" s="57" t="str">
         <f>IF(AND('5-Year Model'!C49&gt;=0,'5-Year Model'!B49&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="54" t="str">
+      <c r="E25" s="57" t="str">
         <f>IF(AND('5-Year Model'!D49&gt;=0,'5-Year Model'!C49&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="54" t="str">
+      <c r="F25" s="57" t="str">
         <f>IF(AND('5-Year Model'!E49&gt;=0,'5-Year Model'!D49&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="54" t="str">
+      <c r="G25" s="57" t="str">
         <f>IF(AND('5-Year Model'!F49&gt;=0,'5-Year Model'!E49&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="50" t="s">
+      <c r="H25" s="50" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="26" t="s">
-        <v>239</v>
-      </c>
-      <c r="C22" s="55">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="C26" s="58">
         <v>3</v>
       </c>
-      <c r="D22" s="55">
+      <c r="D26" s="58">
         <v>10</v>
       </c>
-      <c r="E22" s="56">
+      <c r="E26" s="59">
         <v>21</v>
       </c>
-      <c r="F22" s="52">
+      <c r="F26" s="55">
         <v>34</v>
       </c>
-      <c r="G22" s="52">
+      <c r="G26" s="55">
         <v>47</v>
       </c>
-      <c r="H22" s="50" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="57" t="s">
+      <c r="H26" s="50" t="s">
         <v>245</v>
       </c>
-      <c r="C25" s="34" t="s">
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="C27" s="55">
+        <v>99</v>
+      </c>
+      <c r="D27" s="55">
+        <v>308</v>
+      </c>
+      <c r="E27" s="55">
+        <v>637</v>
+      </c>
+      <c r="F27" s="55">
+        <v>1038</v>
+      </c>
+      <c r="G27" s="55">
+        <v>1432</v>
+      </c>
+      <c r="H27" s="50" t="s">
         <v>246</v>
       </c>
-      <c r="D25" s="58" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="E25" s="58"/>
-      <c r="F25" s="59" t="s">
+      <c r="C29" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="57" t="s">
+      <c r="D29" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="C26" s="34" t="s">
-        <v>246</v>
-      </c>
-      <c r="D26" s="58" t="s">
+      <c r="E29" s="12"/>
+      <c r="F29" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="E26" s="58"/>
-      <c r="F26" s="59" t="s">
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="60" t="s">
         <v>251</v>
       </c>
-      <c r="G26" s="59"/>
-      <c r="H26" s="59"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="57" t="s">
+      <c r="C30" s="34" t="s">
         <v>252</v>
       </c>
-      <c r="C27" s="34" t="s">
-        <v>246</v>
-      </c>
-      <c r="D27" s="58" t="s">
+      <c r="D30" s="61" t="s">
         <v>253</v>
       </c>
-      <c r="E27" s="58"/>
-      <c r="F27" s="59" t="s">
+      <c r="E30" s="61"/>
+      <c r="F30" s="62" t="s">
         <v>254</v>
       </c>
-      <c r="G27" s="59"/>
-      <c r="H27" s="59"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="57" t="s">
+      <c r="G30" s="62"/>
+      <c r="H30" s="62"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="60" t="s">
         <v>255</v>
       </c>
-      <c r="C28" s="34" t="s">
-        <v>246</v>
-      </c>
-      <c r="D28" s="58" t="s">
+      <c r="C31" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="D31" s="61" t="s">
         <v>256</v>
       </c>
-      <c r="E28" s="58"/>
-      <c r="F28" s="59" t="s">
+      <c r="E31" s="61"/>
+      <c r="F31" s="62" t="s">
         <v>257</v>
       </c>
-      <c r="G28" s="59"/>
-      <c r="H28" s="59"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="57" t="s">
+      <c r="G31" s="62"/>
+      <c r="H31" s="62"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="60" t="s">
         <v>258</v>
       </c>
-      <c r="C29" s="34" t="s">
-        <v>246</v>
-      </c>
-      <c r="D29" s="58" t="s">
+      <c r="C32" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="D32" s="61" t="s">
         <v>259</v>
       </c>
-      <c r="E29" s="58"/>
-      <c r="F29" s="59" t="s">
+      <c r="E32" s="61"/>
+      <c r="F32" s="62" t="s">
         <v>260</v>
       </c>
-      <c r="G29" s="59"/>
-      <c r="H29" s="59"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="57" t="s">
+      <c r="G32" s="62"/>
+      <c r="H32" s="62"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="60" t="s">
         <v>261</v>
       </c>
-      <c r="C30" s="34" t="s">
-        <v>246</v>
-      </c>
-      <c r="D30" s="58" t="s">
+      <c r="C33" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="D33" s="61" t="s">
         <v>262</v>
       </c>
-      <c r="E30" s="58"/>
-      <c r="F30" s="59" t="s">
+      <c r="E33" s="61"/>
+      <c r="F33" s="62" t="s">
         <v>263</v>
       </c>
-      <c r="G30" s="59"/>
-      <c r="H30" s="59"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="57" t="s">
+      <c r="G33" s="62"/>
+      <c r="H33" s="62"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="60" t="s">
         <v>264</v>
       </c>
-      <c r="C31" s="34" t="s">
-        <v>246</v>
-      </c>
-      <c r="D31" s="58" t="s">
+      <c r="C34" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="D34" s="61" t="s">
         <v>265</v>
       </c>
-      <c r="E31" s="58"/>
-      <c r="F31" s="59" t="s">
+      <c r="E34" s="61"/>
+      <c r="F34" s="62" t="s">
         <v>266</v>
       </c>
-      <c r="G31" s="59"/>
-      <c r="H31" s="59"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="57" t="s">
+      <c r="G34" s="62"/>
+      <c r="H34" s="62"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="60" t="s">
         <v>267</v>
       </c>
-      <c r="C33" s="26" t="s">
+      <c r="C35" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="D35" s="61" t="s">
         <v>268</v>
       </c>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="60" t="s">
+      <c r="E35" s="61"/>
+      <c r="F35" s="62" t="s">
+        <v>269</v>
+      </c>
+      <c r="G35" s="62"/>
+      <c r="H35" s="62"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="60" t="s">
+        <v>270</v>
+      </c>
+      <c r="C36" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="D36" s="61" t="s">
+        <v>271</v>
+      </c>
+      <c r="E36" s="61"/>
+      <c r="F36" s="62" t="s">
+        <v>272</v>
+      </c>
+      <c r="G36" s="62"/>
+      <c r="H36" s="62"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="60" t="s">
+        <v>273</v>
+      </c>
+      <c r="C38" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="63" t="s">
         <v>129</v>
       </c>
-      <c r="C35" s="60"/>
-      <c r="D35" s="60"/>
-      <c r="E35" s="60"/>
-      <c r="F35" s="60"/>
-      <c r="G35" s="60"/>
-      <c r="H35" s="60"/>
+      <c r="C40" s="63"/>
+      <c r="D40" s="63"/>
+      <c r="E40" s="63"/>
+      <c r="F40" s="63"/>
+      <c r="G40" s="63"/>
+      <c r="H40" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -6132,48 +6265,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
@@ -15,7 +15,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Instructions'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$J56</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'5-Year Model'!$A1:$F76</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'5-Year Model'!$A1:$F77</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N46</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="276">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Bright Horizons Microschool</t>
   </si>
   <si>
-    <t>Generated March 27, 2026 · llc_single</t>
+    <t>Generated April 29, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -422,6 +422,9 @@
     <t>Bright Horizons Microschool - 5-Year Financial Model</t>
   </si>
   <si>
+    <t>Projections prepared on an accrual basis. School currently keeps books on a undetermined basis.</t>
+  </si>
+  <si>
     <t>REVENUE</t>
   </si>
   <si>
@@ -542,7 +545,7 @@
     <t>COVENANT &amp; HEALTH CHECKS</t>
   </si>
   <si>
-    <t>DSCR ≥ 1.20x</t>
+    <t>DSCR ≥ 1.25x</t>
   </si>
   <si>
     <t>Positive Net Income</t>
@@ -656,7 +659,7 @@
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 27, 2026</t>
+    <t>Generated April 29, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -815,7 +818,7 @@
     <t>Facility Burden</t>
   </si>
   <si>
-    <t>Facility costs at 8% of revenue are well-managed and leave budget for programs.</t>
+    <t>Facility costs at 7% of revenue are well-managed and leave budget for programs.</t>
   </si>
   <si>
     <t>Watch for rent escalation clauses that could push this higher over time.</t>
@@ -824,7 +827,7 @@
     <t>Debt Affordability</t>
   </si>
   <si>
-    <t>DSCR of 39.83x provides comfortable coverage of debt payments with room to spare.</t>
+    <t>DSCR of 40.29x provides comfortable coverage of debt payments with room to spare.</t>
   </si>
   <si>
     <t>Maintain this ratio as you take on any additional debt.</t>
@@ -842,7 +845,7 @@
     <t>Reserve Strength</t>
   </si>
   <si>
-    <t>47.1 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+    <t>50.0 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
   </si>
   <si>
     <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
@@ -865,7 +868,7 @@
     <numFmt numFmtId="167" formatCode="0.00x"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -927,6 +930,12 @@
       <i/>
       <color rgb="FF9CA3AF"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF64748B"/>
+      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1097,80 +1106,78 @@
     <xf numFmtId="10" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2651,7 +2658,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -2668,234 +2675,224 @@
       <c r="E1" s="8"/>
       <c r="F1" s="8"/>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B3" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C3" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D3" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="E3" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F3" s="26" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B4" s="28">
         <f>Assumptions!B17</f>
         <v>12</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C4" s="28">
         <f>Assumptions!C17</f>
         <v>18</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D4" s="28">
         <f>Assumptions!D17</f>
         <v>22</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E4" s="28">
         <f>Assumptions!E17</f>
         <v>25</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F4" s="28">
         <f>Assumptions!F17</f>
         <v>25</v>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="21">
-        <v>120000</v>
-      </c>
-      <c r="C6" s="21">
-        <v>221400</v>
-      </c>
-      <c r="D6" s="21">
-        <v>277365</v>
-      </c>
-      <c r="E6" s="21">
-        <v>323067</v>
-      </c>
-      <c r="F6" s="21">
-        <v>331144</v>
-      </c>
+    <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B7" s="21">
-        <v>2500</v>
+        <v>120000</v>
       </c>
       <c r="C7" s="21">
-        <v>4613</v>
+        <v>221400</v>
       </c>
       <c r="D7" s="21">
-        <v>5778</v>
+        <v>277365</v>
       </c>
       <c r="E7" s="21">
-        <v>6731</v>
+        <v>323067</v>
       </c>
       <c r="F7" s="21">
-        <v>6899</v>
+        <v>331144</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B8" s="21">
-        <v>70000</v>
+        <v>2500</v>
       </c>
       <c r="C8" s="21">
-        <v>129150</v>
+        <v>4613</v>
       </c>
       <c r="D8" s="21">
-        <v>161796</v>
+        <v>5778</v>
       </c>
       <c r="E8" s="21">
-        <v>188456</v>
+        <v>6731</v>
       </c>
       <c r="F8" s="21">
-        <v>193167</v>
+        <v>6899</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B9" s="21">
-        <v>4167</v>
+        <v>70000</v>
       </c>
       <c r="C9" s="21">
-        <v>5125</v>
+        <v>129150</v>
       </c>
       <c r="D9" s="21">
-        <v>5253</v>
+        <v>161796</v>
       </c>
       <c r="E9" s="21">
-        <v>5384</v>
+        <v>188456</v>
       </c>
       <c r="F9" s="21">
-        <v>5519</v>
+        <v>193167</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="21">
+        <v>4167</v>
+      </c>
+      <c r="C10" s="21">
+        <v>5125</v>
+      </c>
+      <c r="D10" s="21">
+        <v>5253</v>
+      </c>
+      <c r="E10" s="21">
+        <v>5384</v>
+      </c>
+      <c r="F10" s="21">
+        <v>5519</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B11" s="21">
         <v>-12000</v>
       </c>
-      <c r="C10" s="21">
+      <c r="C11" s="21">
         <v>-22140</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D11" s="21">
         <v>-27736</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E11" s="21">
         <v>-32307</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F11" s="21">
         <v>-33114</v>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="B11" s="28">
-        <f>SUM(B6:B10)</f>
+    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="B12" s="29">
+        <f>SUM(B7:B11)</f>
         <v>184667</v>
       </c>
-      <c r="C11" s="28">
-        <f>SUM(C6:C10)</f>
-        <v>338147</v>
-      </c>
-      <c r="D11" s="28">
-        <f>SUM(D6:D10)</f>
-        <v>422456</v>
-      </c>
-      <c r="E11" s="28">
-        <f>SUM(E6:E10)</f>
-        <v>491331</v>
-      </c>
-      <c r="F11" s="28">
-        <f>SUM(F6:F10)</f>
-        <v>503615</v>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
+      <c r="C12" s="29">
+        <f>SUM(C7:C11)</f>
+        <v>337594</v>
+      </c>
+      <c r="D12" s="29">
+        <f>SUM(D7:D11)</f>
+        <v>421052</v>
+      </c>
+      <c r="E12" s="29">
+        <f>SUM(E7:E11)</f>
+        <v>488847</v>
+      </c>
+      <c r="F12" s="29">
+        <f>SUM(F7:F11)</f>
+        <v>500177</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="B14" s="21">
-        <v>58506</v>
-      </c>
-      <c r="C14" s="21">
-        <v>72314</v>
-      </c>
-      <c r="D14" s="21">
-        <v>74483</v>
-      </c>
-      <c r="E14" s="21">
-        <v>76718</v>
-      </c>
-      <c r="F14" s="21">
-        <v>79019</v>
-      </c>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>135</v>
       </c>
       <c r="B15" s="21">
-        <v>47869</v>
+        <v>58506</v>
       </c>
       <c r="C15" s="21">
-        <v>59166</v>
+        <v>72314</v>
       </c>
       <c r="D15" s="21">
-        <v>60941</v>
+        <v>74483</v>
       </c>
       <c r="E15" s="21">
-        <v>62769</v>
+        <v>76718</v>
       </c>
       <c r="F15" s="21">
-        <v>64652</v>
+        <v>79019</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2903,204 +2900,204 @@
         <v>136</v>
       </c>
       <c r="B16" s="21">
+        <v>47869</v>
+      </c>
+      <c r="C16" s="21">
+        <v>59166</v>
+      </c>
+      <c r="D16" s="21">
+        <v>60941</v>
+      </c>
+      <c r="E16" s="21">
+        <v>62769</v>
+      </c>
+      <c r="F16" s="21">
+        <v>64652</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B17" s="21">
         <v>12559</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C17" s="21">
         <v>15523</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D17" s="21">
         <v>15989</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E17" s="21">
         <v>16468</v>
       </c>
-      <c r="F16" s="21">
+      <c r="F17" s="21">
         <v>16963</v>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="B17" s="28">
-        <f>SUM(B14:B16)</f>
+    <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="B18" s="29">
+        <f>SUM(B15:B17)</f>
         <v>118934</v>
       </c>
-      <c r="C17" s="28">
-        <f>SUM(C14:C16)</f>
+      <c r="C18" s="29">
+        <f>SUM(C15:C17)</f>
         <v>147003</v>
       </c>
-      <c r="D17" s="28">
-        <f>SUM(D14:D16)</f>
+      <c r="D18" s="29">
+        <f>SUM(D15:D17)</f>
         <v>151413</v>
       </c>
-      <c r="E17" s="28">
-        <f>SUM(E14:E16)</f>
+      <c r="E18" s="29">
+        <f>SUM(E15:E17)</f>
         <v>155955</v>
       </c>
-      <c r="F17" s="28">
-        <f>SUM(F14:F16)</f>
+      <c r="F18" s="29">
+        <f>SUM(F15:F17)</f>
         <v>160634</v>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+    <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="B21" s="21">
+        <v>110</v>
+      </c>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B22" s="21">
         <v>5000</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C22" s="21">
         <v>9225</v>
       </c>
-      <c r="D21" s="21">
+      <c r="D22" s="21">
         <v>11557</v>
       </c>
-      <c r="E21" s="21">
+      <c r="E22" s="21">
         <v>13461</v>
       </c>
-      <c r="F21" s="21">
+      <c r="F22" s="21">
         <v>13798</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="B22" s="30">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" s="31">
         <v>5000</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C23" s="31">
         <v>9225</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D23" s="31">
         <v>11557</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E23" s="31">
         <v>13461</v>
       </c>
-      <c r="F22" s="30">
+      <c r="F23" s="31">
         <v>13798</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="B24" s="21">
+        <v>111</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="B25" s="21">
         <v>3000</v>
       </c>
-      <c r="C24" s="21">
+      <c r="C25" s="21">
         <v>5535</v>
       </c>
-      <c r="D24" s="21">
+      <c r="D25" s="21">
         <v>6934</v>
       </c>
-      <c r="E24" s="21">
+      <c r="E25" s="21">
         <v>8077</v>
       </c>
-      <c r="F24" s="21">
+      <c r="F25" s="21">
         <v>8279</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="B25" s="30">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="B26" s="31">
         <v>3000</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C26" s="31">
         <v>5535</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D26" s="31">
         <v>6934</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E26" s="31">
         <v>8077</v>
       </c>
-      <c r="F25" s="30">
+      <c r="F26" s="31">
         <v>8279</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="B27" s="21">
-        <v>25000</v>
-      </c>
-      <c r="C27" s="21">
-        <v>30900</v>
-      </c>
-      <c r="D27" s="21">
-        <v>31827</v>
-      </c>
-      <c r="E27" s="21">
-        <v>32782</v>
-      </c>
-      <c r="F27" s="21">
-        <v>33765</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>143</v>
       </c>
       <c r="B28" s="21">
-        <v>3000</v>
+        <v>25000</v>
       </c>
       <c r="C28" s="21">
-        <v>3690</v>
+        <v>30900</v>
       </c>
       <c r="D28" s="21">
-        <v>3782</v>
+        <v>31827</v>
       </c>
       <c r="E28" s="21">
-        <v>3877</v>
+        <v>32782</v>
       </c>
       <c r="F28" s="21">
-        <v>3974</v>
+        <v>33765</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -3108,229 +3105,224 @@
         <v>144</v>
       </c>
       <c r="B29" s="21">
+        <v>3000</v>
+      </c>
+      <c r="C29" s="21">
+        <v>3690</v>
+      </c>
+      <c r="D29" s="21">
+        <v>3782</v>
+      </c>
+      <c r="E29" s="21">
+        <v>3877</v>
+      </c>
+      <c r="F29" s="21">
+        <v>3974</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="B30" s="21">
         <v>2000</v>
       </c>
-      <c r="C29" s="21">
+      <c r="C30" s="21">
         <v>2460</v>
       </c>
-      <c r="D29" s="21">
+      <c r="D30" s="21">
         <v>2522</v>
       </c>
-      <c r="E29" s="21">
+      <c r="E30" s="21">
         <v>2585</v>
       </c>
-      <c r="F29" s="21">
+      <c r="F30" s="21">
         <v>2649</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="B30" s="30">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="B31" s="31">
         <v>30000</v>
       </c>
-      <c r="C30" s="30">
+      <c r="C31" s="31">
         <v>37050</v>
       </c>
-      <c r="D30" s="30">
+      <c r="D31" s="31">
         <v>38131</v>
       </c>
-      <c r="E30" s="30">
+      <c r="E31" s="31">
         <v>39244</v>
       </c>
-      <c r="F30" s="30">
+      <c r="F31" s="31">
         <v>40388</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="B32" s="21">
+        <v>113</v>
+      </c>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="B33" s="21">
         <v>2500</v>
       </c>
-      <c r="C32" s="21">
+      <c r="C33" s="21">
         <v>3075</v>
       </c>
-      <c r="D32" s="21">
+      <c r="D33" s="21">
         <v>3152</v>
       </c>
-      <c r="E32" s="21">
+      <c r="E33" s="21">
         <v>3231</v>
       </c>
-      <c r="F32" s="21">
+      <c r="F33" s="21">
         <v>3311</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="B33" s="30">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="B34" s="31">
         <v>2500</v>
       </c>
-      <c r="C33" s="30">
+      <c r="C34" s="31">
         <v>3075</v>
       </c>
-      <c r="D33" s="30">
+      <c r="D34" s="31">
         <v>3152</v>
       </c>
-      <c r="E33" s="30">
+      <c r="E34" s="31">
         <v>3231</v>
       </c>
-      <c r="F33" s="30">
+      <c r="F34" s="31">
         <v>3311</v>
       </c>
     </row>
-    <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="B34" s="28">
-        <f>B22+B25+B30+B33</f>
+    <row r="35" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="B35" s="29">
+        <f>B23+B26+B31+B34</f>
         <v>40500</v>
       </c>
-      <c r="C34" s="28">
-        <f>C22+C25+C30+C33</f>
+      <c r="C35" s="29">
+        <f>C23+C26+C31+C34</f>
         <v>54885</v>
       </c>
-      <c r="D34" s="28">
-        <f>D22+D25+D30+D33</f>
+      <c r="D35" s="29">
+        <f>D23+D26+D31+D34</f>
         <v>59774</v>
       </c>
-      <c r="E34" s="28">
-        <f>E22+E25+E30+E33</f>
+      <c r="E35" s="29">
+        <f>E23+E26+E31+E34</f>
         <v>64012</v>
       </c>
-      <c r="F34" s="28">
-        <f>F22+F25+F30+F33</f>
+      <c r="F35" s="29">
+        <f>F23+F26+F31+F34</f>
         <v>65776</v>
       </c>
     </row>
-    <row r="36" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="13" t="s">
+    <row r="37" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="B37" s="21">
+      <c r="B38" s="21">
         <v>6960</v>
       </c>
-      <c r="C37" s="21">
+      <c r="C38" s="21">
         <v>6960</v>
       </c>
-      <c r="D37" s="21">
+      <c r="D38" s="21">
         <v>6960</v>
       </c>
-      <c r="E37" s="21">
+      <c r="E38" s="21">
         <v>6960</v>
       </c>
-      <c r="F37" s="21">
+      <c r="F38" s="21">
         <v>6960</v>
       </c>
     </row>
-    <row r="38" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="B38" s="28">
-        <f>SUM(B37:B37)</f>
+    <row r="39" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="B39" s="29">
+        <f>SUM(B38:B38)</f>
         <v>6960</v>
       </c>
-      <c r="C38" s="28">
-        <f>SUM(C37:C37)</f>
+      <c r="C39" s="29">
+        <f>SUM(C38:C38)</f>
         <v>6960</v>
       </c>
-      <c r="D38" s="28">
-        <f>SUM(D37:D37)</f>
+      <c r="D39" s="29">
+        <f>SUM(D38:D38)</f>
         <v>6960</v>
       </c>
-      <c r="E38" s="28">
-        <f>SUM(E37:E37)</f>
+      <c r="E39" s="29">
+        <f>SUM(E38:E38)</f>
         <v>6960</v>
       </c>
-      <c r="F38" s="28">
-        <f>SUM(F37:F37)</f>
+      <c r="F39" s="29">
+        <f>SUM(F38:F38)</f>
         <v>6960</v>
       </c>
     </row>
-    <row r="40" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="26" t="s">
+    <row r="41" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="B41" s="30">
-        <f>B11</f>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="B42" s="31">
+        <f>B12</f>
         <v>184667</v>
       </c>
-      <c r="C41" s="30">
-        <f>C11</f>
-        <v>338147</v>
-      </c>
-      <c r="D41" s="30">
-        <f>D11</f>
-        <v>422456</v>
-      </c>
-      <c r="E41" s="30">
-        <f>E11</f>
-        <v>491331</v>
-      </c>
-      <c r="F41" s="30">
-        <f>F11</f>
-        <v>503615</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="B42" s="21">
-        <f>B17</f>
-        <v>118934</v>
-      </c>
-      <c r="C42" s="21">
-        <f>C17</f>
-        <v>147003</v>
-      </c>
-      <c r="D42" s="21">
-        <f>D17</f>
-        <v>151413</v>
-      </c>
-      <c r="E42" s="21">
-        <f>E17</f>
-        <v>155955</v>
-      </c>
-      <c r="F42" s="21">
-        <f>F17</f>
-        <v>160634</v>
+      <c r="C42" s="31">
+        <f>C12</f>
+        <v>337594</v>
+      </c>
+      <c r="D42" s="31">
+        <f>D12</f>
+        <v>421052</v>
+      </c>
+      <c r="E42" s="31">
+        <f>E12</f>
+        <v>488847</v>
+      </c>
+      <c r="F42" s="31">
+        <f>F12</f>
+        <v>500177</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -3338,24 +3330,24 @@
         <v>154</v>
       </c>
       <c r="B43" s="21">
-        <f>B34</f>
-        <v>40500</v>
+        <f>B18</f>
+        <v>118934</v>
       </c>
       <c r="C43" s="21">
-        <f>C34</f>
-        <v>54885</v>
+        <f>C18</f>
+        <v>147003</v>
       </c>
       <c r="D43" s="21">
-        <f>D34</f>
-        <v>59774</v>
+        <f>D18</f>
+        <v>151413</v>
       </c>
       <c r="E43" s="21">
-        <f>E34</f>
-        <v>64012</v>
+        <f>E18</f>
+        <v>155955</v>
       </c>
       <c r="F43" s="21">
-        <f>F34</f>
-        <v>65776</v>
+        <f>F18</f>
+        <v>160634</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -3363,309 +3355,309 @@
         <v>155</v>
       </c>
       <c r="B44" s="21">
-        <f>B38</f>
+        <f>B35</f>
+        <v>40500</v>
+      </c>
+      <c r="C44" s="21">
+        <f>C35</f>
+        <v>54885</v>
+      </c>
+      <c r="D44" s="21">
+        <f>D35</f>
+        <v>59774</v>
+      </c>
+      <c r="E44" s="21">
+        <f>E35</f>
+        <v>64012</v>
+      </c>
+      <c r="F44" s="21">
+        <f>F35</f>
+        <v>65776</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="B45" s="21">
+        <f>B39</f>
         <v>6960</v>
       </c>
-      <c r="C44" s="21">
-        <f>C38</f>
+      <c r="C45" s="21">
+        <f>C39</f>
         <v>6960</v>
       </c>
-      <c r="D44" s="21">
-        <f>D38</f>
+      <c r="D45" s="21">
+        <f>D39</f>
         <v>6960</v>
       </c>
-      <c r="E44" s="21">
-        <f>E38</f>
+      <c r="E45" s="21">
+        <f>E39</f>
         <v>6960</v>
       </c>
-      <c r="F44" s="21">
-        <f>F38</f>
+      <c r="F45" s="21">
+        <f>F39</f>
         <v>6960</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="26" t="s">
-        <v>156</v>
-      </c>
-      <c r="B45" s="30">
-        <f>B42+B43+B44</f>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="B46" s="31">
+        <f>B43+B44+B45</f>
         <v>166394</v>
       </c>
-      <c r="C45" s="30">
-        <f>C42+C43+C44</f>
+      <c r="C46" s="31">
+        <f>C43+C44+C45</f>
         <v>208848</v>
       </c>
-      <c r="D45" s="30">
-        <f>D42+D43+D44</f>
+      <c r="D46" s="31">
+        <f>D43+D44+D45</f>
         <v>218147</v>
       </c>
-      <c r="E45" s="30">
-        <f>E42+E43+E44</f>
+      <c r="E46" s="31">
+        <f>E43+E44+E45</f>
         <v>226927</v>
       </c>
-      <c r="F45" s="30">
-        <f>F42+F43+F44</f>
+      <c r="F46" s="31">
+        <f>F43+F44+F45</f>
         <v>233370</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="31" t="s">
-        <v>157</v>
-      </c>
-      <c r="B47" s="32">
-        <f>B41-B45</f>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="32" t="s">
+        <v>158</v>
+      </c>
+      <c r="B48" s="33">
+        <f>B42-B46</f>
         <v>18273</v>
       </c>
-      <c r="C47" s="32">
-        <f>C41-C45</f>
-        <v>129299</v>
-      </c>
-      <c r="D47" s="32">
-        <f>D41-D45</f>
-        <v>204309</v>
-      </c>
-      <c r="E47" s="32">
-        <f>E41-E45</f>
-        <v>264404</v>
-      </c>
-      <c r="F47" s="32">
-        <f>F41-F45</f>
-        <v>270245</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="B48" s="33">
-        <f>IF(B41=0,"",B47/B41)</f>
-        <v>0.1</v>
-      </c>
       <c r="C48" s="33">
-        <f>IF(C41=0,"",C47/C41)</f>
-        <v>0.38</v>
+        <f>C42-C46</f>
+        <v>128746</v>
       </c>
       <c r="D48" s="33">
-        <f>IF(D41=0,"",D47/D41)</f>
-        <v>0.48</v>
+        <f>D42-D46</f>
+        <v>202905</v>
       </c>
       <c r="E48" s="33">
-        <f>IF(E41=0,"",E47/E41)</f>
-        <v>0.54</v>
+        <f>E42-E46</f>
+        <v>261920</v>
       </c>
       <c r="F48" s="33">
-        <f>IF(F41=0,"",F47/F41)</f>
-        <v>0.54</v>
+        <f>F42-F46</f>
+        <v>266807</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="B49" s="21">
-        <f>B47</f>
+      <c r="B49" s="34">
+        <f>IF(B42=0,"",B48/B42)</f>
+        <v>0.09895108</v>
+      </c>
+      <c r="C49" s="34">
+        <f>IF(C42=0,"",C48/C42)</f>
+        <v>0.38136341</v>
+      </c>
+      <c r="D49" s="34">
+        <f>IF(D42=0,"",D48/D42)</f>
+        <v>0.4819001</v>
+      </c>
+      <c r="E49" s="34">
+        <f>IF(E42=0,"",E48/E42)</f>
+        <v>0.53579136</v>
+      </c>
+      <c r="F49" s="34">
+        <f>IF(F42=0,"",F48/F42)</f>
+        <v>0.53342517</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="B50" s="21">
+        <f>B48</f>
         <v>18273</v>
       </c>
-      <c r="C49" s="21">
-        <f>B49+C47</f>
-        <v>147572</v>
-      </c>
-      <c r="D49" s="21">
-        <f>C49+D47</f>
-        <v>351881</v>
-      </c>
-      <c r="E49" s="21">
-        <f>D49+E47</f>
-        <v>616285</v>
-      </c>
-      <c r="F49" s="21">
-        <f>E49+F47</f>
-        <v>886530</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="B50" s="34" t="s">
+      <c r="C50" s="21">
+        <f>B50+C48</f>
+        <v>147019</v>
+      </c>
+      <c r="D50" s="21">
+        <f>C50+D48</f>
+        <v>349924</v>
+      </c>
+      <c r="E50" s="21">
+        <f>D50+E48</f>
+        <v>611844</v>
+      </c>
+      <c r="F50" s="21">
+        <f>E50+F48</f>
+        <v>878651</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="C50" s="35" t="s">
+      <c r="B51" s="35" t="s">
+        <v>162</v>
+      </c>
+      <c r="C51" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="D50" s="35" t="s">
+      <c r="D51" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="E50" s="35" t="s">
+      <c r="E51" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="F50" s="35" t="s">
+      <c r="F51" s="36" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="52" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="B52" s="12"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="26" t="s">
+    <row r="53" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="B53" s="30">
-        <f>B41-B42-B43</f>
+      <c r="B53" s="12"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="B54" s="31">
+        <f>B42-B43-B44</f>
         <v>25233</v>
       </c>
-      <c r="C53" s="30">
-        <f>C41-C42-C43</f>
-        <v>136259</v>
-      </c>
-      <c r="D53" s="30">
-        <f>D41-D42-D43</f>
-        <v>211269</v>
-      </c>
-      <c r="E53" s="30">
-        <f>E41-E42-E43</f>
-        <v>271364</v>
-      </c>
-      <c r="F53" s="30">
-        <f>F41-F42-F43</f>
-        <v>277205</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="B54" s="21">
-        <f>B44</f>
+      <c r="C54" s="31">
+        <f>C42-C43-C44</f>
+        <v>135706</v>
+      </c>
+      <c r="D54" s="31">
+        <f>D42-D43-D44</f>
+        <v>209865</v>
+      </c>
+      <c r="E54" s="31">
+        <f>E42-E43-E44</f>
+        <v>268880</v>
+      </c>
+      <c r="F54" s="31">
+        <f>F42-F43-F44</f>
+        <v>273767</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="B55" s="21">
+        <f>B45</f>
         <v>6960</v>
       </c>
-      <c r="C54" s="21">
-        <f>C44</f>
+      <c r="C55" s="21">
+        <f>C45</f>
         <v>6960</v>
       </c>
-      <c r="D54" s="21">
-        <f>D44</f>
+      <c r="D55" s="21">
+        <f>D45</f>
         <v>6960</v>
       </c>
-      <c r="E54" s="21">
-        <f>E44</f>
+      <c r="E55" s="21">
+        <f>E45</f>
         <v>6960</v>
       </c>
-      <c r="F54" s="21">
-        <f>F44</f>
+      <c r="F55" s="21">
+        <f>F45</f>
         <v>6960</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="26" t="s">
-        <v>165</v>
-      </c>
-      <c r="B55" s="36">
-        <f>IF(B54=0,"N/A",B53/B54)</f>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="B56" s="37">
+        <f>IF(B55=0,"N/A",B54/B55)</f>
         <v>3.63</v>
       </c>
-      <c r="C55" s="36">
-        <f>IF(C54=0,"N/A",C53/C54)</f>
-        <v>19.58</v>
-      </c>
-      <c r="D55" s="36">
-        <f>IF(D54=0,"N/A",D53/D54)</f>
-        <v>30.35</v>
-      </c>
-      <c r="E55" s="36">
-        <f>IF(E54=0,"N/A",E53/E54)</f>
-        <v>38.99</v>
-      </c>
-      <c r="F55" s="36">
-        <f>IF(F54=0,"N/A",F53/F54)</f>
-        <v>39.83</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="13" t="s">
+      <c r="C56" s="37">
+        <f>IF(C55=0,"N/A",C54/C55)</f>
+        <v>19.5</v>
+      </c>
+      <c r="D56" s="37">
+        <f>IF(D55=0,"N/A",D54/D55)</f>
+        <v>30.15</v>
+      </c>
+      <c r="E56" s="37">
+        <f>IF(E55=0,"N/A",E54/E55)</f>
+        <v>38.63</v>
+      </c>
+      <c r="F56" s="37">
+        <f>IF(F55=0,"N/A",F54/F55)</f>
+        <v>39.33</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="B56" s="21" t="str">
+      <c r="B57" s="21" t="str">
         <f>Assumptions!B54</f>
         <v>0</v>
       </c>
-      <c r="C56" s="21">
-        <f>B57</f>
+      <c r="C57" s="21">
+        <f>B58</f>
         <v>18273</v>
       </c>
-      <c r="D56" s="21">
-        <f>C57</f>
-        <v>147572</v>
-      </c>
-      <c r="E56" s="21">
-        <f>D57</f>
-        <v>351881</v>
-      </c>
-      <c r="F56" s="21">
-        <f>E57</f>
-        <v>616285</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="B57" s="30">
-        <f>B56+B47</f>
+      <c r="D57" s="21">
+        <f>C58</f>
+        <v>147019</v>
+      </c>
+      <c r="E57" s="21">
+        <f>D58</f>
+        <v>349924</v>
+      </c>
+      <c r="F57" s="21">
+        <f>E58</f>
+        <v>611844</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="B58" s="31">
+        <f>B57+B48</f>
         <v>18273</v>
       </c>
-      <c r="C57" s="30">
-        <f>C56+C47</f>
-        <v>147572</v>
-      </c>
-      <c r="D57" s="30">
-        <f>D56+D47</f>
-        <v>351881</v>
-      </c>
-      <c r="E57" s="30">
-        <f>E56+E47</f>
-        <v>616285</v>
-      </c>
-      <c r="F57" s="30">
-        <f>F56+F47</f>
-        <v>886530</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="B58" s="37">
-        <f>IF(B45=0,"",B57/B45*365)</f>
-        <v>40</v>
-      </c>
-      <c r="C58" s="37">
-        <f>IF(C45=0,"",C57/C45*365)</f>
-        <v>258</v>
-      </c>
-      <c r="D58" s="37">
-        <f>IF(D45=0,"",D57/D45*365)</f>
-        <v>589</v>
-      </c>
-      <c r="E58" s="37">
-        <f>IF(E45=0,"",E57/E45*365)</f>
-        <v>991</v>
-      </c>
-      <c r="F58" s="37">
-        <f>IF(F45=0,"",F57/F45*365)</f>
-        <v>1387</v>
+      <c r="C58" s="31">
+        <f>C57+C48</f>
+        <v>147019</v>
+      </c>
+      <c r="D58" s="31">
+        <f>D57+D48</f>
+        <v>349924</v>
+      </c>
+      <c r="E58" s="31">
+        <f>E57+E48</f>
+        <v>611844</v>
+      </c>
+      <c r="F58" s="31">
+        <f>F57+F48</f>
+        <v>878651</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -3673,108 +3665,108 @@
         <v>168</v>
       </c>
       <c r="B59" s="38">
-        <f>IF(B45=0,"",B57/(B45/12))</f>
-        <v>1.3</v>
+        <f>IF(B46=0,"",B58/B46*365)</f>
+        <v>40</v>
       </c>
       <c r="C59" s="38">
-        <f>IF(C45=0,"",C57/(C45/12))</f>
-        <v>8.5</v>
+        <f>IF(C46=0,"",C58/C46*365)</f>
+        <v>257</v>
       </c>
       <c r="D59" s="38">
-        <f>IF(D45=0,"",D57/(D45/12))</f>
-        <v>19.4</v>
+        <f>IF(D46=0,"",D58/D46*365)</f>
+        <v>585</v>
       </c>
       <c r="E59" s="38">
-        <f>IF(E45=0,"",E57/(E45/12))</f>
-        <v>32.6</v>
+        <f>IF(E46=0,"",E58/E46*365)</f>
+        <v>984</v>
       </c>
       <c r="F59" s="38">
-        <f>IF(F45=0,"",F57/(F45/12))</f>
-        <v>45.6</v>
+        <f>IF(F46=0,"",F58/F46*365)</f>
+        <v>1374</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="B60" s="33">
-        <f>IF(Assumptions!B12=0,"",B3/Assumptions!B12)</f>
+      <c r="B60" s="39">
+        <f>IF(B46=0,"",B58/(B46/12))</f>
+        <v>1.3</v>
+      </c>
+      <c r="C60" s="39">
+        <f>IF(C46=0,"",C58/(C46/12))</f>
+        <v>8.4</v>
+      </c>
+      <c r="D60" s="39">
+        <f>IF(D46=0,"",D58/(D46/12))</f>
+        <v>19.2</v>
+      </c>
+      <c r="E60" s="39">
+        <f>IF(E46=0,"",E58/(E46/12))</f>
+        <v>32.4</v>
+      </c>
+      <c r="F60" s="39">
+        <f>IF(F46=0,"",F58/(F46/12))</f>
+        <v>45.2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="B61" s="34">
+        <f>IF(Assumptions!B12=0,"",B4/Assumptions!B12)</f>
         <v>0.48</v>
       </c>
-      <c r="C60" s="33">
-        <f>IF(Assumptions!B12=0,"",C3/Assumptions!B12)</f>
+      <c r="C61" s="34">
+        <f>IF(Assumptions!B12=0,"",C4/Assumptions!B12)</f>
         <v>0.72</v>
       </c>
-      <c r="D60" s="33">
-        <f>IF(Assumptions!B12=0,"",D3/Assumptions!B12)</f>
+      <c r="D61" s="34">
+        <f>IF(Assumptions!B12=0,"",D4/Assumptions!B12)</f>
         <v>0.88</v>
       </c>
-      <c r="E60" s="33">
-        <f>IF(Assumptions!B12=0,"",E3/Assumptions!B12)</f>
+      <c r="E61" s="34">
+        <f>IF(Assumptions!B12=0,"",E4/Assumptions!B12)</f>
         <v>1</v>
       </c>
-      <c r="F60" s="33">
-        <f>IF(Assumptions!B12=0,"",F3/Assumptions!B12)</f>
+      <c r="F61" s="34">
+        <f>IF(Assumptions!B12=0,"",F4/Assumptions!B12)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="62" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="B62" s="12"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="12"/>
-      <c r="E62" s="12"/>
-      <c r="F62" s="12"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="13" t="s">
+    <row r="63" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="B63" s="13" t="str">
-        <f>IF(B54=0,"N/A",IF(B55&gt;=1.2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="C63" s="13" t="str">
-        <f>IF(C54=0,"N/A",IF(C55&gt;=1.2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="D63" s="13" t="str">
-        <f>IF(D54=0,"N/A",IF(D55&gt;=1.2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="E63" s="13" t="str">
-        <f>IF(E54=0,"N/A",IF(E55&gt;=1.2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="F63" s="13" t="str">
-        <f>IF(F54=0,"N/A",IF(F55&gt;=1.2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
+      <c r="B63" s="12"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="12"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="13" t="s">
         <v>172</v>
       </c>
       <c r="B64" s="13" t="str">
-        <f>IF(B47&gt;0,"PASS","FAIL")</f>
+        <f>IF(B55=0,"N/A",IF(B56&gt;=1.25,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
       <c r="C64" s="13" t="str">
-        <f>IF(C47&gt;0,"PASS","FAIL")</f>
+        <f>IF(C55=0,"N/A",IF(C56&gt;=1.25,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
       <c r="D64" s="13" t="str">
-        <f>IF(D47&gt;0,"PASS","FAIL")</f>
+        <f>IF(D55=0,"N/A",IF(D56&gt;=1.25,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
       <c r="E64" s="13" t="str">
-        <f>IF(E47&gt;0,"PASS","FAIL")</f>
+        <f>IF(E55=0,"N/A",IF(E56&gt;=1.25,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
       <c r="F64" s="13" t="str">
-        <f>IF(F47&gt;0,"PASS","FAIL")</f>
+        <f>IF(F55=0,"N/A",IF(F56&gt;=1.25,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
@@ -3783,23 +3775,23 @@
         <v>173</v>
       </c>
       <c r="B65" s="13" t="str">
-        <f>IF(Assumptions!B12=0,"N/A",IF(B3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
-        <v>FAIL</v>
+        <f>IF(B48&gt;0,"PASS","FAIL")</f>
+        <v>PASS</v>
       </c>
       <c r="C65" s="13" t="str">
-        <f>IF(Assumptions!B12=0,"N/A",IF(C3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
+        <f>IF(C48&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="D65" s="13" t="str">
-        <f>IF(Assumptions!B12=0,"N/A",IF(D3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
+        <f>IF(D48&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="E65" s="13" t="str">
-        <f>IF(Assumptions!B12=0,"N/A",IF(E3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
+        <f>IF(E48&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="F65" s="13" t="str">
-        <f>IF(Assumptions!B12=0,"N/A",IF(F3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
+        <f>IF(F48&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
@@ -3808,84 +3800,84 @@
         <v>174</v>
       </c>
       <c r="B66" s="13" t="str">
-        <f>IF(B45=0,"N/A",IF(B57/(B45/12)&gt;=2,"PASS","FAIL"))</f>
+        <f>IF(Assumptions!B12=0,"N/A",IF(B4/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
       <c r="C66" s="13" t="str">
-        <f>IF(C45=0,"N/A",IF(C57/(C45/12)&gt;=2,"PASS","FAIL"))</f>
+        <f>IF(Assumptions!B12=0,"N/A",IF(C4/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
       <c r="D66" s="13" t="str">
-        <f>IF(D45=0,"N/A",IF(D57/(D45/12)&gt;=2,"PASS","FAIL"))</f>
+        <f>IF(Assumptions!B12=0,"N/A",IF(D4/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
       <c r="E66" s="13" t="str">
-        <f>IF(E45=0,"N/A",IF(E57/(E45/12)&gt;=2,"PASS","FAIL"))</f>
+        <f>IF(Assumptions!B12=0,"N/A",IF(E4/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
       <c r="F66" s="13" t="str">
-        <f>IF(F45=0,"N/A",IF(F57/(F45/12)&gt;=2,"PASS","FAIL"))</f>
+        <f>IF(Assumptions!B12=0,"N/A",IF(F4/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="68" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="12" t="s">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="B68" s="12"/>
-      <c r="C68" s="12"/>
-      <c r="D68" s="12"/>
-      <c r="E68" s="12"/>
-      <c r="F68" s="12"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="13" t="s">
+      <c r="B67" s="13" t="str">
+        <f>IF(B46=0,"N/A",IF(B58/(B46/12)&gt;=2,"PASS","FAIL"))</f>
+        <v>FAIL</v>
+      </c>
+      <c r="C67" s="13" t="str">
+        <f>IF(C46=0,"N/A",IF(C58/(C46/12)&gt;=2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+      <c r="D67" s="13" t="str">
+        <f>IF(D46=0,"N/A",IF(D58/(D46/12)&gt;=2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+      <c r="E67" s="13" t="str">
+        <f>IF(E46=0,"N/A",IF(E58/(E46/12)&gt;=2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+      <c r="F67" s="13" t="str">
+        <f>IF(F46=0,"N/A",IF(F58/(F46/12)&gt;=2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="69" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="B69" s="21">
-        <f>IF(B3=0,"",B11/B3)</f>
-        <v>15389</v>
-      </c>
-      <c r="C69" s="21">
-        <f>IF(C3=0,"",C11/C3)</f>
-        <v>18786</v>
-      </c>
-      <c r="D69" s="21">
-        <f>IF(D3=0,"",D11/D3)</f>
-        <v>19203</v>
-      </c>
-      <c r="E69" s="21">
-        <f>IF(E3=0,"",E11/E3)</f>
-        <v>19653</v>
-      </c>
-      <c r="F69" s="21">
-        <f>IF(F3=0,"",F11/F3)</f>
-        <v>20145</v>
-      </c>
+      <c r="B69" s="12"/>
+      <c r="C69" s="12"/>
+      <c r="D69" s="12"/>
+      <c r="E69" s="12"/>
+      <c r="F69" s="12"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="13" t="s">
         <v>177</v>
       </c>
       <c r="B70" s="21">
-        <f>IF(B3=0,"",B45/B3)</f>
-        <v>13866</v>
+        <f>IF(B4=0,"",B12/B4)</f>
+        <v>15389</v>
       </c>
       <c r="C70" s="21">
-        <f>IF(C3=0,"",C45/C3)</f>
-        <v>11603</v>
+        <f>IF(C4=0,"",C12/C4)</f>
+        <v>18755</v>
       </c>
       <c r="D70" s="21">
-        <f>IF(D3=0,"",D45/D3)</f>
-        <v>9916</v>
+        <f>IF(D4=0,"",D12/D4)</f>
+        <v>19139</v>
       </c>
       <c r="E70" s="21">
-        <f>IF(E3=0,"",E45/E3)</f>
-        <v>9077</v>
+        <f>IF(E4=0,"",E12/E4)</f>
+        <v>19554</v>
       </c>
       <c r="F70" s="21">
-        <f>IF(F3=0,"",F45/F3)</f>
-        <v>9335</v>
+        <f>IF(F4=0,"",F12/F4)</f>
+        <v>20007</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3893,24 +3885,24 @@
         <v>178</v>
       </c>
       <c r="B71" s="21">
-        <f>B42+B44</f>
-        <v>125894</v>
+        <f>IF(B4=0,"",B46/B4)</f>
+        <v>13866</v>
       </c>
       <c r="C71" s="21">
-        <f>C42+C44</f>
-        <v>153963</v>
+        <f>IF(C4=0,"",C46/C4)</f>
+        <v>11603</v>
       </c>
       <c r="D71" s="21">
-        <f>D42+D44</f>
-        <v>158373</v>
+        <f>IF(D4=0,"",D46/D4)</f>
+        <v>9916</v>
       </c>
       <c r="E71" s="21">
-        <f>E42+E44</f>
-        <v>162915</v>
+        <f>IF(E4=0,"",E46/E4)</f>
+        <v>9077</v>
       </c>
       <c r="F71" s="21">
-        <f>F42+F44</f>
-        <v>167594</v>
+        <f>IF(F4=0,"",F46/F4)</f>
+        <v>9335</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -3918,24 +3910,24 @@
         <v>179</v>
       </c>
       <c r="B72" s="21">
-        <f>IF(B3=0,"",B43/B3)</f>
-        <v>3375</v>
+        <f>B43+B45</f>
+        <v>125894</v>
       </c>
       <c r="C72" s="21">
-        <f>IF(C3=0,"",C43/C3)</f>
-        <v>3049</v>
+        <f>C43+C45</f>
+        <v>153963</v>
       </c>
       <c r="D72" s="21">
-        <f>IF(D3=0,"",D43/D3)</f>
-        <v>2717</v>
+        <f>D43+D45</f>
+        <v>158373</v>
       </c>
       <c r="E72" s="21">
-        <f>IF(E3=0,"",E43/E3)</f>
-        <v>2560</v>
+        <f>E43+E45</f>
+        <v>162915</v>
       </c>
       <c r="F72" s="21">
-        <f>IF(F3=0,"",F43/F3)</f>
-        <v>2631</v>
+        <f>F43+F45</f>
+        <v>167594</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3943,65 +3935,91 @@
         <v>180</v>
       </c>
       <c r="B73" s="21">
-        <f>IF(B3=0,"",B69-B72)</f>
+        <f>IF(B4=0,"",B44/B4)</f>
+        <v>3375</v>
+      </c>
+      <c r="C73" s="21">
+        <f>IF(C4=0,"",C44/C4)</f>
+        <v>3049</v>
+      </c>
+      <c r="D73" s="21">
+        <f>IF(D4=0,"",D44/D4)</f>
+        <v>2717</v>
+      </c>
+      <c r="E73" s="21">
+        <f>IF(E4=0,"",E44/E4)</f>
+        <v>2560</v>
+      </c>
+      <c r="F73" s="21">
+        <f>IF(F4=0,"",F44/F4)</f>
+        <v>2631</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="B74" s="21">
+        <f>IF(B4=0,"",B70-B73)</f>
         <v>12014</v>
       </c>
-      <c r="C73" s="21">
-        <f>IF(C3=0,"",C69-C72)</f>
-        <v>15737</v>
-      </c>
-      <c r="D73" s="21">
-        <f>IF(D3=0,"",D69-D72)</f>
-        <v>16486</v>
-      </c>
-      <c r="E73" s="21">
-        <f>IF(E3=0,"",E69-E72)</f>
-        <v>17093</v>
-      </c>
-      <c r="F73" s="21">
-        <f>IF(F3=0,"",F69-F72)</f>
-        <v>17514</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="39" t="s">
-        <v>181</v>
-      </c>
-      <c r="B74" s="40">
-        <f>IF(B73&lt;=0,"N/A",ROUNDUP(B71/B73,0))</f>
+      <c r="C74" s="21">
+        <f>IF(C4=0,"",C70-C73)</f>
+        <v>15706</v>
+      </c>
+      <c r="D74" s="21">
+        <f>IF(D4=0,"",D70-D73)</f>
+        <v>16422</v>
+      </c>
+      <c r="E74" s="21">
+        <f>IF(E4=0,"",E70-E73)</f>
+        <v>16993</v>
+      </c>
+      <c r="F74" s="21">
+        <f>IF(F4=0,"",F70-F73)</f>
+        <v>17376</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="B75" s="41">
+        <f>IF(B74&lt;=0,"N/A",ROUNDUP(B72/B74,0))</f>
         <v>11</v>
       </c>
-      <c r="C74" s="40">
-        <f>IF(C73&lt;=0,"N/A",ROUNDUP(C71/C73,0))</f>
+      <c r="C75" s="41">
+        <f>IF(C74&lt;=0,"N/A",ROUNDUP(C72/C74,0))</f>
         <v>10</v>
       </c>
-      <c r="D74" s="40">
-        <f>IF(D73&lt;=0,"N/A",ROUNDUP(D71/D73,0))</f>
+      <c r="D75" s="41">
+        <f>IF(D74&lt;=0,"N/A",ROUNDUP(D72/D74,0))</f>
         <v>10</v>
       </c>
-      <c r="E74" s="40">
-        <f>IF(E73&lt;=0,"N/A",ROUNDUP(E71/E73,0))</f>
+      <c r="E75" s="41">
+        <f>IF(E74&lt;=0,"N/A",ROUNDUP(E72/E74,0))</f>
         <v>10</v>
       </c>
-      <c r="F74" s="40">
-        <f>IF(F73&lt;=0,"N/A",ROUNDUP(F71/F73,0))</f>
+      <c r="F75" s="41">
+        <f>IF(F74&lt;=0,"N/A",ROUNDUP(F72/F74,0))</f>
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="24" t="s">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="B76" s="24"/>
-      <c r="C76" s="24"/>
-      <c r="D76" s="24"/>
-      <c r="E76" s="24"/>
-      <c r="F76" s="24"/>
+      <c r="B77" s="24"/>
+      <c r="C77" s="24"/>
+      <c r="D77" s="24"/>
+      <c r="E77" s="24"/>
+      <c r="F77" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A77:F77"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
@@ -4027,7 +4045,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -4044,52 +4062,52 @@
       <c r="N1" s="8"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="25" t="s">
-        <v>183</v>
-      </c>
-      <c r="D2" s="25" t="s">
+      <c r="C2" s="26" t="s">
         <v>184</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="D2" s="26" t="s">
         <v>185</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="E2" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="F2" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="G2" s="26" t="s">
         <v>188</v>
       </c>
-      <c r="I2" s="25" t="s">
+      <c r="H2" s="26" t="s">
         <v>189</v>
       </c>
-      <c r="J2" s="25" t="s">
+      <c r="I2" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="K2" s="25" t="s">
+      <c r="J2" s="26" t="s">
         <v>191</v>
       </c>
-      <c r="L2" s="25" t="s">
+      <c r="K2" s="26" t="s">
         <v>192</v>
       </c>
-      <c r="M2" s="25" t="s">
+      <c r="L2" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="N2" s="25" t="s">
+      <c r="M2" s="26" t="s">
         <v>194</v>
+      </c>
+      <c r="N2" s="26" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -4332,57 +4350,57 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="B9" s="28">
+        <v>133</v>
+      </c>
+      <c r="B9" s="29">
         <f>SUM(B4:B8)</f>
         <v>155900</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="29">
         <f>SUM(C4:C8)</f>
         <v>7460</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="29">
         <f>SUM(D4:D8)</f>
         <v>7460</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="29">
         <f>SUM(E4:E8)</f>
         <v>7460</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="29">
         <f>SUM(F4:F8)</f>
         <v>7460</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="29">
         <f>SUM(G4:G8)</f>
         <v>7460</v>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="29">
         <f>SUM(H4:H8)</f>
         <v>7460</v>
       </c>
-      <c r="I9" s="28">
+      <c r="I9" s="29">
         <f>SUM(I4:I8)</f>
         <v>7460</v>
       </c>
-      <c r="J9" s="28">
+      <c r="J9" s="29">
         <f>SUM(J4:J8)</f>
         <v>7460</v>
       </c>
-      <c r="K9" s="28">
+      <c r="K9" s="29">
         <f>SUM(K4:K8)</f>
         <v>7460</v>
       </c>
-      <c r="L9" s="28">
+      <c r="L9" s="29">
         <f>SUM(L4:L8)</f>
         <v>-1440</v>
       </c>
-      <c r="M9" s="28" t="str">
+      <c r="M9" s="29" t="str">
         <f>SUM(M4:M8)</f>
         <v>0</v>
       </c>
-      <c r="N9" s="28">
+      <c r="N9" s="29">
         <f>SUM(B9:M9)</f>
         <v>221600</v>
       </c>
@@ -4394,7 +4412,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -4547,57 +4565,57 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="B15" s="28">
+        <v>138</v>
+      </c>
+      <c r="B15" s="29">
         <f>SUM(B12:B14)</f>
         <v>11893</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="29">
         <f>SUM(C12:C14)</f>
         <v>11893</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="29">
         <f>SUM(D12:D14)</f>
         <v>11893</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="29">
         <f>SUM(E12:E14)</f>
         <v>11893</v>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="29">
         <f>SUM(F12:F14)</f>
         <v>11893</v>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="29">
         <f>SUM(G12:G14)</f>
         <v>11893</v>
       </c>
-      <c r="H15" s="28">
+      <c r="H15" s="29">
         <f>SUM(H12:H14)</f>
         <v>11893</v>
       </c>
-      <c r="I15" s="28">
+      <c r="I15" s="29">
         <f>SUM(I12:I14)</f>
         <v>11893</v>
       </c>
-      <c r="J15" s="28">
+      <c r="J15" s="29">
         <f>SUM(J12:J14)</f>
         <v>11893</v>
       </c>
-      <c r="K15" s="28">
+      <c r="K15" s="29">
         <f>SUM(K12:K14)</f>
         <v>11893</v>
       </c>
-      <c r="L15" s="28" t="str">
+      <c r="L15" s="29" t="str">
         <f>SUM(L12:L14)</f>
         <v>0</v>
       </c>
-      <c r="M15" s="28" t="str">
+      <c r="M15" s="29" t="str">
         <f>SUM(M12:M14)</f>
         <v>0</v>
       </c>
-      <c r="N15" s="28">
+      <c r="N15" s="29">
         <f>SUM(B15:M15)</f>
         <v>118934</v>
       </c>
@@ -4645,7 +4663,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B19" s="21">
         <v>500</v>
@@ -4689,46 +4707,46 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="B20" s="30">
+      <c r="A20" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="B20" s="31">
         <v>500</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="31">
         <v>500</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="31">
         <v>500</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="31">
         <v>500</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="31">
         <v>500</v>
       </c>
-      <c r="G20" s="30">
+      <c r="G20" s="31">
         <v>500</v>
       </c>
-      <c r="H20" s="30">
+      <c r="H20" s="31">
         <v>500</v>
       </c>
-      <c r="I20" s="30">
+      <c r="I20" s="31">
         <v>500</v>
       </c>
-      <c r="J20" s="30">
+      <c r="J20" s="31">
         <v>500</v>
       </c>
-      <c r="K20" s="30">
+      <c r="K20" s="31">
         <v>500</v>
       </c>
-      <c r="L20" s="30">
-        <v>0</v>
-      </c>
-      <c r="M20" s="30">
-        <v>0</v>
-      </c>
-      <c r="N20" s="30">
+      <c r="L20" s="31">
+        <v>0</v>
+      </c>
+      <c r="M20" s="31">
+        <v>0</v>
+      </c>
+      <c r="N20" s="31">
         <f>SUM(B20:M20)</f>
         <v>5000</v>
       </c>
@@ -4753,7 +4771,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B22" s="21">
         <v>300</v>
@@ -4797,46 +4815,46 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="B23" s="30">
+      <c r="A23" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="B23" s="31">
         <v>300</v>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="31">
         <v>300</v>
       </c>
-      <c r="D23" s="30">
+      <c r="D23" s="31">
         <v>300</v>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="31">
         <v>300</v>
       </c>
-      <c r="F23" s="30">
+      <c r="F23" s="31">
         <v>300</v>
       </c>
-      <c r="G23" s="30">
+      <c r="G23" s="31">
         <v>300</v>
       </c>
-      <c r="H23" s="30">
+      <c r="H23" s="31">
         <v>300</v>
       </c>
-      <c r="I23" s="30">
+      <c r="I23" s="31">
         <v>300</v>
       </c>
-      <c r="J23" s="30">
+      <c r="J23" s="31">
         <v>300</v>
       </c>
-      <c r="K23" s="30">
+      <c r="K23" s="31">
         <v>300</v>
       </c>
-      <c r="L23" s="30">
-        <v>0</v>
-      </c>
-      <c r="M23" s="30">
-        <v>0</v>
-      </c>
-      <c r="N23" s="30">
+      <c r="L23" s="31">
+        <v>0</v>
+      </c>
+      <c r="M23" s="31">
+        <v>0</v>
+      </c>
+      <c r="N23" s="31">
         <f>SUM(B23:M23)</f>
         <v>3000</v>
       </c>
@@ -4861,7 +4879,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B25" s="21">
         <v>2500</v>
@@ -4906,7 +4924,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B26" s="21">
         <v>300</v>
@@ -4951,7 +4969,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B27" s="21">
         <v>200</v>
@@ -4995,46 +5013,46 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="B28" s="30">
+      <c r="A28" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="B28" s="31">
         <v>3000</v>
       </c>
-      <c r="C28" s="30">
+      <c r="C28" s="31">
         <v>3000</v>
       </c>
-      <c r="D28" s="30">
+      <c r="D28" s="31">
         <v>3000</v>
       </c>
-      <c r="E28" s="30">
+      <c r="E28" s="31">
         <v>3000</v>
       </c>
-      <c r="F28" s="30">
+      <c r="F28" s="31">
         <v>3000</v>
       </c>
-      <c r="G28" s="30">
+      <c r="G28" s="31">
         <v>3000</v>
       </c>
-      <c r="H28" s="30">
+      <c r="H28" s="31">
         <v>3000</v>
       </c>
-      <c r="I28" s="30">
+      <c r="I28" s="31">
         <v>3000</v>
       </c>
-      <c r="J28" s="30">
+      <c r="J28" s="31">
         <v>3000</v>
       </c>
-      <c r="K28" s="30">
+      <c r="K28" s="31">
         <v>3000</v>
       </c>
-      <c r="L28" s="30">
-        <v>0</v>
-      </c>
-      <c r="M28" s="30">
-        <v>0</v>
-      </c>
-      <c r="N28" s="30">
+      <c r="L28" s="31">
+        <v>0</v>
+      </c>
+      <c r="M28" s="31">
+        <v>0</v>
+      </c>
+      <c r="N28" s="31">
         <f>SUM(B28:M28)</f>
         <v>30000</v>
       </c>
@@ -5059,7 +5077,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B30" s="21">
         <v>250</v>
@@ -5103,103 +5121,103 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="B31" s="30">
+      <c r="A31" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="B31" s="31">
         <v>250</v>
       </c>
-      <c r="C31" s="30">
+      <c r="C31" s="31">
         <v>250</v>
       </c>
-      <c r="D31" s="30">
+      <c r="D31" s="31">
         <v>250</v>
       </c>
-      <c r="E31" s="30">
+      <c r="E31" s="31">
         <v>250</v>
       </c>
-      <c r="F31" s="30">
+      <c r="F31" s="31">
         <v>250</v>
       </c>
-      <c r="G31" s="30">
+      <c r="G31" s="31">
         <v>250</v>
       </c>
-      <c r="H31" s="30">
+      <c r="H31" s="31">
         <v>250</v>
       </c>
-      <c r="I31" s="30">
+      <c r="I31" s="31">
         <v>250</v>
       </c>
-      <c r="J31" s="30">
+      <c r="J31" s="31">
         <v>250</v>
       </c>
-      <c r="K31" s="30">
+      <c r="K31" s="31">
         <v>250</v>
       </c>
-      <c r="L31" s="30">
-        <v>0</v>
-      </c>
-      <c r="M31" s="30">
-        <v>0</v>
-      </c>
-      <c r="N31" s="30">
+      <c r="L31" s="31">
+        <v>0</v>
+      </c>
+      <c r="M31" s="31">
+        <v>0</v>
+      </c>
+      <c r="N31" s="31">
         <f>SUM(B31:M31)</f>
         <v>2500</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="B32" s="28">
+        <v>149</v>
+      </c>
+      <c r="B32" s="29">
         <f>B20+B23+B28+B31</f>
         <v>4050</v>
       </c>
-      <c r="C32" s="28">
+      <c r="C32" s="29">
         <f>C20+C23+C28+C31</f>
         <v>4050</v>
       </c>
-      <c r="D32" s="28">
+      <c r="D32" s="29">
         <f>D20+D23+D28+D31</f>
         <v>4050</v>
       </c>
-      <c r="E32" s="28">
+      <c r="E32" s="29">
         <f>E20+E23+E28+E31</f>
         <v>4050</v>
       </c>
-      <c r="F32" s="28">
+      <c r="F32" s="29">
         <f>F20+F23+F28+F31</f>
         <v>4050</v>
       </c>
-      <c r="G32" s="28">
+      <c r="G32" s="29">
         <f>G20+G23+G28+G31</f>
         <v>4050</v>
       </c>
-      <c r="H32" s="28">
+      <c r="H32" s="29">
         <f>H20+H23+H28+H31</f>
         <v>4050</v>
       </c>
-      <c r="I32" s="28">
+      <c r="I32" s="29">
         <f>I20+I23+I28+I31</f>
         <v>4050</v>
       </c>
-      <c r="J32" s="28">
+      <c r="J32" s="29">
         <f>J20+J23+J28+J31</f>
         <v>4050</v>
       </c>
-      <c r="K32" s="28">
+      <c r="K32" s="29">
         <f>K20+K23+K28+K31</f>
         <v>4050</v>
       </c>
-      <c r="L32" s="28" t="str">
+      <c r="L32" s="29" t="str">
         <f>L20+L23+L28+L31</f>
         <v>0</v>
       </c>
-      <c r="M32" s="28" t="str">
+      <c r="M32" s="29" t="str">
         <f>M20+M23+M28+M31</f>
         <v>0</v>
       </c>
-      <c r="N32" s="28">
+      <c r="N32" s="29">
         <f>SUM(B32:M32)</f>
         <v>40500</v>
       </c>
@@ -5210,8 +5228,8 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="26" t="s">
-        <v>201</v>
+      <c r="A34" s="27" t="s">
+        <v>202</v>
       </c>
       <c r="B34" s="21">
         <v>580</v>
@@ -5261,7 +5279,7 @@
     </row>
     <row r="36" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
@@ -5278,179 +5296,179 @@
       <c r="N36" s="12"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="26" t="s">
-        <v>156</v>
-      </c>
-      <c r="B37" s="30">
+      <c r="A37" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="B37" s="31">
         <f>B15+B32+B34</f>
         <v>16523</v>
       </c>
-      <c r="C37" s="30">
+      <c r="C37" s="31">
         <f>C15+C32+C34</f>
         <v>16523</v>
       </c>
-      <c r="D37" s="30">
+      <c r="D37" s="31">
         <f>D15+D32+D34</f>
         <v>16523</v>
       </c>
-      <c r="E37" s="30">
+      <c r="E37" s="31">
         <f>E15+E32+E34</f>
         <v>16523</v>
       </c>
-      <c r="F37" s="30">
+      <c r="F37" s="31">
         <f>F15+F32+F34</f>
         <v>16523</v>
       </c>
-      <c r="G37" s="30">
+      <c r="G37" s="31">
         <f>G15+G32+G34</f>
         <v>16523</v>
       </c>
-      <c r="H37" s="30">
+      <c r="H37" s="31">
         <f>H15+H32+H34</f>
         <v>16523</v>
       </c>
-      <c r="I37" s="30">
+      <c r="I37" s="31">
         <f>I15+I32+I34</f>
         <v>16523</v>
       </c>
-      <c r="J37" s="30">
+      <c r="J37" s="31">
         <f>J15+J32+J34</f>
         <v>16523</v>
       </c>
-      <c r="K37" s="30">
+      <c r="K37" s="31">
         <f>K15+K32+K34</f>
         <v>16523</v>
       </c>
-      <c r="L37" s="30">
+      <c r="L37" s="31">
         <f>L15+L32+L34</f>
         <v>580</v>
       </c>
-      <c r="M37" s="30">
+      <c r="M37" s="31">
         <f>M15+M32+M34</f>
         <v>580</v>
       </c>
-      <c r="N37" s="30">
+      <c r="N37" s="31">
         <f>SUM(B37:M37)</f>
         <v>166390</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="B38" s="30">
+      <c r="A38" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="B38" s="31">
         <f>B9-B37</f>
         <v>139377</v>
       </c>
-      <c r="C38" s="30">
+      <c r="C38" s="31">
         <f>C9-C37</f>
         <v>-9063</v>
       </c>
-      <c r="D38" s="30">
+      <c r="D38" s="31">
         <f>D9-D37</f>
         <v>-9063</v>
       </c>
-      <c r="E38" s="30">
+      <c r="E38" s="31">
         <f>E9-E37</f>
         <v>-9063</v>
       </c>
-      <c r="F38" s="30">
+      <c r="F38" s="31">
         <f>F9-F37</f>
         <v>-9063</v>
       </c>
-      <c r="G38" s="30">
+      <c r="G38" s="31">
         <f>G9-G37</f>
         <v>-9063</v>
       </c>
-      <c r="H38" s="30">
+      <c r="H38" s="31">
         <f>H9-H37</f>
         <v>-9063</v>
       </c>
-      <c r="I38" s="30">
+      <c r="I38" s="31">
         <f>I9-I37</f>
         <v>-9063</v>
       </c>
-      <c r="J38" s="30">
+      <c r="J38" s="31">
         <f>J9-J37</f>
         <v>-9063</v>
       </c>
-      <c r="K38" s="30">
+      <c r="K38" s="31">
         <f>K9-K37</f>
         <v>-9063</v>
       </c>
-      <c r="L38" s="30">
+      <c r="L38" s="31">
         <f>L9-L37</f>
         <v>-2020</v>
       </c>
-      <c r="M38" s="30">
+      <c r="M38" s="31">
         <f>M9-M37</f>
         <v>-580</v>
       </c>
-      <c r="N38" s="30">
+      <c r="N38" s="31">
         <f>SUM(B38:M38)</f>
         <v>55210</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="B39" s="30">
+      <c r="A39" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="B39" s="31">
         <f>0+B38</f>
         <v>139377</v>
       </c>
-      <c r="C39" s="30">
+      <c r="C39" s="31">
         <f>B39+C38</f>
         <v>130314</v>
       </c>
-      <c r="D39" s="30">
+      <c r="D39" s="31">
         <f>C39+D38</f>
         <v>121251</v>
       </c>
-      <c r="E39" s="30">
+      <c r="E39" s="31">
         <f>D39+E38</f>
         <v>112188</v>
       </c>
-      <c r="F39" s="30">
+      <c r="F39" s="31">
         <f>E39+F38</f>
         <v>103125</v>
       </c>
-      <c r="G39" s="30">
+      <c r="G39" s="31">
         <f>F39+G38</f>
         <v>94062</v>
       </c>
-      <c r="H39" s="30">
+      <c r="H39" s="31">
         <f>G39+H38</f>
         <v>84999</v>
       </c>
-      <c r="I39" s="30">
+      <c r="I39" s="31">
         <f>H39+I38</f>
         <v>75936</v>
       </c>
-      <c r="J39" s="30">
+      <c r="J39" s="31">
         <f>I39+J38</f>
         <v>66873</v>
       </c>
-      <c r="K39" s="30">
+      <c r="K39" s="31">
         <f>J39+K38</f>
         <v>57810</v>
       </c>
-      <c r="L39" s="30">
+      <c r="L39" s="31">
         <f>K39+L38</f>
         <v>55790</v>
       </c>
-      <c r="M39" s="30">
+      <c r="M39" s="31">
         <f>L39+M38</f>
         <v>55210</v>
       </c>
-      <c r="N39" s="30">
+      <c r="N39" s="31">
         <f>M39</f>
         <v>55210</v>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
@@ -5465,16 +5483,16 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="B43" s="30">
+        <v>207</v>
+      </c>
+      <c r="B43" s="31">
         <f>M39</f>
         <v>55210</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B44" s="21">
         <f>MIN(B39:M39)</f>
@@ -5531,7 +5549,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -5541,388 +5559,388 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="41" t="s">
-        <v>209</v>
-      </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
+      <c r="B3" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="42" t="s">
-        <v>210</v>
-      </c>
-      <c r="D4" s="43" t="s">
+      <c r="B4" s="43" t="s">
         <v>211</v>
       </c>
-      <c r="F4" s="44" t="s">
+      <c r="D4" s="44" t="s">
         <v>212</v>
+      </c>
+      <c r="F4" s="45" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="C7" s="45">
+        <v>221</v>
+      </c>
+      <c r="C7" s="46">
         <v>12</v>
       </c>
-      <c r="D7" s="45">
+      <c r="D7" s="46">
         <v>18</v>
       </c>
-      <c r="E7" s="45">
+      <c r="E7" s="46">
         <v>22</v>
       </c>
-      <c r="F7" s="45">
+      <c r="F7" s="46">
         <v>25</v>
       </c>
-      <c r="G7" s="45">
+      <c r="G7" s="46">
         <v>25</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="C8" s="46">
+        <v>222</v>
+      </c>
+      <c r="C8" s="47">
         <v>221600</v>
       </c>
-      <c r="D8" s="46">
-        <v>338147.49999999994</v>
-      </c>
-      <c r="E8" s="46">
-        <v>422456.3124999999</v>
-      </c>
-      <c r="F8" s="46">
-        <v>491331.3476562498</v>
-      </c>
-      <c r="G8" s="46">
-        <v>503614.631347656</v>
+      <c r="D8" s="47">
+        <v>337593.99999999994</v>
+      </c>
+      <c r="E8" s="47">
+        <v>421052.1521874999</v>
+      </c>
+      <c r="F8" s="47">
+        <v>488847.26385986316</v>
+      </c>
+      <c r="G8" s="47">
+        <v>500176.9311411085</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="C9" s="46">
+        <v>223</v>
+      </c>
+      <c r="C9" s="47">
         <v>118934.16666666667</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="47">
         <v>147002.63</v>
       </c>
-      <c r="E9" s="46">
+      <c r="E9" s="47">
         <v>151412.7089</v>
       </c>
-      <c r="F9" s="46">
+      <c r="F9" s="47">
         <v>155955.090167</v>
       </c>
-      <c r="G9" s="46">
+      <c r="G9" s="47">
         <v>160633.74287201</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="C10" s="46">
-        <v>48600</v>
-      </c>
-      <c r="D10" s="46">
-        <v>54885</v>
-      </c>
-      <c r="E10" s="46">
-        <v>59773.625</v>
-      </c>
-      <c r="F10" s="46">
-        <v>64011.63812499999</v>
-      </c>
-      <c r="G10" s="46">
-        <v>65775.83812812499</v>
+        <v>224</v>
+      </c>
+      <c r="C10" s="47">
+        <v>37600</v>
+      </c>
+      <c r="D10" s="47">
+        <v>48735</v>
+      </c>
+      <c r="E10" s="47">
+        <v>53469.875</v>
+      </c>
+      <c r="F10" s="47">
+        <v>57550.29437499999</v>
+      </c>
+      <c r="G10" s="47">
+        <v>59152.96078437499</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="C11" s="46">
+        <v>165</v>
+      </c>
+      <c r="C11" s="47">
         <v>6959.808550594178</v>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="47">
         <v>6959.808550594178</v>
       </c>
-      <c r="E11" s="46">
+      <c r="E11" s="47">
         <v>6959.808550594178</v>
       </c>
-      <c r="F11" s="46">
+      <c r="F11" s="47">
         <v>6959.808550594178</v>
       </c>
-      <c r="G11" s="46">
+      <c r="G11" s="47">
         <v>6959.808550594178</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="C12" s="47">
-        <v>47106.02478273915</v>
-      </c>
-      <c r="D12" s="47">
-        <v>129300.06144940577</v>
-      </c>
-      <c r="E12" s="47">
-        <v>204310.17004940574</v>
-      </c>
-      <c r="F12" s="47">
-        <v>264404.8108136556</v>
-      </c>
-      <c r="G12" s="47">
-        <v>270245.2417969268</v>
+      <c r="B12" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="C12" s="48">
+        <v>58106.02478273915</v>
+      </c>
+      <c r="D12" s="48">
+        <v>134896.56144940577</v>
+      </c>
+      <c r="E12" s="48">
+        <v>209209.75973690578</v>
+      </c>
+      <c r="F12" s="48">
+        <v>268382.070767269</v>
+      </c>
+      <c r="G12" s="48">
+        <v>273430.41893412935</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="C13" s="47">
-        <v>47106.02478273915</v>
-      </c>
-      <c r="D13" s="47">
-        <v>176406.0862321449</v>
-      </c>
-      <c r="E13" s="47">
-        <v>380716.2562815506</v>
-      </c>
-      <c r="F13" s="47">
-        <v>645121.0670952062</v>
-      </c>
-      <c r="G13" s="47">
-        <v>915366.3088921331</v>
+      <c r="B13" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="C13" s="48">
+        <v>58106.02478273915</v>
+      </c>
+      <c r="D13" s="48">
+        <v>193002.5862321449</v>
+      </c>
+      <c r="E13" s="48">
+        <v>402212.34596905066</v>
+      </c>
+      <c r="F13" s="48">
+        <v>670594.4167363197</v>
+      </c>
+      <c r="G13" s="48">
+        <v>944024.8356704491</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="C14" s="48">
-        <v>0.21257231400153045</v>
-      </c>
-      <c r="D14" s="48">
-        <v>0.3823776944954666</v>
-      </c>
-      <c r="E14" s="48">
-        <v>0.4836243748858784</v>
-      </c>
-      <c r="F14" s="48">
-        <v>0.5381395102814428</v>
-      </c>
-      <c r="G14" s="48">
-        <v>0.5366111804054611</v>
+      <c r="B14" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="C14" s="49">
+        <v>0.26221130317120556</v>
+      </c>
+      <c r="D14" s="49">
+        <v>0.39958222435649265</v>
+      </c>
+      <c r="E14" s="49">
+        <v>0.4968737450930829</v>
+      </c>
+      <c r="F14" s="49">
+        <v>0.5490100704423817</v>
+      </c>
+      <c r="G14" s="49">
+        <v>0.5466673928969945</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="C15" s="49">
+      <c r="B15" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="C15" s="50">
         <v>18466.666666666668</v>
       </c>
-      <c r="D15" s="49">
-        <v>18785.97222222222</v>
-      </c>
-      <c r="E15" s="49">
-        <v>19202.559659090904</v>
-      </c>
-      <c r="F15" s="49">
-        <v>19653.253906249993</v>
-      </c>
-      <c r="G15" s="49">
-        <v>20144.58525390624</v>
-      </c>
-      <c r="H15" s="50" t="s">
-        <v>227</v>
+      <c r="D15" s="50">
+        <v>18755.22222222222</v>
+      </c>
+      <c r="E15" s="50">
+        <v>19138.734190340907</v>
+      </c>
+      <c r="F15" s="50">
+        <v>19553.890554394526</v>
+      </c>
+      <c r="G15" s="50">
+        <v>20007.07724564434</v>
+      </c>
+      <c r="H15" s="51" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="C16" s="51">
-        <v>14541.164601438404</v>
-      </c>
-      <c r="D16" s="51">
-        <v>11602.63547503301</v>
-      </c>
-      <c r="E16" s="51">
-        <v>9915.73374775428</v>
-      </c>
-      <c r="F16" s="51">
-        <v>9077.061473703767</v>
-      </c>
-      <c r="G16" s="51">
-        <v>9334.775582029166</v>
+      <c r="B16" s="27" t="s">
+        <v>229</v>
+      </c>
+      <c r="C16" s="52">
+        <v>13624.497934771738</v>
+      </c>
+      <c r="D16" s="52">
+        <v>11260.968808366342</v>
+      </c>
+      <c r="E16" s="52">
+        <v>9629.199656845189</v>
+      </c>
+      <c r="F16" s="52">
+        <v>8818.607723703766</v>
+      </c>
+      <c r="G16" s="52">
+        <v>9069.860488279168</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="C17" s="46">
+        <v>230</v>
+      </c>
+      <c r="C17" s="47">
         <v>500</v>
       </c>
-      <c r="D17" s="46">
+      <c r="D17" s="47">
         <v>512.5</v>
       </c>
-      <c r="E17" s="46">
+      <c r="E17" s="47">
         <v>525.3125</v>
       </c>
-      <c r="F17" s="46">
+      <c r="F17" s="47">
         <v>538.4453124999998</v>
       </c>
-      <c r="G17" s="46">
+      <c r="G17" s="47">
         <v>551.9064453124997</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="C18" s="52">
-        <v>3000</v>
-      </c>
-      <c r="D18" s="52">
-        <v>2058.3333333333335</v>
-      </c>
-      <c r="E18" s="49">
-        <v>1733.215909090909</v>
-      </c>
-      <c r="F18" s="49">
-        <v>1569.72615</v>
-      </c>
-      <c r="G18" s="49">
-        <v>1615.5256657500001</v>
-      </c>
-      <c r="H18" s="50" t="s">
         <v>231</v>
       </c>
+      <c r="C18" s="53">
+        <v>2083.3333333333335</v>
+      </c>
+      <c r="D18" s="50">
+        <v>1716.6666666666667</v>
+      </c>
+      <c r="E18" s="50">
+        <v>1446.6818181818182</v>
+      </c>
+      <c r="F18" s="50">
+        <v>1311.2723999999998</v>
+      </c>
+      <c r="G18" s="50">
+        <v>1350.610572</v>
+      </c>
+      <c r="H18" s="51" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="26" t="s">
-        <v>232</v>
-      </c>
-      <c r="C19" s="53">
-        <v>3925.5020652282624</v>
-      </c>
-      <c r="D19" s="53">
-        <v>7183.336747189209</v>
-      </c>
-      <c r="E19" s="53">
-        <v>9286.825911336624</v>
-      </c>
-      <c r="F19" s="53">
-        <v>10576.192432546224</v>
-      </c>
-      <c r="G19" s="53">
-        <v>10809.809671877074</v>
+      <c r="B19" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="C19" s="54">
+        <v>4842.168731894929</v>
+      </c>
+      <c r="D19" s="54">
+        <v>7494.253413855876</v>
+      </c>
+      <c r="E19" s="54">
+        <v>9509.534533495716</v>
+      </c>
+      <c r="F19" s="54">
+        <v>10735.28283069076</v>
+      </c>
+      <c r="G19" s="54">
+        <v>10937.216757365175</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="26" t="s">
-        <v>233</v>
-      </c>
-      <c r="C20" s="48">
+      <c r="B20" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="C20" s="49">
         <v>0.5367065282791817</v>
       </c>
-      <c r="D20" s="48">
-        <v>0.4347293119127009</v>
-      </c>
-      <c r="E20" s="48">
-        <v>0.3584103359800075</v>
-      </c>
-      <c r="F20" s="48">
-        <v>0.31741327092386307</v>
-      </c>
-      <c r="G20" s="48">
-        <v>0.31896162834300396</v>
-      </c>
-      <c r="H20" s="50" t="s">
-        <v>234</v>
+      <c r="D20" s="49">
+        <v>0.43544206946805936</v>
+      </c>
+      <c r="E20" s="49">
+        <v>0.3596055930681337</v>
+      </c>
+      <c r="F20" s="49">
+        <v>0.31902621063193126</v>
+      </c>
+      <c r="G20" s="49">
+        <v>0.3211538415127196</v>
+      </c>
+      <c r="H20" s="51" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="26" t="s">
-        <v>235</v>
-      </c>
-      <c r="C21" s="54">
-        <v>0.1624548736462094</v>
-      </c>
-      <c r="D21" s="48">
-        <v>0.10956757036500346</v>
-      </c>
-      <c r="E21" s="48">
-        <v>0.09025962891725049</v>
-      </c>
-      <c r="F21" s="48">
-        <v>0.07987105633946989</v>
-      </c>
-      <c r="G21" s="48">
-        <v>0.08019652156585022</v>
-      </c>
-      <c r="H21" s="50" t="s">
+      <c r="B21" s="27" t="s">
         <v>236</v>
       </c>
+      <c r="C21" s="49">
+        <v>0.11281588447653429</v>
+      </c>
+      <c r="D21" s="49">
+        <v>0.09153006273808185</v>
+      </c>
+      <c r="E21" s="49">
+        <v>0.07558921106245059</v>
+      </c>
+      <c r="F21" s="49">
+        <v>0.06705941185220071</v>
+      </c>
+      <c r="G21" s="49">
+        <v>0.06750664054611155</v>
+      </c>
+      <c r="H21" s="51" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="C22" s="48">
-        <v>0.2439793922984356</v>
-      </c>
-      <c r="D22" s="48">
-        <v>0.40295986219031626</v>
-      </c>
-      <c r="E22" s="48">
-        <v>0.5000989980472832</v>
-      </c>
-      <c r="F22" s="48">
-        <v>0.5523047138325573</v>
-      </c>
-      <c r="G22" s="48">
-        <v>0.5504308911870363</v>
-      </c>
-      <c r="H22" s="50" t="s">
+      <c r="B22" s="27" t="s">
         <v>238</v>
       </c>
+      <c r="C22" s="49">
+        <v>0.2936183814681107</v>
+      </c>
+      <c r="D22" s="49">
+        <v>0.4201981374076552</v>
+      </c>
+      <c r="E22" s="49">
+        <v>0.5134033092205568</v>
+      </c>
+      <c r="F22" s="49">
+        <v>0.5632472546615191</v>
+      </c>
+      <c r="G22" s="49">
+        <v>0.5605820861130851</v>
+      </c>
+      <c r="H22" s="51" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="26" t="s">
-        <v>239</v>
+      <c r="B23" s="27" t="s">
+        <v>240</v>
       </c>
       <c r="C23" s="55">
         <v>3</v>
@@ -5939,253 +5957,253 @@
       <c r="G23" s="55">
         <v>3</v>
       </c>
-      <c r="H23" s="50" t="s">
-        <v>240</v>
+      <c r="H23" s="51" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="26" t="s">
-        <v>241</v>
+      <c r="B24" s="27" t="s">
+        <v>242</v>
       </c>
       <c r="C24" s="56">
-        <v>7.768293185121821</v>
+        <v>9.348796430295266</v>
       </c>
       <c r="D24" s="56">
-        <v>19.57810606562835</v>
+        <v>20.382223012138642</v>
       </c>
       <c r="E24" s="56">
-        <v>30.35571698045677</v>
+        <v>31.059700380557874</v>
       </c>
       <c r="F24" s="56">
-        <v>38.99024195731399</v>
+        <v>39.561703072185296</v>
       </c>
       <c r="G24" s="56">
-        <v>39.82940742297506</v>
-      </c>
-      <c r="H24" s="50" t="s">
-        <v>242</v>
+        <v>40.287060404956954</v>
+      </c>
+      <c r="H24" s="51" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="C25" s="34" t="str">
-        <f>IF('5-Year Model'!B49&gt;=0,"✓ Break-even","")</f>
+      <c r="B25" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="C25" s="35" t="str">
+        <f>IF('5-Year Model'!B50&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
       <c r="D25" s="57" t="str">
-        <f>IF(AND('5-Year Model'!C49&gt;=0,'5-Year Model'!B49&lt;0),"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Model'!C50&gt;=0,'5-Year Model'!B50&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="E25" s="57" t="str">
-        <f>IF(AND('5-Year Model'!D49&gt;=0,'5-Year Model'!C49&lt;0),"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Model'!D50&gt;=0,'5-Year Model'!C50&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="F25" s="57" t="str">
-        <f>IF(AND('5-Year Model'!E49&gt;=0,'5-Year Model'!D49&lt;0),"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Model'!E50&gt;=0,'5-Year Model'!D50&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="G25" s="57" t="str">
-        <f>IF(AND('5-Year Model'!F49&gt;=0,'5-Year Model'!E49&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="50" t="s">
-        <v>214</v>
+        <f>IF(AND('5-Year Model'!F50&gt;=0,'5-Year Model'!E50&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="51" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="26" t="s">
-        <v>244</v>
+      <c r="B26" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="C26" s="58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" s="58">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E26" s="59">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F26" s="55">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G26" s="55">
-        <v>47</v>
-      </c>
-      <c r="H26" s="50" t="s">
-        <v>245</v>
+        <v>50</v>
+      </c>
+      <c r="H26" s="51" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="26" t="s">
-        <v>167</v>
+      <c r="B27" s="27" t="s">
+        <v>168</v>
       </c>
       <c r="C27" s="55">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="D27" s="55">
-        <v>308</v>
+        <v>348</v>
       </c>
       <c r="E27" s="55">
-        <v>637</v>
+        <v>693</v>
       </c>
       <c r="F27" s="55">
-        <v>1038</v>
+        <v>1110</v>
       </c>
       <c r="G27" s="55">
-        <v>1432</v>
-      </c>
-      <c r="H27" s="50" t="s">
-        <v>246</v>
+        <v>1520</v>
+      </c>
+      <c r="H27" s="51" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E29" s="12"/>
       <c r="F29" s="12" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="60" t="s">
-        <v>251</v>
-      </c>
-      <c r="C30" s="34" t="s">
         <v>252</v>
       </c>
+      <c r="C30" s="35" t="s">
+        <v>253</v>
+      </c>
       <c r="D30" s="61" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E30" s="61"/>
       <c r="F30" s="62" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G30" s="62"/>
       <c r="H30" s="62"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="60" t="s">
-        <v>255</v>
-      </c>
-      <c r="C31" s="34" t="s">
-        <v>252</v>
+        <v>256</v>
+      </c>
+      <c r="C31" s="35" t="s">
+        <v>253</v>
       </c>
       <c r="D31" s="61" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E31" s="61"/>
       <c r="F31" s="62" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G31" s="62"/>
       <c r="H31" s="62"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
-        <v>258</v>
-      </c>
-      <c r="C32" s="34" t="s">
-        <v>252</v>
+        <v>259</v>
+      </c>
+      <c r="C32" s="35" t="s">
+        <v>253</v>
       </c>
       <c r="D32" s="61" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E32" s="61"/>
       <c r="F32" s="62" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G32" s="62"/>
       <c r="H32" s="62"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="60" t="s">
-        <v>261</v>
-      </c>
-      <c r="C33" s="34" t="s">
-        <v>252</v>
+        <v>262</v>
+      </c>
+      <c r="C33" s="35" t="s">
+        <v>253</v>
       </c>
       <c r="D33" s="61" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E33" s="61"/>
       <c r="F33" s="62" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G33" s="62"/>
       <c r="H33" s="62"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="60" t="s">
-        <v>264</v>
-      </c>
-      <c r="C34" s="34" t="s">
-        <v>252</v>
+        <v>265</v>
+      </c>
+      <c r="C34" s="35" t="s">
+        <v>253</v>
       </c>
       <c r="D34" s="61" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E34" s="61"/>
       <c r="F34" s="62" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G34" s="62"/>
       <c r="H34" s="62"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="60" t="s">
-        <v>267</v>
-      </c>
-      <c r="C35" s="34" t="s">
-        <v>252</v>
+        <v>268</v>
+      </c>
+      <c r="C35" s="35" t="s">
+        <v>253</v>
       </c>
       <c r="D35" s="61" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E35" s="61"/>
       <c r="F35" s="62" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G35" s="62"/>
       <c r="H35" s="62"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="60" t="s">
-        <v>270</v>
-      </c>
-      <c r="C36" s="34" t="s">
-        <v>252</v>
+        <v>271</v>
+      </c>
+      <c r="C36" s="35" t="s">
+        <v>253</v>
       </c>
       <c r="D36" s="61" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E36" s="61"/>
       <c r="F36" s="62" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G36" s="62"/>
       <c r="H36" s="62"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="60" t="s">
-        <v>273</v>
-      </c>
-      <c r="C38" s="26" t="s">
         <v>274</v>
       </c>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="26"/>
+      <c r="C38" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40" s="63" t="s">
@@ -6303,10 +6321,10 @@
       <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C24&gt;=1.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C24&lt;1.15</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
@@ -8,7 +8,8 @@
     <sheet sheetId="2" name="Assumptions" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="5-Year Model" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Year 1 Pro Forma" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Financial Health" state="visible" r:id="rId8"/>
+    <sheet sheetId="5" name="Decision History" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Financial Health" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Instructions'!$A1:$B37</definedName>
@@ -19,15 +20,17 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N46</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H40</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Decision History'!$A1:$H4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Decision History'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Financial Health'!$A1:$H40</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="279">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -654,6 +657,15 @@
   </si>
   <si>
     <t>Minimum Cash Month</t>
+  </si>
+  <si>
+    <t>Decision History</t>
+  </si>
+  <si>
+    <t>No decisions have been tracked with an outcome yet. As the team marks saved scenarios as Pursued, Declined, or On hold, those outcomes (and any retrospective notes) will appear here so reviewers can see what actually happened versus what was modeled.</t>
+  </si>
+  <si>
+    <t>Once decisions are saved with a Pursued / Declined / On hold outcome inside the planner, they will be summarized here.</t>
   </si>
   <si>
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
@@ -1074,7 +1086,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1129,6 +1141,13 @@
     <xf numFmtId="168" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5537,6 +5556,73 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="B1:H4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="42" t="s">
+        <v>209</v>
+      </c>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+    </row>
+    <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="43" t="s">
+        <v>210</v>
+      </c>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="44" t="s">
+        <v>211</v>
+      </c>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B4:H4"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;10&amp;BBright Horizons Microschool&amp;R&amp;8&amp;IDecision History</oddHeader>
+    <oddFooter>&amp;L&amp;8Built by SchoolStack Budget  •  budget.schoolstack.ai&amp;C&amp;8Page &amp;P of &amp;N&amp;R&amp;8&amp;D</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -5549,7 +5635,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -5559,127 +5645,127 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="42" t="s">
-        <v>210</v>
-      </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
+      <c r="B3" s="45" t="s">
+        <v>213</v>
+      </c>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="43" t="s">
-        <v>211</v>
-      </c>
-      <c r="D4" s="44" t="s">
-        <v>212</v>
-      </c>
-      <c r="F4" s="45" t="s">
-        <v>213</v>
+      <c r="B4" s="46" t="s">
+        <v>214</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>215</v>
+      </c>
+      <c r="F4" s="48" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="C7" s="46">
+        <v>224</v>
+      </c>
+      <c r="C7" s="49">
         <v>12</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="49">
         <v>18</v>
       </c>
-      <c r="E7" s="46">
+      <c r="E7" s="49">
         <v>22</v>
       </c>
-      <c r="F7" s="46">
+      <c r="F7" s="49">
         <v>25</v>
       </c>
-      <c r="G7" s="46">
+      <c r="G7" s="49">
         <v>25</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="C8" s="47">
+        <v>225</v>
+      </c>
+      <c r="C8" s="50">
         <v>221600</v>
       </c>
-      <c r="D8" s="47">
+      <c r="D8" s="50">
         <v>337593.99999999994</v>
       </c>
-      <c r="E8" s="47">
+      <c r="E8" s="50">
         <v>421052.1521874999</v>
       </c>
-      <c r="F8" s="47">
+      <c r="F8" s="50">
         <v>488847.26385986316</v>
       </c>
-      <c r="G8" s="47">
+      <c r="G8" s="50">
         <v>500176.9311411085</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="C9" s="47">
+        <v>226</v>
+      </c>
+      <c r="C9" s="50">
         <v>118934.16666666667</v>
       </c>
-      <c r="D9" s="47">
+      <c r="D9" s="50">
         <v>147002.63</v>
       </c>
-      <c r="E9" s="47">
+      <c r="E9" s="50">
         <v>151412.7089</v>
       </c>
-      <c r="F9" s="47">
+      <c r="F9" s="50">
         <v>155955.090167</v>
       </c>
-      <c r="G9" s="47">
+      <c r="G9" s="50">
         <v>160633.74287201</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="C10" s="47">
+        <v>227</v>
+      </c>
+      <c r="C10" s="50">
         <v>37600</v>
       </c>
-      <c r="D10" s="47">
+      <c r="D10" s="50">
         <v>48735</v>
       </c>
-      <c r="E10" s="47">
+      <c r="E10" s="50">
         <v>53469.875</v>
       </c>
-      <c r="F10" s="47">
+      <c r="F10" s="50">
         <v>57550.29437499999</v>
       </c>
-      <c r="G10" s="47">
+      <c r="G10" s="50">
         <v>59152.96078437499</v>
       </c>
     </row>
@@ -5687,39 +5773,39 @@
       <c r="B11" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="C11" s="47">
+      <c r="C11" s="50">
         <v>6959.808550594178</v>
       </c>
-      <c r="D11" s="47">
+      <c r="D11" s="50">
         <v>6959.808550594178</v>
       </c>
-      <c r="E11" s="47">
+      <c r="E11" s="50">
         <v>6959.808550594178</v>
       </c>
-      <c r="F11" s="47">
+      <c r="F11" s="50">
         <v>6959.808550594178</v>
       </c>
-      <c r="G11" s="47">
+      <c r="G11" s="50">
         <v>6959.808550594178</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="27" t="s">
-        <v>225</v>
-      </c>
-      <c r="C12" s="48">
+        <v>228</v>
+      </c>
+      <c r="C12" s="51">
         <v>58106.02478273915</v>
       </c>
-      <c r="D12" s="48">
+      <c r="D12" s="51">
         <v>134896.56144940577</v>
       </c>
-      <c r="E12" s="48">
+      <c r="E12" s="51">
         <v>209209.75973690578</v>
       </c>
-      <c r="F12" s="48">
+      <c r="F12" s="51">
         <v>268382.070767269</v>
       </c>
-      <c r="G12" s="48">
+      <c r="G12" s="51">
         <v>273430.41893412935</v>
       </c>
     </row>
@@ -5727,494 +5813,494 @@
       <c r="B13" s="27" t="s">
         <v>167</v>
       </c>
-      <c r="C13" s="48">
+      <c r="C13" s="51">
         <v>58106.02478273915</v>
       </c>
-      <c r="D13" s="48">
+      <c r="D13" s="51">
         <v>193002.5862321449</v>
       </c>
-      <c r="E13" s="48">
+      <c r="E13" s="51">
         <v>402212.34596905066</v>
       </c>
-      <c r="F13" s="48">
+      <c r="F13" s="51">
         <v>670594.4167363197</v>
       </c>
-      <c r="G13" s="48">
+      <c r="G13" s="51">
         <v>944024.8356704491</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="27" t="s">
-        <v>226</v>
-      </c>
-      <c r="C14" s="49">
+        <v>229</v>
+      </c>
+      <c r="C14" s="52">
         <v>0.26221130317120556</v>
       </c>
-      <c r="D14" s="49">
+      <c r="D14" s="52">
         <v>0.39958222435649265</v>
       </c>
-      <c r="E14" s="49">
+      <c r="E14" s="52">
         <v>0.4968737450930829</v>
       </c>
-      <c r="F14" s="49">
+      <c r="F14" s="52">
         <v>0.5490100704423817</v>
       </c>
-      <c r="G14" s="49">
+      <c r="G14" s="52">
         <v>0.5466673928969945</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="C15" s="50">
+        <v>230</v>
+      </c>
+      <c r="C15" s="53">
         <v>18466.666666666668</v>
       </c>
-      <c r="D15" s="50">
+      <c r="D15" s="53">
         <v>18755.22222222222</v>
       </c>
-      <c r="E15" s="50">
+      <c r="E15" s="53">
         <v>19138.734190340907</v>
       </c>
-      <c r="F15" s="50">
+      <c r="F15" s="53">
         <v>19553.890554394526</v>
       </c>
-      <c r="G15" s="50">
+      <c r="G15" s="53">
         <v>20007.07724564434</v>
       </c>
-      <c r="H15" s="51" t="s">
-        <v>228</v>
+      <c r="H15" s="54" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="27" t="s">
-        <v>229</v>
-      </c>
-      <c r="C16" s="52">
+        <v>232</v>
+      </c>
+      <c r="C16" s="55">
         <v>13624.497934771738</v>
       </c>
-      <c r="D16" s="52">
+      <c r="D16" s="55">
         <v>11260.968808366342</v>
       </c>
-      <c r="E16" s="52">
+      <c r="E16" s="55">
         <v>9629.199656845189</v>
       </c>
-      <c r="F16" s="52">
+      <c r="F16" s="55">
         <v>8818.607723703766</v>
       </c>
-      <c r="G16" s="52">
+      <c r="G16" s="55">
         <v>9069.860488279168</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="C17" s="47">
+        <v>233</v>
+      </c>
+      <c r="C17" s="50">
         <v>500</v>
       </c>
-      <c r="D17" s="47">
+      <c r="D17" s="50">
         <v>512.5</v>
       </c>
-      <c r="E17" s="47">
+      <c r="E17" s="50">
         <v>525.3125</v>
       </c>
-      <c r="F17" s="47">
+      <c r="F17" s="50">
         <v>538.4453124999998</v>
       </c>
-      <c r="G17" s="47">
+      <c r="G17" s="50">
         <v>551.9064453124997</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="C18" s="53">
+        <v>234</v>
+      </c>
+      <c r="C18" s="56">
         <v>2083.3333333333335</v>
       </c>
-      <c r="D18" s="50">
+      <c r="D18" s="53">
         <v>1716.6666666666667</v>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="53">
         <v>1446.6818181818182</v>
       </c>
-      <c r="F18" s="50">
+      <c r="F18" s="53">
         <v>1311.2723999999998</v>
       </c>
-      <c r="G18" s="50">
+      <c r="G18" s="53">
         <v>1350.610572</v>
       </c>
-      <c r="H18" s="51" t="s">
-        <v>232</v>
+      <c r="H18" s="54" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="27" t="s">
-        <v>233</v>
-      </c>
-      <c r="C19" s="54">
+        <v>236</v>
+      </c>
+      <c r="C19" s="57">
         <v>4842.168731894929</v>
       </c>
-      <c r="D19" s="54">
+      <c r="D19" s="57">
         <v>7494.253413855876</v>
       </c>
-      <c r="E19" s="54">
+      <c r="E19" s="57">
         <v>9509.534533495716</v>
       </c>
-      <c r="F19" s="54">
+      <c r="F19" s="57">
         <v>10735.28283069076</v>
       </c>
-      <c r="G19" s="54">
+      <c r="G19" s="57">
         <v>10937.216757365175</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="27" t="s">
-        <v>234</v>
-      </c>
-      <c r="C20" s="49">
+        <v>237</v>
+      </c>
+      <c r="C20" s="52">
         <v>0.5367065282791817</v>
       </c>
-      <c r="D20" s="49">
+      <c r="D20" s="52">
         <v>0.43544206946805936</v>
       </c>
-      <c r="E20" s="49">
+      <c r="E20" s="52">
         <v>0.3596055930681337</v>
       </c>
-      <c r="F20" s="49">
+      <c r="F20" s="52">
         <v>0.31902621063193126</v>
       </c>
-      <c r="G20" s="49">
+      <c r="G20" s="52">
         <v>0.3211538415127196</v>
       </c>
-      <c r="H20" s="51" t="s">
-        <v>235</v>
+      <c r="H20" s="54" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="27" t="s">
-        <v>236</v>
-      </c>
-      <c r="C21" s="49">
+        <v>239</v>
+      </c>
+      <c r="C21" s="52">
         <v>0.11281588447653429</v>
       </c>
-      <c r="D21" s="49">
+      <c r="D21" s="52">
         <v>0.09153006273808185</v>
       </c>
-      <c r="E21" s="49">
+      <c r="E21" s="52">
         <v>0.07558921106245059</v>
       </c>
-      <c r="F21" s="49">
+      <c r="F21" s="52">
         <v>0.06705941185220071</v>
       </c>
-      <c r="G21" s="49">
+      <c r="G21" s="52">
         <v>0.06750664054611155</v>
       </c>
-      <c r="H21" s="51" t="s">
-        <v>237</v>
+      <c r="H21" s="54" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="27" t="s">
-        <v>238</v>
-      </c>
-      <c r="C22" s="49">
+        <v>241</v>
+      </c>
+      <c r="C22" s="52">
         <v>0.2936183814681107</v>
       </c>
-      <c r="D22" s="49">
+      <c r="D22" s="52">
         <v>0.4201981374076552</v>
       </c>
-      <c r="E22" s="49">
+      <c r="E22" s="52">
         <v>0.5134033092205568</v>
       </c>
-      <c r="F22" s="49">
+      <c r="F22" s="52">
         <v>0.5632472546615191</v>
       </c>
-      <c r="G22" s="49">
+      <c r="G22" s="52">
         <v>0.5605820861130851</v>
       </c>
-      <c r="H22" s="51" t="s">
-        <v>239</v>
+      <c r="H22" s="54" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="27" t="s">
-        <v>240</v>
-      </c>
-      <c r="C23" s="55">
+        <v>243</v>
+      </c>
+      <c r="C23" s="58">
         <v>3</v>
       </c>
-      <c r="D23" s="55">
+      <c r="D23" s="58">
         <v>3</v>
       </c>
-      <c r="E23" s="55">
+      <c r="E23" s="58">
         <v>3</v>
       </c>
-      <c r="F23" s="55">
+      <c r="F23" s="58">
         <v>3</v>
       </c>
-      <c r="G23" s="55">
+      <c r="G23" s="58">
         <v>3</v>
       </c>
-      <c r="H23" s="51" t="s">
-        <v>241</v>
+      <c r="H23" s="54" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="27" t="s">
-        <v>242</v>
-      </c>
-      <c r="C24" s="56">
+        <v>245</v>
+      </c>
+      <c r="C24" s="59">
         <v>9.348796430295266</v>
       </c>
-      <c r="D24" s="56">
+      <c r="D24" s="59">
         <v>20.382223012138642</v>
       </c>
-      <c r="E24" s="56">
+      <c r="E24" s="59">
         <v>31.059700380557874</v>
       </c>
-      <c r="F24" s="56">
+      <c r="F24" s="59">
         <v>39.561703072185296</v>
       </c>
-      <c r="G24" s="56">
+      <c r="G24" s="59">
         <v>40.287060404956954</v>
       </c>
-      <c r="H24" s="51" t="s">
-        <v>243</v>
+      <c r="H24" s="54" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="27" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C25" s="35" t="str">
         <f>IF('5-Year Model'!B50&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D25" s="57" t="str">
+      <c r="D25" s="60" t="str">
         <f>IF(AND('5-Year Model'!C50&gt;=0,'5-Year Model'!B50&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E25" s="57" t="str">
+      <c r="E25" s="60" t="str">
         <f>IF(AND('5-Year Model'!D50&gt;=0,'5-Year Model'!C50&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F25" s="57" t="str">
+      <c r="F25" s="60" t="str">
         <f>IF(AND('5-Year Model'!E50&gt;=0,'5-Year Model'!D50&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G25" s="57" t="str">
+      <c r="G25" s="60" t="str">
         <f>IF(AND('5-Year Model'!F50&gt;=0,'5-Year Model'!E50&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="51" t="s">
-        <v>215</v>
+      <c r="H25" s="54" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="C26" s="58">
+        <v>248</v>
+      </c>
+      <c r="C26" s="61">
         <v>4</v>
       </c>
-      <c r="D26" s="58">
+      <c r="D26" s="61">
         <v>11</v>
       </c>
-      <c r="E26" s="59">
+      <c r="E26" s="62">
         <v>23</v>
       </c>
-      <c r="F26" s="55">
+      <c r="F26" s="58">
         <v>37</v>
       </c>
-      <c r="G26" s="55">
+      <c r="G26" s="58">
         <v>50</v>
       </c>
-      <c r="H26" s="51" t="s">
-        <v>246</v>
+      <c r="H26" s="54" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="27" t="s">
         <v>168</v>
       </c>
-      <c r="C27" s="55">
+      <c r="C27" s="58">
         <v>130</v>
       </c>
-      <c r="D27" s="55">
+      <c r="D27" s="58">
         <v>348</v>
       </c>
-      <c r="E27" s="55">
+      <c r="E27" s="58">
         <v>693</v>
       </c>
-      <c r="F27" s="55">
+      <c r="F27" s="58">
         <v>1110</v>
       </c>
-      <c r="G27" s="55">
+      <c r="G27" s="58">
         <v>1520</v>
       </c>
-      <c r="H27" s="51" t="s">
-        <v>247</v>
+      <c r="H27" s="54" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E29" s="12"/>
       <c r="F29" s="12" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="60" t="s">
-        <v>252</v>
+      <c r="B30" s="63" t="s">
+        <v>255</v>
       </c>
       <c r="C30" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="D30" s="61" t="s">
-        <v>254</v>
-      </c>
-      <c r="E30" s="61"/>
-      <c r="F30" s="62" t="s">
-        <v>255</v>
-      </c>
-      <c r="G30" s="62"/>
-      <c r="H30" s="62"/>
+        <v>256</v>
+      </c>
+      <c r="D30" s="64" t="s">
+        <v>257</v>
+      </c>
+      <c r="E30" s="64"/>
+      <c r="F30" s="65" t="s">
+        <v>258</v>
+      </c>
+      <c r="G30" s="65"/>
+      <c r="H30" s="65"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="60" t="s">
+      <c r="B31" s="63" t="s">
+        <v>259</v>
+      </c>
+      <c r="C31" s="35" t="s">
         <v>256</v>
       </c>
-      <c r="C31" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="D31" s="61" t="s">
-        <v>257</v>
-      </c>
-      <c r="E31" s="61"/>
-      <c r="F31" s="62" t="s">
-        <v>258</v>
-      </c>
-      <c r="G31" s="62"/>
-      <c r="H31" s="62"/>
+      <c r="D31" s="64" t="s">
+        <v>260</v>
+      </c>
+      <c r="E31" s="64"/>
+      <c r="F31" s="65" t="s">
+        <v>261</v>
+      </c>
+      <c r="G31" s="65"/>
+      <c r="H31" s="65"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="60" t="s">
-        <v>259</v>
+      <c r="B32" s="63" t="s">
+        <v>262</v>
       </c>
       <c r="C32" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="D32" s="61" t="s">
-        <v>260</v>
-      </c>
-      <c r="E32" s="61"/>
-      <c r="F32" s="62" t="s">
-        <v>261</v>
-      </c>
-      <c r="G32" s="62"/>
-      <c r="H32" s="62"/>
+        <v>256</v>
+      </c>
+      <c r="D32" s="64" t="s">
+        <v>263</v>
+      </c>
+      <c r="E32" s="64"/>
+      <c r="F32" s="65" t="s">
+        <v>264</v>
+      </c>
+      <c r="G32" s="65"/>
+      <c r="H32" s="65"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="60" t="s">
-        <v>262</v>
+      <c r="B33" s="63" t="s">
+        <v>265</v>
       </c>
       <c r="C33" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="D33" s="61" t="s">
-        <v>263</v>
-      </c>
-      <c r="E33" s="61"/>
-      <c r="F33" s="62" t="s">
-        <v>264</v>
-      </c>
-      <c r="G33" s="62"/>
-      <c r="H33" s="62"/>
+        <v>256</v>
+      </c>
+      <c r="D33" s="64" t="s">
+        <v>266</v>
+      </c>
+      <c r="E33" s="64"/>
+      <c r="F33" s="65" t="s">
+        <v>267</v>
+      </c>
+      <c r="G33" s="65"/>
+      <c r="H33" s="65"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="60" t="s">
-        <v>265</v>
+      <c r="B34" s="63" t="s">
+        <v>268</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="D34" s="61" t="s">
-        <v>266</v>
-      </c>
-      <c r="E34" s="61"/>
-      <c r="F34" s="62" t="s">
-        <v>267</v>
-      </c>
-      <c r="G34" s="62"/>
-      <c r="H34" s="62"/>
+        <v>256</v>
+      </c>
+      <c r="D34" s="64" t="s">
+        <v>269</v>
+      </c>
+      <c r="E34" s="64"/>
+      <c r="F34" s="65" t="s">
+        <v>270</v>
+      </c>
+      <c r="G34" s="65"/>
+      <c r="H34" s="65"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="60" t="s">
-        <v>268</v>
+      <c r="B35" s="63" t="s">
+        <v>271</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="D35" s="61" t="s">
-        <v>269</v>
-      </c>
-      <c r="E35" s="61"/>
-      <c r="F35" s="62" t="s">
-        <v>270</v>
-      </c>
-      <c r="G35" s="62"/>
-      <c r="H35" s="62"/>
+        <v>256</v>
+      </c>
+      <c r="D35" s="64" t="s">
+        <v>272</v>
+      </c>
+      <c r="E35" s="64"/>
+      <c r="F35" s="65" t="s">
+        <v>273</v>
+      </c>
+      <c r="G35" s="65"/>
+      <c r="H35" s="65"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="60" t="s">
-        <v>271</v>
+      <c r="B36" s="63" t="s">
+        <v>274</v>
       </c>
       <c r="C36" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="D36" s="61" t="s">
-        <v>272</v>
-      </c>
-      <c r="E36" s="61"/>
-      <c r="F36" s="62" t="s">
-        <v>273</v>
-      </c>
-      <c r="G36" s="62"/>
-      <c r="H36" s="62"/>
+        <v>256</v>
+      </c>
+      <c r="D36" s="64" t="s">
+        <v>275</v>
+      </c>
+      <c r="E36" s="64"/>
+      <c r="F36" s="65" t="s">
+        <v>276</v>
+      </c>
+      <c r="G36" s="65"/>
+      <c r="H36" s="65"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="60" t="s">
-        <v>274</v>
+      <c r="B38" s="63" t="s">
+        <v>277</v>
       </c>
       <c r="C38" s="27" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D38" s="27"/>
       <c r="E38" s="27"/>
       <c r="F38" s="27"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="63" t="s">
+      <c r="B40" s="66" t="s">
         <v>129</v>
       </c>
-      <c r="C40" s="63"/>
-      <c r="D40" s="63"/>
-      <c r="E40" s="63"/>
-      <c r="F40" s="63"/>
-      <c r="G40" s="63"/>
-      <c r="H40" s="63"/>
+      <c r="C40" s="66"/>
+      <c r="D40" s="66"/>
+      <c r="E40" s="66"/>
+      <c r="F40" s="66"/>
+      <c r="G40" s="66"/>
+      <c r="H40" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
@@ -38,7 +38,7 @@
     <t>Bright Horizons Microschool</t>
   </si>
   <si>
-    <t>Generated April 29, 2026 · llc_single</t>
+    <t>Generated May 1, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -671,7 +671,7 @@
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated April 29, 2026</t>
+    <t>Generated May 1, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>

--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Decision History'!$A1:$H4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Decision History'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Financial Health'!$A1:$H40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Financial Health'!$A1:$I40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -38,7 +38,7 @@
     <t>Bright Horizons Microschool</t>
   </si>
   <si>
-    <t>Generated May 1, 2026 · llc_single</t>
+    <t>Generated May 7, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -671,7 +671,7 @@
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 1, 2026</t>
+    <t>Generated May 7, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -806,7 +806,7 @@
     <t>The model reaches profit early and sustains strong margins through Year 5.</t>
   </si>
   <si>
-    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+    <t>Compare your real Year 1 enrollment against this projection as students enroll.</t>
   </si>
   <si>
     <t>Liquidity</t>
@@ -5623,7 +5623,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:I40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -5633,7 +5633,7 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>212</v>
       </c>
@@ -5643,8 +5643,9 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="45" t="s">
         <v>213</v>
       </c>
@@ -5654,6 +5655,7 @@
       <c r="F3" s="45"/>
       <c r="G3" s="45"/>
       <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="46" t="s">
@@ -6144,7 +6146,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="12" t="s">
         <v>251</v>
       </c>
@@ -6160,8 +6162,9 @@
       </c>
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="12"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="63" t="s">
         <v>255</v>
       </c>
@@ -6177,8 +6180,9 @@
       </c>
       <c r="G30" s="65"/>
       <c r="H30" s="65"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="65"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="63" t="s">
         <v>259</v>
       </c>
@@ -6194,8 +6198,9 @@
       </c>
       <c r="G31" s="65"/>
       <c r="H31" s="65"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="65"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="63" t="s">
         <v>262</v>
       </c>
@@ -6211,8 +6216,9 @@
       </c>
       <c r="G32" s="65"/>
       <c r="H32" s="65"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="65"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="63" t="s">
         <v>265</v>
       </c>
@@ -6228,8 +6234,9 @@
       </c>
       <c r="G33" s="65"/>
       <c r="H33" s="65"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="65"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="63" t="s">
         <v>268</v>
       </c>
@@ -6245,8 +6252,9 @@
       </c>
       <c r="G34" s="65"/>
       <c r="H34" s="65"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="65"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="63" t="s">
         <v>271</v>
       </c>
@@ -6262,8 +6270,9 @@
       </c>
       <c r="G35" s="65"/>
       <c r="H35" s="65"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I35" s="65"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="63" t="s">
         <v>274</v>
       </c>
@@ -6279,6 +6288,7 @@
       </c>
       <c r="G36" s="65"/>
       <c r="H36" s="65"/>
+      <c r="I36" s="65"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="63" t="s">
@@ -6291,7 +6301,7 @@
       <c r="E38" s="27"/>
       <c r="F38" s="27"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" s="66" t="s">
         <v>129</v>
       </c>
@@ -6301,29 +6311,30 @@
       <c r="F40" s="66"/>
       <c r="G40" s="66"/>
       <c r="H40" s="66"/>
+      <c r="I40" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F29:I29"/>
     <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F31:I31"/>
     <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F32:I32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F33:I33"/>
     <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F34:I34"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F35:I35"/>
     <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F36:I36"/>
     <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B40:I40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_Startup.xlsx
@@ -38,7 +38,7 @@
     <t>Bright Horizons Microschool</t>
   </si>
   <si>
-    <t>Generated May 7, 2026 · llc_single</t>
+    <t>Generated May 9, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -671,7 +671,7 @@
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 7, 2026</t>
+    <t>Generated May 9, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
